--- a/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
@@ -21,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -47,6 +48,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="007A5AA8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="003B1F5E"/>
       <sz val="10"/>
@@ -61,11 +67,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="007A5AA8"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -231,7 +232,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -244,58 +245,58 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -811,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -943,34 +944,58 @@
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1005,7 +1030,7 @@
     <row r="1">
       <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · funil em "&amp;TEXT(Config!B5,"dd/mm/yyyy")</f>
-        <v>Prisma Comunicação (exemplo fictício) · funil em 17/09/2026</v>
+        <v>Prisma Comunicação (exemplo fictício) · funil em 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1336,23 +1361,23 @@
       </c>
       <c r="B21" s="21" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$A$5:$A$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Studio Yoga</v>
+        <v>Construtora Vale</v>
       </c>
       <c r="C21" s="21" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$B$5:$B$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Site simples</v>
+        <v>Vídeo institucional</v>
       </c>
       <c r="D21" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$F$5:$F$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Contato</v>
+        <v>Proposta enviada</v>
       </c>
       <c r="E21" s="23">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$E$5:$E$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>8500</v>
+        <v>45000</v>
       </c>
       <c r="F21" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G21" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -1360,7 +1385,7 @@
       </c>
       <c r="H21" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,1)&gt;0,INDEX(Propostas!$D$5:$D$404,MATCH(LARGE(Propostas!$P$5:$P$404,1),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Diego</v>
+        <v>Bruno</v>
       </c>
     </row>
     <row r="22">
@@ -1369,11 +1394,11 @@
       </c>
       <c r="B22" s="21" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$A$5:$A$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Construtora Vale</v>
+        <v>Clínica Bem-Estar</v>
       </c>
       <c r="C22" s="21" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$B$5:$B$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Vídeo institucional</v>
+        <v>Gestão de redes (mensal)</v>
       </c>
       <c r="D22" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$F$5:$F$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -1381,11 +1406,11 @@
       </c>
       <c r="E22" s="23">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$E$5:$E$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>45000</v>
+        <v>4500</v>
       </c>
       <c r="F22" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G22" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -1393,7 +1418,7 @@
       </c>
       <c r="H22" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,2)&gt;0,INDEX(Propostas!$D$5:$D$404,MATCH(LARGE(Propostas!$P$5:$P$404,2),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Bruno</v>
+        <v>Carla</v>
       </c>
     </row>
     <row r="23">
@@ -1402,31 +1427,31 @@
       </c>
       <c r="B23" s="21" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$A$5:$A$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Clínica Bem-Estar</v>
+        <v>Studio Yoga</v>
       </c>
       <c r="C23" s="21" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$B$5:$B$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Gestão de redes (mensal)</v>
+        <v>Site simples</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$F$5:$F$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Proposta enviada</v>
+        <v>Contato</v>
       </c>
       <c r="E23" s="23">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$E$5:$E$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="F23" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G23" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Fechamento vencido</v>
+        <v>Parada</v>
       </c>
       <c r="H23" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,3)&gt;0,INDEX(Propostas!$D$5:$D$404,MATCH(LARGE(Propostas!$P$5:$P$404,3),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>Carla</v>
+        <v>Diego</v>
       </c>
     </row>
     <row r="24">
@@ -1451,7 +1476,7 @@
       </c>
       <c r="F24" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,4)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,4),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G24" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,4)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,4),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -1484,7 +1509,7 @@
       </c>
       <c r="F25" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,5)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,5),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G25" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,5)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,5),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -1517,7 +1542,7 @@
       </c>
       <c r="F26" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,6)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,6),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G26" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,6)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,6),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -1550,7 +1575,7 @@
       </c>
       <c r="F27" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,7)&gt;0,INDEX(Propostas!$N$5:$N$404,MATCH(LARGE(Propostas!$P$5:$P$404,7),Propostas!$P$5:$P$404,0)),""),"")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27" s="22" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$P$5:$P$404,7)&gt;0,INDEX(Propostas!$O$5:$O$404,MATCH(LARGE(Propostas!$P$5:$P$404,7),Propostas!$P$5:$P$404,0)),""),"")</f>
@@ -2126,9 +2151,13 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="30">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="B5" s="30" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2743,7 +2772,7 @@
       </c>
       <c r="N9" s="26">
         <f>IF(OR(F9="",F9="Ganha",F9="Perdida"),"",Config!$B$5-IF(H9="",G9,H9))</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O9" s="22" t="str">
         <f>IF(F9="","",IF(F9="Ganha","Fechada",IF(F9="Perdida","Perdida",IF(AND(I9&lt;&gt;"",I9&lt;Config!$B$5),"Fechamento vencido",IF(N9&gt;Config!$B$7,"Parada","Ativa")))))</f>
@@ -2751,7 +2780,7 @@
       </c>
       <c r="P9" s="35">
         <f>IF(OR(F9="",O9="Fechada",O9="Perdida"),0,IF(O9="Fechamento vencido",3000,IF(O9="Parada",2000,1000))+MIN(N9,500)+E9/1000000-ROW()/100000)</f>
-        <v>1008.02191</v>
+        <v>1005.02191</v>
       </c>
     </row>
     <row r="10">
@@ -2804,7 +2833,7 @@
       </c>
       <c r="N10" s="26">
         <f>IF(OR(F10="",F10="Ganha",F10="Perdida"),"",Config!$B$5-IF(H10="",G10,H10))</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O10" s="22" t="str">
         <f>IF(F10="","",IF(F10="Ganha","Fechada",IF(F10="Perdida","Perdida",IF(AND(I10&lt;&gt;"",I10&lt;Config!$B$5),"Fechamento vencido",IF(N10&gt;Config!$B$7,"Parada","Ativa")))))</f>
@@ -2812,7 +2841,7 @@
       </c>
       <c r="P10" s="35">
         <f>IF(OR(F10="",O10="Fechada",O10="Perdida"),0,IF(O10="Fechamento vencido",3000,IF(O10="Parada",2000,1000))+MIN(N10,500)+E10/1000000-ROW()/100000)</f>
-        <v>3013.0044</v>
+        <v>3010.0044</v>
       </c>
     </row>
     <row r="11">
@@ -2865,7 +2894,7 @@
       </c>
       <c r="N11" s="26">
         <f>IF(OR(F11="",F11="Ganha",F11="Perdida"),"",Config!$B$5-IF(H11="",G11,H11))</f>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O11" s="22" t="str">
         <f>IF(F11="","",IF(F11="Ganha","Fechada",IF(F11="Perdida","Perdida",IF(AND(I11&lt;&gt;"",I11&lt;Config!$B$5),"Fechamento vencido",IF(N11&gt;Config!$B$7,"Parada","Ativa")))))</f>
@@ -2873,7 +2902,7 @@
       </c>
       <c r="P11" s="35">
         <f>IF(OR(F11="",O11="Fechada",O11="Perdida"),0,IF(O11="Fechamento vencido",3000,IF(O11="Parada",2000,1000))+MIN(N11,500)+E11/1000000-ROW()/100000)</f>
-        <v>3022.04489</v>
+        <v>3019.04489</v>
       </c>
     </row>
     <row r="12">
@@ -2926,7 +2955,7 @@
       </c>
       <c r="N12" s="26">
         <f>IF(OR(F12="",F12="Ganha",F12="Perdida"),"",Config!$B$5-IF(H12="",G12,H12))</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O12" s="22" t="str">
         <f>IF(F12="","",IF(F12="Ganha","Fechada",IF(F12="Perdida","Perdida",IF(AND(I12&lt;&gt;"",I12&lt;Config!$B$5),"Fechamento vencido",IF(N12&gt;Config!$B$7,"Parada","Ativa")))))</f>
@@ -2934,7 +2963,7 @@
       </c>
       <c r="P12" s="35">
         <f>IF(OR(F12="",O12="Fechada",O12="Perdida"),0,IF(O12="Fechamento vencido",3000,IF(O12="Parada",2000,1000))+MIN(N12,500)+E12/1000000-ROW()/100000)</f>
-        <v>1009.03088</v>
+        <v>1006.03088</v>
       </c>
     </row>
     <row r="13">
@@ -2985,7 +3014,7 @@
       </c>
       <c r="N13" s="26">
         <f>IF(OR(F13="",F13="Ganha",F13="Perdida"),"",Config!$B$5-IF(H13="",G13,H13))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O13" s="22" t="str">
         <f>IF(F13="","",IF(F13="Ganha","Fechada",IF(F13="Perdida","Perdida",IF(AND(I13&lt;&gt;"",I13&lt;Config!$B$5),"Fechamento vencido",IF(N13&gt;Config!$B$7,"Parada","Ativa")))))</f>
@@ -2993,7 +3022,7 @@
       </c>
       <c r="P13" s="35">
         <f>IF(OR(F13="",O13="Fechada",O13="Perdida"),0,IF(O13="Fechamento vencido",3000,IF(O13="Parada",2000,1000))+MIN(N13,500)+E13/1000000-ROW()/100000)</f>
-        <v>1006.00767</v>
+        <v>1003.00767</v>
       </c>
     </row>
     <row r="14">
@@ -3046,7 +3075,7 @@
       </c>
       <c r="N14" s="26">
         <f>IF(OR(F14="",F14="Ganha",F14="Perdida"),"",Config!$B$5-IF(H14="",G14,H14))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O14" s="22" t="str">
         <f>IF(F14="","",IF(F14="Ganha","Fechada",IF(F14="Perdida","Perdida",IF(AND(I14&lt;&gt;"",I14&lt;Config!$B$5),"Fechamento vencido",IF(N14&gt;Config!$B$7,"Parada","Ativa")))))</f>
@@ -3054,7 +3083,7 @@
       </c>
       <c r="P14" s="35">
         <f>IF(OR(F14="",O14="Fechada",O14="Perdida"),0,IF(O14="Fechamento vencido",3000,IF(O14="Parada",2000,1000))+MIN(N14,500)+E14/1000000-ROW()/100000)</f>
-        <v>1005.00606</v>
+        <v>1002.00606</v>
       </c>
     </row>
     <row r="15">
@@ -3308,15 +3337,15 @@
       </c>
       <c r="N18" s="26">
         <f>IF(OR(F18="",F18="Ganha",F18="Perdida"),"",Config!$B$5-IF(H18="",G18,H18))</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O18" s="22" t="str">
         <f>IF(F18="","",IF(F18="Ganha","Fechada",IF(F18="Perdida","Perdida",IF(AND(I18&lt;&gt;"",I18&lt;Config!$B$5),"Fechamento vencido",IF(N18&gt;Config!$B$7,"Parada","Ativa")))))</f>
-        <v>Fechamento vencido</v>
+        <v>Parada</v>
       </c>
       <c r="P18" s="35">
         <f>IF(OR(F18="",O18="Fechada",O18="Perdida"),0,IF(O18="Fechamento vencido",3000,IF(O18="Parada",2000,1000))+MIN(N18,500)+E18/1000000-ROW()/100000)</f>
-        <v>3036.00832</v>
+        <v>2033.00832</v>
       </c>
     </row>
     <row r="19">

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
         <v>Fechada</v>
       </c>
       <c r="P5" s="35">
-        <f>IF(OR(F5="",O5="Fechada",O5="Perdida"),0,IF(O5="Fechamento vencido",3000,IF(O5="Parada",2000,1000))+MIN(N5,500)+E5/1000000-ROW()/100000)</f>
+        <f>IF(OR(F5="",O5="Fechada",O5="Perdida"),0,IF(O5="Fechamento vencido",3,IF(O5="Parada",2,1))*1E+13+MIN(N(N5),500)*1E+10+MIN(ROUND(N(E5),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>Fechada</v>
       </c>
       <c r="P6" s="35">
-        <f>IF(OR(F6="",O6="Fechada",O6="Perdida"),0,IF(O6="Fechamento vencido",3000,IF(O6="Parada",2000,1000))+MIN(N6,500)+E6/1000000-ROW()/100000)</f>
+        <f>IF(OR(F6="",O6="Fechada",O6="Perdida"),0,IF(O6="Fechamento vencido",3,IF(O6="Parada",2,1))*1E+13+MIN(N(N6),500)*1E+10+MIN(ROUND(N(E6),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         <v>Fechada</v>
       </c>
       <c r="P7" s="35">
-        <f>IF(OR(F7="",O7="Fechada",O7="Perdida"),0,IF(O7="Fechamento vencido",3000,IF(O7="Parada",2000,1000))+MIN(N7,500)+E7/1000000-ROW()/100000)</f>
+        <f>IF(OR(F7="",O7="Fechada",O7="Perdida"),0,IF(O7="Fechamento vencido",3,IF(O7="Parada",2,1))*1E+13+MIN(N(N7),500)*1E+10+MIN(ROUND(N(E7),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
         <v>Fechada</v>
       </c>
       <c r="P8" s="35">
-        <f>IF(OR(F8="",O8="Fechada",O8="Perdida"),0,IF(O8="Fechamento vencido",3000,IF(O8="Parada",2000,1000))+MIN(N8,500)+E8/1000000-ROW()/100000)</f>
+        <f>IF(OR(F8="",O8="Fechada",O8="Perdida"),0,IF(O8="Fechamento vencido",3,IF(O8="Parada",2,1))*1E+13+MIN(N(N8),500)*1E+10+MIN(ROUND(N(E8),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2779,8 +2779,8 @@
         <v>Ativa</v>
       </c>
       <c r="P9" s="35">
-        <f>IF(OR(F9="",O9="Fechada",O9="Perdida"),0,IF(O9="Fechamento vencido",3000,IF(O9="Parada",2000,1000))+MIN(N9,500)+E9/1000000-ROW()/100000)</f>
-        <v>1005.02191</v>
+        <f>IF(OR(F9="",O9="Fechada",O9="Perdida"),0,IF(O9="Fechamento vencido",3,IF(O9="Parada",2,1))*1E+13+MIN(N(N9),500)*1E+10+MIN(ROUND(N(E9),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>10050220000396</v>
       </c>
     </row>
     <row r="10">
@@ -2840,8 +2840,8 @@
         <v>Fechamento vencido</v>
       </c>
       <c r="P10" s="35">
-        <f>IF(OR(F10="",O10="Fechada",O10="Perdida"),0,IF(O10="Fechamento vencido",3000,IF(O10="Parada",2000,1000))+MIN(N10,500)+E10/1000000-ROW()/100000)</f>
-        <v>3010.0044</v>
+        <f>IF(OR(F10="",O10="Fechada",O10="Perdida"),0,IF(O10="Fechamento vencido",3,IF(O10="Parada",2,1))*1E+13+MIN(N(N10),500)*1E+10+MIN(ROUND(N(E10),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>30100045000395</v>
       </c>
     </row>
     <row r="11">
@@ -2901,8 +2901,8 @@
         <v>Fechamento vencido</v>
       </c>
       <c r="P11" s="35">
-        <f>IF(OR(F11="",O11="Fechada",O11="Perdida"),0,IF(O11="Fechamento vencido",3000,IF(O11="Parada",2000,1000))+MIN(N11,500)+E11/1000000-ROW()/100000)</f>
-        <v>3019.04489</v>
+        <f>IF(OR(F11="",O11="Fechada",O11="Perdida"),0,IF(O11="Fechamento vencido",3,IF(O11="Parada",2,1))*1E+13+MIN(N(N11),500)*1E+10+MIN(ROUND(N(E11),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>30190450000394</v>
       </c>
     </row>
     <row r="12">
@@ -2962,8 +2962,8 @@
         <v>Ativa</v>
       </c>
       <c r="P12" s="35">
-        <f>IF(OR(F12="",O12="Fechada",O12="Perdida"),0,IF(O12="Fechamento vencido",3000,IF(O12="Parada",2000,1000))+MIN(N12,500)+E12/1000000-ROW()/100000)</f>
-        <v>1006.03088</v>
+        <f>IF(OR(F12="",O12="Fechada",O12="Perdida"),0,IF(O12="Fechamento vencido",3,IF(O12="Parada",2,1))*1E+13+MIN(N(N12),500)*1E+10+MIN(ROUND(N(E12),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>10060310000393</v>
       </c>
     </row>
     <row r="13">
@@ -3021,8 +3021,8 @@
         <v>Ativa</v>
       </c>
       <c r="P13" s="35">
-        <f>IF(OR(F13="",O13="Fechada",O13="Perdida"),0,IF(O13="Fechamento vencido",3000,IF(O13="Parada",2000,1000))+MIN(N13,500)+E13/1000000-ROW()/100000)</f>
-        <v>1003.00767</v>
+        <f>IF(OR(F13="",O13="Fechada",O13="Perdida"),0,IF(O13="Fechamento vencido",3,IF(O13="Parada",2,1))*1E+13+MIN(N(N13),500)*1E+10+MIN(ROUND(N(E13),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>10030078000392</v>
       </c>
     </row>
     <row r="14">
@@ -3082,8 +3082,8 @@
         <v>Ativa</v>
       </c>
       <c r="P14" s="35">
-        <f>IF(OR(F14="",O14="Fechada",O14="Perdida"),0,IF(O14="Fechamento vencido",3000,IF(O14="Parada",2000,1000))+MIN(N14,500)+E14/1000000-ROW()/100000)</f>
-        <v>1002.00606</v>
+        <f>IF(OR(F14="",O14="Fechada",O14="Perdida"),0,IF(O14="Fechamento vencido",3,IF(O14="Parada",2,1))*1E+13+MIN(N(N14),500)*1E+10+MIN(ROUND(N(E14),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>10020062000391</v>
       </c>
     </row>
     <row r="15">
@@ -3149,7 +3149,7 @@
         <v>Perdida</v>
       </c>
       <c r="P15" s="35">
-        <f>IF(OR(F15="",O15="Fechada",O15="Perdida"),0,IF(O15="Fechamento vencido",3000,IF(O15="Parada",2000,1000))+MIN(N15,500)+E15/1000000-ROW()/100000)</f>
+        <f>IF(OR(F15="",O15="Fechada",O15="Perdida"),0,IF(O15="Fechamento vencido",3,IF(O15="Parada",2,1))*1E+13+MIN(N(N15),500)*1E+10+MIN(ROUND(N(E15),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
         <v>Perdida</v>
       </c>
       <c r="P16" s="35">
-        <f>IF(OR(F16="",O16="Fechada",O16="Perdida"),0,IF(O16="Fechamento vencido",3000,IF(O16="Parada",2000,1000))+MIN(N16,500)+E16/1000000-ROW()/100000)</f>
+        <f>IF(OR(F16="",O16="Fechada",O16="Perdida"),0,IF(O16="Fechamento vencido",3,IF(O16="Parada",2,1))*1E+13+MIN(N(N16),500)*1E+10+MIN(ROUND(N(E16),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
         <v>Perdida</v>
       </c>
       <c r="P17" s="35">
-        <f>IF(OR(F17="",O17="Fechada",O17="Perdida"),0,IF(O17="Fechamento vencido",3000,IF(O17="Parada",2000,1000))+MIN(N17,500)+E17/1000000-ROW()/100000)</f>
+        <f>IF(OR(F17="",O17="Fechada",O17="Perdida"),0,IF(O17="Fechamento vencido",3,IF(O17="Parada",2,1))*1E+13+MIN(N(N17),500)*1E+10+MIN(ROUND(N(E17),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3344,8 +3344,8 @@
         <v>Parada</v>
       </c>
       <c r="P18" s="35">
-        <f>IF(OR(F18="",O18="Fechada",O18="Perdida"),0,IF(O18="Fechamento vencido",3000,IF(O18="Parada",2000,1000))+MIN(N18,500)+E18/1000000-ROW()/100000)</f>
-        <v>2033.00832</v>
+        <f>IF(OR(F18="",O18="Fechada",O18="Perdida"),0,IF(O18="Fechamento vencido",3,IF(O18="Parada",2,1))*1E+13+MIN(N(N18),500)*1E+10+MIN(ROUND(N(E18),0),999999)*1E+4+(404+1-ROW()))</f>
+        <v>20330085000387</v>
       </c>
     </row>
     <row r="19">
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="P19" s="35">
-        <f>IF(OR(F19="",O19="Fechada",O19="Perdida"),0,IF(O19="Fechamento vencido",3000,IF(O19="Parada",2000,1000))+MIN(N19,500)+E19/1000000-ROW()/100000)</f>
+        <f>IF(OR(F19="",O19="Fechada",O19="Perdida"),0,IF(O19="Fechamento vencido",3,IF(O19="Parada",2,1))*1E+13+MIN(N(N19),500)*1E+10+MIN(ROUND(N(E19),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
         <v/>
       </c>
       <c r="P20" s="35">
-        <f>IF(OR(F20="",O20="Fechada",O20="Perdida"),0,IF(O20="Fechamento vencido",3000,IF(O20="Parada",2000,1000))+MIN(N20,500)+E20/1000000-ROW()/100000)</f>
+        <f>IF(OR(F20="",O20="Fechada",O20="Perdida"),0,IF(O20="Fechamento vencido",3,IF(O20="Parada",2,1))*1E+13+MIN(N(N20),500)*1E+10+MIN(ROUND(N(E20),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
         <v/>
       </c>
       <c r="P21" s="35">
-        <f>IF(OR(F21="",O21="Fechada",O21="Perdida"),0,IF(O21="Fechamento vencido",3000,IF(O21="Parada",2000,1000))+MIN(N21,500)+E21/1000000-ROW()/100000)</f>
+        <f>IF(OR(F21="",O21="Fechada",O21="Perdida"),0,IF(O21="Fechamento vencido",3,IF(O21="Parada",2,1))*1E+13+MIN(N(N21),500)*1E+10+MIN(ROUND(N(E21),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v/>
       </c>
       <c r="P22" s="35">
-        <f>IF(OR(F22="",O22="Fechada",O22="Perdida"),0,IF(O22="Fechamento vencido",3000,IF(O22="Parada",2000,1000))+MIN(N22,500)+E22/1000000-ROW()/100000)</f>
+        <f>IF(OR(F22="",O22="Fechada",O22="Perdida"),0,IF(O22="Fechamento vencido",3,IF(O22="Parada",2,1))*1E+13+MIN(N(N22),500)*1E+10+MIN(ROUND(N(E22),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
         <v/>
       </c>
       <c r="P23" s="35">
-        <f>IF(OR(F23="",O23="Fechada",O23="Perdida"),0,IF(O23="Fechamento vencido",3000,IF(O23="Parada",2000,1000))+MIN(N23,500)+E23/1000000-ROW()/100000)</f>
+        <f>IF(OR(F23="",O23="Fechada",O23="Perdida"),0,IF(O23="Fechamento vencido",3,IF(O23="Parada",2,1))*1E+13+MIN(N(N23),500)*1E+10+MIN(ROUND(N(E23),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v/>
       </c>
       <c r="P24" s="35">
-        <f>IF(OR(F24="",O24="Fechada",O24="Perdida"),0,IF(O24="Fechamento vencido",3000,IF(O24="Parada",2000,1000))+MIN(N24,500)+E24/1000000-ROW()/100000)</f>
+        <f>IF(OR(F24="",O24="Fechada",O24="Perdida"),0,IF(O24="Fechamento vencido",3,IF(O24="Parada",2,1))*1E+13+MIN(N(N24),500)*1E+10+MIN(ROUND(N(E24),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
         <v/>
       </c>
       <c r="P25" s="35">
-        <f>IF(OR(F25="",O25="Fechada",O25="Perdida"),0,IF(O25="Fechamento vencido",3000,IF(O25="Parada",2000,1000))+MIN(N25,500)+E25/1000000-ROW()/100000)</f>
+        <f>IF(OR(F25="",O25="Fechada",O25="Perdida"),0,IF(O25="Fechamento vencido",3,IF(O25="Parada",2,1))*1E+13+MIN(N(N25),500)*1E+10+MIN(ROUND(N(E25),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="P26" s="35">
-        <f>IF(OR(F26="",O26="Fechada",O26="Perdida"),0,IF(O26="Fechamento vencido",3000,IF(O26="Parada",2000,1000))+MIN(N26,500)+E26/1000000-ROW()/100000)</f>
+        <f>IF(OR(F26="",O26="Fechada",O26="Perdida"),0,IF(O26="Fechamento vencido",3,IF(O26="Parada",2,1))*1E+13+MIN(N(N26),500)*1E+10+MIN(ROUND(N(E26),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
         <v/>
       </c>
       <c r="P27" s="35">
-        <f>IF(OR(F27="",O27="Fechada",O27="Perdida"),0,IF(O27="Fechamento vencido",3000,IF(O27="Parada",2000,1000))+MIN(N27,500)+E27/1000000-ROW()/100000)</f>
+        <f>IF(OR(F27="",O27="Fechada",O27="Perdida"),0,IF(O27="Fechamento vencido",3,IF(O27="Parada",2,1))*1E+13+MIN(N(N27),500)*1E+10+MIN(ROUND(N(E27),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
         <v/>
       </c>
       <c r="P28" s="35">
-        <f>IF(OR(F28="",O28="Fechada",O28="Perdida"),0,IF(O28="Fechamento vencido",3000,IF(O28="Parada",2000,1000))+MIN(N28,500)+E28/1000000-ROW()/100000)</f>
+        <f>IF(OR(F28="",O28="Fechada",O28="Perdida"),0,IF(O28="Fechamento vencido",3,IF(O28="Parada",2,1))*1E+13+MIN(N(N28),500)*1E+10+MIN(ROUND(N(E28),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         <v/>
       </c>
       <c r="P29" s="35">
-        <f>IF(OR(F29="",O29="Fechada",O29="Perdida"),0,IF(O29="Fechamento vencido",3000,IF(O29="Parada",2000,1000))+MIN(N29,500)+E29/1000000-ROW()/100000)</f>
+        <f>IF(OR(F29="",O29="Fechada",O29="Perdida"),0,IF(O29="Fechamento vencido",3,IF(O29="Parada",2,1))*1E+13+MIN(N(N29),500)*1E+10+MIN(ROUND(N(E29),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v/>
       </c>
       <c r="P30" s="35">
-        <f>IF(OR(F30="",O30="Fechada",O30="Perdida"),0,IF(O30="Fechamento vencido",3000,IF(O30="Parada",2000,1000))+MIN(N30,500)+E30/1000000-ROW()/100000)</f>
+        <f>IF(OR(F30="",O30="Fechada",O30="Perdida"),0,IF(O30="Fechamento vencido",3,IF(O30="Parada",2,1))*1E+13+MIN(N(N30),500)*1E+10+MIN(ROUND(N(E30),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
         <v/>
       </c>
       <c r="P31" s="35">
-        <f>IF(OR(F31="",O31="Fechada",O31="Perdida"),0,IF(O31="Fechamento vencido",3000,IF(O31="Parada",2000,1000))+MIN(N31,500)+E31/1000000-ROW()/100000)</f>
+        <f>IF(OR(F31="",O31="Fechada",O31="Perdida"),0,IF(O31="Fechamento vencido",3,IF(O31="Parada",2,1))*1E+13+MIN(N(N31),500)*1E+10+MIN(ROUND(N(E31),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="P32" s="35">
-        <f>IF(OR(F32="",O32="Fechada",O32="Perdida"),0,IF(O32="Fechamento vencido",3000,IF(O32="Parada",2000,1000))+MIN(N32,500)+E32/1000000-ROW()/100000)</f>
+        <f>IF(OR(F32="",O32="Fechada",O32="Perdida"),0,IF(O32="Fechamento vencido",3,IF(O32="Parada",2,1))*1E+13+MIN(N(N32),500)*1E+10+MIN(ROUND(N(E32),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="P33" s="35">
-        <f>IF(OR(F33="",O33="Fechada",O33="Perdida"),0,IF(O33="Fechamento vencido",3000,IF(O33="Parada",2000,1000))+MIN(N33,500)+E33/1000000-ROW()/100000)</f>
+        <f>IF(OR(F33="",O33="Fechada",O33="Perdida"),0,IF(O33="Fechamento vencido",3,IF(O33="Parada",2,1))*1E+13+MIN(N(N33),500)*1E+10+MIN(ROUND(N(E33),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v/>
       </c>
       <c r="P34" s="35">
-        <f>IF(OR(F34="",O34="Fechada",O34="Perdida"),0,IF(O34="Fechamento vencido",3000,IF(O34="Parada",2000,1000))+MIN(N34,500)+E34/1000000-ROW()/100000)</f>
+        <f>IF(OR(F34="",O34="Fechada",O34="Perdida"),0,IF(O34="Fechamento vencido",3,IF(O34="Parada",2,1))*1E+13+MIN(N(N34),500)*1E+10+MIN(ROUND(N(E34),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         <v/>
       </c>
       <c r="P35" s="35">
-        <f>IF(OR(F35="",O35="Fechada",O35="Perdida"),0,IF(O35="Fechamento vencido",3000,IF(O35="Parada",2000,1000))+MIN(N35,500)+E35/1000000-ROW()/100000)</f>
+        <f>IF(OR(F35="",O35="Fechada",O35="Perdida"),0,IF(O35="Fechamento vencido",3,IF(O35="Parada",2,1))*1E+13+MIN(N(N35),500)*1E+10+MIN(ROUND(N(E35),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v/>
       </c>
       <c r="P36" s="35">
-        <f>IF(OR(F36="",O36="Fechada",O36="Perdida"),0,IF(O36="Fechamento vencido",3000,IF(O36="Parada",2000,1000))+MIN(N36,500)+E36/1000000-ROW()/100000)</f>
+        <f>IF(OR(F36="",O36="Fechada",O36="Perdida"),0,IF(O36="Fechamento vencido",3,IF(O36="Parada",2,1))*1E+13+MIN(N(N36),500)*1E+10+MIN(ROUND(N(E36),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v/>
       </c>
       <c r="P37" s="35">
-        <f>IF(OR(F37="",O37="Fechada",O37="Perdida"),0,IF(O37="Fechamento vencido",3000,IF(O37="Parada",2000,1000))+MIN(N37,500)+E37/1000000-ROW()/100000)</f>
+        <f>IF(OR(F37="",O37="Fechada",O37="Perdida"),0,IF(O37="Fechamento vencido",3,IF(O37="Parada",2,1))*1E+13+MIN(N(N37),500)*1E+10+MIN(ROUND(N(E37),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
         <v/>
       </c>
       <c r="P38" s="35">
-        <f>IF(OR(F38="",O38="Fechada",O38="Perdida"),0,IF(O38="Fechamento vencido",3000,IF(O38="Parada",2000,1000))+MIN(N38,500)+E38/1000000-ROW()/100000)</f>
+        <f>IF(OR(F38="",O38="Fechada",O38="Perdida"),0,IF(O38="Fechamento vencido",3,IF(O38="Parada",2,1))*1E+13+MIN(N(N38),500)*1E+10+MIN(ROUND(N(E38),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
         <v/>
       </c>
       <c r="P39" s="35">
-        <f>IF(OR(F39="",O39="Fechada",O39="Perdida"),0,IF(O39="Fechamento vencido",3000,IF(O39="Parada",2000,1000))+MIN(N39,500)+E39/1000000-ROW()/100000)</f>
+        <f>IF(OR(F39="",O39="Fechada",O39="Perdida"),0,IF(O39="Fechamento vencido",3,IF(O39="Parada",2,1))*1E+13+MIN(N(N39),500)*1E+10+MIN(ROUND(N(E39),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v/>
       </c>
       <c r="P40" s="35">
-        <f>IF(OR(F40="",O40="Fechada",O40="Perdida"),0,IF(O40="Fechamento vencido",3000,IF(O40="Parada",2000,1000))+MIN(N40,500)+E40/1000000-ROW()/100000)</f>
+        <f>IF(OR(F40="",O40="Fechada",O40="Perdida"),0,IF(O40="Fechamento vencido",3,IF(O40="Parada",2,1))*1E+13+MIN(N(N40),500)*1E+10+MIN(ROUND(N(E40),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
         <v/>
       </c>
       <c r="P41" s="35">
-        <f>IF(OR(F41="",O41="Fechada",O41="Perdida"),0,IF(O41="Fechamento vencido",3000,IF(O41="Parada",2000,1000))+MIN(N41,500)+E41/1000000-ROW()/100000)</f>
+        <f>IF(OR(F41="",O41="Fechada",O41="Perdida"),0,IF(O41="Fechamento vencido",3,IF(O41="Parada",2,1))*1E+13+MIN(N(N41),500)*1E+10+MIN(ROUND(N(E41),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
         <v/>
       </c>
       <c r="P42" s="35">
-        <f>IF(OR(F42="",O42="Fechada",O42="Perdida"),0,IF(O42="Fechamento vencido",3000,IF(O42="Parada",2000,1000))+MIN(N42,500)+E42/1000000-ROW()/100000)</f>
+        <f>IF(OR(F42="",O42="Fechada",O42="Perdida"),0,IF(O42="Fechamento vencido",3,IF(O42="Parada",2,1))*1E+13+MIN(N(N42),500)*1E+10+MIN(ROUND(N(E42),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
         <v/>
       </c>
       <c r="P43" s="35">
-        <f>IF(OR(F43="",O43="Fechada",O43="Perdida"),0,IF(O43="Fechamento vencido",3000,IF(O43="Parada",2000,1000))+MIN(N43,500)+E43/1000000-ROW()/100000)</f>
+        <f>IF(OR(F43="",O43="Fechada",O43="Perdida"),0,IF(O43="Fechamento vencido",3,IF(O43="Parada",2,1))*1E+13+MIN(N(N43),500)*1E+10+MIN(ROUND(N(E43),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
         <v/>
       </c>
       <c r="P44" s="35">
-        <f>IF(OR(F44="",O44="Fechada",O44="Perdida"),0,IF(O44="Fechamento vencido",3000,IF(O44="Parada",2000,1000))+MIN(N44,500)+E44/1000000-ROW()/100000)</f>
+        <f>IF(OR(F44="",O44="Fechada",O44="Perdida"),0,IF(O44="Fechamento vencido",3,IF(O44="Parada",2,1))*1E+13+MIN(N(N44),500)*1E+10+MIN(ROUND(N(E44),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
         <v/>
       </c>
       <c r="P45" s="35">
-        <f>IF(OR(F45="",O45="Fechada",O45="Perdida"),0,IF(O45="Fechamento vencido",3000,IF(O45="Parada",2000,1000))+MIN(N45,500)+E45/1000000-ROW()/100000)</f>
+        <f>IF(OR(F45="",O45="Fechada",O45="Perdida"),0,IF(O45="Fechamento vencido",3,IF(O45="Parada",2,1))*1E+13+MIN(N(N45),500)*1E+10+MIN(ROUND(N(E45),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
         <v/>
       </c>
       <c r="P46" s="35">
-        <f>IF(OR(F46="",O46="Fechada",O46="Perdida"),0,IF(O46="Fechamento vencido",3000,IF(O46="Parada",2000,1000))+MIN(N46,500)+E46/1000000-ROW()/100000)</f>
+        <f>IF(OR(F46="",O46="Fechada",O46="Perdida"),0,IF(O46="Fechamento vencido",3,IF(O46="Parada",2,1))*1E+13+MIN(N(N46),500)*1E+10+MIN(ROUND(N(E46),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="P47" s="35">
-        <f>IF(OR(F47="",O47="Fechada",O47="Perdida"),0,IF(O47="Fechamento vencido",3000,IF(O47="Parada",2000,1000))+MIN(N47,500)+E47/1000000-ROW()/100000)</f>
+        <f>IF(OR(F47="",O47="Fechada",O47="Perdida"),0,IF(O47="Fechamento vencido",3,IF(O47="Parada",2,1))*1E+13+MIN(N(N47),500)*1E+10+MIN(ROUND(N(E47),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
         <v/>
       </c>
       <c r="P48" s="35">
-        <f>IF(OR(F48="",O48="Fechada",O48="Perdida"),0,IF(O48="Fechamento vencido",3000,IF(O48="Parada",2000,1000))+MIN(N48,500)+E48/1000000-ROW()/100000)</f>
+        <f>IF(OR(F48="",O48="Fechada",O48="Perdida"),0,IF(O48="Fechamento vencido",3,IF(O48="Parada",2,1))*1E+13+MIN(N(N48),500)*1E+10+MIN(ROUND(N(E48),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
         <v/>
       </c>
       <c r="P49" s="35">
-        <f>IF(OR(F49="",O49="Fechada",O49="Perdida"),0,IF(O49="Fechamento vencido",3000,IF(O49="Parada",2000,1000))+MIN(N49,500)+E49/1000000-ROW()/100000)</f>
+        <f>IF(OR(F49="",O49="Fechada",O49="Perdida"),0,IF(O49="Fechamento vencido",3,IF(O49="Parada",2,1))*1E+13+MIN(N(N49),500)*1E+10+MIN(ROUND(N(E49),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
         <v/>
       </c>
       <c r="P50" s="35">
-        <f>IF(OR(F50="",O50="Fechada",O50="Perdida"),0,IF(O50="Fechamento vencido",3000,IF(O50="Parada",2000,1000))+MIN(N50,500)+E50/1000000-ROW()/100000)</f>
+        <f>IF(OR(F50="",O50="Fechada",O50="Perdida"),0,IF(O50="Fechamento vencido",3,IF(O50="Parada",2,1))*1E+13+MIN(N(N50),500)*1E+10+MIN(ROUND(N(E50),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
         <v/>
       </c>
       <c r="P51" s="35">
-        <f>IF(OR(F51="",O51="Fechada",O51="Perdida"),0,IF(O51="Fechamento vencido",3000,IF(O51="Parada",2000,1000))+MIN(N51,500)+E51/1000000-ROW()/100000)</f>
+        <f>IF(OR(F51="",O51="Fechada",O51="Perdida"),0,IF(O51="Fechamento vencido",3,IF(O51="Parada",2,1))*1E+13+MIN(N(N51),500)*1E+10+MIN(ROUND(N(E51),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
         <v/>
       </c>
       <c r="P52" s="35">
-        <f>IF(OR(F52="",O52="Fechada",O52="Perdida"),0,IF(O52="Fechamento vencido",3000,IF(O52="Parada",2000,1000))+MIN(N52,500)+E52/1000000-ROW()/100000)</f>
+        <f>IF(OR(F52="",O52="Fechada",O52="Perdida"),0,IF(O52="Fechamento vencido",3,IF(O52="Parada",2,1))*1E+13+MIN(N(N52),500)*1E+10+MIN(ROUND(N(E52),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
         <v/>
       </c>
       <c r="P53" s="35">
-        <f>IF(OR(F53="",O53="Fechada",O53="Perdida"),0,IF(O53="Fechamento vencido",3000,IF(O53="Parada",2000,1000))+MIN(N53,500)+E53/1000000-ROW()/100000)</f>
+        <f>IF(OR(F53="",O53="Fechada",O53="Perdida"),0,IF(O53="Fechamento vencido",3,IF(O53="Parada",2,1))*1E+13+MIN(N(N53),500)*1E+10+MIN(ROUND(N(E53),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
         <v/>
       </c>
       <c r="P54" s="35">
-        <f>IF(OR(F54="",O54="Fechada",O54="Perdida"),0,IF(O54="Fechamento vencido",3000,IF(O54="Parada",2000,1000))+MIN(N54,500)+E54/1000000-ROW()/100000)</f>
+        <f>IF(OR(F54="",O54="Fechada",O54="Perdida"),0,IF(O54="Fechamento vencido",3,IF(O54="Parada",2,1))*1E+13+MIN(N(N54),500)*1E+10+MIN(ROUND(N(E54),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         <v/>
       </c>
       <c r="P55" s="35">
-        <f>IF(OR(F55="",O55="Fechada",O55="Perdida"),0,IF(O55="Fechamento vencido",3000,IF(O55="Parada",2000,1000))+MIN(N55,500)+E55/1000000-ROW()/100000)</f>
+        <f>IF(OR(F55="",O55="Fechada",O55="Perdida"),0,IF(O55="Fechamento vencido",3,IF(O55="Parada",2,1))*1E+13+MIN(N(N55),500)*1E+10+MIN(ROUND(N(E55),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
         <v/>
       </c>
       <c r="P56" s="35">
-        <f>IF(OR(F56="",O56="Fechada",O56="Perdida"),0,IF(O56="Fechamento vencido",3000,IF(O56="Parada",2000,1000))+MIN(N56,500)+E56/1000000-ROW()/100000)</f>
+        <f>IF(OR(F56="",O56="Fechada",O56="Perdida"),0,IF(O56="Fechamento vencido",3,IF(O56="Parada",2,1))*1E+13+MIN(N(N56),500)*1E+10+MIN(ROUND(N(E56),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
         <v/>
       </c>
       <c r="P57" s="35">
-        <f>IF(OR(F57="",O57="Fechada",O57="Perdida"),0,IF(O57="Fechamento vencido",3000,IF(O57="Parada",2000,1000))+MIN(N57,500)+E57/1000000-ROW()/100000)</f>
+        <f>IF(OR(F57="",O57="Fechada",O57="Perdida"),0,IF(O57="Fechamento vencido",3,IF(O57="Parada",2,1))*1E+13+MIN(N(N57),500)*1E+10+MIN(ROUND(N(E57),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
         <v/>
       </c>
       <c r="P58" s="35">
-        <f>IF(OR(F58="",O58="Fechada",O58="Perdida"),0,IF(O58="Fechamento vencido",3000,IF(O58="Parada",2000,1000))+MIN(N58,500)+E58/1000000-ROW()/100000)</f>
+        <f>IF(OR(F58="",O58="Fechada",O58="Perdida"),0,IF(O58="Fechamento vencido",3,IF(O58="Parada",2,1))*1E+13+MIN(N(N58),500)*1E+10+MIN(ROUND(N(E58),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="P59" s="35">
-        <f>IF(OR(F59="",O59="Fechada",O59="Perdida"),0,IF(O59="Fechamento vencido",3000,IF(O59="Parada",2000,1000))+MIN(N59,500)+E59/1000000-ROW()/100000)</f>
+        <f>IF(OR(F59="",O59="Fechada",O59="Perdida"),0,IF(O59="Fechamento vencido",3,IF(O59="Parada",2,1))*1E+13+MIN(N(N59),500)*1E+10+MIN(ROUND(N(E59),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
         <v/>
       </c>
       <c r="P60" s="35">
-        <f>IF(OR(F60="",O60="Fechada",O60="Perdida"),0,IF(O60="Fechamento vencido",3000,IF(O60="Parada",2000,1000))+MIN(N60,500)+E60/1000000-ROW()/100000)</f>
+        <f>IF(OR(F60="",O60="Fechada",O60="Perdida"),0,IF(O60="Fechamento vencido",3,IF(O60="Parada",2,1))*1E+13+MIN(N(N60),500)*1E+10+MIN(ROUND(N(E60),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4763,7 +4763,7 @@
         <v/>
       </c>
       <c r="P61" s="35">
-        <f>IF(OR(F61="",O61="Fechada",O61="Perdida"),0,IF(O61="Fechamento vencido",3000,IF(O61="Parada",2000,1000))+MIN(N61,500)+E61/1000000-ROW()/100000)</f>
+        <f>IF(OR(F61="",O61="Fechada",O61="Perdida"),0,IF(O61="Fechamento vencido",3,IF(O61="Parada",2,1))*1E+13+MIN(N(N61),500)*1E+10+MIN(ROUND(N(E61),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
         <v/>
       </c>
       <c r="P62" s="35">
-        <f>IF(OR(F62="",O62="Fechada",O62="Perdida"),0,IF(O62="Fechamento vencido",3000,IF(O62="Parada",2000,1000))+MIN(N62,500)+E62/1000000-ROW()/100000)</f>
+        <f>IF(OR(F62="",O62="Fechada",O62="Perdida"),0,IF(O62="Fechamento vencido",3,IF(O62="Parada",2,1))*1E+13+MIN(N(N62),500)*1E+10+MIN(ROUND(N(E62),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
         <v/>
       </c>
       <c r="P63" s="35">
-        <f>IF(OR(F63="",O63="Fechada",O63="Perdida"),0,IF(O63="Fechamento vencido",3000,IF(O63="Parada",2000,1000))+MIN(N63,500)+E63/1000000-ROW()/100000)</f>
+        <f>IF(OR(F63="",O63="Fechada",O63="Perdida"),0,IF(O63="Fechamento vencido",3,IF(O63="Parada",2,1))*1E+13+MIN(N(N63),500)*1E+10+MIN(ROUND(N(E63),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
         <v/>
       </c>
       <c r="P64" s="35">
-        <f>IF(OR(F64="",O64="Fechada",O64="Perdida"),0,IF(O64="Fechamento vencido",3000,IF(O64="Parada",2000,1000))+MIN(N64,500)+E64/1000000-ROW()/100000)</f>
+        <f>IF(OR(F64="",O64="Fechada",O64="Perdida"),0,IF(O64="Fechamento vencido",3,IF(O64="Parada",2,1))*1E+13+MIN(N(N64),500)*1E+10+MIN(ROUND(N(E64),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
         <v/>
       </c>
       <c r="P65" s="35">
-        <f>IF(OR(F65="",O65="Fechada",O65="Perdida"),0,IF(O65="Fechamento vencido",3000,IF(O65="Parada",2000,1000))+MIN(N65,500)+E65/1000000-ROW()/100000)</f>
+        <f>IF(OR(F65="",O65="Fechada",O65="Perdida"),0,IF(O65="Fechamento vencido",3,IF(O65="Parada",2,1))*1E+13+MIN(N(N65),500)*1E+10+MIN(ROUND(N(E65),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
         <v/>
       </c>
       <c r="P66" s="35">
-        <f>IF(OR(F66="",O66="Fechada",O66="Perdida"),0,IF(O66="Fechamento vencido",3000,IF(O66="Parada",2000,1000))+MIN(N66,500)+E66/1000000-ROW()/100000)</f>
+        <f>IF(OR(F66="",O66="Fechada",O66="Perdida"),0,IF(O66="Fechamento vencido",3,IF(O66="Parada",2,1))*1E+13+MIN(N(N66),500)*1E+10+MIN(ROUND(N(E66),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
         <v/>
       </c>
       <c r="P67" s="35">
-        <f>IF(OR(F67="",O67="Fechada",O67="Perdida"),0,IF(O67="Fechamento vencido",3000,IF(O67="Parada",2000,1000))+MIN(N67,500)+E67/1000000-ROW()/100000)</f>
+        <f>IF(OR(F67="",O67="Fechada",O67="Perdida"),0,IF(O67="Fechamento vencido",3,IF(O67="Parada",2,1))*1E+13+MIN(N(N67),500)*1E+10+MIN(ROUND(N(E67),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
         <v/>
       </c>
       <c r="P68" s="35">
-        <f>IF(OR(F68="",O68="Fechada",O68="Perdida"),0,IF(O68="Fechamento vencido",3000,IF(O68="Parada",2000,1000))+MIN(N68,500)+E68/1000000-ROW()/100000)</f>
+        <f>IF(OR(F68="",O68="Fechada",O68="Perdida"),0,IF(O68="Fechamento vencido",3,IF(O68="Parada",2,1))*1E+13+MIN(N(N68),500)*1E+10+MIN(ROUND(N(E68),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="P69" s="35">
-        <f>IF(OR(F69="",O69="Fechada",O69="Perdida"),0,IF(O69="Fechamento vencido",3000,IF(O69="Parada",2000,1000))+MIN(N69,500)+E69/1000000-ROW()/100000)</f>
+        <f>IF(OR(F69="",O69="Fechada",O69="Perdida"),0,IF(O69="Fechamento vencido",3,IF(O69="Parada",2,1))*1E+13+MIN(N(N69),500)*1E+10+MIN(ROUND(N(E69),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
         <v/>
       </c>
       <c r="P70" s="35">
-        <f>IF(OR(F70="",O70="Fechada",O70="Perdida"),0,IF(O70="Fechamento vencido",3000,IF(O70="Parada",2000,1000))+MIN(N70,500)+E70/1000000-ROW()/100000)</f>
+        <f>IF(OR(F70="",O70="Fechada",O70="Perdida"),0,IF(O70="Fechamento vencido",3,IF(O70="Parada",2,1))*1E+13+MIN(N(N70),500)*1E+10+MIN(ROUND(N(E70),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
         <v/>
       </c>
       <c r="P71" s="35">
-        <f>IF(OR(F71="",O71="Fechada",O71="Perdida"),0,IF(O71="Fechamento vencido",3000,IF(O71="Parada",2000,1000))+MIN(N71,500)+E71/1000000-ROW()/100000)</f>
+        <f>IF(OR(F71="",O71="Fechada",O71="Perdida"),0,IF(O71="Fechamento vencido",3,IF(O71="Parada",2,1))*1E+13+MIN(N(N71),500)*1E+10+MIN(ROUND(N(E71),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
         <v/>
       </c>
       <c r="P72" s="35">
-        <f>IF(OR(F72="",O72="Fechada",O72="Perdida"),0,IF(O72="Fechamento vencido",3000,IF(O72="Parada",2000,1000))+MIN(N72,500)+E72/1000000-ROW()/100000)</f>
+        <f>IF(OR(F72="",O72="Fechada",O72="Perdida"),0,IF(O72="Fechamento vencido",3,IF(O72="Parada",2,1))*1E+13+MIN(N(N72),500)*1E+10+MIN(ROUND(N(E72),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
         <v/>
       </c>
       <c r="P73" s="35">
-        <f>IF(OR(F73="",O73="Fechada",O73="Perdida"),0,IF(O73="Fechamento vencido",3000,IF(O73="Parada",2000,1000))+MIN(N73,500)+E73/1000000-ROW()/100000)</f>
+        <f>IF(OR(F73="",O73="Fechada",O73="Perdida"),0,IF(O73="Fechamento vencido",3,IF(O73="Parada",2,1))*1E+13+MIN(N(N73),500)*1E+10+MIN(ROUND(N(E73),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
         <v/>
       </c>
       <c r="P74" s="35">
-        <f>IF(OR(F74="",O74="Fechada",O74="Perdida"),0,IF(O74="Fechamento vencido",3000,IF(O74="Parada",2000,1000))+MIN(N74,500)+E74/1000000-ROW()/100000)</f>
+        <f>IF(OR(F74="",O74="Fechada",O74="Perdida"),0,IF(O74="Fechamento vencido",3,IF(O74="Parada",2,1))*1E+13+MIN(N(N74),500)*1E+10+MIN(ROUND(N(E74),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v/>
       </c>
       <c r="P75" s="35">
-        <f>IF(OR(F75="",O75="Fechada",O75="Perdida"),0,IF(O75="Fechamento vencido",3000,IF(O75="Parada",2000,1000))+MIN(N75,500)+E75/1000000-ROW()/100000)</f>
+        <f>IF(OR(F75="",O75="Fechada",O75="Perdida"),0,IF(O75="Fechamento vencido",3,IF(O75="Parada",2,1))*1E+13+MIN(N(N75),500)*1E+10+MIN(ROUND(N(E75),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="P76" s="35">
-        <f>IF(OR(F76="",O76="Fechada",O76="Perdida"),0,IF(O76="Fechamento vencido",3000,IF(O76="Parada",2000,1000))+MIN(N76,500)+E76/1000000-ROW()/100000)</f>
+        <f>IF(OR(F76="",O76="Fechada",O76="Perdida"),0,IF(O76="Fechamento vencido",3,IF(O76="Parada",2,1))*1E+13+MIN(N(N76),500)*1E+10+MIN(ROUND(N(E76),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
         <v/>
       </c>
       <c r="P77" s="35">
-        <f>IF(OR(F77="",O77="Fechada",O77="Perdida"),0,IF(O77="Fechamento vencido",3000,IF(O77="Parada",2000,1000))+MIN(N77,500)+E77/1000000-ROW()/100000)</f>
+        <f>IF(OR(F77="",O77="Fechada",O77="Perdida"),0,IF(O77="Fechamento vencido",3,IF(O77="Parada",2,1))*1E+13+MIN(N(N77),500)*1E+10+MIN(ROUND(N(E77),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
         <v/>
       </c>
       <c r="P78" s="35">
-        <f>IF(OR(F78="",O78="Fechada",O78="Perdida"),0,IF(O78="Fechamento vencido",3000,IF(O78="Parada",2000,1000))+MIN(N78,500)+E78/1000000-ROW()/100000)</f>
+        <f>IF(OR(F78="",O78="Fechada",O78="Perdida"),0,IF(O78="Fechamento vencido",3,IF(O78="Parada",2,1))*1E+13+MIN(N(N78),500)*1E+10+MIN(ROUND(N(E78),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
         <v/>
       </c>
       <c r="P79" s="35">
-        <f>IF(OR(F79="",O79="Fechada",O79="Perdida"),0,IF(O79="Fechamento vencido",3000,IF(O79="Parada",2000,1000))+MIN(N79,500)+E79/1000000-ROW()/100000)</f>
+        <f>IF(OR(F79="",O79="Fechada",O79="Perdida"),0,IF(O79="Fechamento vencido",3,IF(O79="Parada",2,1))*1E+13+MIN(N(N79),500)*1E+10+MIN(ROUND(N(E79),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v/>
       </c>
       <c r="P80" s="35">
-        <f>IF(OR(F80="",O80="Fechada",O80="Perdida"),0,IF(O80="Fechamento vencido",3000,IF(O80="Parada",2000,1000))+MIN(N80,500)+E80/1000000-ROW()/100000)</f>
+        <f>IF(OR(F80="",O80="Fechada",O80="Perdida"),0,IF(O80="Fechamento vencido",3,IF(O80="Parada",2,1))*1E+13+MIN(N(N80),500)*1E+10+MIN(ROUND(N(E80),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
         <v/>
       </c>
       <c r="P81" s="35">
-        <f>IF(OR(F81="",O81="Fechada",O81="Perdida"),0,IF(O81="Fechamento vencido",3000,IF(O81="Parada",2000,1000))+MIN(N81,500)+E81/1000000-ROW()/100000)</f>
+        <f>IF(OR(F81="",O81="Fechada",O81="Perdida"),0,IF(O81="Fechamento vencido",3,IF(O81="Parada",2,1))*1E+13+MIN(N(N81),500)*1E+10+MIN(ROUND(N(E81),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
         <v/>
       </c>
       <c r="P82" s="35">
-        <f>IF(OR(F82="",O82="Fechada",O82="Perdida"),0,IF(O82="Fechamento vencido",3000,IF(O82="Parada",2000,1000))+MIN(N82,500)+E82/1000000-ROW()/100000)</f>
+        <f>IF(OR(F82="",O82="Fechada",O82="Perdida"),0,IF(O82="Fechamento vencido",3,IF(O82="Parada",2,1))*1E+13+MIN(N(N82),500)*1E+10+MIN(ROUND(N(E82),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
         <v/>
       </c>
       <c r="P83" s="35">
-        <f>IF(OR(F83="",O83="Fechada",O83="Perdida"),0,IF(O83="Fechamento vencido",3000,IF(O83="Parada",2000,1000))+MIN(N83,500)+E83/1000000-ROW()/100000)</f>
+        <f>IF(OR(F83="",O83="Fechada",O83="Perdida"),0,IF(O83="Fechamento vencido",3,IF(O83="Parada",2,1))*1E+13+MIN(N(N83),500)*1E+10+MIN(ROUND(N(E83),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
         <v/>
       </c>
       <c r="P84" s="35">
-        <f>IF(OR(F84="",O84="Fechada",O84="Perdida"),0,IF(O84="Fechamento vencido",3000,IF(O84="Parada",2000,1000))+MIN(N84,500)+E84/1000000-ROW()/100000)</f>
+        <f>IF(OR(F84="",O84="Fechada",O84="Perdida"),0,IF(O84="Fechamento vencido",3,IF(O84="Parada",2,1))*1E+13+MIN(N(N84),500)*1E+10+MIN(ROUND(N(E84),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="P85" s="35">
-        <f>IF(OR(F85="",O85="Fechada",O85="Perdida"),0,IF(O85="Fechamento vencido",3000,IF(O85="Parada",2000,1000))+MIN(N85,500)+E85/1000000-ROW()/100000)</f>
+        <f>IF(OR(F85="",O85="Fechada",O85="Perdida"),0,IF(O85="Fechamento vencido",3,IF(O85="Parada",2,1))*1E+13+MIN(N(N85),500)*1E+10+MIN(ROUND(N(E85),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
         <v/>
       </c>
       <c r="P86" s="35">
-        <f>IF(OR(F86="",O86="Fechada",O86="Perdida"),0,IF(O86="Fechamento vencido",3000,IF(O86="Parada",2000,1000))+MIN(N86,500)+E86/1000000-ROW()/100000)</f>
+        <f>IF(OR(F86="",O86="Fechada",O86="Perdida"),0,IF(O86="Fechamento vencido",3,IF(O86="Parada",2,1))*1E+13+MIN(N(N86),500)*1E+10+MIN(ROUND(N(E86),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="P87" s="35">
-        <f>IF(OR(F87="",O87="Fechada",O87="Perdida"),0,IF(O87="Fechamento vencido",3000,IF(O87="Parada",2000,1000))+MIN(N87,500)+E87/1000000-ROW()/100000)</f>
+        <f>IF(OR(F87="",O87="Fechada",O87="Perdida"),0,IF(O87="Fechamento vencido",3,IF(O87="Parada",2,1))*1E+13+MIN(N(N87),500)*1E+10+MIN(ROUND(N(E87),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
         <v/>
       </c>
       <c r="P88" s="35">
-        <f>IF(OR(F88="",O88="Fechada",O88="Perdida"),0,IF(O88="Fechamento vencido",3000,IF(O88="Parada",2000,1000))+MIN(N88,500)+E88/1000000-ROW()/100000)</f>
+        <f>IF(OR(F88="",O88="Fechada",O88="Perdida"),0,IF(O88="Fechamento vencido",3,IF(O88="Parada",2,1))*1E+13+MIN(N(N88),500)*1E+10+MIN(ROUND(N(E88),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
         <v/>
       </c>
       <c r="P89" s="35">
-        <f>IF(OR(F89="",O89="Fechada",O89="Perdida"),0,IF(O89="Fechamento vencido",3000,IF(O89="Parada",2000,1000))+MIN(N89,500)+E89/1000000-ROW()/100000)</f>
+        <f>IF(OR(F89="",O89="Fechada",O89="Perdida"),0,IF(O89="Fechamento vencido",3,IF(O89="Parada",2,1))*1E+13+MIN(N(N89),500)*1E+10+MIN(ROUND(N(E89),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
         <v/>
       </c>
       <c r="P90" s="35">
-        <f>IF(OR(F90="",O90="Fechada",O90="Perdida"),0,IF(O90="Fechamento vencido",3000,IF(O90="Parada",2000,1000))+MIN(N90,500)+E90/1000000-ROW()/100000)</f>
+        <f>IF(OR(F90="",O90="Fechada",O90="Perdida"),0,IF(O90="Fechamento vencido",3,IF(O90="Parada",2,1))*1E+13+MIN(N(N90),500)*1E+10+MIN(ROUND(N(E90),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
         <v/>
       </c>
       <c r="P91" s="35">
-        <f>IF(OR(F91="",O91="Fechada",O91="Perdida"),0,IF(O91="Fechamento vencido",3000,IF(O91="Parada",2000,1000))+MIN(N91,500)+E91/1000000-ROW()/100000)</f>
+        <f>IF(OR(F91="",O91="Fechada",O91="Perdida"),0,IF(O91="Fechamento vencido",3,IF(O91="Parada",2,1))*1E+13+MIN(N(N91),500)*1E+10+MIN(ROUND(N(E91),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
         <v/>
       </c>
       <c r="P92" s="35">
-        <f>IF(OR(F92="",O92="Fechada",O92="Perdida"),0,IF(O92="Fechamento vencido",3000,IF(O92="Parada",2000,1000))+MIN(N92,500)+E92/1000000-ROW()/100000)</f>
+        <f>IF(OR(F92="",O92="Fechada",O92="Perdida"),0,IF(O92="Fechamento vencido",3,IF(O92="Parada",2,1))*1E+13+MIN(N(N92),500)*1E+10+MIN(ROUND(N(E92),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
         <v/>
       </c>
       <c r="P93" s="35">
-        <f>IF(OR(F93="",O93="Fechada",O93="Perdida"),0,IF(O93="Fechamento vencido",3000,IF(O93="Parada",2000,1000))+MIN(N93,500)+E93/1000000-ROW()/100000)</f>
+        <f>IF(OR(F93="",O93="Fechada",O93="Perdida"),0,IF(O93="Fechamento vencido",3,IF(O93="Parada",2,1))*1E+13+MIN(N(N93),500)*1E+10+MIN(ROUND(N(E93),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="P94" s="35">
-        <f>IF(OR(F94="",O94="Fechada",O94="Perdida"),0,IF(O94="Fechamento vencido",3000,IF(O94="Parada",2000,1000))+MIN(N94,500)+E94/1000000-ROW()/100000)</f>
+        <f>IF(OR(F94="",O94="Fechada",O94="Perdida"),0,IF(O94="Fechamento vencido",3,IF(O94="Parada",2,1))*1E+13+MIN(N(N94),500)*1E+10+MIN(ROUND(N(E94),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
         <v/>
       </c>
       <c r="P95" s="35">
-        <f>IF(OR(F95="",O95="Fechada",O95="Perdida"),0,IF(O95="Fechamento vencido",3000,IF(O95="Parada",2000,1000))+MIN(N95,500)+E95/1000000-ROW()/100000)</f>
+        <f>IF(OR(F95="",O95="Fechada",O95="Perdida"),0,IF(O95="Fechamento vencido",3,IF(O95="Parada",2,1))*1E+13+MIN(N(N95),500)*1E+10+MIN(ROUND(N(E95),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
         <v/>
       </c>
       <c r="P96" s="35">
-        <f>IF(OR(F96="",O96="Fechada",O96="Perdida"),0,IF(O96="Fechamento vencido",3000,IF(O96="Parada",2000,1000))+MIN(N96,500)+E96/1000000-ROW()/100000)</f>
+        <f>IF(OR(F96="",O96="Fechada",O96="Perdida"),0,IF(O96="Fechamento vencido",3,IF(O96="Parada",2,1))*1E+13+MIN(N(N96),500)*1E+10+MIN(ROUND(N(E96),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
         <v/>
       </c>
       <c r="P97" s="35">
-        <f>IF(OR(F97="",O97="Fechada",O97="Perdida"),0,IF(O97="Fechamento vencido",3000,IF(O97="Parada",2000,1000))+MIN(N97,500)+E97/1000000-ROW()/100000)</f>
+        <f>IF(OR(F97="",O97="Fechada",O97="Perdida"),0,IF(O97="Fechamento vencido",3,IF(O97="Parada",2,1))*1E+13+MIN(N(N97),500)*1E+10+MIN(ROUND(N(E97),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
         <v/>
       </c>
       <c r="P98" s="35">
-        <f>IF(OR(F98="",O98="Fechada",O98="Perdida"),0,IF(O98="Fechamento vencido",3000,IF(O98="Parada",2000,1000))+MIN(N98,500)+E98/1000000-ROW()/100000)</f>
+        <f>IF(OR(F98="",O98="Fechada",O98="Perdida"),0,IF(O98="Fechamento vencido",3,IF(O98="Parada",2,1))*1E+13+MIN(N(N98),500)*1E+10+MIN(ROUND(N(E98),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
         <v/>
       </c>
       <c r="P99" s="35">
-        <f>IF(OR(F99="",O99="Fechada",O99="Perdida"),0,IF(O99="Fechamento vencido",3000,IF(O99="Parada",2000,1000))+MIN(N99,500)+E99/1000000-ROW()/100000)</f>
+        <f>IF(OR(F99="",O99="Fechada",O99="Perdida"),0,IF(O99="Fechamento vencido",3,IF(O99="Parada",2,1))*1E+13+MIN(N(N99),500)*1E+10+MIN(ROUND(N(E99),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="P100" s="35">
-        <f>IF(OR(F100="",O100="Fechada",O100="Perdida"),0,IF(O100="Fechamento vencido",3000,IF(O100="Parada",2000,1000))+MIN(N100,500)+E100/1000000-ROW()/100000)</f>
+        <f>IF(OR(F100="",O100="Fechada",O100="Perdida"),0,IF(O100="Fechamento vencido",3,IF(O100="Parada",2,1))*1E+13+MIN(N(N100),500)*1E+10+MIN(ROUND(N(E100),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
         <v/>
       </c>
       <c r="P101" s="35">
-        <f>IF(OR(F101="",O101="Fechada",O101="Perdida"),0,IF(O101="Fechamento vencido",3000,IF(O101="Parada",2000,1000))+MIN(N101,500)+E101/1000000-ROW()/100000)</f>
+        <f>IF(OR(F101="",O101="Fechada",O101="Perdida"),0,IF(O101="Fechamento vencido",3,IF(O101="Parada",2,1))*1E+13+MIN(N(N101),500)*1E+10+MIN(ROUND(N(E101),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
         <v/>
       </c>
       <c r="P102" s="35">
-        <f>IF(OR(F102="",O102="Fechada",O102="Perdida"),0,IF(O102="Fechamento vencido",3000,IF(O102="Parada",2000,1000))+MIN(N102,500)+E102/1000000-ROW()/100000)</f>
+        <f>IF(OR(F102="",O102="Fechada",O102="Perdida"),0,IF(O102="Fechamento vencido",3,IF(O102="Parada",2,1))*1E+13+MIN(N(N102),500)*1E+10+MIN(ROUND(N(E102),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
         <v/>
       </c>
       <c r="P103" s="35">
-        <f>IF(OR(F103="",O103="Fechada",O103="Perdida"),0,IF(O103="Fechamento vencido",3000,IF(O103="Parada",2000,1000))+MIN(N103,500)+E103/1000000-ROW()/100000)</f>
+        <f>IF(OR(F103="",O103="Fechada",O103="Perdida"),0,IF(O103="Fechamento vencido",3,IF(O103="Parada",2,1))*1E+13+MIN(N(N103),500)*1E+10+MIN(ROUND(N(E103),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
         <v/>
       </c>
       <c r="P104" s="35">
-        <f>IF(OR(F104="",O104="Fechada",O104="Perdida"),0,IF(O104="Fechamento vencido",3000,IF(O104="Parada",2000,1000))+MIN(N104,500)+E104/1000000-ROW()/100000)</f>
+        <f>IF(OR(F104="",O104="Fechada",O104="Perdida"),0,IF(O104="Fechamento vencido",3,IF(O104="Parada",2,1))*1E+13+MIN(N(N104),500)*1E+10+MIN(ROUND(N(E104),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v/>
       </c>
       <c r="P105" s="35">
-        <f>IF(OR(F105="",O105="Fechada",O105="Perdida"),0,IF(O105="Fechamento vencido",3000,IF(O105="Parada",2000,1000))+MIN(N105,500)+E105/1000000-ROW()/100000)</f>
+        <f>IF(OR(F105="",O105="Fechada",O105="Perdida"),0,IF(O105="Fechamento vencido",3,IF(O105="Parada",2,1))*1E+13+MIN(N(N105),500)*1E+10+MIN(ROUND(N(E105),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
         <v/>
       </c>
       <c r="P106" s="35">
-        <f>IF(OR(F106="",O106="Fechada",O106="Perdida"),0,IF(O106="Fechamento vencido",3000,IF(O106="Parada",2000,1000))+MIN(N106,500)+E106/1000000-ROW()/100000)</f>
+        <f>IF(OR(F106="",O106="Fechada",O106="Perdida"),0,IF(O106="Fechamento vencido",3,IF(O106="Parada",2,1))*1E+13+MIN(N(N106),500)*1E+10+MIN(ROUND(N(E106),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
         <v/>
       </c>
       <c r="P107" s="35">
-        <f>IF(OR(F107="",O107="Fechada",O107="Perdida"),0,IF(O107="Fechamento vencido",3000,IF(O107="Parada",2000,1000))+MIN(N107,500)+E107/1000000-ROW()/100000)</f>
+        <f>IF(OR(F107="",O107="Fechada",O107="Perdida"),0,IF(O107="Fechamento vencido",3,IF(O107="Parada",2,1))*1E+13+MIN(N(N107),500)*1E+10+MIN(ROUND(N(E107),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
         <v/>
       </c>
       <c r="P108" s="35">
-        <f>IF(OR(F108="",O108="Fechada",O108="Perdida"),0,IF(O108="Fechamento vencido",3000,IF(O108="Parada",2000,1000))+MIN(N108,500)+E108/1000000-ROW()/100000)</f>
+        <f>IF(OR(F108="",O108="Fechada",O108="Perdida"),0,IF(O108="Fechamento vencido",3,IF(O108="Parada",2,1))*1E+13+MIN(N(N108),500)*1E+10+MIN(ROUND(N(E108),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
         <v/>
       </c>
       <c r="P109" s="35">
-        <f>IF(OR(F109="",O109="Fechada",O109="Perdida"),0,IF(O109="Fechamento vencido",3000,IF(O109="Parada",2000,1000))+MIN(N109,500)+E109/1000000-ROW()/100000)</f>
+        <f>IF(OR(F109="",O109="Fechada",O109="Perdida"),0,IF(O109="Fechamento vencido",3,IF(O109="Parada",2,1))*1E+13+MIN(N(N109),500)*1E+10+MIN(ROUND(N(E109),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
         <v/>
       </c>
       <c r="P110" s="35">
-        <f>IF(OR(F110="",O110="Fechada",O110="Perdida"),0,IF(O110="Fechamento vencido",3000,IF(O110="Parada",2000,1000))+MIN(N110,500)+E110/1000000-ROW()/100000)</f>
+        <f>IF(OR(F110="",O110="Fechada",O110="Perdida"),0,IF(O110="Fechamento vencido",3,IF(O110="Parada",2,1))*1E+13+MIN(N(N110),500)*1E+10+MIN(ROUND(N(E110),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
         <v/>
       </c>
       <c r="P111" s="35">
-        <f>IF(OR(F111="",O111="Fechada",O111="Perdida"),0,IF(O111="Fechamento vencido",3000,IF(O111="Parada",2000,1000))+MIN(N111,500)+E111/1000000-ROW()/100000)</f>
+        <f>IF(OR(F111="",O111="Fechada",O111="Perdida"),0,IF(O111="Fechamento vencido",3,IF(O111="Parada",2,1))*1E+13+MIN(N(N111),500)*1E+10+MIN(ROUND(N(E111),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
         <v/>
       </c>
       <c r="P112" s="35">
-        <f>IF(OR(F112="",O112="Fechada",O112="Perdida"),0,IF(O112="Fechamento vencido",3000,IF(O112="Parada",2000,1000))+MIN(N112,500)+E112/1000000-ROW()/100000)</f>
+        <f>IF(OR(F112="",O112="Fechada",O112="Perdida"),0,IF(O112="Fechamento vencido",3,IF(O112="Parada",2,1))*1E+13+MIN(N(N112),500)*1E+10+MIN(ROUND(N(E112),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
         <v/>
       </c>
       <c r="P113" s="35">
-        <f>IF(OR(F113="",O113="Fechada",O113="Perdida"),0,IF(O113="Fechamento vencido",3000,IF(O113="Parada",2000,1000))+MIN(N113,500)+E113/1000000-ROW()/100000)</f>
+        <f>IF(OR(F113="",O113="Fechada",O113="Perdida"),0,IF(O113="Fechamento vencido",3,IF(O113="Parada",2,1))*1E+13+MIN(N(N113),500)*1E+10+MIN(ROUND(N(E113),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
         <v/>
       </c>
       <c r="P114" s="35">
-        <f>IF(OR(F114="",O114="Fechada",O114="Perdida"),0,IF(O114="Fechamento vencido",3000,IF(O114="Parada",2000,1000))+MIN(N114,500)+E114/1000000-ROW()/100000)</f>
+        <f>IF(OR(F114="",O114="Fechada",O114="Perdida"),0,IF(O114="Fechamento vencido",3,IF(O114="Parada",2,1))*1E+13+MIN(N(N114),500)*1E+10+MIN(ROUND(N(E114),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
         <v/>
       </c>
       <c r="P115" s="35">
-        <f>IF(OR(F115="",O115="Fechada",O115="Perdida"),0,IF(O115="Fechamento vencido",3000,IF(O115="Parada",2000,1000))+MIN(N115,500)+E115/1000000-ROW()/100000)</f>
+        <f>IF(OR(F115="",O115="Fechada",O115="Perdida"),0,IF(O115="Fechamento vencido",3,IF(O115="Parada",2,1))*1E+13+MIN(N(N115),500)*1E+10+MIN(ROUND(N(E115),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
         <v/>
       </c>
       <c r="P116" s="35">
-        <f>IF(OR(F116="",O116="Fechada",O116="Perdida"),0,IF(O116="Fechamento vencido",3000,IF(O116="Parada",2000,1000))+MIN(N116,500)+E116/1000000-ROW()/100000)</f>
+        <f>IF(OR(F116="",O116="Fechada",O116="Perdida"),0,IF(O116="Fechamento vencido",3,IF(O116="Parada",2,1))*1E+13+MIN(N(N116),500)*1E+10+MIN(ROUND(N(E116),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
         <v/>
       </c>
       <c r="P117" s="35">
-        <f>IF(OR(F117="",O117="Fechada",O117="Perdida"),0,IF(O117="Fechamento vencido",3000,IF(O117="Parada",2000,1000))+MIN(N117,500)+E117/1000000-ROW()/100000)</f>
+        <f>IF(OR(F117="",O117="Fechada",O117="Perdida"),0,IF(O117="Fechamento vencido",3,IF(O117="Parada",2,1))*1E+13+MIN(N(N117),500)*1E+10+MIN(ROUND(N(E117),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
         <v/>
       </c>
       <c r="P118" s="35">
-        <f>IF(OR(F118="",O118="Fechada",O118="Perdida"),0,IF(O118="Fechamento vencido",3000,IF(O118="Parada",2000,1000))+MIN(N118,500)+E118/1000000-ROW()/100000)</f>
+        <f>IF(OR(F118="",O118="Fechada",O118="Perdida"),0,IF(O118="Fechamento vencido",3,IF(O118="Parada",2,1))*1E+13+MIN(N(N118),500)*1E+10+MIN(ROUND(N(E118),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
         <v/>
       </c>
       <c r="P119" s="35">
-        <f>IF(OR(F119="",O119="Fechada",O119="Perdida"),0,IF(O119="Fechamento vencido",3000,IF(O119="Parada",2000,1000))+MIN(N119,500)+E119/1000000-ROW()/100000)</f>
+        <f>IF(OR(F119="",O119="Fechada",O119="Perdida"),0,IF(O119="Fechamento vencido",3,IF(O119="Parada",2,1))*1E+13+MIN(N(N119),500)*1E+10+MIN(ROUND(N(E119),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
         <v/>
       </c>
       <c r="P120" s="35">
-        <f>IF(OR(F120="",O120="Fechada",O120="Perdida"),0,IF(O120="Fechamento vencido",3000,IF(O120="Parada",2000,1000))+MIN(N120,500)+E120/1000000-ROW()/100000)</f>
+        <f>IF(OR(F120="",O120="Fechada",O120="Perdida"),0,IF(O120="Fechamento vencido",3,IF(O120="Parada",2,1))*1E+13+MIN(N(N120),500)*1E+10+MIN(ROUND(N(E120),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
         <v/>
       </c>
       <c r="P121" s="35">
-        <f>IF(OR(F121="",O121="Fechada",O121="Perdida"),0,IF(O121="Fechamento vencido",3000,IF(O121="Parada",2000,1000))+MIN(N121,500)+E121/1000000-ROW()/100000)</f>
+        <f>IF(OR(F121="",O121="Fechada",O121="Perdida"),0,IF(O121="Fechamento vencido",3,IF(O121="Parada",2,1))*1E+13+MIN(N(N121),500)*1E+10+MIN(ROUND(N(E121),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
         <v/>
       </c>
       <c r="P122" s="35">
-        <f>IF(OR(F122="",O122="Fechada",O122="Perdida"),0,IF(O122="Fechamento vencido",3000,IF(O122="Parada",2000,1000))+MIN(N122,500)+E122/1000000-ROW()/100000)</f>
+        <f>IF(OR(F122="",O122="Fechada",O122="Perdida"),0,IF(O122="Fechamento vencido",3,IF(O122="Parada",2,1))*1E+13+MIN(N(N122),500)*1E+10+MIN(ROUND(N(E122),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
         <v/>
       </c>
       <c r="P123" s="35">
-        <f>IF(OR(F123="",O123="Fechada",O123="Perdida"),0,IF(O123="Fechamento vencido",3000,IF(O123="Parada",2000,1000))+MIN(N123,500)+E123/1000000-ROW()/100000)</f>
+        <f>IF(OR(F123="",O123="Fechada",O123="Perdida"),0,IF(O123="Fechamento vencido",3,IF(O123="Parada",2,1))*1E+13+MIN(N(N123),500)*1E+10+MIN(ROUND(N(E123),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
         <v/>
       </c>
       <c r="P124" s="35">
-        <f>IF(OR(F124="",O124="Fechada",O124="Perdida"),0,IF(O124="Fechamento vencido",3000,IF(O124="Parada",2000,1000))+MIN(N124,500)+E124/1000000-ROW()/100000)</f>
+        <f>IF(OR(F124="",O124="Fechada",O124="Perdida"),0,IF(O124="Fechamento vencido",3,IF(O124="Parada",2,1))*1E+13+MIN(N(N124),500)*1E+10+MIN(ROUND(N(E124),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
         <v/>
       </c>
       <c r="P125" s="35">
-        <f>IF(OR(F125="",O125="Fechada",O125="Perdida"),0,IF(O125="Fechamento vencido",3000,IF(O125="Parada",2000,1000))+MIN(N125,500)+E125/1000000-ROW()/100000)</f>
+        <f>IF(OR(F125="",O125="Fechada",O125="Perdida"),0,IF(O125="Fechamento vencido",3,IF(O125="Parada",2,1))*1E+13+MIN(N(N125),500)*1E+10+MIN(ROUND(N(E125),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
         <v/>
       </c>
       <c r="P126" s="35">
-        <f>IF(OR(F126="",O126="Fechada",O126="Perdida"),0,IF(O126="Fechamento vencido",3000,IF(O126="Parada",2000,1000))+MIN(N126,500)+E126/1000000-ROW()/100000)</f>
+        <f>IF(OR(F126="",O126="Fechada",O126="Perdida"),0,IF(O126="Fechamento vencido",3,IF(O126="Parada",2,1))*1E+13+MIN(N(N126),500)*1E+10+MIN(ROUND(N(E126),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
         <v/>
       </c>
       <c r="P127" s="35">
-        <f>IF(OR(F127="",O127="Fechada",O127="Perdida"),0,IF(O127="Fechamento vencido",3000,IF(O127="Parada",2000,1000))+MIN(N127,500)+E127/1000000-ROW()/100000)</f>
+        <f>IF(OR(F127="",O127="Fechada",O127="Perdida"),0,IF(O127="Fechamento vencido",3,IF(O127="Parada",2,1))*1E+13+MIN(N(N127),500)*1E+10+MIN(ROUND(N(E127),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v/>
       </c>
       <c r="P128" s="35">
-        <f>IF(OR(F128="",O128="Fechada",O128="Perdida"),0,IF(O128="Fechamento vencido",3000,IF(O128="Parada",2000,1000))+MIN(N128,500)+E128/1000000-ROW()/100000)</f>
+        <f>IF(OR(F128="",O128="Fechada",O128="Perdida"),0,IF(O128="Fechamento vencido",3,IF(O128="Parada",2,1))*1E+13+MIN(N(N128),500)*1E+10+MIN(ROUND(N(E128),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
         <v/>
       </c>
       <c r="P129" s="35">
-        <f>IF(OR(F129="",O129="Fechada",O129="Perdida"),0,IF(O129="Fechamento vencido",3000,IF(O129="Parada",2000,1000))+MIN(N129,500)+E129/1000000-ROW()/100000)</f>
+        <f>IF(OR(F129="",O129="Fechada",O129="Perdida"),0,IF(O129="Fechamento vencido",3,IF(O129="Parada",2,1))*1E+13+MIN(N(N129),500)*1E+10+MIN(ROUND(N(E129),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
         <v/>
       </c>
       <c r="P130" s="35">
-        <f>IF(OR(F130="",O130="Fechada",O130="Perdida"),0,IF(O130="Fechamento vencido",3000,IF(O130="Parada",2000,1000))+MIN(N130,500)+E130/1000000-ROW()/100000)</f>
+        <f>IF(OR(F130="",O130="Fechada",O130="Perdida"),0,IF(O130="Fechamento vencido",3,IF(O130="Parada",2,1))*1E+13+MIN(N(N130),500)*1E+10+MIN(ROUND(N(E130),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
         <v/>
       </c>
       <c r="P131" s="35">
-        <f>IF(OR(F131="",O131="Fechada",O131="Perdida"),0,IF(O131="Fechamento vencido",3000,IF(O131="Parada",2000,1000))+MIN(N131,500)+E131/1000000-ROW()/100000)</f>
+        <f>IF(OR(F131="",O131="Fechada",O131="Perdida"),0,IF(O131="Fechamento vencido",3,IF(O131="Parada",2,1))*1E+13+MIN(N(N131),500)*1E+10+MIN(ROUND(N(E131),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
         <v/>
       </c>
       <c r="P132" s="35">
-        <f>IF(OR(F132="",O132="Fechada",O132="Perdida"),0,IF(O132="Fechamento vencido",3000,IF(O132="Parada",2000,1000))+MIN(N132,500)+E132/1000000-ROW()/100000)</f>
+        <f>IF(OR(F132="",O132="Fechada",O132="Perdida"),0,IF(O132="Fechamento vencido",3,IF(O132="Parada",2,1))*1E+13+MIN(N(N132),500)*1E+10+MIN(ROUND(N(E132),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
         <v/>
       </c>
       <c r="P133" s="35">
-        <f>IF(OR(F133="",O133="Fechada",O133="Perdida"),0,IF(O133="Fechamento vencido",3000,IF(O133="Parada",2000,1000))+MIN(N133,500)+E133/1000000-ROW()/100000)</f>
+        <f>IF(OR(F133="",O133="Fechada",O133="Perdida"),0,IF(O133="Fechamento vencido",3,IF(O133="Parada",2,1))*1E+13+MIN(N(N133),500)*1E+10+MIN(ROUND(N(E133),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
         <v/>
       </c>
       <c r="P134" s="35">
-        <f>IF(OR(F134="",O134="Fechada",O134="Perdida"),0,IF(O134="Fechamento vencido",3000,IF(O134="Parada",2000,1000))+MIN(N134,500)+E134/1000000-ROW()/100000)</f>
+        <f>IF(OR(F134="",O134="Fechada",O134="Perdida"),0,IF(O134="Fechamento vencido",3,IF(O134="Parada",2,1))*1E+13+MIN(N(N134),500)*1E+10+MIN(ROUND(N(E134),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
         <v/>
       </c>
       <c r="P135" s="35">
-        <f>IF(OR(F135="",O135="Fechada",O135="Perdida"),0,IF(O135="Fechamento vencido",3000,IF(O135="Parada",2000,1000))+MIN(N135,500)+E135/1000000-ROW()/100000)</f>
+        <f>IF(OR(F135="",O135="Fechada",O135="Perdida"),0,IF(O135="Fechamento vencido",3,IF(O135="Parada",2,1))*1E+13+MIN(N(N135),500)*1E+10+MIN(ROUND(N(E135),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
         <v/>
       </c>
       <c r="P136" s="35">
-        <f>IF(OR(F136="",O136="Fechada",O136="Perdida"),0,IF(O136="Fechamento vencido",3000,IF(O136="Parada",2000,1000))+MIN(N136,500)+E136/1000000-ROW()/100000)</f>
+        <f>IF(OR(F136="",O136="Fechada",O136="Perdida"),0,IF(O136="Fechamento vencido",3,IF(O136="Parada",2,1))*1E+13+MIN(N(N136),500)*1E+10+MIN(ROUND(N(E136),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         <v/>
       </c>
       <c r="P137" s="35">
-        <f>IF(OR(F137="",O137="Fechada",O137="Perdida"),0,IF(O137="Fechamento vencido",3000,IF(O137="Parada",2000,1000))+MIN(N137,500)+E137/1000000-ROW()/100000)</f>
+        <f>IF(OR(F137="",O137="Fechada",O137="Perdida"),0,IF(O137="Fechamento vencido",3,IF(O137="Parada",2,1))*1E+13+MIN(N(N137),500)*1E+10+MIN(ROUND(N(E137),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
         <v/>
       </c>
       <c r="P138" s="35">
-        <f>IF(OR(F138="",O138="Fechada",O138="Perdida"),0,IF(O138="Fechamento vencido",3000,IF(O138="Parada",2000,1000))+MIN(N138,500)+E138/1000000-ROW()/100000)</f>
+        <f>IF(OR(F138="",O138="Fechada",O138="Perdida"),0,IF(O138="Fechamento vencido",3,IF(O138="Parada",2,1))*1E+13+MIN(N(N138),500)*1E+10+MIN(ROUND(N(E138),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
         <v/>
       </c>
       <c r="P139" s="35">
-        <f>IF(OR(F139="",O139="Fechada",O139="Perdida"),0,IF(O139="Fechamento vencido",3000,IF(O139="Parada",2000,1000))+MIN(N139,500)+E139/1000000-ROW()/100000)</f>
+        <f>IF(OR(F139="",O139="Fechada",O139="Perdida"),0,IF(O139="Fechamento vencido",3,IF(O139="Parada",2,1))*1E+13+MIN(N(N139),500)*1E+10+MIN(ROUND(N(E139),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
         <v/>
       </c>
       <c r="P140" s="35">
-        <f>IF(OR(F140="",O140="Fechada",O140="Perdida"),0,IF(O140="Fechamento vencido",3000,IF(O140="Parada",2000,1000))+MIN(N140,500)+E140/1000000-ROW()/100000)</f>
+        <f>IF(OR(F140="",O140="Fechada",O140="Perdida"),0,IF(O140="Fechamento vencido",3,IF(O140="Parada",2,1))*1E+13+MIN(N(N140),500)*1E+10+MIN(ROUND(N(E140),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
         <v/>
       </c>
       <c r="P141" s="35">
-        <f>IF(OR(F141="",O141="Fechada",O141="Perdida"),0,IF(O141="Fechamento vencido",3000,IF(O141="Parada",2000,1000))+MIN(N141,500)+E141/1000000-ROW()/100000)</f>
+        <f>IF(OR(F141="",O141="Fechada",O141="Perdida"),0,IF(O141="Fechamento vencido",3,IF(O141="Parada",2,1))*1E+13+MIN(N(N141),500)*1E+10+MIN(ROUND(N(E141),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
         <v/>
       </c>
       <c r="P142" s="35">
-        <f>IF(OR(F142="",O142="Fechada",O142="Perdida"),0,IF(O142="Fechamento vencido",3000,IF(O142="Parada",2000,1000))+MIN(N142,500)+E142/1000000-ROW()/100000)</f>
+        <f>IF(OR(F142="",O142="Fechada",O142="Perdida"),0,IF(O142="Fechamento vencido",3,IF(O142="Parada",2,1))*1E+13+MIN(N(N142),500)*1E+10+MIN(ROUND(N(E142),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
         <v/>
       </c>
       <c r="P143" s="35">
-        <f>IF(OR(F143="",O143="Fechada",O143="Perdida"),0,IF(O143="Fechamento vencido",3000,IF(O143="Parada",2000,1000))+MIN(N143,500)+E143/1000000-ROW()/100000)</f>
+        <f>IF(OR(F143="",O143="Fechada",O143="Perdida"),0,IF(O143="Fechamento vencido",3,IF(O143="Parada",2,1))*1E+13+MIN(N(N143),500)*1E+10+MIN(ROUND(N(E143),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="P144" s="35">
-        <f>IF(OR(F144="",O144="Fechada",O144="Perdida"),0,IF(O144="Fechamento vencido",3000,IF(O144="Parada",2000,1000))+MIN(N144,500)+E144/1000000-ROW()/100000)</f>
+        <f>IF(OR(F144="",O144="Fechada",O144="Perdida"),0,IF(O144="Fechamento vencido",3,IF(O144="Parada",2,1))*1E+13+MIN(N(N144),500)*1E+10+MIN(ROUND(N(E144),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
         <v/>
       </c>
       <c r="P145" s="35">
-        <f>IF(OR(F145="",O145="Fechada",O145="Perdida"),0,IF(O145="Fechamento vencido",3000,IF(O145="Parada",2000,1000))+MIN(N145,500)+E145/1000000-ROW()/100000)</f>
+        <f>IF(OR(F145="",O145="Fechada",O145="Perdida"),0,IF(O145="Fechamento vencido",3,IF(O145="Parada",2,1))*1E+13+MIN(N(N145),500)*1E+10+MIN(ROUND(N(E145),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         <v/>
       </c>
       <c r="P146" s="35">
-        <f>IF(OR(F146="",O146="Fechada",O146="Perdida"),0,IF(O146="Fechamento vencido",3000,IF(O146="Parada",2000,1000))+MIN(N146,500)+E146/1000000-ROW()/100000)</f>
+        <f>IF(OR(F146="",O146="Fechada",O146="Perdida"),0,IF(O146="Fechamento vencido",3,IF(O146="Parada",2,1))*1E+13+MIN(N(N146),500)*1E+10+MIN(ROUND(N(E146),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
         <v/>
       </c>
       <c r="P147" s="35">
-        <f>IF(OR(F147="",O147="Fechada",O147="Perdida"),0,IF(O147="Fechamento vencido",3000,IF(O147="Parada",2000,1000))+MIN(N147,500)+E147/1000000-ROW()/100000)</f>
+        <f>IF(OR(F147="",O147="Fechada",O147="Perdida"),0,IF(O147="Fechamento vencido",3,IF(O147="Parada",2,1))*1E+13+MIN(N(N147),500)*1E+10+MIN(ROUND(N(E147),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
         <v/>
       </c>
       <c r="P148" s="35">
-        <f>IF(OR(F148="",O148="Fechada",O148="Perdida"),0,IF(O148="Fechamento vencido",3000,IF(O148="Parada",2000,1000))+MIN(N148,500)+E148/1000000-ROW()/100000)</f>
+        <f>IF(OR(F148="",O148="Fechada",O148="Perdida"),0,IF(O148="Fechamento vencido",3,IF(O148="Parada",2,1))*1E+13+MIN(N(N148),500)*1E+10+MIN(ROUND(N(E148),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
         <v/>
       </c>
       <c r="P149" s="35">
-        <f>IF(OR(F149="",O149="Fechada",O149="Perdida"),0,IF(O149="Fechamento vencido",3000,IF(O149="Parada",2000,1000))+MIN(N149,500)+E149/1000000-ROW()/100000)</f>
+        <f>IF(OR(F149="",O149="Fechada",O149="Perdida"),0,IF(O149="Fechamento vencido",3,IF(O149="Parada",2,1))*1E+13+MIN(N(N149),500)*1E+10+MIN(ROUND(N(E149),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
         <v/>
       </c>
       <c r="P150" s="35">
-        <f>IF(OR(F150="",O150="Fechada",O150="Perdida"),0,IF(O150="Fechamento vencido",3000,IF(O150="Parada",2000,1000))+MIN(N150,500)+E150/1000000-ROW()/100000)</f>
+        <f>IF(OR(F150="",O150="Fechada",O150="Perdida"),0,IF(O150="Fechamento vencido",3,IF(O150="Parada",2,1))*1E+13+MIN(N(N150),500)*1E+10+MIN(ROUND(N(E150),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v/>
       </c>
       <c r="P151" s="35">
-        <f>IF(OR(F151="",O151="Fechada",O151="Perdida"),0,IF(O151="Fechamento vencido",3000,IF(O151="Parada",2000,1000))+MIN(N151,500)+E151/1000000-ROW()/100000)</f>
+        <f>IF(OR(F151="",O151="Fechada",O151="Perdida"),0,IF(O151="Fechamento vencido",3,IF(O151="Parada",2,1))*1E+13+MIN(N(N151),500)*1E+10+MIN(ROUND(N(E151),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
         <v/>
       </c>
       <c r="P152" s="35">
-        <f>IF(OR(F152="",O152="Fechada",O152="Perdida"),0,IF(O152="Fechamento vencido",3000,IF(O152="Parada",2000,1000))+MIN(N152,500)+E152/1000000-ROW()/100000)</f>
+        <f>IF(OR(F152="",O152="Fechada",O152="Perdida"),0,IF(O152="Fechamento vencido",3,IF(O152="Parada",2,1))*1E+13+MIN(N(N152),500)*1E+10+MIN(ROUND(N(E152),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="P153" s="35">
-        <f>IF(OR(F153="",O153="Fechada",O153="Perdida"),0,IF(O153="Fechamento vencido",3000,IF(O153="Parada",2000,1000))+MIN(N153,500)+E153/1000000-ROW()/100000)</f>
+        <f>IF(OR(F153="",O153="Fechada",O153="Perdida"),0,IF(O153="Fechamento vencido",3,IF(O153="Parada",2,1))*1E+13+MIN(N(N153),500)*1E+10+MIN(ROUND(N(E153),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
         <v/>
       </c>
       <c r="P154" s="35">
-        <f>IF(OR(F154="",O154="Fechada",O154="Perdida"),0,IF(O154="Fechamento vencido",3000,IF(O154="Parada",2000,1000))+MIN(N154,500)+E154/1000000-ROW()/100000)</f>
+        <f>IF(OR(F154="",O154="Fechada",O154="Perdida"),0,IF(O154="Fechamento vencido",3,IF(O154="Parada",2,1))*1E+13+MIN(N(N154),500)*1E+10+MIN(ROUND(N(E154),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
         <v/>
       </c>
       <c r="P155" s="35">
-        <f>IF(OR(F155="",O155="Fechada",O155="Perdida"),0,IF(O155="Fechamento vencido",3000,IF(O155="Parada",2000,1000))+MIN(N155,500)+E155/1000000-ROW()/100000)</f>
+        <f>IF(OR(F155="",O155="Fechada",O155="Perdida"),0,IF(O155="Fechamento vencido",3,IF(O155="Parada",2,1))*1E+13+MIN(N(N155),500)*1E+10+MIN(ROUND(N(E155),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
         <v/>
       </c>
       <c r="P156" s="35">
-        <f>IF(OR(F156="",O156="Fechada",O156="Perdida"),0,IF(O156="Fechamento vencido",3000,IF(O156="Parada",2000,1000))+MIN(N156,500)+E156/1000000-ROW()/100000)</f>
+        <f>IF(OR(F156="",O156="Fechada",O156="Perdida"),0,IF(O156="Fechamento vencido",3,IF(O156="Parada",2,1))*1E+13+MIN(N(N156),500)*1E+10+MIN(ROUND(N(E156),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         <v/>
       </c>
       <c r="P157" s="35">
-        <f>IF(OR(F157="",O157="Fechada",O157="Perdida"),0,IF(O157="Fechamento vencido",3000,IF(O157="Parada",2000,1000))+MIN(N157,500)+E157/1000000-ROW()/100000)</f>
+        <f>IF(OR(F157="",O157="Fechada",O157="Perdida"),0,IF(O157="Fechamento vencido",3,IF(O157="Parada",2,1))*1E+13+MIN(N(N157),500)*1E+10+MIN(ROUND(N(E157),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
         <v/>
       </c>
       <c r="P158" s="35">
-        <f>IF(OR(F158="",O158="Fechada",O158="Perdida"),0,IF(O158="Fechamento vencido",3000,IF(O158="Parada",2000,1000))+MIN(N158,500)+E158/1000000-ROW()/100000)</f>
+        <f>IF(OR(F158="",O158="Fechada",O158="Perdida"),0,IF(O158="Fechamento vencido",3,IF(O158="Parada",2,1))*1E+13+MIN(N(N158),500)*1E+10+MIN(ROUND(N(E158),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
         <v/>
       </c>
       <c r="P159" s="35">
-        <f>IF(OR(F159="",O159="Fechada",O159="Perdida"),0,IF(O159="Fechamento vencido",3000,IF(O159="Parada",2000,1000))+MIN(N159,500)+E159/1000000-ROW()/100000)</f>
+        <f>IF(OR(F159="",O159="Fechada",O159="Perdida"),0,IF(O159="Fechamento vencido",3,IF(O159="Parada",2,1))*1E+13+MIN(N(N159),500)*1E+10+MIN(ROUND(N(E159),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         <v/>
       </c>
       <c r="P160" s="35">
-        <f>IF(OR(F160="",O160="Fechada",O160="Perdida"),0,IF(O160="Fechamento vencido",3000,IF(O160="Parada",2000,1000))+MIN(N160,500)+E160/1000000-ROW()/100000)</f>
+        <f>IF(OR(F160="",O160="Fechada",O160="Perdida"),0,IF(O160="Fechamento vencido",3,IF(O160="Parada",2,1))*1E+13+MIN(N(N160),500)*1E+10+MIN(ROUND(N(E160),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
         <v/>
       </c>
       <c r="P161" s="35">
-        <f>IF(OR(F161="",O161="Fechada",O161="Perdida"),0,IF(O161="Fechamento vencido",3000,IF(O161="Parada",2000,1000))+MIN(N161,500)+E161/1000000-ROW()/100000)</f>
+        <f>IF(OR(F161="",O161="Fechada",O161="Perdida"),0,IF(O161="Fechamento vencido",3,IF(O161="Parada",2,1))*1E+13+MIN(N(N161),500)*1E+10+MIN(ROUND(N(E161),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
         <v/>
       </c>
       <c r="P162" s="35">
-        <f>IF(OR(F162="",O162="Fechada",O162="Perdida"),0,IF(O162="Fechamento vencido",3000,IF(O162="Parada",2000,1000))+MIN(N162,500)+E162/1000000-ROW()/100000)</f>
+        <f>IF(OR(F162="",O162="Fechada",O162="Perdida"),0,IF(O162="Fechamento vencido",3,IF(O162="Parada",2,1))*1E+13+MIN(N(N162),500)*1E+10+MIN(ROUND(N(E162),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         <v/>
       </c>
       <c r="P163" s="35">
-        <f>IF(OR(F163="",O163="Fechada",O163="Perdida"),0,IF(O163="Fechamento vencido",3000,IF(O163="Parada",2000,1000))+MIN(N163,500)+E163/1000000-ROW()/100000)</f>
+        <f>IF(OR(F163="",O163="Fechada",O163="Perdida"),0,IF(O163="Fechamento vencido",3,IF(O163="Parada",2,1))*1E+13+MIN(N(N163),500)*1E+10+MIN(ROUND(N(E163),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
         <v/>
       </c>
       <c r="P164" s="35">
-        <f>IF(OR(F164="",O164="Fechada",O164="Perdida"),0,IF(O164="Fechamento vencido",3000,IF(O164="Parada",2000,1000))+MIN(N164,500)+E164/1000000-ROW()/100000)</f>
+        <f>IF(OR(F164="",O164="Fechada",O164="Perdida"),0,IF(O164="Fechamento vencido",3,IF(O164="Parada",2,1))*1E+13+MIN(N(N164),500)*1E+10+MIN(ROUND(N(E164),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
         <v/>
       </c>
       <c r="P165" s="35">
-        <f>IF(OR(F165="",O165="Fechada",O165="Perdida"),0,IF(O165="Fechamento vencido",3000,IF(O165="Parada",2000,1000))+MIN(N165,500)+E165/1000000-ROW()/100000)</f>
+        <f>IF(OR(F165="",O165="Fechada",O165="Perdida"),0,IF(O165="Fechamento vencido",3,IF(O165="Parada",2,1))*1E+13+MIN(N(N165),500)*1E+10+MIN(ROUND(N(E165),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
         <v/>
       </c>
       <c r="P166" s="35">
-        <f>IF(OR(F166="",O166="Fechada",O166="Perdida"),0,IF(O166="Fechamento vencido",3000,IF(O166="Parada",2000,1000))+MIN(N166,500)+E166/1000000-ROW()/100000)</f>
+        <f>IF(OR(F166="",O166="Fechada",O166="Perdida"),0,IF(O166="Fechamento vencido",3,IF(O166="Parada",2,1))*1E+13+MIN(N(N166),500)*1E+10+MIN(ROUND(N(E166),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
         <v/>
       </c>
       <c r="P167" s="35">
-        <f>IF(OR(F167="",O167="Fechada",O167="Perdida"),0,IF(O167="Fechamento vencido",3000,IF(O167="Parada",2000,1000))+MIN(N167,500)+E167/1000000-ROW()/100000)</f>
+        <f>IF(OR(F167="",O167="Fechada",O167="Perdida"),0,IF(O167="Fechamento vencido",3,IF(O167="Parada",2,1))*1E+13+MIN(N(N167),500)*1E+10+MIN(ROUND(N(E167),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
         <v/>
       </c>
       <c r="P168" s="35">
-        <f>IF(OR(F168="",O168="Fechada",O168="Perdida"),0,IF(O168="Fechamento vencido",3000,IF(O168="Parada",2000,1000))+MIN(N168,500)+E168/1000000-ROW()/100000)</f>
+        <f>IF(OR(F168="",O168="Fechada",O168="Perdida"),0,IF(O168="Fechamento vencido",3,IF(O168="Parada",2,1))*1E+13+MIN(N(N168),500)*1E+10+MIN(ROUND(N(E168),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
         <v/>
       </c>
       <c r="P169" s="35">
-        <f>IF(OR(F169="",O169="Fechada",O169="Perdida"),0,IF(O169="Fechamento vencido",3000,IF(O169="Parada",2000,1000))+MIN(N169,500)+E169/1000000-ROW()/100000)</f>
+        <f>IF(OR(F169="",O169="Fechada",O169="Perdida"),0,IF(O169="Fechamento vencido",3,IF(O169="Parada",2,1))*1E+13+MIN(N(N169),500)*1E+10+MIN(ROUND(N(E169),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
         <v/>
       </c>
       <c r="P170" s="35">
-        <f>IF(OR(F170="",O170="Fechada",O170="Perdida"),0,IF(O170="Fechamento vencido",3000,IF(O170="Parada",2000,1000))+MIN(N170,500)+E170/1000000-ROW()/100000)</f>
+        <f>IF(OR(F170="",O170="Fechada",O170="Perdida"),0,IF(O170="Fechamento vencido",3,IF(O170="Parada",2,1))*1E+13+MIN(N(N170),500)*1E+10+MIN(ROUND(N(E170),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
         <v/>
       </c>
       <c r="P171" s="35">
-        <f>IF(OR(F171="",O171="Fechada",O171="Perdida"),0,IF(O171="Fechamento vencido",3000,IF(O171="Parada",2000,1000))+MIN(N171,500)+E171/1000000-ROW()/100000)</f>
+        <f>IF(OR(F171="",O171="Fechada",O171="Perdida"),0,IF(O171="Fechamento vencido",3,IF(O171="Parada",2,1))*1E+13+MIN(N(N171),500)*1E+10+MIN(ROUND(N(E171),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
         <v/>
       </c>
       <c r="P172" s="35">
-        <f>IF(OR(F172="",O172="Fechada",O172="Perdida"),0,IF(O172="Fechamento vencido",3000,IF(O172="Parada",2000,1000))+MIN(N172,500)+E172/1000000-ROW()/100000)</f>
+        <f>IF(OR(F172="",O172="Fechada",O172="Perdida"),0,IF(O172="Fechamento vencido",3,IF(O172="Parada",2,1))*1E+13+MIN(N(N172),500)*1E+10+MIN(ROUND(N(E172),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
         <v/>
       </c>
       <c r="P173" s="35">
-        <f>IF(OR(F173="",O173="Fechada",O173="Perdida"),0,IF(O173="Fechamento vencido",3000,IF(O173="Parada",2000,1000))+MIN(N173,500)+E173/1000000-ROW()/100000)</f>
+        <f>IF(OR(F173="",O173="Fechada",O173="Perdida"),0,IF(O173="Fechamento vencido",3,IF(O173="Parada",2,1))*1E+13+MIN(N(N173),500)*1E+10+MIN(ROUND(N(E173),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v/>
       </c>
       <c r="P174" s="35">
-        <f>IF(OR(F174="",O174="Fechada",O174="Perdida"),0,IF(O174="Fechamento vencido",3000,IF(O174="Parada",2000,1000))+MIN(N174,500)+E174/1000000-ROW()/100000)</f>
+        <f>IF(OR(F174="",O174="Fechada",O174="Perdida"),0,IF(O174="Fechamento vencido",3,IF(O174="Parada",2,1))*1E+13+MIN(N(N174),500)*1E+10+MIN(ROUND(N(E174),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
         <v/>
       </c>
       <c r="P175" s="35">
-        <f>IF(OR(F175="",O175="Fechada",O175="Perdida"),0,IF(O175="Fechamento vencido",3000,IF(O175="Parada",2000,1000))+MIN(N175,500)+E175/1000000-ROW()/100000)</f>
+        <f>IF(OR(F175="",O175="Fechada",O175="Perdida"),0,IF(O175="Fechamento vencido",3,IF(O175="Parada",2,1))*1E+13+MIN(N(N175),500)*1E+10+MIN(ROUND(N(E175),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
         <v/>
       </c>
       <c r="P176" s="35">
-        <f>IF(OR(F176="",O176="Fechada",O176="Perdida"),0,IF(O176="Fechamento vencido",3000,IF(O176="Parada",2000,1000))+MIN(N176,500)+E176/1000000-ROW()/100000)</f>
+        <f>IF(OR(F176="",O176="Fechada",O176="Perdida"),0,IF(O176="Fechamento vencido",3,IF(O176="Parada",2,1))*1E+13+MIN(N(N176),500)*1E+10+MIN(ROUND(N(E176),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
         <v/>
       </c>
       <c r="P177" s="35">
-        <f>IF(OR(F177="",O177="Fechada",O177="Perdida"),0,IF(O177="Fechamento vencido",3000,IF(O177="Parada",2000,1000))+MIN(N177,500)+E177/1000000-ROW()/100000)</f>
+        <f>IF(OR(F177="",O177="Fechada",O177="Perdida"),0,IF(O177="Fechamento vencido",3,IF(O177="Parada",2,1))*1E+13+MIN(N(N177),500)*1E+10+MIN(ROUND(N(E177),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8624,7 +8624,7 @@
         <v/>
       </c>
       <c r="P178" s="35">
-        <f>IF(OR(F178="",O178="Fechada",O178="Perdida"),0,IF(O178="Fechamento vencido",3000,IF(O178="Parada",2000,1000))+MIN(N178,500)+E178/1000000-ROW()/100000)</f>
+        <f>IF(OR(F178="",O178="Fechada",O178="Perdida"),0,IF(O178="Fechamento vencido",3,IF(O178="Parada",2,1))*1E+13+MIN(N(N178),500)*1E+10+MIN(ROUND(N(E178),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
         <v/>
       </c>
       <c r="P179" s="35">
-        <f>IF(OR(F179="",O179="Fechada",O179="Perdida"),0,IF(O179="Fechamento vencido",3000,IF(O179="Parada",2000,1000))+MIN(N179,500)+E179/1000000-ROW()/100000)</f>
+        <f>IF(OR(F179="",O179="Fechada",O179="Perdida"),0,IF(O179="Fechamento vencido",3,IF(O179="Parada",2,1))*1E+13+MIN(N(N179),500)*1E+10+MIN(ROUND(N(E179),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
         <v/>
       </c>
       <c r="P180" s="35">
-        <f>IF(OR(F180="",O180="Fechada",O180="Perdida"),0,IF(O180="Fechamento vencido",3000,IF(O180="Parada",2000,1000))+MIN(N180,500)+E180/1000000-ROW()/100000)</f>
+        <f>IF(OR(F180="",O180="Fechada",O180="Perdida"),0,IF(O180="Fechamento vencido",3,IF(O180="Parada",2,1))*1E+13+MIN(N(N180),500)*1E+10+MIN(ROUND(N(E180),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
         <v/>
       </c>
       <c r="P181" s="35">
-        <f>IF(OR(F181="",O181="Fechada",O181="Perdida"),0,IF(O181="Fechamento vencido",3000,IF(O181="Parada",2000,1000))+MIN(N181,500)+E181/1000000-ROW()/100000)</f>
+        <f>IF(OR(F181="",O181="Fechada",O181="Perdida"),0,IF(O181="Fechamento vencido",3,IF(O181="Parada",2,1))*1E+13+MIN(N(N181),500)*1E+10+MIN(ROUND(N(E181),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
         <v/>
       </c>
       <c r="P182" s="35">
-        <f>IF(OR(F182="",O182="Fechada",O182="Perdida"),0,IF(O182="Fechamento vencido",3000,IF(O182="Parada",2000,1000))+MIN(N182,500)+E182/1000000-ROW()/100000)</f>
+        <f>IF(OR(F182="",O182="Fechada",O182="Perdida"),0,IF(O182="Fechamento vencido",3,IF(O182="Parada",2,1))*1E+13+MIN(N(N182),500)*1E+10+MIN(ROUND(N(E182),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
         <v/>
       </c>
       <c r="P183" s="35">
-        <f>IF(OR(F183="",O183="Fechada",O183="Perdida"),0,IF(O183="Fechamento vencido",3000,IF(O183="Parada",2000,1000))+MIN(N183,500)+E183/1000000-ROW()/100000)</f>
+        <f>IF(OR(F183="",O183="Fechada",O183="Perdida"),0,IF(O183="Fechamento vencido",3,IF(O183="Parada",2,1))*1E+13+MIN(N(N183),500)*1E+10+MIN(ROUND(N(E183),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
         <v/>
       </c>
       <c r="P184" s="35">
-        <f>IF(OR(F184="",O184="Fechada",O184="Perdida"),0,IF(O184="Fechamento vencido",3000,IF(O184="Parada",2000,1000))+MIN(N184,500)+E184/1000000-ROW()/100000)</f>
+        <f>IF(OR(F184="",O184="Fechada",O184="Perdida"),0,IF(O184="Fechamento vencido",3,IF(O184="Parada",2,1))*1E+13+MIN(N(N184),500)*1E+10+MIN(ROUND(N(E184),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
         <v/>
       </c>
       <c r="P185" s="35">
-        <f>IF(OR(F185="",O185="Fechada",O185="Perdida"),0,IF(O185="Fechamento vencido",3000,IF(O185="Parada",2000,1000))+MIN(N185,500)+E185/1000000-ROW()/100000)</f>
+        <f>IF(OR(F185="",O185="Fechada",O185="Perdida"),0,IF(O185="Fechamento vencido",3,IF(O185="Parada",2,1))*1E+13+MIN(N(N185),500)*1E+10+MIN(ROUND(N(E185),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
         <v/>
       </c>
       <c r="P186" s="35">
-        <f>IF(OR(F186="",O186="Fechada",O186="Perdida"),0,IF(O186="Fechamento vencido",3000,IF(O186="Parada",2000,1000))+MIN(N186,500)+E186/1000000-ROW()/100000)</f>
+        <f>IF(OR(F186="",O186="Fechada",O186="Perdida"),0,IF(O186="Fechamento vencido",3,IF(O186="Parada",2,1))*1E+13+MIN(N(N186),500)*1E+10+MIN(ROUND(N(E186),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
         <v/>
       </c>
       <c r="P187" s="35">
-        <f>IF(OR(F187="",O187="Fechada",O187="Perdida"),0,IF(O187="Fechamento vencido",3000,IF(O187="Parada",2000,1000))+MIN(N187,500)+E187/1000000-ROW()/100000)</f>
+        <f>IF(OR(F187="",O187="Fechada",O187="Perdida"),0,IF(O187="Fechamento vencido",3,IF(O187="Parada",2,1))*1E+13+MIN(N(N187),500)*1E+10+MIN(ROUND(N(E187),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
         <v/>
       </c>
       <c r="P188" s="35">
-        <f>IF(OR(F188="",O188="Fechada",O188="Perdida"),0,IF(O188="Fechamento vencido",3000,IF(O188="Parada",2000,1000))+MIN(N188,500)+E188/1000000-ROW()/100000)</f>
+        <f>IF(OR(F188="",O188="Fechada",O188="Perdida"),0,IF(O188="Fechamento vencido",3,IF(O188="Parada",2,1))*1E+13+MIN(N(N188),500)*1E+10+MIN(ROUND(N(E188),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
         <v/>
       </c>
       <c r="P189" s="35">
-        <f>IF(OR(F189="",O189="Fechada",O189="Perdida"),0,IF(O189="Fechamento vencido",3000,IF(O189="Parada",2000,1000))+MIN(N189,500)+E189/1000000-ROW()/100000)</f>
+        <f>IF(OR(F189="",O189="Fechada",O189="Perdida"),0,IF(O189="Fechamento vencido",3,IF(O189="Parada",2,1))*1E+13+MIN(N(N189),500)*1E+10+MIN(ROUND(N(E189),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
         <v/>
       </c>
       <c r="P190" s="35">
-        <f>IF(OR(F190="",O190="Fechada",O190="Perdida"),0,IF(O190="Fechamento vencido",3000,IF(O190="Parada",2000,1000))+MIN(N190,500)+E190/1000000-ROW()/100000)</f>
+        <f>IF(OR(F190="",O190="Fechada",O190="Perdida"),0,IF(O190="Fechamento vencido",3,IF(O190="Parada",2,1))*1E+13+MIN(N(N190),500)*1E+10+MIN(ROUND(N(E190),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
         <v/>
       </c>
       <c r="P191" s="35">
-        <f>IF(OR(F191="",O191="Fechada",O191="Perdida"),0,IF(O191="Fechamento vencido",3000,IF(O191="Parada",2000,1000))+MIN(N191,500)+E191/1000000-ROW()/100000)</f>
+        <f>IF(OR(F191="",O191="Fechada",O191="Perdida"),0,IF(O191="Fechamento vencido",3,IF(O191="Parada",2,1))*1E+13+MIN(N(N191),500)*1E+10+MIN(ROUND(N(E191),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="P192" s="35">
-        <f>IF(OR(F192="",O192="Fechada",O192="Perdida"),0,IF(O192="Fechamento vencido",3000,IF(O192="Parada",2000,1000))+MIN(N192,500)+E192/1000000-ROW()/100000)</f>
+        <f>IF(OR(F192="",O192="Fechada",O192="Perdida"),0,IF(O192="Fechamento vencido",3,IF(O192="Parada",2,1))*1E+13+MIN(N(N192),500)*1E+10+MIN(ROUND(N(E192),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
         <v/>
       </c>
       <c r="P193" s="35">
-        <f>IF(OR(F193="",O193="Fechada",O193="Perdida"),0,IF(O193="Fechamento vencido",3000,IF(O193="Parada",2000,1000))+MIN(N193,500)+E193/1000000-ROW()/100000)</f>
+        <f>IF(OR(F193="",O193="Fechada",O193="Perdida"),0,IF(O193="Fechamento vencido",3,IF(O193="Parada",2,1))*1E+13+MIN(N(N193),500)*1E+10+MIN(ROUND(N(E193),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
         <v/>
       </c>
       <c r="P194" s="35">
-        <f>IF(OR(F194="",O194="Fechada",O194="Perdida"),0,IF(O194="Fechamento vencido",3000,IF(O194="Parada",2000,1000))+MIN(N194,500)+E194/1000000-ROW()/100000)</f>
+        <f>IF(OR(F194="",O194="Fechada",O194="Perdida"),0,IF(O194="Fechamento vencido",3,IF(O194="Parada",2,1))*1E+13+MIN(N(N194),500)*1E+10+MIN(ROUND(N(E194),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
         <v/>
       </c>
       <c r="P195" s="35">
-        <f>IF(OR(F195="",O195="Fechada",O195="Perdida"),0,IF(O195="Fechamento vencido",3000,IF(O195="Parada",2000,1000))+MIN(N195,500)+E195/1000000-ROW()/100000)</f>
+        <f>IF(OR(F195="",O195="Fechada",O195="Perdida"),0,IF(O195="Fechamento vencido",3,IF(O195="Parada",2,1))*1E+13+MIN(N(N195),500)*1E+10+MIN(ROUND(N(E195),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
         <v/>
       </c>
       <c r="P196" s="35">
-        <f>IF(OR(F196="",O196="Fechada",O196="Perdida"),0,IF(O196="Fechamento vencido",3000,IF(O196="Parada",2000,1000))+MIN(N196,500)+E196/1000000-ROW()/100000)</f>
+        <f>IF(OR(F196="",O196="Fechada",O196="Perdida"),0,IF(O196="Fechamento vencido",3,IF(O196="Parada",2,1))*1E+13+MIN(N(N196),500)*1E+10+MIN(ROUND(N(E196),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v/>
       </c>
       <c r="P197" s="35">
-        <f>IF(OR(F197="",O197="Fechada",O197="Perdida"),0,IF(O197="Fechamento vencido",3000,IF(O197="Parada",2000,1000))+MIN(N197,500)+E197/1000000-ROW()/100000)</f>
+        <f>IF(OR(F197="",O197="Fechada",O197="Perdida"),0,IF(O197="Fechamento vencido",3,IF(O197="Parada",2,1))*1E+13+MIN(N(N197),500)*1E+10+MIN(ROUND(N(E197),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
         <v/>
       </c>
       <c r="P198" s="35">
-        <f>IF(OR(F198="",O198="Fechada",O198="Perdida"),0,IF(O198="Fechamento vencido",3000,IF(O198="Parada",2000,1000))+MIN(N198,500)+E198/1000000-ROW()/100000)</f>
+        <f>IF(OR(F198="",O198="Fechada",O198="Perdida"),0,IF(O198="Fechamento vencido",3,IF(O198="Parada",2,1))*1E+13+MIN(N(N198),500)*1E+10+MIN(ROUND(N(E198),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v/>
       </c>
       <c r="P199" s="35">
-        <f>IF(OR(F199="",O199="Fechada",O199="Perdida"),0,IF(O199="Fechamento vencido",3000,IF(O199="Parada",2000,1000))+MIN(N199,500)+E199/1000000-ROW()/100000)</f>
+        <f>IF(OR(F199="",O199="Fechada",O199="Perdida"),0,IF(O199="Fechamento vencido",3,IF(O199="Parada",2,1))*1E+13+MIN(N(N199),500)*1E+10+MIN(ROUND(N(E199),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
         <v/>
       </c>
       <c r="P200" s="35">
-        <f>IF(OR(F200="",O200="Fechada",O200="Perdida"),0,IF(O200="Fechamento vencido",3000,IF(O200="Parada",2000,1000))+MIN(N200,500)+E200/1000000-ROW()/100000)</f>
+        <f>IF(OR(F200="",O200="Fechada",O200="Perdida"),0,IF(O200="Fechamento vencido",3,IF(O200="Parada",2,1))*1E+13+MIN(N(N200),500)*1E+10+MIN(ROUND(N(E200),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
         <v/>
       </c>
       <c r="P201" s="35">
-        <f>IF(OR(F201="",O201="Fechada",O201="Perdida"),0,IF(O201="Fechamento vencido",3000,IF(O201="Parada",2000,1000))+MIN(N201,500)+E201/1000000-ROW()/100000)</f>
+        <f>IF(OR(F201="",O201="Fechada",O201="Perdida"),0,IF(O201="Fechamento vencido",3,IF(O201="Parada",2,1))*1E+13+MIN(N(N201),500)*1E+10+MIN(ROUND(N(E201),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
         <v/>
       </c>
       <c r="P202" s="35">
-        <f>IF(OR(F202="",O202="Fechada",O202="Perdida"),0,IF(O202="Fechamento vencido",3000,IF(O202="Parada",2000,1000))+MIN(N202,500)+E202/1000000-ROW()/100000)</f>
+        <f>IF(OR(F202="",O202="Fechada",O202="Perdida"),0,IF(O202="Fechamento vencido",3,IF(O202="Parada",2,1))*1E+13+MIN(N(N202),500)*1E+10+MIN(ROUND(N(E202),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="P203" s="35">
-        <f>IF(OR(F203="",O203="Fechada",O203="Perdida"),0,IF(O203="Fechamento vencido",3000,IF(O203="Parada",2000,1000))+MIN(N203,500)+E203/1000000-ROW()/100000)</f>
+        <f>IF(OR(F203="",O203="Fechada",O203="Perdida"),0,IF(O203="Fechamento vencido",3,IF(O203="Parada",2,1))*1E+13+MIN(N(N203),500)*1E+10+MIN(ROUND(N(E203),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
         <v/>
       </c>
       <c r="P204" s="35">
-        <f>IF(OR(F204="",O204="Fechada",O204="Perdida"),0,IF(O204="Fechamento vencido",3000,IF(O204="Parada",2000,1000))+MIN(N204,500)+E204/1000000-ROW()/100000)</f>
+        <f>IF(OR(F204="",O204="Fechada",O204="Perdida"),0,IF(O204="Fechamento vencido",3,IF(O204="Parada",2,1))*1E+13+MIN(N(N204),500)*1E+10+MIN(ROUND(N(E204),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
         <v/>
       </c>
       <c r="P205" s="35">
-        <f>IF(OR(F205="",O205="Fechada",O205="Perdida"),0,IF(O205="Fechamento vencido",3000,IF(O205="Parada",2000,1000))+MIN(N205,500)+E205/1000000-ROW()/100000)</f>
+        <f>IF(OR(F205="",O205="Fechada",O205="Perdida"),0,IF(O205="Fechamento vencido",3,IF(O205="Parada",2,1))*1E+13+MIN(N(N205),500)*1E+10+MIN(ROUND(N(E205),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="P206" s="35">
-        <f>IF(OR(F206="",O206="Fechada",O206="Perdida"),0,IF(O206="Fechamento vencido",3000,IF(O206="Parada",2000,1000))+MIN(N206,500)+E206/1000000-ROW()/100000)</f>
+        <f>IF(OR(F206="",O206="Fechada",O206="Perdida"),0,IF(O206="Fechamento vencido",3,IF(O206="Parada",2,1))*1E+13+MIN(N(N206),500)*1E+10+MIN(ROUND(N(E206),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
         <v/>
       </c>
       <c r="P207" s="35">
-        <f>IF(OR(F207="",O207="Fechada",O207="Perdida"),0,IF(O207="Fechamento vencido",3000,IF(O207="Parada",2000,1000))+MIN(N207,500)+E207/1000000-ROW()/100000)</f>
+        <f>IF(OR(F207="",O207="Fechada",O207="Perdida"),0,IF(O207="Fechamento vencido",3,IF(O207="Parada",2,1))*1E+13+MIN(N(N207),500)*1E+10+MIN(ROUND(N(E207),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
         <v/>
       </c>
       <c r="P208" s="35">
-        <f>IF(OR(F208="",O208="Fechada",O208="Perdida"),0,IF(O208="Fechamento vencido",3000,IF(O208="Parada",2000,1000))+MIN(N208,500)+E208/1000000-ROW()/100000)</f>
+        <f>IF(OR(F208="",O208="Fechada",O208="Perdida"),0,IF(O208="Fechamento vencido",3,IF(O208="Parada",2,1))*1E+13+MIN(N(N208),500)*1E+10+MIN(ROUND(N(E208),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
         <v/>
       </c>
       <c r="P209" s="35">
-        <f>IF(OR(F209="",O209="Fechada",O209="Perdida"),0,IF(O209="Fechamento vencido",3000,IF(O209="Parada",2000,1000))+MIN(N209,500)+E209/1000000-ROW()/100000)</f>
+        <f>IF(OR(F209="",O209="Fechada",O209="Perdida"),0,IF(O209="Fechamento vencido",3,IF(O209="Parada",2,1))*1E+13+MIN(N(N209),500)*1E+10+MIN(ROUND(N(E209),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9680,7 +9680,7 @@
         <v/>
       </c>
       <c r="P210" s="35">
-        <f>IF(OR(F210="",O210="Fechada",O210="Perdida"),0,IF(O210="Fechamento vencido",3000,IF(O210="Parada",2000,1000))+MIN(N210,500)+E210/1000000-ROW()/100000)</f>
+        <f>IF(OR(F210="",O210="Fechada",O210="Perdida"),0,IF(O210="Fechamento vencido",3,IF(O210="Parada",2,1))*1E+13+MIN(N(N210),500)*1E+10+MIN(ROUND(N(E210),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
         <v/>
       </c>
       <c r="P211" s="35">
-        <f>IF(OR(F211="",O211="Fechada",O211="Perdida"),0,IF(O211="Fechamento vencido",3000,IF(O211="Parada",2000,1000))+MIN(N211,500)+E211/1000000-ROW()/100000)</f>
+        <f>IF(OR(F211="",O211="Fechada",O211="Perdida"),0,IF(O211="Fechamento vencido",3,IF(O211="Parada",2,1))*1E+13+MIN(N(N211),500)*1E+10+MIN(ROUND(N(E211),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
         <v/>
       </c>
       <c r="P212" s="35">
-        <f>IF(OR(F212="",O212="Fechada",O212="Perdida"),0,IF(O212="Fechamento vencido",3000,IF(O212="Parada",2000,1000))+MIN(N212,500)+E212/1000000-ROW()/100000)</f>
+        <f>IF(OR(F212="",O212="Fechada",O212="Perdida"),0,IF(O212="Fechamento vencido",3,IF(O212="Parada",2,1))*1E+13+MIN(N(N212),500)*1E+10+MIN(ROUND(N(E212),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
         <v/>
       </c>
       <c r="P213" s="35">
-        <f>IF(OR(F213="",O213="Fechada",O213="Perdida"),0,IF(O213="Fechamento vencido",3000,IF(O213="Parada",2000,1000))+MIN(N213,500)+E213/1000000-ROW()/100000)</f>
+        <f>IF(OR(F213="",O213="Fechada",O213="Perdida"),0,IF(O213="Fechamento vencido",3,IF(O213="Parada",2,1))*1E+13+MIN(N(N213),500)*1E+10+MIN(ROUND(N(E213),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
         <v/>
       </c>
       <c r="P214" s="35">
-        <f>IF(OR(F214="",O214="Fechada",O214="Perdida"),0,IF(O214="Fechamento vencido",3000,IF(O214="Parada",2000,1000))+MIN(N214,500)+E214/1000000-ROW()/100000)</f>
+        <f>IF(OR(F214="",O214="Fechada",O214="Perdida"),0,IF(O214="Fechamento vencido",3,IF(O214="Parada",2,1))*1E+13+MIN(N(N214),500)*1E+10+MIN(ROUND(N(E214),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
         <v/>
       </c>
       <c r="P215" s="35">
-        <f>IF(OR(F215="",O215="Fechada",O215="Perdida"),0,IF(O215="Fechamento vencido",3000,IF(O215="Parada",2000,1000))+MIN(N215,500)+E215/1000000-ROW()/100000)</f>
+        <f>IF(OR(F215="",O215="Fechada",O215="Perdida"),0,IF(O215="Fechamento vencido",3,IF(O215="Parada",2,1))*1E+13+MIN(N(N215),500)*1E+10+MIN(ROUND(N(E215),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v/>
       </c>
       <c r="P216" s="35">
-        <f>IF(OR(F216="",O216="Fechada",O216="Perdida"),0,IF(O216="Fechamento vencido",3000,IF(O216="Parada",2000,1000))+MIN(N216,500)+E216/1000000-ROW()/100000)</f>
+        <f>IF(OR(F216="",O216="Fechada",O216="Perdida"),0,IF(O216="Fechamento vencido",3,IF(O216="Parada",2,1))*1E+13+MIN(N(N216),500)*1E+10+MIN(ROUND(N(E216),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
         <v/>
       </c>
       <c r="P217" s="35">
-        <f>IF(OR(F217="",O217="Fechada",O217="Perdida"),0,IF(O217="Fechamento vencido",3000,IF(O217="Parada",2000,1000))+MIN(N217,500)+E217/1000000-ROW()/100000)</f>
+        <f>IF(OR(F217="",O217="Fechada",O217="Perdida"),0,IF(O217="Fechamento vencido",3,IF(O217="Parada",2,1))*1E+13+MIN(N(N217),500)*1E+10+MIN(ROUND(N(E217),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
         <v/>
       </c>
       <c r="P218" s="35">
-        <f>IF(OR(F218="",O218="Fechada",O218="Perdida"),0,IF(O218="Fechamento vencido",3000,IF(O218="Parada",2000,1000))+MIN(N218,500)+E218/1000000-ROW()/100000)</f>
+        <f>IF(OR(F218="",O218="Fechada",O218="Perdida"),0,IF(O218="Fechamento vencido",3,IF(O218="Parada",2,1))*1E+13+MIN(N(N218),500)*1E+10+MIN(ROUND(N(E218),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
         <v/>
       </c>
       <c r="P219" s="35">
-        <f>IF(OR(F219="",O219="Fechada",O219="Perdida"),0,IF(O219="Fechamento vencido",3000,IF(O219="Parada",2000,1000))+MIN(N219,500)+E219/1000000-ROW()/100000)</f>
+        <f>IF(OR(F219="",O219="Fechada",O219="Perdida"),0,IF(O219="Fechamento vencido",3,IF(O219="Parada",2,1))*1E+13+MIN(N(N219),500)*1E+10+MIN(ROUND(N(E219),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v/>
       </c>
       <c r="P220" s="35">
-        <f>IF(OR(F220="",O220="Fechada",O220="Perdida"),0,IF(O220="Fechamento vencido",3000,IF(O220="Parada",2000,1000))+MIN(N220,500)+E220/1000000-ROW()/100000)</f>
+        <f>IF(OR(F220="",O220="Fechada",O220="Perdida"),0,IF(O220="Fechamento vencido",3,IF(O220="Parada",2,1))*1E+13+MIN(N(N220),500)*1E+10+MIN(ROUND(N(E220),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
         <v/>
       </c>
       <c r="P221" s="35">
-        <f>IF(OR(F221="",O221="Fechada",O221="Perdida"),0,IF(O221="Fechamento vencido",3000,IF(O221="Parada",2000,1000))+MIN(N221,500)+E221/1000000-ROW()/100000)</f>
+        <f>IF(OR(F221="",O221="Fechada",O221="Perdida"),0,IF(O221="Fechamento vencido",3,IF(O221="Parada",2,1))*1E+13+MIN(N(N221),500)*1E+10+MIN(ROUND(N(E221),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
         <v/>
       </c>
       <c r="P222" s="35">
-        <f>IF(OR(F222="",O222="Fechada",O222="Perdida"),0,IF(O222="Fechamento vencido",3000,IF(O222="Parada",2000,1000))+MIN(N222,500)+E222/1000000-ROW()/100000)</f>
+        <f>IF(OR(F222="",O222="Fechada",O222="Perdida"),0,IF(O222="Fechamento vencido",3,IF(O222="Parada",2,1))*1E+13+MIN(N(N222),500)*1E+10+MIN(ROUND(N(E222),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
         <v/>
       </c>
       <c r="P223" s="35">
-        <f>IF(OR(F223="",O223="Fechada",O223="Perdida"),0,IF(O223="Fechamento vencido",3000,IF(O223="Parada",2000,1000))+MIN(N223,500)+E223/1000000-ROW()/100000)</f>
+        <f>IF(OR(F223="",O223="Fechada",O223="Perdida"),0,IF(O223="Fechamento vencido",3,IF(O223="Parada",2,1))*1E+13+MIN(N(N223),500)*1E+10+MIN(ROUND(N(E223),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
         <v/>
       </c>
       <c r="P224" s="35">
-        <f>IF(OR(F224="",O224="Fechada",O224="Perdida"),0,IF(O224="Fechamento vencido",3000,IF(O224="Parada",2000,1000))+MIN(N224,500)+E224/1000000-ROW()/100000)</f>
+        <f>IF(OR(F224="",O224="Fechada",O224="Perdida"),0,IF(O224="Fechamento vencido",3,IF(O224="Parada",2,1))*1E+13+MIN(N(N224),500)*1E+10+MIN(ROUND(N(E224),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
         <v/>
       </c>
       <c r="P225" s="35">
-        <f>IF(OR(F225="",O225="Fechada",O225="Perdida"),0,IF(O225="Fechamento vencido",3000,IF(O225="Parada",2000,1000))+MIN(N225,500)+E225/1000000-ROW()/100000)</f>
+        <f>IF(OR(F225="",O225="Fechada",O225="Perdida"),0,IF(O225="Fechamento vencido",3,IF(O225="Parada",2,1))*1E+13+MIN(N(N225),500)*1E+10+MIN(ROUND(N(E225),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
         <v/>
       </c>
       <c r="P226" s="35">
-        <f>IF(OR(F226="",O226="Fechada",O226="Perdida"),0,IF(O226="Fechamento vencido",3000,IF(O226="Parada",2000,1000))+MIN(N226,500)+E226/1000000-ROW()/100000)</f>
+        <f>IF(OR(F226="",O226="Fechada",O226="Perdida"),0,IF(O226="Fechamento vencido",3,IF(O226="Parada",2,1))*1E+13+MIN(N(N226),500)*1E+10+MIN(ROUND(N(E226),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
         <v/>
       </c>
       <c r="P227" s="35">
-        <f>IF(OR(F227="",O227="Fechada",O227="Perdida"),0,IF(O227="Fechamento vencido",3000,IF(O227="Parada",2000,1000))+MIN(N227,500)+E227/1000000-ROW()/100000)</f>
+        <f>IF(OR(F227="",O227="Fechada",O227="Perdida"),0,IF(O227="Fechamento vencido",3,IF(O227="Parada",2,1))*1E+13+MIN(N(N227),500)*1E+10+MIN(ROUND(N(E227),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
         <v/>
       </c>
       <c r="P228" s="35">
-        <f>IF(OR(F228="",O228="Fechada",O228="Perdida"),0,IF(O228="Fechamento vencido",3000,IF(O228="Parada",2000,1000))+MIN(N228,500)+E228/1000000-ROW()/100000)</f>
+        <f>IF(OR(F228="",O228="Fechada",O228="Perdida"),0,IF(O228="Fechamento vencido",3,IF(O228="Parada",2,1))*1E+13+MIN(N(N228),500)*1E+10+MIN(ROUND(N(E228),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
         <v/>
       </c>
       <c r="P229" s="35">
-        <f>IF(OR(F229="",O229="Fechada",O229="Perdida"),0,IF(O229="Fechamento vencido",3000,IF(O229="Parada",2000,1000))+MIN(N229,500)+E229/1000000-ROW()/100000)</f>
+        <f>IF(OR(F229="",O229="Fechada",O229="Perdida"),0,IF(O229="Fechamento vencido",3,IF(O229="Parada",2,1))*1E+13+MIN(N(N229),500)*1E+10+MIN(ROUND(N(E229),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
         <v/>
       </c>
       <c r="P230" s="35">
-        <f>IF(OR(F230="",O230="Fechada",O230="Perdida"),0,IF(O230="Fechamento vencido",3000,IF(O230="Parada",2000,1000))+MIN(N230,500)+E230/1000000-ROW()/100000)</f>
+        <f>IF(OR(F230="",O230="Fechada",O230="Perdida"),0,IF(O230="Fechamento vencido",3,IF(O230="Parada",2,1))*1E+13+MIN(N(N230),500)*1E+10+MIN(ROUND(N(E230),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
         <v/>
       </c>
       <c r="P231" s="35">
-        <f>IF(OR(F231="",O231="Fechada",O231="Perdida"),0,IF(O231="Fechamento vencido",3000,IF(O231="Parada",2000,1000))+MIN(N231,500)+E231/1000000-ROW()/100000)</f>
+        <f>IF(OR(F231="",O231="Fechada",O231="Perdida"),0,IF(O231="Fechamento vencido",3,IF(O231="Parada",2,1))*1E+13+MIN(N(N231),500)*1E+10+MIN(ROUND(N(E231),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
         <v/>
       </c>
       <c r="P232" s="35">
-        <f>IF(OR(F232="",O232="Fechada",O232="Perdida"),0,IF(O232="Fechamento vencido",3000,IF(O232="Parada",2000,1000))+MIN(N232,500)+E232/1000000-ROW()/100000)</f>
+        <f>IF(OR(F232="",O232="Fechada",O232="Perdida"),0,IF(O232="Fechamento vencido",3,IF(O232="Parada",2,1))*1E+13+MIN(N(N232),500)*1E+10+MIN(ROUND(N(E232),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
         <v/>
       </c>
       <c r="P233" s="35">
-        <f>IF(OR(F233="",O233="Fechada",O233="Perdida"),0,IF(O233="Fechamento vencido",3000,IF(O233="Parada",2000,1000))+MIN(N233,500)+E233/1000000-ROW()/100000)</f>
+        <f>IF(OR(F233="",O233="Fechada",O233="Perdida"),0,IF(O233="Fechamento vencido",3,IF(O233="Parada",2,1))*1E+13+MIN(N(N233),500)*1E+10+MIN(ROUND(N(E233),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
         <v/>
       </c>
       <c r="P234" s="35">
-        <f>IF(OR(F234="",O234="Fechada",O234="Perdida"),0,IF(O234="Fechamento vencido",3000,IF(O234="Parada",2000,1000))+MIN(N234,500)+E234/1000000-ROW()/100000)</f>
+        <f>IF(OR(F234="",O234="Fechada",O234="Perdida"),0,IF(O234="Fechamento vencido",3,IF(O234="Parada",2,1))*1E+13+MIN(N(N234),500)*1E+10+MIN(ROUND(N(E234),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
         <v/>
       </c>
       <c r="P235" s="35">
-        <f>IF(OR(F235="",O235="Fechada",O235="Perdida"),0,IF(O235="Fechamento vencido",3000,IF(O235="Parada",2000,1000))+MIN(N235,500)+E235/1000000-ROW()/100000)</f>
+        <f>IF(OR(F235="",O235="Fechada",O235="Perdida"),0,IF(O235="Fechamento vencido",3,IF(O235="Parada",2,1))*1E+13+MIN(N(N235),500)*1E+10+MIN(ROUND(N(E235),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
         <v/>
       </c>
       <c r="P236" s="35">
-        <f>IF(OR(F236="",O236="Fechada",O236="Perdida"),0,IF(O236="Fechamento vencido",3000,IF(O236="Parada",2000,1000))+MIN(N236,500)+E236/1000000-ROW()/100000)</f>
+        <f>IF(OR(F236="",O236="Fechada",O236="Perdida"),0,IF(O236="Fechamento vencido",3,IF(O236="Parada",2,1))*1E+13+MIN(N(N236),500)*1E+10+MIN(ROUND(N(E236),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
         <v/>
       </c>
       <c r="P237" s="35">
-        <f>IF(OR(F237="",O237="Fechada",O237="Perdida"),0,IF(O237="Fechamento vencido",3000,IF(O237="Parada",2000,1000))+MIN(N237,500)+E237/1000000-ROW()/100000)</f>
+        <f>IF(OR(F237="",O237="Fechada",O237="Perdida"),0,IF(O237="Fechamento vencido",3,IF(O237="Parada",2,1))*1E+13+MIN(N(N237),500)*1E+10+MIN(ROUND(N(E237),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
         <v/>
       </c>
       <c r="P238" s="35">
-        <f>IF(OR(F238="",O238="Fechada",O238="Perdida"),0,IF(O238="Fechamento vencido",3000,IF(O238="Parada",2000,1000))+MIN(N238,500)+E238/1000000-ROW()/100000)</f>
+        <f>IF(OR(F238="",O238="Fechada",O238="Perdida"),0,IF(O238="Fechamento vencido",3,IF(O238="Parada",2,1))*1E+13+MIN(N(N238),500)*1E+10+MIN(ROUND(N(E238),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10637,7 +10637,7 @@
         <v/>
       </c>
       <c r="P239" s="35">
-        <f>IF(OR(F239="",O239="Fechada",O239="Perdida"),0,IF(O239="Fechamento vencido",3000,IF(O239="Parada",2000,1000))+MIN(N239,500)+E239/1000000-ROW()/100000)</f>
+        <f>IF(OR(F239="",O239="Fechada",O239="Perdida"),0,IF(O239="Fechamento vencido",3,IF(O239="Parada",2,1))*1E+13+MIN(N(N239),500)*1E+10+MIN(ROUND(N(E239),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
         <v/>
       </c>
       <c r="P240" s="35">
-        <f>IF(OR(F240="",O240="Fechada",O240="Perdida"),0,IF(O240="Fechamento vencido",3000,IF(O240="Parada",2000,1000))+MIN(N240,500)+E240/1000000-ROW()/100000)</f>
+        <f>IF(OR(F240="",O240="Fechada",O240="Perdida"),0,IF(O240="Fechamento vencido",3,IF(O240="Parada",2,1))*1E+13+MIN(N(N240),500)*1E+10+MIN(ROUND(N(E240),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
         <v/>
       </c>
       <c r="P241" s="35">
-        <f>IF(OR(F241="",O241="Fechada",O241="Perdida"),0,IF(O241="Fechamento vencido",3000,IF(O241="Parada",2000,1000))+MIN(N241,500)+E241/1000000-ROW()/100000)</f>
+        <f>IF(OR(F241="",O241="Fechada",O241="Perdida"),0,IF(O241="Fechamento vencido",3,IF(O241="Parada",2,1))*1E+13+MIN(N(N241),500)*1E+10+MIN(ROUND(N(E241),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
         <v/>
       </c>
       <c r="P242" s="35">
-        <f>IF(OR(F242="",O242="Fechada",O242="Perdida"),0,IF(O242="Fechamento vencido",3000,IF(O242="Parada",2000,1000))+MIN(N242,500)+E242/1000000-ROW()/100000)</f>
+        <f>IF(OR(F242="",O242="Fechada",O242="Perdida"),0,IF(O242="Fechamento vencido",3,IF(O242="Parada",2,1))*1E+13+MIN(N(N242),500)*1E+10+MIN(ROUND(N(E242),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
         <v/>
       </c>
       <c r="P243" s="35">
-        <f>IF(OR(F243="",O243="Fechada",O243="Perdida"),0,IF(O243="Fechamento vencido",3000,IF(O243="Parada",2000,1000))+MIN(N243,500)+E243/1000000-ROW()/100000)</f>
+        <f>IF(OR(F243="",O243="Fechada",O243="Perdida"),0,IF(O243="Fechamento vencido",3,IF(O243="Parada",2,1))*1E+13+MIN(N(N243),500)*1E+10+MIN(ROUND(N(E243),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
         <v/>
       </c>
       <c r="P244" s="35">
-        <f>IF(OR(F244="",O244="Fechada",O244="Perdida"),0,IF(O244="Fechamento vencido",3000,IF(O244="Parada",2000,1000))+MIN(N244,500)+E244/1000000-ROW()/100000)</f>
+        <f>IF(OR(F244="",O244="Fechada",O244="Perdida"),0,IF(O244="Fechamento vencido",3,IF(O244="Parada",2,1))*1E+13+MIN(N(N244),500)*1E+10+MIN(ROUND(N(E244),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10835,7 +10835,7 @@
         <v/>
       </c>
       <c r="P245" s="35">
-        <f>IF(OR(F245="",O245="Fechada",O245="Perdida"),0,IF(O245="Fechamento vencido",3000,IF(O245="Parada",2000,1000))+MIN(N245,500)+E245/1000000-ROW()/100000)</f>
+        <f>IF(OR(F245="",O245="Fechada",O245="Perdida"),0,IF(O245="Fechamento vencido",3,IF(O245="Parada",2,1))*1E+13+MIN(N(N245),500)*1E+10+MIN(ROUND(N(E245),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
         <v/>
       </c>
       <c r="P246" s="35">
-        <f>IF(OR(F246="",O246="Fechada",O246="Perdida"),0,IF(O246="Fechamento vencido",3000,IF(O246="Parada",2000,1000))+MIN(N246,500)+E246/1000000-ROW()/100000)</f>
+        <f>IF(OR(F246="",O246="Fechada",O246="Perdida"),0,IF(O246="Fechamento vencido",3,IF(O246="Parada",2,1))*1E+13+MIN(N(N246),500)*1E+10+MIN(ROUND(N(E246),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
         <v/>
       </c>
       <c r="P247" s="35">
-        <f>IF(OR(F247="",O247="Fechada",O247="Perdida"),0,IF(O247="Fechamento vencido",3000,IF(O247="Parada",2000,1000))+MIN(N247,500)+E247/1000000-ROW()/100000)</f>
+        <f>IF(OR(F247="",O247="Fechada",O247="Perdida"),0,IF(O247="Fechamento vencido",3,IF(O247="Parada",2,1))*1E+13+MIN(N(N247),500)*1E+10+MIN(ROUND(N(E247),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
         <v/>
       </c>
       <c r="P248" s="35">
-        <f>IF(OR(F248="",O248="Fechada",O248="Perdida"),0,IF(O248="Fechamento vencido",3000,IF(O248="Parada",2000,1000))+MIN(N248,500)+E248/1000000-ROW()/100000)</f>
+        <f>IF(OR(F248="",O248="Fechada",O248="Perdida"),0,IF(O248="Fechamento vencido",3,IF(O248="Parada",2,1))*1E+13+MIN(N(N248),500)*1E+10+MIN(ROUND(N(E248),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
         <v/>
       </c>
       <c r="P249" s="35">
-        <f>IF(OR(F249="",O249="Fechada",O249="Perdida"),0,IF(O249="Fechamento vencido",3000,IF(O249="Parada",2000,1000))+MIN(N249,500)+E249/1000000-ROW()/100000)</f>
+        <f>IF(OR(F249="",O249="Fechada",O249="Perdida"),0,IF(O249="Fechamento vencido",3,IF(O249="Parada",2,1))*1E+13+MIN(N(N249),500)*1E+10+MIN(ROUND(N(E249),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
         <v/>
       </c>
       <c r="P250" s="35">
-        <f>IF(OR(F250="",O250="Fechada",O250="Perdida"),0,IF(O250="Fechamento vencido",3000,IF(O250="Parada",2000,1000))+MIN(N250,500)+E250/1000000-ROW()/100000)</f>
+        <f>IF(OR(F250="",O250="Fechada",O250="Perdida"),0,IF(O250="Fechamento vencido",3,IF(O250="Parada",2,1))*1E+13+MIN(N(N250),500)*1E+10+MIN(ROUND(N(E250),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11033,7 +11033,7 @@
         <v/>
       </c>
       <c r="P251" s="35">
-        <f>IF(OR(F251="",O251="Fechada",O251="Perdida"),0,IF(O251="Fechamento vencido",3000,IF(O251="Parada",2000,1000))+MIN(N251,500)+E251/1000000-ROW()/100000)</f>
+        <f>IF(OR(F251="",O251="Fechada",O251="Perdida"),0,IF(O251="Fechamento vencido",3,IF(O251="Parada",2,1))*1E+13+MIN(N(N251),500)*1E+10+MIN(ROUND(N(E251),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
         <v/>
       </c>
       <c r="P252" s="35">
-        <f>IF(OR(F252="",O252="Fechada",O252="Perdida"),0,IF(O252="Fechamento vencido",3000,IF(O252="Parada",2000,1000))+MIN(N252,500)+E252/1000000-ROW()/100000)</f>
+        <f>IF(OR(F252="",O252="Fechada",O252="Perdida"),0,IF(O252="Fechamento vencido",3,IF(O252="Parada",2,1))*1E+13+MIN(N(N252),500)*1E+10+MIN(ROUND(N(E252),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
         <v/>
       </c>
       <c r="P253" s="35">
-        <f>IF(OR(F253="",O253="Fechada",O253="Perdida"),0,IF(O253="Fechamento vencido",3000,IF(O253="Parada",2000,1000))+MIN(N253,500)+E253/1000000-ROW()/100000)</f>
+        <f>IF(OR(F253="",O253="Fechada",O253="Perdida"),0,IF(O253="Fechamento vencido",3,IF(O253="Parada",2,1))*1E+13+MIN(N(N253),500)*1E+10+MIN(ROUND(N(E253),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
         <v/>
       </c>
       <c r="P254" s="35">
-        <f>IF(OR(F254="",O254="Fechada",O254="Perdida"),0,IF(O254="Fechamento vencido",3000,IF(O254="Parada",2000,1000))+MIN(N254,500)+E254/1000000-ROW()/100000)</f>
+        <f>IF(OR(F254="",O254="Fechada",O254="Perdida"),0,IF(O254="Fechamento vencido",3,IF(O254="Parada",2,1))*1E+13+MIN(N(N254),500)*1E+10+MIN(ROUND(N(E254),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11165,7 +11165,7 @@
         <v/>
       </c>
       <c r="P255" s="35">
-        <f>IF(OR(F255="",O255="Fechada",O255="Perdida"),0,IF(O255="Fechamento vencido",3000,IF(O255="Parada",2000,1000))+MIN(N255,500)+E255/1000000-ROW()/100000)</f>
+        <f>IF(OR(F255="",O255="Fechada",O255="Perdida"),0,IF(O255="Fechamento vencido",3,IF(O255="Parada",2,1))*1E+13+MIN(N(N255),500)*1E+10+MIN(ROUND(N(E255),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
         <v/>
       </c>
       <c r="P256" s="35">
-        <f>IF(OR(F256="",O256="Fechada",O256="Perdida"),0,IF(O256="Fechamento vencido",3000,IF(O256="Parada",2000,1000))+MIN(N256,500)+E256/1000000-ROW()/100000)</f>
+        <f>IF(OR(F256="",O256="Fechada",O256="Perdida"),0,IF(O256="Fechamento vencido",3,IF(O256="Parada",2,1))*1E+13+MIN(N(N256),500)*1E+10+MIN(ROUND(N(E256),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11231,7 +11231,7 @@
         <v/>
       </c>
       <c r="P257" s="35">
-        <f>IF(OR(F257="",O257="Fechada",O257="Perdida"),0,IF(O257="Fechamento vencido",3000,IF(O257="Parada",2000,1000))+MIN(N257,500)+E257/1000000-ROW()/100000)</f>
+        <f>IF(OR(F257="",O257="Fechada",O257="Perdida"),0,IF(O257="Fechamento vencido",3,IF(O257="Parada",2,1))*1E+13+MIN(N(N257),500)*1E+10+MIN(ROUND(N(E257),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11264,7 +11264,7 @@
         <v/>
       </c>
       <c r="P258" s="35">
-        <f>IF(OR(F258="",O258="Fechada",O258="Perdida"),0,IF(O258="Fechamento vencido",3000,IF(O258="Parada",2000,1000))+MIN(N258,500)+E258/1000000-ROW()/100000)</f>
+        <f>IF(OR(F258="",O258="Fechada",O258="Perdida"),0,IF(O258="Fechamento vencido",3,IF(O258="Parada",2,1))*1E+13+MIN(N(N258),500)*1E+10+MIN(ROUND(N(E258),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
         <v/>
       </c>
       <c r="P259" s="35">
-        <f>IF(OR(F259="",O259="Fechada",O259="Perdida"),0,IF(O259="Fechamento vencido",3000,IF(O259="Parada",2000,1000))+MIN(N259,500)+E259/1000000-ROW()/100000)</f>
+        <f>IF(OR(F259="",O259="Fechada",O259="Perdida"),0,IF(O259="Fechamento vencido",3,IF(O259="Parada",2,1))*1E+13+MIN(N(N259),500)*1E+10+MIN(ROUND(N(E259),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
         <v/>
       </c>
       <c r="P260" s="35">
-        <f>IF(OR(F260="",O260="Fechada",O260="Perdida"),0,IF(O260="Fechamento vencido",3000,IF(O260="Parada",2000,1000))+MIN(N260,500)+E260/1000000-ROW()/100000)</f>
+        <f>IF(OR(F260="",O260="Fechada",O260="Perdida"),0,IF(O260="Fechamento vencido",3,IF(O260="Parada",2,1))*1E+13+MIN(N(N260),500)*1E+10+MIN(ROUND(N(E260),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
         <v/>
       </c>
       <c r="P261" s="35">
-        <f>IF(OR(F261="",O261="Fechada",O261="Perdida"),0,IF(O261="Fechamento vencido",3000,IF(O261="Parada",2000,1000))+MIN(N261,500)+E261/1000000-ROW()/100000)</f>
+        <f>IF(OR(F261="",O261="Fechada",O261="Perdida"),0,IF(O261="Fechamento vencido",3,IF(O261="Parada",2,1))*1E+13+MIN(N(N261),500)*1E+10+MIN(ROUND(N(E261),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
         <v/>
       </c>
       <c r="P262" s="35">
-        <f>IF(OR(F262="",O262="Fechada",O262="Perdida"),0,IF(O262="Fechamento vencido",3000,IF(O262="Parada",2000,1000))+MIN(N262,500)+E262/1000000-ROW()/100000)</f>
+        <f>IF(OR(F262="",O262="Fechada",O262="Perdida"),0,IF(O262="Fechamento vencido",3,IF(O262="Parada",2,1))*1E+13+MIN(N(N262),500)*1E+10+MIN(ROUND(N(E262),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
         <v/>
       </c>
       <c r="P263" s="35">
-        <f>IF(OR(F263="",O263="Fechada",O263="Perdida"),0,IF(O263="Fechamento vencido",3000,IF(O263="Parada",2000,1000))+MIN(N263,500)+E263/1000000-ROW()/100000)</f>
+        <f>IF(OR(F263="",O263="Fechada",O263="Perdida"),0,IF(O263="Fechamento vencido",3,IF(O263="Parada",2,1))*1E+13+MIN(N(N263),500)*1E+10+MIN(ROUND(N(E263),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11462,7 +11462,7 @@
         <v/>
       </c>
       <c r="P264" s="35">
-        <f>IF(OR(F264="",O264="Fechada",O264="Perdida"),0,IF(O264="Fechamento vencido",3000,IF(O264="Parada",2000,1000))+MIN(N264,500)+E264/1000000-ROW()/100000)</f>
+        <f>IF(OR(F264="",O264="Fechada",O264="Perdida"),0,IF(O264="Fechamento vencido",3,IF(O264="Parada",2,1))*1E+13+MIN(N(N264),500)*1E+10+MIN(ROUND(N(E264),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
         <v/>
       </c>
       <c r="P265" s="35">
-        <f>IF(OR(F265="",O265="Fechada",O265="Perdida"),0,IF(O265="Fechamento vencido",3000,IF(O265="Parada",2000,1000))+MIN(N265,500)+E265/1000000-ROW()/100000)</f>
+        <f>IF(OR(F265="",O265="Fechada",O265="Perdida"),0,IF(O265="Fechamento vencido",3,IF(O265="Parada",2,1))*1E+13+MIN(N(N265),500)*1E+10+MIN(ROUND(N(E265),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v/>
       </c>
       <c r="P266" s="35">
-        <f>IF(OR(F266="",O266="Fechada",O266="Perdida"),0,IF(O266="Fechamento vencido",3000,IF(O266="Parada",2000,1000))+MIN(N266,500)+E266/1000000-ROW()/100000)</f>
+        <f>IF(OR(F266="",O266="Fechada",O266="Perdida"),0,IF(O266="Fechamento vencido",3,IF(O266="Parada",2,1))*1E+13+MIN(N(N266),500)*1E+10+MIN(ROUND(N(E266),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
         <v/>
       </c>
       <c r="P267" s="35">
-        <f>IF(OR(F267="",O267="Fechada",O267="Perdida"),0,IF(O267="Fechamento vencido",3000,IF(O267="Parada",2000,1000))+MIN(N267,500)+E267/1000000-ROW()/100000)</f>
+        <f>IF(OR(F267="",O267="Fechada",O267="Perdida"),0,IF(O267="Fechamento vencido",3,IF(O267="Parada",2,1))*1E+13+MIN(N(N267),500)*1E+10+MIN(ROUND(N(E267),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
         <v/>
       </c>
       <c r="P268" s="35">
-        <f>IF(OR(F268="",O268="Fechada",O268="Perdida"),0,IF(O268="Fechamento vencido",3000,IF(O268="Parada",2000,1000))+MIN(N268,500)+E268/1000000-ROW()/100000)</f>
+        <f>IF(OR(F268="",O268="Fechada",O268="Perdida"),0,IF(O268="Fechamento vencido",3,IF(O268="Parada",2,1))*1E+13+MIN(N(N268),500)*1E+10+MIN(ROUND(N(E268),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
         <v/>
       </c>
       <c r="P269" s="35">
-        <f>IF(OR(F269="",O269="Fechada",O269="Perdida"),0,IF(O269="Fechamento vencido",3000,IF(O269="Parada",2000,1000))+MIN(N269,500)+E269/1000000-ROW()/100000)</f>
+        <f>IF(OR(F269="",O269="Fechada",O269="Perdida"),0,IF(O269="Fechamento vencido",3,IF(O269="Parada",2,1))*1E+13+MIN(N(N269),500)*1E+10+MIN(ROUND(N(E269),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
         <v/>
       </c>
       <c r="P270" s="35">
-        <f>IF(OR(F270="",O270="Fechada",O270="Perdida"),0,IF(O270="Fechamento vencido",3000,IF(O270="Parada",2000,1000))+MIN(N270,500)+E270/1000000-ROW()/100000)</f>
+        <f>IF(OR(F270="",O270="Fechada",O270="Perdida"),0,IF(O270="Fechamento vencido",3,IF(O270="Parada",2,1))*1E+13+MIN(N(N270),500)*1E+10+MIN(ROUND(N(E270),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
         <v/>
       </c>
       <c r="P271" s="35">
-        <f>IF(OR(F271="",O271="Fechada",O271="Perdida"),0,IF(O271="Fechamento vencido",3000,IF(O271="Parada",2000,1000))+MIN(N271,500)+E271/1000000-ROW()/100000)</f>
+        <f>IF(OR(F271="",O271="Fechada",O271="Perdida"),0,IF(O271="Fechamento vencido",3,IF(O271="Parada",2,1))*1E+13+MIN(N(N271),500)*1E+10+MIN(ROUND(N(E271),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
         <v/>
       </c>
       <c r="P272" s="35">
-        <f>IF(OR(F272="",O272="Fechada",O272="Perdida"),0,IF(O272="Fechamento vencido",3000,IF(O272="Parada",2000,1000))+MIN(N272,500)+E272/1000000-ROW()/100000)</f>
+        <f>IF(OR(F272="",O272="Fechada",O272="Perdida"),0,IF(O272="Fechamento vencido",3,IF(O272="Parada",2,1))*1E+13+MIN(N(N272),500)*1E+10+MIN(ROUND(N(E272),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
         <v/>
       </c>
       <c r="P273" s="35">
-        <f>IF(OR(F273="",O273="Fechada",O273="Perdida"),0,IF(O273="Fechamento vencido",3000,IF(O273="Parada",2000,1000))+MIN(N273,500)+E273/1000000-ROW()/100000)</f>
+        <f>IF(OR(F273="",O273="Fechada",O273="Perdida"),0,IF(O273="Fechamento vencido",3,IF(O273="Parada",2,1))*1E+13+MIN(N(N273),500)*1E+10+MIN(ROUND(N(E273),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11792,7 +11792,7 @@
         <v/>
       </c>
       <c r="P274" s="35">
-        <f>IF(OR(F274="",O274="Fechada",O274="Perdida"),0,IF(O274="Fechamento vencido",3000,IF(O274="Parada",2000,1000))+MIN(N274,500)+E274/1000000-ROW()/100000)</f>
+        <f>IF(OR(F274="",O274="Fechada",O274="Perdida"),0,IF(O274="Fechamento vencido",3,IF(O274="Parada",2,1))*1E+13+MIN(N(N274),500)*1E+10+MIN(ROUND(N(E274),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
         <v/>
       </c>
       <c r="P275" s="35">
-        <f>IF(OR(F275="",O275="Fechada",O275="Perdida"),0,IF(O275="Fechamento vencido",3000,IF(O275="Parada",2000,1000))+MIN(N275,500)+E275/1000000-ROW()/100000)</f>
+        <f>IF(OR(F275="",O275="Fechada",O275="Perdida"),0,IF(O275="Fechamento vencido",3,IF(O275="Parada",2,1))*1E+13+MIN(N(N275),500)*1E+10+MIN(ROUND(N(E275),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
         <v/>
       </c>
       <c r="P276" s="35">
-        <f>IF(OR(F276="",O276="Fechada",O276="Perdida"),0,IF(O276="Fechamento vencido",3000,IF(O276="Parada",2000,1000))+MIN(N276,500)+E276/1000000-ROW()/100000)</f>
+        <f>IF(OR(F276="",O276="Fechada",O276="Perdida"),0,IF(O276="Fechamento vencido",3,IF(O276="Parada",2,1))*1E+13+MIN(N(N276),500)*1E+10+MIN(ROUND(N(E276),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
         <v/>
       </c>
       <c r="P277" s="35">
-        <f>IF(OR(F277="",O277="Fechada",O277="Perdida"),0,IF(O277="Fechamento vencido",3000,IF(O277="Parada",2000,1000))+MIN(N277,500)+E277/1000000-ROW()/100000)</f>
+        <f>IF(OR(F277="",O277="Fechada",O277="Perdida"),0,IF(O277="Fechamento vencido",3,IF(O277="Parada",2,1))*1E+13+MIN(N(N277),500)*1E+10+MIN(ROUND(N(E277),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
         <v/>
       </c>
       <c r="P278" s="35">
-        <f>IF(OR(F278="",O278="Fechada",O278="Perdida"),0,IF(O278="Fechamento vencido",3000,IF(O278="Parada",2000,1000))+MIN(N278,500)+E278/1000000-ROW()/100000)</f>
+        <f>IF(OR(F278="",O278="Fechada",O278="Perdida"),0,IF(O278="Fechamento vencido",3,IF(O278="Parada",2,1))*1E+13+MIN(N(N278),500)*1E+10+MIN(ROUND(N(E278),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11957,7 +11957,7 @@
         <v/>
       </c>
       <c r="P279" s="35">
-        <f>IF(OR(F279="",O279="Fechada",O279="Perdida"),0,IF(O279="Fechamento vencido",3000,IF(O279="Parada",2000,1000))+MIN(N279,500)+E279/1000000-ROW()/100000)</f>
+        <f>IF(OR(F279="",O279="Fechada",O279="Perdida"),0,IF(O279="Fechamento vencido",3,IF(O279="Parada",2,1))*1E+13+MIN(N(N279),500)*1E+10+MIN(ROUND(N(E279),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
         <v/>
       </c>
       <c r="P280" s="35">
-        <f>IF(OR(F280="",O280="Fechada",O280="Perdida"),0,IF(O280="Fechamento vencido",3000,IF(O280="Parada",2000,1000))+MIN(N280,500)+E280/1000000-ROW()/100000)</f>
+        <f>IF(OR(F280="",O280="Fechada",O280="Perdida"),0,IF(O280="Fechamento vencido",3,IF(O280="Parada",2,1))*1E+13+MIN(N(N280),500)*1E+10+MIN(ROUND(N(E280),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
         <v/>
       </c>
       <c r="P281" s="35">
-        <f>IF(OR(F281="",O281="Fechada",O281="Perdida"),0,IF(O281="Fechamento vencido",3000,IF(O281="Parada",2000,1000))+MIN(N281,500)+E281/1000000-ROW()/100000)</f>
+        <f>IF(OR(F281="",O281="Fechada",O281="Perdida"),0,IF(O281="Fechamento vencido",3,IF(O281="Parada",2,1))*1E+13+MIN(N(N281),500)*1E+10+MIN(ROUND(N(E281),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
         <v/>
       </c>
       <c r="P282" s="35">
-        <f>IF(OR(F282="",O282="Fechada",O282="Perdida"),0,IF(O282="Fechamento vencido",3000,IF(O282="Parada",2000,1000))+MIN(N282,500)+E282/1000000-ROW()/100000)</f>
+        <f>IF(OR(F282="",O282="Fechada",O282="Perdida"),0,IF(O282="Fechamento vencido",3,IF(O282="Parada",2,1))*1E+13+MIN(N(N282),500)*1E+10+MIN(ROUND(N(E282),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
         <v/>
       </c>
       <c r="P283" s="35">
-        <f>IF(OR(F283="",O283="Fechada",O283="Perdida"),0,IF(O283="Fechamento vencido",3000,IF(O283="Parada",2000,1000))+MIN(N283,500)+E283/1000000-ROW()/100000)</f>
+        <f>IF(OR(F283="",O283="Fechada",O283="Perdida"),0,IF(O283="Fechamento vencido",3,IF(O283="Parada",2,1))*1E+13+MIN(N(N283),500)*1E+10+MIN(ROUND(N(E283),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
         <v/>
       </c>
       <c r="P284" s="35">
-        <f>IF(OR(F284="",O284="Fechada",O284="Perdida"),0,IF(O284="Fechamento vencido",3000,IF(O284="Parada",2000,1000))+MIN(N284,500)+E284/1000000-ROW()/100000)</f>
+        <f>IF(OR(F284="",O284="Fechada",O284="Perdida"),0,IF(O284="Fechamento vencido",3,IF(O284="Parada",2,1))*1E+13+MIN(N(N284),500)*1E+10+MIN(ROUND(N(E284),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         <v/>
       </c>
       <c r="P285" s="35">
-        <f>IF(OR(F285="",O285="Fechada",O285="Perdida"),0,IF(O285="Fechamento vencido",3000,IF(O285="Parada",2000,1000))+MIN(N285,500)+E285/1000000-ROW()/100000)</f>
+        <f>IF(OR(F285="",O285="Fechada",O285="Perdida"),0,IF(O285="Fechamento vencido",3,IF(O285="Parada",2,1))*1E+13+MIN(N(N285),500)*1E+10+MIN(ROUND(N(E285),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12188,7 +12188,7 @@
         <v/>
       </c>
       <c r="P286" s="35">
-        <f>IF(OR(F286="",O286="Fechada",O286="Perdida"),0,IF(O286="Fechamento vencido",3000,IF(O286="Parada",2000,1000))+MIN(N286,500)+E286/1000000-ROW()/100000)</f>
+        <f>IF(OR(F286="",O286="Fechada",O286="Perdida"),0,IF(O286="Fechamento vencido",3,IF(O286="Parada",2,1))*1E+13+MIN(N(N286),500)*1E+10+MIN(ROUND(N(E286),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
         <v/>
       </c>
       <c r="P287" s="35">
-        <f>IF(OR(F287="",O287="Fechada",O287="Perdida"),0,IF(O287="Fechamento vencido",3000,IF(O287="Parada",2000,1000))+MIN(N287,500)+E287/1000000-ROW()/100000)</f>
+        <f>IF(OR(F287="",O287="Fechada",O287="Perdida"),0,IF(O287="Fechamento vencido",3,IF(O287="Parada",2,1))*1E+13+MIN(N(N287),500)*1E+10+MIN(ROUND(N(E287),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
         <v/>
       </c>
       <c r="P288" s="35">
-        <f>IF(OR(F288="",O288="Fechada",O288="Perdida"),0,IF(O288="Fechamento vencido",3000,IF(O288="Parada",2000,1000))+MIN(N288,500)+E288/1000000-ROW()/100000)</f>
+        <f>IF(OR(F288="",O288="Fechada",O288="Perdida"),0,IF(O288="Fechamento vencido",3,IF(O288="Parada",2,1))*1E+13+MIN(N(N288),500)*1E+10+MIN(ROUND(N(E288),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         <v/>
       </c>
       <c r="P289" s="35">
-        <f>IF(OR(F289="",O289="Fechada",O289="Perdida"),0,IF(O289="Fechamento vencido",3000,IF(O289="Parada",2000,1000))+MIN(N289,500)+E289/1000000-ROW()/100000)</f>
+        <f>IF(OR(F289="",O289="Fechada",O289="Perdida"),0,IF(O289="Fechamento vencido",3,IF(O289="Parada",2,1))*1E+13+MIN(N(N289),500)*1E+10+MIN(ROUND(N(E289),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
         <v/>
       </c>
       <c r="P290" s="35">
-        <f>IF(OR(F290="",O290="Fechada",O290="Perdida"),0,IF(O290="Fechamento vencido",3000,IF(O290="Parada",2000,1000))+MIN(N290,500)+E290/1000000-ROW()/100000)</f>
+        <f>IF(OR(F290="",O290="Fechada",O290="Perdida"),0,IF(O290="Fechamento vencido",3,IF(O290="Parada",2,1))*1E+13+MIN(N(N290),500)*1E+10+MIN(ROUND(N(E290),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
         <v/>
       </c>
       <c r="P291" s="35">
-        <f>IF(OR(F291="",O291="Fechada",O291="Perdida"),0,IF(O291="Fechamento vencido",3000,IF(O291="Parada",2000,1000))+MIN(N291,500)+E291/1000000-ROW()/100000)</f>
+        <f>IF(OR(F291="",O291="Fechada",O291="Perdida"),0,IF(O291="Fechamento vencido",3,IF(O291="Parada",2,1))*1E+13+MIN(N(N291),500)*1E+10+MIN(ROUND(N(E291),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
         <v/>
       </c>
       <c r="P292" s="35">
-        <f>IF(OR(F292="",O292="Fechada",O292="Perdida"),0,IF(O292="Fechamento vencido",3000,IF(O292="Parada",2000,1000))+MIN(N292,500)+E292/1000000-ROW()/100000)</f>
+        <f>IF(OR(F292="",O292="Fechada",O292="Perdida"),0,IF(O292="Fechamento vencido",3,IF(O292="Parada",2,1))*1E+13+MIN(N(N292),500)*1E+10+MIN(ROUND(N(E292),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12419,7 +12419,7 @@
         <v/>
       </c>
       <c r="P293" s="35">
-        <f>IF(OR(F293="",O293="Fechada",O293="Perdida"),0,IF(O293="Fechamento vencido",3000,IF(O293="Parada",2000,1000))+MIN(N293,500)+E293/1000000-ROW()/100000)</f>
+        <f>IF(OR(F293="",O293="Fechada",O293="Perdida"),0,IF(O293="Fechamento vencido",3,IF(O293="Parada",2,1))*1E+13+MIN(N(N293),500)*1E+10+MIN(ROUND(N(E293),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
         <v/>
       </c>
       <c r="P294" s="35">
-        <f>IF(OR(F294="",O294="Fechada",O294="Perdida"),0,IF(O294="Fechamento vencido",3000,IF(O294="Parada",2000,1000))+MIN(N294,500)+E294/1000000-ROW()/100000)</f>
+        <f>IF(OR(F294="",O294="Fechada",O294="Perdida"),0,IF(O294="Fechamento vencido",3,IF(O294="Parada",2,1))*1E+13+MIN(N(N294),500)*1E+10+MIN(ROUND(N(E294),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
         <v/>
       </c>
       <c r="P295" s="35">
-        <f>IF(OR(F295="",O295="Fechada",O295="Perdida"),0,IF(O295="Fechamento vencido",3000,IF(O295="Parada",2000,1000))+MIN(N295,500)+E295/1000000-ROW()/100000)</f>
+        <f>IF(OR(F295="",O295="Fechada",O295="Perdida"),0,IF(O295="Fechamento vencido",3,IF(O295="Parada",2,1))*1E+13+MIN(N(N295),500)*1E+10+MIN(ROUND(N(E295),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
         <v/>
       </c>
       <c r="P296" s="35">
-        <f>IF(OR(F296="",O296="Fechada",O296="Perdida"),0,IF(O296="Fechamento vencido",3000,IF(O296="Parada",2000,1000))+MIN(N296,500)+E296/1000000-ROW()/100000)</f>
+        <f>IF(OR(F296="",O296="Fechada",O296="Perdida"),0,IF(O296="Fechamento vencido",3,IF(O296="Parada",2,1))*1E+13+MIN(N(N296),500)*1E+10+MIN(ROUND(N(E296),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
         <v/>
       </c>
       <c r="P297" s="35">
-        <f>IF(OR(F297="",O297="Fechada",O297="Perdida"),0,IF(O297="Fechamento vencido",3000,IF(O297="Parada",2000,1000))+MIN(N297,500)+E297/1000000-ROW()/100000)</f>
+        <f>IF(OR(F297="",O297="Fechada",O297="Perdida"),0,IF(O297="Fechamento vencido",3,IF(O297="Parada",2,1))*1E+13+MIN(N(N297),500)*1E+10+MIN(ROUND(N(E297),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
         <v/>
       </c>
       <c r="P298" s="35">
-        <f>IF(OR(F298="",O298="Fechada",O298="Perdida"),0,IF(O298="Fechamento vencido",3000,IF(O298="Parada",2000,1000))+MIN(N298,500)+E298/1000000-ROW()/100000)</f>
+        <f>IF(OR(F298="",O298="Fechada",O298="Perdida"),0,IF(O298="Fechamento vencido",3,IF(O298="Parada",2,1))*1E+13+MIN(N(N298),500)*1E+10+MIN(ROUND(N(E298),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12617,7 +12617,7 @@
         <v/>
       </c>
       <c r="P299" s="35">
-        <f>IF(OR(F299="",O299="Fechada",O299="Perdida"),0,IF(O299="Fechamento vencido",3000,IF(O299="Parada",2000,1000))+MIN(N299,500)+E299/1000000-ROW()/100000)</f>
+        <f>IF(OR(F299="",O299="Fechada",O299="Perdida"),0,IF(O299="Fechamento vencido",3,IF(O299="Parada",2,1))*1E+13+MIN(N(N299),500)*1E+10+MIN(ROUND(N(E299),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
         <v/>
       </c>
       <c r="P300" s="35">
-        <f>IF(OR(F300="",O300="Fechada",O300="Perdida"),0,IF(O300="Fechamento vencido",3000,IF(O300="Parada",2000,1000))+MIN(N300,500)+E300/1000000-ROW()/100000)</f>
+        <f>IF(OR(F300="",O300="Fechada",O300="Perdida"),0,IF(O300="Fechamento vencido",3,IF(O300="Parada",2,1))*1E+13+MIN(N(N300),500)*1E+10+MIN(ROUND(N(E300),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12683,7 +12683,7 @@
         <v/>
       </c>
       <c r="P301" s="35">
-        <f>IF(OR(F301="",O301="Fechada",O301="Perdida"),0,IF(O301="Fechamento vencido",3000,IF(O301="Parada",2000,1000))+MIN(N301,500)+E301/1000000-ROW()/100000)</f>
+        <f>IF(OR(F301="",O301="Fechada",O301="Perdida"),0,IF(O301="Fechamento vencido",3,IF(O301="Parada",2,1))*1E+13+MIN(N(N301),500)*1E+10+MIN(ROUND(N(E301),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
         <v/>
       </c>
       <c r="P302" s="35">
-        <f>IF(OR(F302="",O302="Fechada",O302="Perdida"),0,IF(O302="Fechamento vencido",3000,IF(O302="Parada",2000,1000))+MIN(N302,500)+E302/1000000-ROW()/100000)</f>
+        <f>IF(OR(F302="",O302="Fechada",O302="Perdida"),0,IF(O302="Fechamento vencido",3,IF(O302="Parada",2,1))*1E+13+MIN(N(N302),500)*1E+10+MIN(ROUND(N(E302),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12749,7 +12749,7 @@
         <v/>
       </c>
       <c r="P303" s="35">
-        <f>IF(OR(F303="",O303="Fechada",O303="Perdida"),0,IF(O303="Fechamento vencido",3000,IF(O303="Parada",2000,1000))+MIN(N303,500)+E303/1000000-ROW()/100000)</f>
+        <f>IF(OR(F303="",O303="Fechada",O303="Perdida"),0,IF(O303="Fechamento vencido",3,IF(O303="Parada",2,1))*1E+13+MIN(N(N303),500)*1E+10+MIN(ROUND(N(E303),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
         <v/>
       </c>
       <c r="P304" s="35">
-        <f>IF(OR(F304="",O304="Fechada",O304="Perdida"),0,IF(O304="Fechamento vencido",3000,IF(O304="Parada",2000,1000))+MIN(N304,500)+E304/1000000-ROW()/100000)</f>
+        <f>IF(OR(F304="",O304="Fechada",O304="Perdida"),0,IF(O304="Fechamento vencido",3,IF(O304="Parada",2,1))*1E+13+MIN(N(N304),500)*1E+10+MIN(ROUND(N(E304),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
         <v/>
       </c>
       <c r="P305" s="35">
-        <f>IF(OR(F305="",O305="Fechada",O305="Perdida"),0,IF(O305="Fechamento vencido",3000,IF(O305="Parada",2000,1000))+MIN(N305,500)+E305/1000000-ROW()/100000)</f>
+        <f>IF(OR(F305="",O305="Fechada",O305="Perdida"),0,IF(O305="Fechamento vencido",3,IF(O305="Parada",2,1))*1E+13+MIN(N(N305),500)*1E+10+MIN(ROUND(N(E305),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12848,7 +12848,7 @@
         <v/>
       </c>
       <c r="P306" s="35">
-        <f>IF(OR(F306="",O306="Fechada",O306="Perdida"),0,IF(O306="Fechamento vencido",3000,IF(O306="Parada",2000,1000))+MIN(N306,500)+E306/1000000-ROW()/100000)</f>
+        <f>IF(OR(F306="",O306="Fechada",O306="Perdida"),0,IF(O306="Fechamento vencido",3,IF(O306="Parada",2,1))*1E+13+MIN(N(N306),500)*1E+10+MIN(ROUND(N(E306),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
         <v/>
       </c>
       <c r="P307" s="35">
-        <f>IF(OR(F307="",O307="Fechada",O307="Perdida"),0,IF(O307="Fechamento vencido",3000,IF(O307="Parada",2000,1000))+MIN(N307,500)+E307/1000000-ROW()/100000)</f>
+        <f>IF(OR(F307="",O307="Fechada",O307="Perdida"),0,IF(O307="Fechamento vencido",3,IF(O307="Parada",2,1))*1E+13+MIN(N(N307),500)*1E+10+MIN(ROUND(N(E307),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
         <v/>
       </c>
       <c r="P308" s="35">
-        <f>IF(OR(F308="",O308="Fechada",O308="Perdida"),0,IF(O308="Fechamento vencido",3000,IF(O308="Parada",2000,1000))+MIN(N308,500)+E308/1000000-ROW()/100000)</f>
+        <f>IF(OR(F308="",O308="Fechada",O308="Perdida"),0,IF(O308="Fechamento vencido",3,IF(O308="Parada",2,1))*1E+13+MIN(N(N308),500)*1E+10+MIN(ROUND(N(E308),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12947,7 +12947,7 @@
         <v/>
       </c>
       <c r="P309" s="35">
-        <f>IF(OR(F309="",O309="Fechada",O309="Perdida"),0,IF(O309="Fechamento vencido",3000,IF(O309="Parada",2000,1000))+MIN(N309,500)+E309/1000000-ROW()/100000)</f>
+        <f>IF(OR(F309="",O309="Fechada",O309="Perdida"),0,IF(O309="Fechamento vencido",3,IF(O309="Parada",2,1))*1E+13+MIN(N(N309),500)*1E+10+MIN(ROUND(N(E309),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
         <v/>
       </c>
       <c r="P310" s="35">
-        <f>IF(OR(F310="",O310="Fechada",O310="Perdida"),0,IF(O310="Fechamento vencido",3000,IF(O310="Parada",2000,1000))+MIN(N310,500)+E310/1000000-ROW()/100000)</f>
+        <f>IF(OR(F310="",O310="Fechada",O310="Perdida"),0,IF(O310="Fechamento vencido",3,IF(O310="Parada",2,1))*1E+13+MIN(N(N310),500)*1E+10+MIN(ROUND(N(E310),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13013,7 +13013,7 @@
         <v/>
       </c>
       <c r="P311" s="35">
-        <f>IF(OR(F311="",O311="Fechada",O311="Perdida"),0,IF(O311="Fechamento vencido",3000,IF(O311="Parada",2000,1000))+MIN(N311,500)+E311/1000000-ROW()/100000)</f>
+        <f>IF(OR(F311="",O311="Fechada",O311="Perdida"),0,IF(O311="Fechamento vencido",3,IF(O311="Parada",2,1))*1E+13+MIN(N(N311),500)*1E+10+MIN(ROUND(N(E311),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13046,7 +13046,7 @@
         <v/>
       </c>
       <c r="P312" s="35">
-        <f>IF(OR(F312="",O312="Fechada",O312="Perdida"),0,IF(O312="Fechamento vencido",3000,IF(O312="Parada",2000,1000))+MIN(N312,500)+E312/1000000-ROW()/100000)</f>
+        <f>IF(OR(F312="",O312="Fechada",O312="Perdida"),0,IF(O312="Fechamento vencido",3,IF(O312="Parada",2,1))*1E+13+MIN(N(N312),500)*1E+10+MIN(ROUND(N(E312),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
         <v/>
       </c>
       <c r="P313" s="35">
-        <f>IF(OR(F313="",O313="Fechada",O313="Perdida"),0,IF(O313="Fechamento vencido",3000,IF(O313="Parada",2000,1000))+MIN(N313,500)+E313/1000000-ROW()/100000)</f>
+        <f>IF(OR(F313="",O313="Fechada",O313="Perdida"),0,IF(O313="Fechamento vencido",3,IF(O313="Parada",2,1))*1E+13+MIN(N(N313),500)*1E+10+MIN(ROUND(N(E313),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
         <v/>
       </c>
       <c r="P314" s="35">
-        <f>IF(OR(F314="",O314="Fechada",O314="Perdida"),0,IF(O314="Fechamento vencido",3000,IF(O314="Parada",2000,1000))+MIN(N314,500)+E314/1000000-ROW()/100000)</f>
+        <f>IF(OR(F314="",O314="Fechada",O314="Perdida"),0,IF(O314="Fechamento vencido",3,IF(O314="Parada",2,1))*1E+13+MIN(N(N314),500)*1E+10+MIN(ROUND(N(E314),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
         <v/>
       </c>
       <c r="P315" s="35">
-        <f>IF(OR(F315="",O315="Fechada",O315="Perdida"),0,IF(O315="Fechamento vencido",3000,IF(O315="Parada",2000,1000))+MIN(N315,500)+E315/1000000-ROW()/100000)</f>
+        <f>IF(OR(F315="",O315="Fechada",O315="Perdida"),0,IF(O315="Fechamento vencido",3,IF(O315="Parada",2,1))*1E+13+MIN(N(N315),500)*1E+10+MIN(ROUND(N(E315),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
         <v/>
       </c>
       <c r="P316" s="35">
-        <f>IF(OR(F316="",O316="Fechada",O316="Perdida"),0,IF(O316="Fechamento vencido",3000,IF(O316="Parada",2000,1000))+MIN(N316,500)+E316/1000000-ROW()/100000)</f>
+        <f>IF(OR(F316="",O316="Fechada",O316="Perdida"),0,IF(O316="Fechamento vencido",3,IF(O316="Parada",2,1))*1E+13+MIN(N(N316),500)*1E+10+MIN(ROUND(N(E316),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13211,7 +13211,7 @@
         <v/>
       </c>
       <c r="P317" s="35">
-        <f>IF(OR(F317="",O317="Fechada",O317="Perdida"),0,IF(O317="Fechamento vencido",3000,IF(O317="Parada",2000,1000))+MIN(N317,500)+E317/1000000-ROW()/100000)</f>
+        <f>IF(OR(F317="",O317="Fechada",O317="Perdida"),0,IF(O317="Fechamento vencido",3,IF(O317="Parada",2,1))*1E+13+MIN(N(N317),500)*1E+10+MIN(ROUND(N(E317),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
         <v/>
       </c>
       <c r="P318" s="35">
-        <f>IF(OR(F318="",O318="Fechada",O318="Perdida"),0,IF(O318="Fechamento vencido",3000,IF(O318="Parada",2000,1000))+MIN(N318,500)+E318/1000000-ROW()/100000)</f>
+        <f>IF(OR(F318="",O318="Fechada",O318="Perdida"),0,IF(O318="Fechamento vencido",3,IF(O318="Parada",2,1))*1E+13+MIN(N(N318),500)*1E+10+MIN(ROUND(N(E318),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
         <v/>
       </c>
       <c r="P319" s="35">
-        <f>IF(OR(F319="",O319="Fechada",O319="Perdida"),0,IF(O319="Fechamento vencido",3000,IF(O319="Parada",2000,1000))+MIN(N319,500)+E319/1000000-ROW()/100000)</f>
+        <f>IF(OR(F319="",O319="Fechada",O319="Perdida"),0,IF(O319="Fechamento vencido",3,IF(O319="Parada",2,1))*1E+13+MIN(N(N319),500)*1E+10+MIN(ROUND(N(E319),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13310,7 +13310,7 @@
         <v/>
       </c>
       <c r="P320" s="35">
-        <f>IF(OR(F320="",O320="Fechada",O320="Perdida"),0,IF(O320="Fechamento vencido",3000,IF(O320="Parada",2000,1000))+MIN(N320,500)+E320/1000000-ROW()/100000)</f>
+        <f>IF(OR(F320="",O320="Fechada",O320="Perdida"),0,IF(O320="Fechamento vencido",3,IF(O320="Parada",2,1))*1E+13+MIN(N(N320),500)*1E+10+MIN(ROUND(N(E320),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
         <v/>
       </c>
       <c r="P321" s="35">
-        <f>IF(OR(F321="",O321="Fechada",O321="Perdida"),0,IF(O321="Fechamento vencido",3000,IF(O321="Parada",2000,1000))+MIN(N321,500)+E321/1000000-ROW()/100000)</f>
+        <f>IF(OR(F321="",O321="Fechada",O321="Perdida"),0,IF(O321="Fechamento vencido",3,IF(O321="Parada",2,1))*1E+13+MIN(N(N321),500)*1E+10+MIN(ROUND(N(E321),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v/>
       </c>
       <c r="P322" s="35">
-        <f>IF(OR(F322="",O322="Fechada",O322="Perdida"),0,IF(O322="Fechamento vencido",3000,IF(O322="Parada",2000,1000))+MIN(N322,500)+E322/1000000-ROW()/100000)</f>
+        <f>IF(OR(F322="",O322="Fechada",O322="Perdida"),0,IF(O322="Fechamento vencido",3,IF(O322="Parada",2,1))*1E+13+MIN(N(N322),500)*1E+10+MIN(ROUND(N(E322),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
         <v/>
       </c>
       <c r="P323" s="35">
-        <f>IF(OR(F323="",O323="Fechada",O323="Perdida"),0,IF(O323="Fechamento vencido",3000,IF(O323="Parada",2000,1000))+MIN(N323,500)+E323/1000000-ROW()/100000)</f>
+        <f>IF(OR(F323="",O323="Fechada",O323="Perdida"),0,IF(O323="Fechamento vencido",3,IF(O323="Parada",2,1))*1E+13+MIN(N(N323),500)*1E+10+MIN(ROUND(N(E323),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13442,7 +13442,7 @@
         <v/>
       </c>
       <c r="P324" s="35">
-        <f>IF(OR(F324="",O324="Fechada",O324="Perdida"),0,IF(O324="Fechamento vencido",3000,IF(O324="Parada",2000,1000))+MIN(N324,500)+E324/1000000-ROW()/100000)</f>
+        <f>IF(OR(F324="",O324="Fechada",O324="Perdida"),0,IF(O324="Fechamento vencido",3,IF(O324="Parada",2,1))*1E+13+MIN(N(N324),500)*1E+10+MIN(ROUND(N(E324),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
         <v/>
       </c>
       <c r="P325" s="35">
-        <f>IF(OR(F325="",O325="Fechada",O325="Perdida"),0,IF(O325="Fechamento vencido",3000,IF(O325="Parada",2000,1000))+MIN(N325,500)+E325/1000000-ROW()/100000)</f>
+        <f>IF(OR(F325="",O325="Fechada",O325="Perdida"),0,IF(O325="Fechamento vencido",3,IF(O325="Parada",2,1))*1E+13+MIN(N(N325),500)*1E+10+MIN(ROUND(N(E325),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
         <v/>
       </c>
       <c r="P326" s="35">
-        <f>IF(OR(F326="",O326="Fechada",O326="Perdida"),0,IF(O326="Fechamento vencido",3000,IF(O326="Parada",2000,1000))+MIN(N326,500)+E326/1000000-ROW()/100000)</f>
+        <f>IF(OR(F326="",O326="Fechada",O326="Perdida"),0,IF(O326="Fechamento vencido",3,IF(O326="Parada",2,1))*1E+13+MIN(N(N326),500)*1E+10+MIN(ROUND(N(E326),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
         <v/>
       </c>
       <c r="P327" s="35">
-        <f>IF(OR(F327="",O327="Fechada",O327="Perdida"),0,IF(O327="Fechamento vencido",3000,IF(O327="Parada",2000,1000))+MIN(N327,500)+E327/1000000-ROW()/100000)</f>
+        <f>IF(OR(F327="",O327="Fechada",O327="Perdida"),0,IF(O327="Fechamento vencido",3,IF(O327="Parada",2,1))*1E+13+MIN(N(N327),500)*1E+10+MIN(ROUND(N(E327),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
         <v/>
       </c>
       <c r="P328" s="35">
-        <f>IF(OR(F328="",O328="Fechada",O328="Perdida"),0,IF(O328="Fechamento vencido",3000,IF(O328="Parada",2000,1000))+MIN(N328,500)+E328/1000000-ROW()/100000)</f>
+        <f>IF(OR(F328="",O328="Fechada",O328="Perdida"),0,IF(O328="Fechamento vencido",3,IF(O328="Parada",2,1))*1E+13+MIN(N(N328),500)*1E+10+MIN(ROUND(N(E328),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13607,7 +13607,7 @@
         <v/>
       </c>
       <c r="P329" s="35">
-        <f>IF(OR(F329="",O329="Fechada",O329="Perdida"),0,IF(O329="Fechamento vencido",3000,IF(O329="Parada",2000,1000))+MIN(N329,500)+E329/1000000-ROW()/100000)</f>
+        <f>IF(OR(F329="",O329="Fechada",O329="Perdida"),0,IF(O329="Fechamento vencido",3,IF(O329="Parada",2,1))*1E+13+MIN(N(N329),500)*1E+10+MIN(ROUND(N(E329),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
         <v/>
       </c>
       <c r="P330" s="35">
-        <f>IF(OR(F330="",O330="Fechada",O330="Perdida"),0,IF(O330="Fechamento vencido",3000,IF(O330="Parada",2000,1000))+MIN(N330,500)+E330/1000000-ROW()/100000)</f>
+        <f>IF(OR(F330="",O330="Fechada",O330="Perdida"),0,IF(O330="Fechamento vencido",3,IF(O330="Parada",2,1))*1E+13+MIN(N(N330),500)*1E+10+MIN(ROUND(N(E330),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
         <v/>
       </c>
       <c r="P331" s="35">
-        <f>IF(OR(F331="",O331="Fechada",O331="Perdida"),0,IF(O331="Fechamento vencido",3000,IF(O331="Parada",2000,1000))+MIN(N331,500)+E331/1000000-ROW()/100000)</f>
+        <f>IF(OR(F331="",O331="Fechada",O331="Perdida"),0,IF(O331="Fechamento vencido",3,IF(O331="Parada",2,1))*1E+13+MIN(N(N331),500)*1E+10+MIN(ROUND(N(E331),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13706,7 +13706,7 @@
         <v/>
       </c>
       <c r="P332" s="35">
-        <f>IF(OR(F332="",O332="Fechada",O332="Perdida"),0,IF(O332="Fechamento vencido",3000,IF(O332="Parada",2000,1000))+MIN(N332,500)+E332/1000000-ROW()/100000)</f>
+        <f>IF(OR(F332="",O332="Fechada",O332="Perdida"),0,IF(O332="Fechamento vencido",3,IF(O332="Parada",2,1))*1E+13+MIN(N(N332),500)*1E+10+MIN(ROUND(N(E332),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13739,7 +13739,7 @@
         <v/>
       </c>
       <c r="P333" s="35">
-        <f>IF(OR(F333="",O333="Fechada",O333="Perdida"),0,IF(O333="Fechamento vencido",3000,IF(O333="Parada",2000,1000))+MIN(N333,500)+E333/1000000-ROW()/100000)</f>
+        <f>IF(OR(F333="",O333="Fechada",O333="Perdida"),0,IF(O333="Fechamento vencido",3,IF(O333="Parada",2,1))*1E+13+MIN(N(N333),500)*1E+10+MIN(ROUND(N(E333),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
         <v/>
       </c>
       <c r="P334" s="35">
-        <f>IF(OR(F334="",O334="Fechada",O334="Perdida"),0,IF(O334="Fechamento vencido",3000,IF(O334="Parada",2000,1000))+MIN(N334,500)+E334/1000000-ROW()/100000)</f>
+        <f>IF(OR(F334="",O334="Fechada",O334="Perdida"),0,IF(O334="Fechamento vencido",3,IF(O334="Parada",2,1))*1E+13+MIN(N(N334),500)*1E+10+MIN(ROUND(N(E334),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13805,7 +13805,7 @@
         <v/>
       </c>
       <c r="P335" s="35">
-        <f>IF(OR(F335="",O335="Fechada",O335="Perdida"),0,IF(O335="Fechamento vencido",3000,IF(O335="Parada",2000,1000))+MIN(N335,500)+E335/1000000-ROW()/100000)</f>
+        <f>IF(OR(F335="",O335="Fechada",O335="Perdida"),0,IF(O335="Fechamento vencido",3,IF(O335="Parada",2,1))*1E+13+MIN(N(N335),500)*1E+10+MIN(ROUND(N(E335),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
         <v/>
       </c>
       <c r="P336" s="35">
-        <f>IF(OR(F336="",O336="Fechada",O336="Perdida"),0,IF(O336="Fechamento vencido",3000,IF(O336="Parada",2000,1000))+MIN(N336,500)+E336/1000000-ROW()/100000)</f>
+        <f>IF(OR(F336="",O336="Fechada",O336="Perdida"),0,IF(O336="Fechamento vencido",3,IF(O336="Parada",2,1))*1E+13+MIN(N(N336),500)*1E+10+MIN(ROUND(N(E336),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
         <v/>
       </c>
       <c r="P337" s="35">
-        <f>IF(OR(F337="",O337="Fechada",O337="Perdida"),0,IF(O337="Fechamento vencido",3000,IF(O337="Parada",2000,1000))+MIN(N337,500)+E337/1000000-ROW()/100000)</f>
+        <f>IF(OR(F337="",O337="Fechada",O337="Perdida"),0,IF(O337="Fechamento vencido",3,IF(O337="Parada",2,1))*1E+13+MIN(N(N337),500)*1E+10+MIN(ROUND(N(E337),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
         <v/>
       </c>
       <c r="P338" s="35">
-        <f>IF(OR(F338="",O338="Fechada",O338="Perdida"),0,IF(O338="Fechamento vencido",3000,IF(O338="Parada",2000,1000))+MIN(N338,500)+E338/1000000-ROW()/100000)</f>
+        <f>IF(OR(F338="",O338="Fechada",O338="Perdida"),0,IF(O338="Fechamento vencido",3,IF(O338="Parada",2,1))*1E+13+MIN(N(N338),500)*1E+10+MIN(ROUND(N(E338),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
         <v/>
       </c>
       <c r="P339" s="35">
-        <f>IF(OR(F339="",O339="Fechada",O339="Perdida"),0,IF(O339="Fechamento vencido",3000,IF(O339="Parada",2000,1000))+MIN(N339,500)+E339/1000000-ROW()/100000)</f>
+        <f>IF(OR(F339="",O339="Fechada",O339="Perdida"),0,IF(O339="Fechamento vencido",3,IF(O339="Parada",2,1))*1E+13+MIN(N(N339),500)*1E+10+MIN(ROUND(N(E339),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
         <v/>
       </c>
       <c r="P340" s="35">
-        <f>IF(OR(F340="",O340="Fechada",O340="Perdida"),0,IF(O340="Fechamento vencido",3000,IF(O340="Parada",2000,1000))+MIN(N340,500)+E340/1000000-ROW()/100000)</f>
+        <f>IF(OR(F340="",O340="Fechada",O340="Perdida"),0,IF(O340="Fechamento vencido",3,IF(O340="Parada",2,1))*1E+13+MIN(N(N340),500)*1E+10+MIN(ROUND(N(E340),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14003,7 +14003,7 @@
         <v/>
       </c>
       <c r="P341" s="35">
-        <f>IF(OR(F341="",O341="Fechada",O341="Perdida"),0,IF(O341="Fechamento vencido",3000,IF(O341="Parada",2000,1000))+MIN(N341,500)+E341/1000000-ROW()/100000)</f>
+        <f>IF(OR(F341="",O341="Fechada",O341="Perdida"),0,IF(O341="Fechamento vencido",3,IF(O341="Parada",2,1))*1E+13+MIN(N(N341),500)*1E+10+MIN(ROUND(N(E341),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14036,7 +14036,7 @@
         <v/>
       </c>
       <c r="P342" s="35">
-        <f>IF(OR(F342="",O342="Fechada",O342="Perdida"),0,IF(O342="Fechamento vencido",3000,IF(O342="Parada",2000,1000))+MIN(N342,500)+E342/1000000-ROW()/100000)</f>
+        <f>IF(OR(F342="",O342="Fechada",O342="Perdida"),0,IF(O342="Fechamento vencido",3,IF(O342="Parada",2,1))*1E+13+MIN(N(N342),500)*1E+10+MIN(ROUND(N(E342),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14069,7 +14069,7 @@
         <v/>
       </c>
       <c r="P343" s="35">
-        <f>IF(OR(F343="",O343="Fechada",O343="Perdida"),0,IF(O343="Fechamento vencido",3000,IF(O343="Parada",2000,1000))+MIN(N343,500)+E343/1000000-ROW()/100000)</f>
+        <f>IF(OR(F343="",O343="Fechada",O343="Perdida"),0,IF(O343="Fechamento vencido",3,IF(O343="Parada",2,1))*1E+13+MIN(N(N343),500)*1E+10+MIN(ROUND(N(E343),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
         <v/>
       </c>
       <c r="P344" s="35">
-        <f>IF(OR(F344="",O344="Fechada",O344="Perdida"),0,IF(O344="Fechamento vencido",3000,IF(O344="Parada",2000,1000))+MIN(N344,500)+E344/1000000-ROW()/100000)</f>
+        <f>IF(OR(F344="",O344="Fechada",O344="Perdida"),0,IF(O344="Fechamento vencido",3,IF(O344="Parada",2,1))*1E+13+MIN(N(N344),500)*1E+10+MIN(ROUND(N(E344),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14135,7 +14135,7 @@
         <v/>
       </c>
       <c r="P345" s="35">
-        <f>IF(OR(F345="",O345="Fechada",O345="Perdida"),0,IF(O345="Fechamento vencido",3000,IF(O345="Parada",2000,1000))+MIN(N345,500)+E345/1000000-ROW()/100000)</f>
+        <f>IF(OR(F345="",O345="Fechada",O345="Perdida"),0,IF(O345="Fechamento vencido",3,IF(O345="Parada",2,1))*1E+13+MIN(N(N345),500)*1E+10+MIN(ROUND(N(E345),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
         <v/>
       </c>
       <c r="P346" s="35">
-        <f>IF(OR(F346="",O346="Fechada",O346="Perdida"),0,IF(O346="Fechamento vencido",3000,IF(O346="Parada",2000,1000))+MIN(N346,500)+E346/1000000-ROW()/100000)</f>
+        <f>IF(OR(F346="",O346="Fechada",O346="Perdida"),0,IF(O346="Fechamento vencido",3,IF(O346="Parada",2,1))*1E+13+MIN(N(N346),500)*1E+10+MIN(ROUND(N(E346),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
         <v/>
       </c>
       <c r="P347" s="35">
-        <f>IF(OR(F347="",O347="Fechada",O347="Perdida"),0,IF(O347="Fechamento vencido",3000,IF(O347="Parada",2000,1000))+MIN(N347,500)+E347/1000000-ROW()/100000)</f>
+        <f>IF(OR(F347="",O347="Fechada",O347="Perdida"),0,IF(O347="Fechamento vencido",3,IF(O347="Parada",2,1))*1E+13+MIN(N(N347),500)*1E+10+MIN(ROUND(N(E347),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14234,7 +14234,7 @@
         <v/>
       </c>
       <c r="P348" s="35">
-        <f>IF(OR(F348="",O348="Fechada",O348="Perdida"),0,IF(O348="Fechamento vencido",3000,IF(O348="Parada",2000,1000))+MIN(N348,500)+E348/1000000-ROW()/100000)</f>
+        <f>IF(OR(F348="",O348="Fechada",O348="Perdida"),0,IF(O348="Fechamento vencido",3,IF(O348="Parada",2,1))*1E+13+MIN(N(N348),500)*1E+10+MIN(ROUND(N(E348),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
         <v/>
       </c>
       <c r="P349" s="35">
-        <f>IF(OR(F349="",O349="Fechada",O349="Perdida"),0,IF(O349="Fechamento vencido",3000,IF(O349="Parada",2000,1000))+MIN(N349,500)+E349/1000000-ROW()/100000)</f>
+        <f>IF(OR(F349="",O349="Fechada",O349="Perdida"),0,IF(O349="Fechamento vencido",3,IF(O349="Parada",2,1))*1E+13+MIN(N(N349),500)*1E+10+MIN(ROUND(N(E349),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
         <v/>
       </c>
       <c r="P350" s="35">
-        <f>IF(OR(F350="",O350="Fechada",O350="Perdida"),0,IF(O350="Fechamento vencido",3000,IF(O350="Parada",2000,1000))+MIN(N350,500)+E350/1000000-ROW()/100000)</f>
+        <f>IF(OR(F350="",O350="Fechada",O350="Perdida"),0,IF(O350="Fechamento vencido",3,IF(O350="Parada",2,1))*1E+13+MIN(N(N350),500)*1E+10+MIN(ROUND(N(E350),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14333,7 +14333,7 @@
         <v/>
       </c>
       <c r="P351" s="35">
-        <f>IF(OR(F351="",O351="Fechada",O351="Perdida"),0,IF(O351="Fechamento vencido",3000,IF(O351="Parada",2000,1000))+MIN(N351,500)+E351/1000000-ROW()/100000)</f>
+        <f>IF(OR(F351="",O351="Fechada",O351="Perdida"),0,IF(O351="Fechamento vencido",3,IF(O351="Parada",2,1))*1E+13+MIN(N(N351),500)*1E+10+MIN(ROUND(N(E351),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
         <v/>
       </c>
       <c r="P352" s="35">
-        <f>IF(OR(F352="",O352="Fechada",O352="Perdida"),0,IF(O352="Fechamento vencido",3000,IF(O352="Parada",2000,1000))+MIN(N352,500)+E352/1000000-ROW()/100000)</f>
+        <f>IF(OR(F352="",O352="Fechada",O352="Perdida"),0,IF(O352="Fechamento vencido",3,IF(O352="Parada",2,1))*1E+13+MIN(N(N352),500)*1E+10+MIN(ROUND(N(E352),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14399,7 +14399,7 @@
         <v/>
       </c>
       <c r="P353" s="35">
-        <f>IF(OR(F353="",O353="Fechada",O353="Perdida"),0,IF(O353="Fechamento vencido",3000,IF(O353="Parada",2000,1000))+MIN(N353,500)+E353/1000000-ROW()/100000)</f>
+        <f>IF(OR(F353="",O353="Fechada",O353="Perdida"),0,IF(O353="Fechamento vencido",3,IF(O353="Parada",2,1))*1E+13+MIN(N(N353),500)*1E+10+MIN(ROUND(N(E353),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
         <v/>
       </c>
       <c r="P354" s="35">
-        <f>IF(OR(F354="",O354="Fechada",O354="Perdida"),0,IF(O354="Fechamento vencido",3000,IF(O354="Parada",2000,1000))+MIN(N354,500)+E354/1000000-ROW()/100000)</f>
+        <f>IF(OR(F354="",O354="Fechada",O354="Perdida"),0,IF(O354="Fechamento vencido",3,IF(O354="Parada",2,1))*1E+13+MIN(N(N354),500)*1E+10+MIN(ROUND(N(E354),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14465,7 +14465,7 @@
         <v/>
       </c>
       <c r="P355" s="35">
-        <f>IF(OR(F355="",O355="Fechada",O355="Perdida"),0,IF(O355="Fechamento vencido",3000,IF(O355="Parada",2000,1000))+MIN(N355,500)+E355/1000000-ROW()/100000)</f>
+        <f>IF(OR(F355="",O355="Fechada",O355="Perdida"),0,IF(O355="Fechamento vencido",3,IF(O355="Parada",2,1))*1E+13+MIN(N(N355),500)*1E+10+MIN(ROUND(N(E355),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
         <v/>
       </c>
       <c r="P356" s="35">
-        <f>IF(OR(F356="",O356="Fechada",O356="Perdida"),0,IF(O356="Fechamento vencido",3000,IF(O356="Parada",2000,1000))+MIN(N356,500)+E356/1000000-ROW()/100000)</f>
+        <f>IF(OR(F356="",O356="Fechada",O356="Perdida"),0,IF(O356="Fechamento vencido",3,IF(O356="Parada",2,1))*1E+13+MIN(N(N356),500)*1E+10+MIN(ROUND(N(E356),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         <v/>
       </c>
       <c r="P357" s="35">
-        <f>IF(OR(F357="",O357="Fechada",O357="Perdida"),0,IF(O357="Fechamento vencido",3000,IF(O357="Parada",2000,1000))+MIN(N357,500)+E357/1000000-ROW()/100000)</f>
+        <f>IF(OR(F357="",O357="Fechada",O357="Perdida"),0,IF(O357="Fechamento vencido",3,IF(O357="Parada",2,1))*1E+13+MIN(N(N357),500)*1E+10+MIN(ROUND(N(E357),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
         <v/>
       </c>
       <c r="P358" s="35">
-        <f>IF(OR(F358="",O358="Fechada",O358="Perdida"),0,IF(O358="Fechamento vencido",3000,IF(O358="Parada",2000,1000))+MIN(N358,500)+E358/1000000-ROW()/100000)</f>
+        <f>IF(OR(F358="",O358="Fechada",O358="Perdida"),0,IF(O358="Fechamento vencido",3,IF(O358="Parada",2,1))*1E+13+MIN(N(N358),500)*1E+10+MIN(ROUND(N(E358),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14597,7 +14597,7 @@
         <v/>
       </c>
       <c r="P359" s="35">
-        <f>IF(OR(F359="",O359="Fechada",O359="Perdida"),0,IF(O359="Fechamento vencido",3000,IF(O359="Parada",2000,1000))+MIN(N359,500)+E359/1000000-ROW()/100000)</f>
+        <f>IF(OR(F359="",O359="Fechada",O359="Perdida"),0,IF(O359="Fechamento vencido",3,IF(O359="Parada",2,1))*1E+13+MIN(N(N359),500)*1E+10+MIN(ROUND(N(E359),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
         <v/>
       </c>
       <c r="P360" s="35">
-        <f>IF(OR(F360="",O360="Fechada",O360="Perdida"),0,IF(O360="Fechamento vencido",3000,IF(O360="Parada",2000,1000))+MIN(N360,500)+E360/1000000-ROW()/100000)</f>
+        <f>IF(OR(F360="",O360="Fechada",O360="Perdida"),0,IF(O360="Fechamento vencido",3,IF(O360="Parada",2,1))*1E+13+MIN(N(N360),500)*1E+10+MIN(ROUND(N(E360),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
         <v/>
       </c>
       <c r="P361" s="35">
-        <f>IF(OR(F361="",O361="Fechada",O361="Perdida"),0,IF(O361="Fechamento vencido",3000,IF(O361="Parada",2000,1000))+MIN(N361,500)+E361/1000000-ROW()/100000)</f>
+        <f>IF(OR(F361="",O361="Fechada",O361="Perdida"),0,IF(O361="Fechamento vencido",3,IF(O361="Parada",2,1))*1E+13+MIN(N(N361),500)*1E+10+MIN(ROUND(N(E361),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
         <v/>
       </c>
       <c r="P362" s="35">
-        <f>IF(OR(F362="",O362="Fechada",O362="Perdida"),0,IF(O362="Fechamento vencido",3000,IF(O362="Parada",2000,1000))+MIN(N362,500)+E362/1000000-ROW()/100000)</f>
+        <f>IF(OR(F362="",O362="Fechada",O362="Perdida"),0,IF(O362="Fechamento vencido",3,IF(O362="Parada",2,1))*1E+13+MIN(N(N362),500)*1E+10+MIN(ROUND(N(E362),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
         <v/>
       </c>
       <c r="P363" s="35">
-        <f>IF(OR(F363="",O363="Fechada",O363="Perdida"),0,IF(O363="Fechamento vencido",3000,IF(O363="Parada",2000,1000))+MIN(N363,500)+E363/1000000-ROW()/100000)</f>
+        <f>IF(OR(F363="",O363="Fechada",O363="Perdida"),0,IF(O363="Fechamento vencido",3,IF(O363="Parada",2,1))*1E+13+MIN(N(N363),500)*1E+10+MIN(ROUND(N(E363),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
         <v/>
       </c>
       <c r="P364" s="35">
-        <f>IF(OR(F364="",O364="Fechada",O364="Perdida"),0,IF(O364="Fechamento vencido",3000,IF(O364="Parada",2000,1000))+MIN(N364,500)+E364/1000000-ROW()/100000)</f>
+        <f>IF(OR(F364="",O364="Fechada",O364="Perdida"),0,IF(O364="Fechamento vencido",3,IF(O364="Parada",2,1))*1E+13+MIN(N(N364),500)*1E+10+MIN(ROUND(N(E364),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14795,7 +14795,7 @@
         <v/>
       </c>
       <c r="P365" s="35">
-        <f>IF(OR(F365="",O365="Fechada",O365="Perdida"),0,IF(O365="Fechamento vencido",3000,IF(O365="Parada",2000,1000))+MIN(N365,500)+E365/1000000-ROW()/100000)</f>
+        <f>IF(OR(F365="",O365="Fechada",O365="Perdida"),0,IF(O365="Fechamento vencido",3,IF(O365="Parada",2,1))*1E+13+MIN(N(N365),500)*1E+10+MIN(ROUND(N(E365),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
         <v/>
       </c>
       <c r="P366" s="35">
-        <f>IF(OR(F366="",O366="Fechada",O366="Perdida"),0,IF(O366="Fechamento vencido",3000,IF(O366="Parada",2000,1000))+MIN(N366,500)+E366/1000000-ROW()/100000)</f>
+        <f>IF(OR(F366="",O366="Fechada",O366="Perdida"),0,IF(O366="Fechamento vencido",3,IF(O366="Parada",2,1))*1E+13+MIN(N(N366),500)*1E+10+MIN(ROUND(N(E366),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14861,7 +14861,7 @@
         <v/>
       </c>
       <c r="P367" s="35">
-        <f>IF(OR(F367="",O367="Fechada",O367="Perdida"),0,IF(O367="Fechamento vencido",3000,IF(O367="Parada",2000,1000))+MIN(N367,500)+E367/1000000-ROW()/100000)</f>
+        <f>IF(OR(F367="",O367="Fechada",O367="Perdida"),0,IF(O367="Fechamento vencido",3,IF(O367="Parada",2,1))*1E+13+MIN(N(N367),500)*1E+10+MIN(ROUND(N(E367),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14894,7 +14894,7 @@
         <v/>
       </c>
       <c r="P368" s="35">
-        <f>IF(OR(F368="",O368="Fechada",O368="Perdida"),0,IF(O368="Fechamento vencido",3000,IF(O368="Parada",2000,1000))+MIN(N368,500)+E368/1000000-ROW()/100000)</f>
+        <f>IF(OR(F368="",O368="Fechada",O368="Perdida"),0,IF(O368="Fechamento vencido",3,IF(O368="Parada",2,1))*1E+13+MIN(N(N368),500)*1E+10+MIN(ROUND(N(E368),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
         <v/>
       </c>
       <c r="P369" s="35">
-        <f>IF(OR(F369="",O369="Fechada",O369="Perdida"),0,IF(O369="Fechamento vencido",3000,IF(O369="Parada",2000,1000))+MIN(N369,500)+E369/1000000-ROW()/100000)</f>
+        <f>IF(OR(F369="",O369="Fechada",O369="Perdida"),0,IF(O369="Fechamento vencido",3,IF(O369="Parada",2,1))*1E+13+MIN(N(N369),500)*1E+10+MIN(ROUND(N(E369),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14960,7 +14960,7 @@
         <v/>
       </c>
       <c r="P370" s="35">
-        <f>IF(OR(F370="",O370="Fechada",O370="Perdida"),0,IF(O370="Fechamento vencido",3000,IF(O370="Parada",2000,1000))+MIN(N370,500)+E370/1000000-ROW()/100000)</f>
+        <f>IF(OR(F370="",O370="Fechada",O370="Perdida"),0,IF(O370="Fechamento vencido",3,IF(O370="Parada",2,1))*1E+13+MIN(N(N370),500)*1E+10+MIN(ROUND(N(E370),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
         <v/>
       </c>
       <c r="P371" s="35">
-        <f>IF(OR(F371="",O371="Fechada",O371="Perdida"),0,IF(O371="Fechamento vencido",3000,IF(O371="Parada",2000,1000))+MIN(N371,500)+E371/1000000-ROW()/100000)</f>
+        <f>IF(OR(F371="",O371="Fechada",O371="Perdida"),0,IF(O371="Fechamento vencido",3,IF(O371="Parada",2,1))*1E+13+MIN(N(N371),500)*1E+10+MIN(ROUND(N(E371),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
         <v/>
       </c>
       <c r="P372" s="35">
-        <f>IF(OR(F372="",O372="Fechada",O372="Perdida"),0,IF(O372="Fechamento vencido",3000,IF(O372="Parada",2000,1000))+MIN(N372,500)+E372/1000000-ROW()/100000)</f>
+        <f>IF(OR(F372="",O372="Fechada",O372="Perdida"),0,IF(O372="Fechamento vencido",3,IF(O372="Parada",2,1))*1E+13+MIN(N(N372),500)*1E+10+MIN(ROUND(N(E372),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
         <v/>
       </c>
       <c r="P373" s="35">
-        <f>IF(OR(F373="",O373="Fechada",O373="Perdida"),0,IF(O373="Fechamento vencido",3000,IF(O373="Parada",2000,1000))+MIN(N373,500)+E373/1000000-ROW()/100000)</f>
+        <f>IF(OR(F373="",O373="Fechada",O373="Perdida"),0,IF(O373="Fechamento vencido",3,IF(O373="Parada",2,1))*1E+13+MIN(N(N373),500)*1E+10+MIN(ROUND(N(E373),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
         <v/>
       </c>
       <c r="P374" s="35">
-        <f>IF(OR(F374="",O374="Fechada",O374="Perdida"),0,IF(O374="Fechamento vencido",3000,IF(O374="Parada",2000,1000))+MIN(N374,500)+E374/1000000-ROW()/100000)</f>
+        <f>IF(OR(F374="",O374="Fechada",O374="Perdida"),0,IF(O374="Fechamento vencido",3,IF(O374="Parada",2,1))*1E+13+MIN(N(N374),500)*1E+10+MIN(ROUND(N(E374),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15125,7 +15125,7 @@
         <v/>
       </c>
       <c r="P375" s="35">
-        <f>IF(OR(F375="",O375="Fechada",O375="Perdida"),0,IF(O375="Fechamento vencido",3000,IF(O375="Parada",2000,1000))+MIN(N375,500)+E375/1000000-ROW()/100000)</f>
+        <f>IF(OR(F375="",O375="Fechada",O375="Perdida"),0,IF(O375="Fechamento vencido",3,IF(O375="Parada",2,1))*1E+13+MIN(N(N375),500)*1E+10+MIN(ROUND(N(E375),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
         <v/>
       </c>
       <c r="P376" s="35">
-        <f>IF(OR(F376="",O376="Fechada",O376="Perdida"),0,IF(O376="Fechamento vencido",3000,IF(O376="Parada",2000,1000))+MIN(N376,500)+E376/1000000-ROW()/100000)</f>
+        <f>IF(OR(F376="",O376="Fechada",O376="Perdida"),0,IF(O376="Fechamento vencido",3,IF(O376="Parada",2,1))*1E+13+MIN(N(N376),500)*1E+10+MIN(ROUND(N(E376),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15191,7 +15191,7 @@
         <v/>
       </c>
       <c r="P377" s="35">
-        <f>IF(OR(F377="",O377="Fechada",O377="Perdida"),0,IF(O377="Fechamento vencido",3000,IF(O377="Parada",2000,1000))+MIN(N377,500)+E377/1000000-ROW()/100000)</f>
+        <f>IF(OR(F377="",O377="Fechada",O377="Perdida"),0,IF(O377="Fechamento vencido",3,IF(O377="Parada",2,1))*1E+13+MIN(N(N377),500)*1E+10+MIN(ROUND(N(E377),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
         <v/>
       </c>
       <c r="P378" s="35">
-        <f>IF(OR(F378="",O378="Fechada",O378="Perdida"),0,IF(O378="Fechamento vencido",3000,IF(O378="Parada",2000,1000))+MIN(N378,500)+E378/1000000-ROW()/100000)</f>
+        <f>IF(OR(F378="",O378="Fechada",O378="Perdida"),0,IF(O378="Fechamento vencido",3,IF(O378="Parada",2,1))*1E+13+MIN(N(N378),500)*1E+10+MIN(ROUND(N(E378),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15257,7 +15257,7 @@
         <v/>
       </c>
       <c r="P379" s="35">
-        <f>IF(OR(F379="",O379="Fechada",O379="Perdida"),0,IF(O379="Fechamento vencido",3000,IF(O379="Parada",2000,1000))+MIN(N379,500)+E379/1000000-ROW()/100000)</f>
+        <f>IF(OR(F379="",O379="Fechada",O379="Perdida"),0,IF(O379="Fechamento vencido",3,IF(O379="Parada",2,1))*1E+13+MIN(N(N379),500)*1E+10+MIN(ROUND(N(E379),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
         <v/>
       </c>
       <c r="P380" s="35">
-        <f>IF(OR(F380="",O380="Fechada",O380="Perdida"),0,IF(O380="Fechamento vencido",3000,IF(O380="Parada",2000,1000))+MIN(N380,500)+E380/1000000-ROW()/100000)</f>
+        <f>IF(OR(F380="",O380="Fechada",O380="Perdida"),0,IF(O380="Fechamento vencido",3,IF(O380="Parada",2,1))*1E+13+MIN(N(N380),500)*1E+10+MIN(ROUND(N(E380),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
         <v/>
       </c>
       <c r="P381" s="35">
-        <f>IF(OR(F381="",O381="Fechada",O381="Perdida"),0,IF(O381="Fechamento vencido",3000,IF(O381="Parada",2000,1000))+MIN(N381,500)+E381/1000000-ROW()/100000)</f>
+        <f>IF(OR(F381="",O381="Fechada",O381="Perdida"),0,IF(O381="Fechamento vencido",3,IF(O381="Parada",2,1))*1E+13+MIN(N(N381),500)*1E+10+MIN(ROUND(N(E381),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15356,7 +15356,7 @@
         <v/>
       </c>
       <c r="P382" s="35">
-        <f>IF(OR(F382="",O382="Fechada",O382="Perdida"),0,IF(O382="Fechamento vencido",3000,IF(O382="Parada",2000,1000))+MIN(N382,500)+E382/1000000-ROW()/100000)</f>
+        <f>IF(OR(F382="",O382="Fechada",O382="Perdida"),0,IF(O382="Fechamento vencido",3,IF(O382="Parada",2,1))*1E+13+MIN(N(N382),500)*1E+10+MIN(ROUND(N(E382),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15389,7 +15389,7 @@
         <v/>
       </c>
       <c r="P383" s="35">
-        <f>IF(OR(F383="",O383="Fechada",O383="Perdida"),0,IF(O383="Fechamento vencido",3000,IF(O383="Parada",2000,1000))+MIN(N383,500)+E383/1000000-ROW()/100000)</f>
+        <f>IF(OR(F383="",O383="Fechada",O383="Perdida"),0,IF(O383="Fechamento vencido",3,IF(O383="Parada",2,1))*1E+13+MIN(N(N383),500)*1E+10+MIN(ROUND(N(E383),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15422,7 +15422,7 @@
         <v/>
       </c>
       <c r="P384" s="35">
-        <f>IF(OR(F384="",O384="Fechada",O384="Perdida"),0,IF(O384="Fechamento vencido",3000,IF(O384="Parada",2000,1000))+MIN(N384,500)+E384/1000000-ROW()/100000)</f>
+        <f>IF(OR(F384="",O384="Fechada",O384="Perdida"),0,IF(O384="Fechamento vencido",3,IF(O384="Parada",2,1))*1E+13+MIN(N(N384),500)*1E+10+MIN(ROUND(N(E384),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15455,7 +15455,7 @@
         <v/>
       </c>
       <c r="P385" s="35">
-        <f>IF(OR(F385="",O385="Fechada",O385="Perdida"),0,IF(O385="Fechamento vencido",3000,IF(O385="Parada",2000,1000))+MIN(N385,500)+E385/1000000-ROW()/100000)</f>
+        <f>IF(OR(F385="",O385="Fechada",O385="Perdida"),0,IF(O385="Fechamento vencido",3,IF(O385="Parada",2,1))*1E+13+MIN(N(N385),500)*1E+10+MIN(ROUND(N(E385),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15488,7 +15488,7 @@
         <v/>
       </c>
       <c r="P386" s="35">
-        <f>IF(OR(F386="",O386="Fechada",O386="Perdida"),0,IF(O386="Fechamento vencido",3000,IF(O386="Parada",2000,1000))+MIN(N386,500)+E386/1000000-ROW()/100000)</f>
+        <f>IF(OR(F386="",O386="Fechada",O386="Perdida"),0,IF(O386="Fechamento vencido",3,IF(O386="Parada",2,1))*1E+13+MIN(N(N386),500)*1E+10+MIN(ROUND(N(E386),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
         <v/>
       </c>
       <c r="P387" s="35">
-        <f>IF(OR(F387="",O387="Fechada",O387="Perdida"),0,IF(O387="Fechamento vencido",3000,IF(O387="Parada",2000,1000))+MIN(N387,500)+E387/1000000-ROW()/100000)</f>
+        <f>IF(OR(F387="",O387="Fechada",O387="Perdida"),0,IF(O387="Fechamento vencido",3,IF(O387="Parada",2,1))*1E+13+MIN(N(N387),500)*1E+10+MIN(ROUND(N(E387),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15554,7 +15554,7 @@
         <v/>
       </c>
       <c r="P388" s="35">
-        <f>IF(OR(F388="",O388="Fechada",O388="Perdida"),0,IF(O388="Fechamento vencido",3000,IF(O388="Parada",2000,1000))+MIN(N388,500)+E388/1000000-ROW()/100000)</f>
+        <f>IF(OR(F388="",O388="Fechada",O388="Perdida"),0,IF(O388="Fechamento vencido",3,IF(O388="Parada",2,1))*1E+13+MIN(N(N388),500)*1E+10+MIN(ROUND(N(E388),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
         <v/>
       </c>
       <c r="P389" s="35">
-        <f>IF(OR(F389="",O389="Fechada",O389="Perdida"),0,IF(O389="Fechamento vencido",3000,IF(O389="Parada",2000,1000))+MIN(N389,500)+E389/1000000-ROW()/100000)</f>
+        <f>IF(OR(F389="",O389="Fechada",O389="Perdida"),0,IF(O389="Fechamento vencido",3,IF(O389="Parada",2,1))*1E+13+MIN(N(N389),500)*1E+10+MIN(ROUND(N(E389),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15620,7 +15620,7 @@
         <v/>
       </c>
       <c r="P390" s="35">
-        <f>IF(OR(F390="",O390="Fechada",O390="Perdida"),0,IF(O390="Fechamento vencido",3000,IF(O390="Parada",2000,1000))+MIN(N390,500)+E390/1000000-ROW()/100000)</f>
+        <f>IF(OR(F390="",O390="Fechada",O390="Perdida"),0,IF(O390="Fechamento vencido",3,IF(O390="Parada",2,1))*1E+13+MIN(N(N390),500)*1E+10+MIN(ROUND(N(E390),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15653,7 +15653,7 @@
         <v/>
       </c>
       <c r="P391" s="35">
-        <f>IF(OR(F391="",O391="Fechada",O391="Perdida"),0,IF(O391="Fechamento vencido",3000,IF(O391="Parada",2000,1000))+MIN(N391,500)+E391/1000000-ROW()/100000)</f>
+        <f>IF(OR(F391="",O391="Fechada",O391="Perdida"),0,IF(O391="Fechamento vencido",3,IF(O391="Parada",2,1))*1E+13+MIN(N(N391),500)*1E+10+MIN(ROUND(N(E391),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15686,7 +15686,7 @@
         <v/>
       </c>
       <c r="P392" s="35">
-        <f>IF(OR(F392="",O392="Fechada",O392="Perdida"),0,IF(O392="Fechamento vencido",3000,IF(O392="Parada",2000,1000))+MIN(N392,500)+E392/1000000-ROW()/100000)</f>
+        <f>IF(OR(F392="",O392="Fechada",O392="Perdida"),0,IF(O392="Fechamento vencido",3,IF(O392="Parada",2,1))*1E+13+MIN(N(N392),500)*1E+10+MIN(ROUND(N(E392),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
         <v/>
       </c>
       <c r="P393" s="35">
-        <f>IF(OR(F393="",O393="Fechada",O393="Perdida"),0,IF(O393="Fechamento vencido",3000,IF(O393="Parada",2000,1000))+MIN(N393,500)+E393/1000000-ROW()/100000)</f>
+        <f>IF(OR(F393="",O393="Fechada",O393="Perdida"),0,IF(O393="Fechamento vencido",3,IF(O393="Parada",2,1))*1E+13+MIN(N(N393),500)*1E+10+MIN(ROUND(N(E393),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
         <v/>
       </c>
       <c r="P394" s="35">
-        <f>IF(OR(F394="",O394="Fechada",O394="Perdida"),0,IF(O394="Fechamento vencido",3000,IF(O394="Parada",2000,1000))+MIN(N394,500)+E394/1000000-ROW()/100000)</f>
+        <f>IF(OR(F394="",O394="Fechada",O394="Perdida"),0,IF(O394="Fechamento vencido",3,IF(O394="Parada",2,1))*1E+13+MIN(N(N394),500)*1E+10+MIN(ROUND(N(E394),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
         <v/>
       </c>
       <c r="P395" s="35">
-        <f>IF(OR(F395="",O395="Fechada",O395="Perdida"),0,IF(O395="Fechamento vencido",3000,IF(O395="Parada",2000,1000))+MIN(N395,500)+E395/1000000-ROW()/100000)</f>
+        <f>IF(OR(F395="",O395="Fechada",O395="Perdida"),0,IF(O395="Fechamento vencido",3,IF(O395="Parada",2,1))*1E+13+MIN(N(N395),500)*1E+10+MIN(ROUND(N(E395),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15818,7 +15818,7 @@
         <v/>
       </c>
       <c r="P396" s="35">
-        <f>IF(OR(F396="",O396="Fechada",O396="Perdida"),0,IF(O396="Fechamento vencido",3000,IF(O396="Parada",2000,1000))+MIN(N396,500)+E396/1000000-ROW()/100000)</f>
+        <f>IF(OR(F396="",O396="Fechada",O396="Perdida"),0,IF(O396="Fechamento vencido",3,IF(O396="Parada",2,1))*1E+13+MIN(N(N396),500)*1E+10+MIN(ROUND(N(E396),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
         <v/>
       </c>
       <c r="P397" s="35">
-        <f>IF(OR(F397="",O397="Fechada",O397="Perdida"),0,IF(O397="Fechamento vencido",3000,IF(O397="Parada",2000,1000))+MIN(N397,500)+E397/1000000-ROW()/100000)</f>
+        <f>IF(OR(F397="",O397="Fechada",O397="Perdida"),0,IF(O397="Fechamento vencido",3,IF(O397="Parada",2,1))*1E+13+MIN(N(N397),500)*1E+10+MIN(ROUND(N(E397),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         <v/>
       </c>
       <c r="P398" s="35">
-        <f>IF(OR(F398="",O398="Fechada",O398="Perdida"),0,IF(O398="Fechamento vencido",3000,IF(O398="Parada",2000,1000))+MIN(N398,500)+E398/1000000-ROW()/100000)</f>
+        <f>IF(OR(F398="",O398="Fechada",O398="Perdida"),0,IF(O398="Fechamento vencido",3,IF(O398="Parada",2,1))*1E+13+MIN(N(N398),500)*1E+10+MIN(ROUND(N(E398),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15917,7 +15917,7 @@
         <v/>
       </c>
       <c r="P399" s="35">
-        <f>IF(OR(F399="",O399="Fechada",O399="Perdida"),0,IF(O399="Fechamento vencido",3000,IF(O399="Parada",2000,1000))+MIN(N399,500)+E399/1000000-ROW()/100000)</f>
+        <f>IF(OR(F399="",O399="Fechada",O399="Perdida"),0,IF(O399="Fechamento vencido",3,IF(O399="Parada",2,1))*1E+13+MIN(N(N399),500)*1E+10+MIN(ROUND(N(E399),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15950,7 +15950,7 @@
         <v/>
       </c>
       <c r="P400" s="35">
-        <f>IF(OR(F400="",O400="Fechada",O400="Perdida"),0,IF(O400="Fechamento vencido",3000,IF(O400="Parada",2000,1000))+MIN(N400,500)+E400/1000000-ROW()/100000)</f>
+        <f>IF(OR(F400="",O400="Fechada",O400="Perdida"),0,IF(O400="Fechamento vencido",3,IF(O400="Parada",2,1))*1E+13+MIN(N(N400),500)*1E+10+MIN(ROUND(N(E400),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
         <v/>
       </c>
       <c r="P401" s="35">
-        <f>IF(OR(F401="",O401="Fechada",O401="Perdida"),0,IF(O401="Fechamento vencido",3000,IF(O401="Parada",2000,1000))+MIN(N401,500)+E401/1000000-ROW()/100000)</f>
+        <f>IF(OR(F401="",O401="Fechada",O401="Perdida"),0,IF(O401="Fechamento vencido",3,IF(O401="Parada",2,1))*1E+13+MIN(N(N401),500)*1E+10+MIN(ROUND(N(E401),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -16016,7 +16016,7 @@
         <v/>
       </c>
       <c r="P402" s="35">
-        <f>IF(OR(F402="",O402="Fechada",O402="Perdida"),0,IF(O402="Fechamento vencido",3000,IF(O402="Parada",2000,1000))+MIN(N402,500)+E402/1000000-ROW()/100000)</f>
+        <f>IF(OR(F402="",O402="Fechada",O402="Perdida"),0,IF(O402="Fechamento vencido",3,IF(O402="Parada",2,1))*1E+13+MIN(N(N402),500)*1E+10+MIN(ROUND(N(E402),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -16049,7 +16049,7 @@
         <v/>
       </c>
       <c r="P403" s="35">
-        <f>IF(OR(F403="",O403="Fechada",O403="Perdida"),0,IF(O403="Fechamento vencido",3000,IF(O403="Parada",2000,1000))+MIN(N403,500)+E403/1000000-ROW()/100000)</f>
+        <f>IF(OR(F403="",O403="Fechada",O403="Perdida"),0,IF(O403="Fechamento vencido",3,IF(O403="Parada",2,1))*1E+13+MIN(N(N403),500)*1E+10+MIN(ROUND(N(E403),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
         <v/>
       </c>
       <c r="P404" s="35">
-        <f>IF(OR(F404="",O404="Fechada",O404="Perdida"),0,IF(O404="Fechamento vencido",3000,IF(O404="Parada",2000,1000))+MIN(N404,500)+E404/1000000-ROW()/100000)</f>
+        <f>IF(OR(F404="",O404="Fechada",O404="Perdida"),0,IF(O404="Fechamento vencido",3,IF(O404="Parada",2,1))*1E+13+MIN(N(N404),500)*1E+10+MIN(ROUND(N(E404),0),999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
@@ -2529,7 +2529,7 @@
         <v>Fechada</v>
       </c>
       <c r="P5" s="35">
-        <f>IF(OR(F5="",O5="Fechada",O5="Perdida"),0,IF(O5="Fechamento vencido",3,IF(O5="Parada",2,1))*1E+13+MIN(N(N5),500)*1E+10+MIN(ROUND(N(E5),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F5="",O5="Fechada",O5="Perdida"),0,IF(O5="Fechamento vencido",3,IF(O5="Parada",2,1))*1E+15+MIN(N(N5),500)*1E+12+MIN(ROUND(N(E5)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>Fechada</v>
       </c>
       <c r="P6" s="35">
-        <f>IF(OR(F6="",O6="Fechada",O6="Perdida"),0,IF(O6="Fechamento vencido",3,IF(O6="Parada",2,1))*1E+13+MIN(N(N6),500)*1E+10+MIN(ROUND(N(E6),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F6="",O6="Fechada",O6="Perdida"),0,IF(O6="Fechamento vencido",3,IF(O6="Parada",2,1))*1E+15+MIN(N(N6),500)*1E+12+MIN(ROUND(N(E6)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         <v>Fechada</v>
       </c>
       <c r="P7" s="35">
-        <f>IF(OR(F7="",O7="Fechada",O7="Perdida"),0,IF(O7="Fechamento vencido",3,IF(O7="Parada",2,1))*1E+13+MIN(N(N7),500)*1E+10+MIN(ROUND(N(E7),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F7="",O7="Fechada",O7="Perdida"),0,IF(O7="Fechamento vencido",3,IF(O7="Parada",2,1))*1E+15+MIN(N(N7),500)*1E+12+MIN(ROUND(N(E7)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
         <v>Fechada</v>
       </c>
       <c r="P8" s="35">
-        <f>IF(OR(F8="",O8="Fechada",O8="Perdida"),0,IF(O8="Fechamento vencido",3,IF(O8="Parada",2,1))*1E+13+MIN(N(N8),500)*1E+10+MIN(ROUND(N(E8),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F8="",O8="Fechada",O8="Perdida"),0,IF(O8="Fechamento vencido",3,IF(O8="Parada",2,1))*1E+15+MIN(N(N8),500)*1E+12+MIN(ROUND(N(E8)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -2779,8 +2779,8 @@
         <v>Ativa</v>
       </c>
       <c r="P9" s="35">
-        <f>IF(OR(F9="",O9="Fechada",O9="Perdida"),0,IF(O9="Fechamento vencido",3,IF(O9="Parada",2,1))*1E+13+MIN(N(N9),500)*1E+10+MIN(ROUND(N(E9),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>10050220000396</v>
+        <f>IF(OR(F9="",O9="Fechada",O9="Perdida"),0,IF(O9="Fechamento vencido",3,IF(O9="Parada",2,1))*1E+15+MIN(N(N9),500)*1E+12+MIN(ROUND(N(E9)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>1005022000000396</v>
       </c>
     </row>
     <row r="10">
@@ -2840,8 +2840,8 @@
         <v>Fechamento vencido</v>
       </c>
       <c r="P10" s="35">
-        <f>IF(OR(F10="",O10="Fechada",O10="Perdida"),0,IF(O10="Fechamento vencido",3,IF(O10="Parada",2,1))*1E+13+MIN(N(N10),500)*1E+10+MIN(ROUND(N(E10),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>30100045000395</v>
+        <f>IF(OR(F10="",O10="Fechada",O10="Perdida"),0,IF(O10="Fechamento vencido",3,IF(O10="Parada",2,1))*1E+15+MIN(N(N10),500)*1E+12+MIN(ROUND(N(E10)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>3010004500000395</v>
       </c>
     </row>
     <row r="11">
@@ -2901,8 +2901,8 @@
         <v>Fechamento vencido</v>
       </c>
       <c r="P11" s="35">
-        <f>IF(OR(F11="",O11="Fechada",O11="Perdida"),0,IF(O11="Fechamento vencido",3,IF(O11="Parada",2,1))*1E+13+MIN(N(N11),500)*1E+10+MIN(ROUND(N(E11),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>30190450000394</v>
+        <f>IF(OR(F11="",O11="Fechada",O11="Perdida"),0,IF(O11="Fechamento vencido",3,IF(O11="Parada",2,1))*1E+15+MIN(N(N11),500)*1E+12+MIN(ROUND(N(E11)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>3019045000000394</v>
       </c>
     </row>
     <row r="12">
@@ -2962,8 +2962,8 @@
         <v>Ativa</v>
       </c>
       <c r="P12" s="35">
-        <f>IF(OR(F12="",O12="Fechada",O12="Perdida"),0,IF(O12="Fechamento vencido",3,IF(O12="Parada",2,1))*1E+13+MIN(N(N12),500)*1E+10+MIN(ROUND(N(E12),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>10060310000393</v>
+        <f>IF(OR(F12="",O12="Fechada",O12="Perdida"),0,IF(O12="Fechamento vencido",3,IF(O12="Parada",2,1))*1E+15+MIN(N(N12),500)*1E+12+MIN(ROUND(N(E12)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>1006031000000393</v>
       </c>
     </row>
     <row r="13">
@@ -3021,8 +3021,8 @@
         <v>Ativa</v>
       </c>
       <c r="P13" s="35">
-        <f>IF(OR(F13="",O13="Fechada",O13="Perdida"),0,IF(O13="Fechamento vencido",3,IF(O13="Parada",2,1))*1E+13+MIN(N(N13),500)*1E+10+MIN(ROUND(N(E13),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>10030078000392</v>
+        <f>IF(OR(F13="",O13="Fechada",O13="Perdida"),0,IF(O13="Fechamento vencido",3,IF(O13="Parada",2,1))*1E+15+MIN(N(N13),500)*1E+12+MIN(ROUND(N(E13)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>1003007800000392</v>
       </c>
     </row>
     <row r="14">
@@ -3082,8 +3082,8 @@
         <v>Ativa</v>
       </c>
       <c r="P14" s="35">
-        <f>IF(OR(F14="",O14="Fechada",O14="Perdida"),0,IF(O14="Fechamento vencido",3,IF(O14="Parada",2,1))*1E+13+MIN(N(N14),500)*1E+10+MIN(ROUND(N(E14),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>10020062000391</v>
+        <f>IF(OR(F14="",O14="Fechada",O14="Perdida"),0,IF(O14="Fechamento vencido",3,IF(O14="Parada",2,1))*1E+15+MIN(N(N14),500)*1E+12+MIN(ROUND(N(E14)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>1002006200000391</v>
       </c>
     </row>
     <row r="15">
@@ -3149,7 +3149,7 @@
         <v>Perdida</v>
       </c>
       <c r="P15" s="35">
-        <f>IF(OR(F15="",O15="Fechada",O15="Perdida"),0,IF(O15="Fechamento vencido",3,IF(O15="Parada",2,1))*1E+13+MIN(N(N15),500)*1E+10+MIN(ROUND(N(E15),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F15="",O15="Fechada",O15="Perdida"),0,IF(O15="Fechamento vencido",3,IF(O15="Parada",2,1))*1E+15+MIN(N(N15),500)*1E+12+MIN(ROUND(N(E15)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
         <v>Perdida</v>
       </c>
       <c r="P16" s="35">
-        <f>IF(OR(F16="",O16="Fechada",O16="Perdida"),0,IF(O16="Fechamento vencido",3,IF(O16="Parada",2,1))*1E+13+MIN(N(N16),500)*1E+10+MIN(ROUND(N(E16),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F16="",O16="Fechada",O16="Perdida"),0,IF(O16="Fechamento vencido",3,IF(O16="Parada",2,1))*1E+15+MIN(N(N16),500)*1E+12+MIN(ROUND(N(E16)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
         <v>Perdida</v>
       </c>
       <c r="P17" s="35">
-        <f>IF(OR(F17="",O17="Fechada",O17="Perdida"),0,IF(O17="Fechamento vencido",3,IF(O17="Parada",2,1))*1E+13+MIN(N(N17),500)*1E+10+MIN(ROUND(N(E17),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F17="",O17="Fechada",O17="Perdida"),0,IF(O17="Fechamento vencido",3,IF(O17="Parada",2,1))*1E+15+MIN(N(N17),500)*1E+12+MIN(ROUND(N(E17)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3344,8 +3344,8 @@
         <v>Parada</v>
       </c>
       <c r="P18" s="35">
-        <f>IF(OR(F18="",O18="Fechada",O18="Perdida"),0,IF(O18="Fechamento vencido",3,IF(O18="Parada",2,1))*1E+13+MIN(N(N18),500)*1E+10+MIN(ROUND(N(E18),0),999999)*1E+4+(404+1-ROW()))</f>
-        <v>20330085000387</v>
+        <f>IF(OR(F18="",O18="Fechada",O18="Perdida"),0,IF(O18="Fechamento vencido",3,IF(O18="Parada",2,1))*1E+15+MIN(N(N18),500)*1E+12+MIN(ROUND(N(E18)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
+        <v>2033008500000387</v>
       </c>
     </row>
     <row r="19">
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="P19" s="35">
-        <f>IF(OR(F19="",O19="Fechada",O19="Perdida"),0,IF(O19="Fechamento vencido",3,IF(O19="Parada",2,1))*1E+13+MIN(N(N19),500)*1E+10+MIN(ROUND(N(E19),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F19="",O19="Fechada",O19="Perdida"),0,IF(O19="Fechamento vencido",3,IF(O19="Parada",2,1))*1E+15+MIN(N(N19),500)*1E+12+MIN(ROUND(N(E19)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
         <v/>
       </c>
       <c r="P20" s="35">
-        <f>IF(OR(F20="",O20="Fechada",O20="Perdida"),0,IF(O20="Fechamento vencido",3,IF(O20="Parada",2,1))*1E+13+MIN(N(N20),500)*1E+10+MIN(ROUND(N(E20),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F20="",O20="Fechada",O20="Perdida"),0,IF(O20="Fechamento vencido",3,IF(O20="Parada",2,1))*1E+15+MIN(N(N20),500)*1E+12+MIN(ROUND(N(E20)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
         <v/>
       </c>
       <c r="P21" s="35">
-        <f>IF(OR(F21="",O21="Fechada",O21="Perdida"),0,IF(O21="Fechamento vencido",3,IF(O21="Parada",2,1))*1E+13+MIN(N(N21),500)*1E+10+MIN(ROUND(N(E21),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F21="",O21="Fechada",O21="Perdida"),0,IF(O21="Fechamento vencido",3,IF(O21="Parada",2,1))*1E+15+MIN(N(N21),500)*1E+12+MIN(ROUND(N(E21)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v/>
       </c>
       <c r="P22" s="35">
-        <f>IF(OR(F22="",O22="Fechada",O22="Perdida"),0,IF(O22="Fechamento vencido",3,IF(O22="Parada",2,1))*1E+13+MIN(N(N22),500)*1E+10+MIN(ROUND(N(E22),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F22="",O22="Fechada",O22="Perdida"),0,IF(O22="Fechamento vencido",3,IF(O22="Parada",2,1))*1E+15+MIN(N(N22),500)*1E+12+MIN(ROUND(N(E22)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
         <v/>
       </c>
       <c r="P23" s="35">
-        <f>IF(OR(F23="",O23="Fechada",O23="Perdida"),0,IF(O23="Fechamento vencido",3,IF(O23="Parada",2,1))*1E+13+MIN(N(N23),500)*1E+10+MIN(ROUND(N(E23),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F23="",O23="Fechada",O23="Perdida"),0,IF(O23="Fechamento vencido",3,IF(O23="Parada",2,1))*1E+15+MIN(N(N23),500)*1E+12+MIN(ROUND(N(E23)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v/>
       </c>
       <c r="P24" s="35">
-        <f>IF(OR(F24="",O24="Fechada",O24="Perdida"),0,IF(O24="Fechamento vencido",3,IF(O24="Parada",2,1))*1E+13+MIN(N(N24),500)*1E+10+MIN(ROUND(N(E24),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F24="",O24="Fechada",O24="Perdida"),0,IF(O24="Fechamento vencido",3,IF(O24="Parada",2,1))*1E+15+MIN(N(N24),500)*1E+12+MIN(ROUND(N(E24)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
         <v/>
       </c>
       <c r="P25" s="35">
-        <f>IF(OR(F25="",O25="Fechada",O25="Perdida"),0,IF(O25="Fechamento vencido",3,IF(O25="Parada",2,1))*1E+13+MIN(N(N25),500)*1E+10+MIN(ROUND(N(E25),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F25="",O25="Fechada",O25="Perdida"),0,IF(O25="Fechamento vencido",3,IF(O25="Parada",2,1))*1E+15+MIN(N(N25),500)*1E+12+MIN(ROUND(N(E25)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="P26" s="35">
-        <f>IF(OR(F26="",O26="Fechada",O26="Perdida"),0,IF(O26="Fechamento vencido",3,IF(O26="Parada",2,1))*1E+13+MIN(N(N26),500)*1E+10+MIN(ROUND(N(E26),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F26="",O26="Fechada",O26="Perdida"),0,IF(O26="Fechamento vencido",3,IF(O26="Parada",2,1))*1E+15+MIN(N(N26),500)*1E+12+MIN(ROUND(N(E26)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
         <v/>
       </c>
       <c r="P27" s="35">
-        <f>IF(OR(F27="",O27="Fechada",O27="Perdida"),0,IF(O27="Fechamento vencido",3,IF(O27="Parada",2,1))*1E+13+MIN(N(N27),500)*1E+10+MIN(ROUND(N(E27),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F27="",O27="Fechada",O27="Perdida"),0,IF(O27="Fechamento vencido",3,IF(O27="Parada",2,1))*1E+15+MIN(N(N27),500)*1E+12+MIN(ROUND(N(E27)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
         <v/>
       </c>
       <c r="P28" s="35">
-        <f>IF(OR(F28="",O28="Fechada",O28="Perdida"),0,IF(O28="Fechamento vencido",3,IF(O28="Parada",2,1))*1E+13+MIN(N(N28),500)*1E+10+MIN(ROUND(N(E28),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F28="",O28="Fechada",O28="Perdida"),0,IF(O28="Fechamento vencido",3,IF(O28="Parada",2,1))*1E+15+MIN(N(N28),500)*1E+12+MIN(ROUND(N(E28)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         <v/>
       </c>
       <c r="P29" s="35">
-        <f>IF(OR(F29="",O29="Fechada",O29="Perdida"),0,IF(O29="Fechamento vencido",3,IF(O29="Parada",2,1))*1E+13+MIN(N(N29),500)*1E+10+MIN(ROUND(N(E29),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F29="",O29="Fechada",O29="Perdida"),0,IF(O29="Fechamento vencido",3,IF(O29="Parada",2,1))*1E+15+MIN(N(N29),500)*1E+12+MIN(ROUND(N(E29)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v/>
       </c>
       <c r="P30" s="35">
-        <f>IF(OR(F30="",O30="Fechada",O30="Perdida"),0,IF(O30="Fechamento vencido",3,IF(O30="Parada",2,1))*1E+13+MIN(N(N30),500)*1E+10+MIN(ROUND(N(E30),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F30="",O30="Fechada",O30="Perdida"),0,IF(O30="Fechamento vencido",3,IF(O30="Parada",2,1))*1E+15+MIN(N(N30),500)*1E+12+MIN(ROUND(N(E30)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
         <v/>
       </c>
       <c r="P31" s="35">
-        <f>IF(OR(F31="",O31="Fechada",O31="Perdida"),0,IF(O31="Fechamento vencido",3,IF(O31="Parada",2,1))*1E+13+MIN(N(N31),500)*1E+10+MIN(ROUND(N(E31),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F31="",O31="Fechada",O31="Perdida"),0,IF(O31="Fechamento vencido",3,IF(O31="Parada",2,1))*1E+15+MIN(N(N31),500)*1E+12+MIN(ROUND(N(E31)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="P32" s="35">
-        <f>IF(OR(F32="",O32="Fechada",O32="Perdida"),0,IF(O32="Fechamento vencido",3,IF(O32="Parada",2,1))*1E+13+MIN(N(N32),500)*1E+10+MIN(ROUND(N(E32),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F32="",O32="Fechada",O32="Perdida"),0,IF(O32="Fechamento vencido",3,IF(O32="Parada",2,1))*1E+15+MIN(N(N32),500)*1E+12+MIN(ROUND(N(E32)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="P33" s="35">
-        <f>IF(OR(F33="",O33="Fechada",O33="Perdida"),0,IF(O33="Fechamento vencido",3,IF(O33="Parada",2,1))*1E+13+MIN(N(N33),500)*1E+10+MIN(ROUND(N(E33),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F33="",O33="Fechada",O33="Perdida"),0,IF(O33="Fechamento vencido",3,IF(O33="Parada",2,1))*1E+15+MIN(N(N33),500)*1E+12+MIN(ROUND(N(E33)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v/>
       </c>
       <c r="P34" s="35">
-        <f>IF(OR(F34="",O34="Fechada",O34="Perdida"),0,IF(O34="Fechamento vencido",3,IF(O34="Parada",2,1))*1E+13+MIN(N(N34),500)*1E+10+MIN(ROUND(N(E34),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F34="",O34="Fechada",O34="Perdida"),0,IF(O34="Fechamento vencido",3,IF(O34="Parada",2,1))*1E+15+MIN(N(N34),500)*1E+12+MIN(ROUND(N(E34)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         <v/>
       </c>
       <c r="P35" s="35">
-        <f>IF(OR(F35="",O35="Fechada",O35="Perdida"),0,IF(O35="Fechamento vencido",3,IF(O35="Parada",2,1))*1E+13+MIN(N(N35),500)*1E+10+MIN(ROUND(N(E35),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F35="",O35="Fechada",O35="Perdida"),0,IF(O35="Fechamento vencido",3,IF(O35="Parada",2,1))*1E+15+MIN(N(N35),500)*1E+12+MIN(ROUND(N(E35)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v/>
       </c>
       <c r="P36" s="35">
-        <f>IF(OR(F36="",O36="Fechada",O36="Perdida"),0,IF(O36="Fechamento vencido",3,IF(O36="Parada",2,1))*1E+13+MIN(N(N36),500)*1E+10+MIN(ROUND(N(E36),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F36="",O36="Fechada",O36="Perdida"),0,IF(O36="Fechamento vencido",3,IF(O36="Parada",2,1))*1E+15+MIN(N(N36),500)*1E+12+MIN(ROUND(N(E36)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         <v/>
       </c>
       <c r="P37" s="35">
-        <f>IF(OR(F37="",O37="Fechada",O37="Perdida"),0,IF(O37="Fechamento vencido",3,IF(O37="Parada",2,1))*1E+13+MIN(N(N37),500)*1E+10+MIN(ROUND(N(E37),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F37="",O37="Fechada",O37="Perdida"),0,IF(O37="Fechamento vencido",3,IF(O37="Parada",2,1))*1E+15+MIN(N(N37),500)*1E+12+MIN(ROUND(N(E37)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
         <v/>
       </c>
       <c r="P38" s="35">
-        <f>IF(OR(F38="",O38="Fechada",O38="Perdida"),0,IF(O38="Fechamento vencido",3,IF(O38="Parada",2,1))*1E+13+MIN(N(N38),500)*1E+10+MIN(ROUND(N(E38),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F38="",O38="Fechada",O38="Perdida"),0,IF(O38="Fechamento vencido",3,IF(O38="Parada",2,1))*1E+15+MIN(N(N38),500)*1E+12+MIN(ROUND(N(E38)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
         <v/>
       </c>
       <c r="P39" s="35">
-        <f>IF(OR(F39="",O39="Fechada",O39="Perdida"),0,IF(O39="Fechamento vencido",3,IF(O39="Parada",2,1))*1E+13+MIN(N(N39),500)*1E+10+MIN(ROUND(N(E39),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F39="",O39="Fechada",O39="Perdida"),0,IF(O39="Fechamento vencido",3,IF(O39="Parada",2,1))*1E+15+MIN(N(N39),500)*1E+12+MIN(ROUND(N(E39)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v/>
       </c>
       <c r="P40" s="35">
-        <f>IF(OR(F40="",O40="Fechada",O40="Perdida"),0,IF(O40="Fechamento vencido",3,IF(O40="Parada",2,1))*1E+13+MIN(N(N40),500)*1E+10+MIN(ROUND(N(E40),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F40="",O40="Fechada",O40="Perdida"),0,IF(O40="Fechamento vencido",3,IF(O40="Parada",2,1))*1E+15+MIN(N(N40),500)*1E+12+MIN(ROUND(N(E40)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
         <v/>
       </c>
       <c r="P41" s="35">
-        <f>IF(OR(F41="",O41="Fechada",O41="Perdida"),0,IF(O41="Fechamento vencido",3,IF(O41="Parada",2,1))*1E+13+MIN(N(N41),500)*1E+10+MIN(ROUND(N(E41),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F41="",O41="Fechada",O41="Perdida"),0,IF(O41="Fechamento vencido",3,IF(O41="Parada",2,1))*1E+15+MIN(N(N41),500)*1E+12+MIN(ROUND(N(E41)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
         <v/>
       </c>
       <c r="P42" s="35">
-        <f>IF(OR(F42="",O42="Fechada",O42="Perdida"),0,IF(O42="Fechamento vencido",3,IF(O42="Parada",2,1))*1E+13+MIN(N(N42),500)*1E+10+MIN(ROUND(N(E42),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F42="",O42="Fechada",O42="Perdida"),0,IF(O42="Fechamento vencido",3,IF(O42="Parada",2,1))*1E+15+MIN(N(N42),500)*1E+12+MIN(ROUND(N(E42)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
         <v/>
       </c>
       <c r="P43" s="35">
-        <f>IF(OR(F43="",O43="Fechada",O43="Perdida"),0,IF(O43="Fechamento vencido",3,IF(O43="Parada",2,1))*1E+13+MIN(N(N43),500)*1E+10+MIN(ROUND(N(E43),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F43="",O43="Fechada",O43="Perdida"),0,IF(O43="Fechamento vencido",3,IF(O43="Parada",2,1))*1E+15+MIN(N(N43),500)*1E+12+MIN(ROUND(N(E43)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
         <v/>
       </c>
       <c r="P44" s="35">
-        <f>IF(OR(F44="",O44="Fechada",O44="Perdida"),0,IF(O44="Fechamento vencido",3,IF(O44="Parada",2,1))*1E+13+MIN(N(N44),500)*1E+10+MIN(ROUND(N(E44),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F44="",O44="Fechada",O44="Perdida"),0,IF(O44="Fechamento vencido",3,IF(O44="Parada",2,1))*1E+15+MIN(N(N44),500)*1E+12+MIN(ROUND(N(E44)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
         <v/>
       </c>
       <c r="P45" s="35">
-        <f>IF(OR(F45="",O45="Fechada",O45="Perdida"),0,IF(O45="Fechamento vencido",3,IF(O45="Parada",2,1))*1E+13+MIN(N(N45),500)*1E+10+MIN(ROUND(N(E45),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F45="",O45="Fechada",O45="Perdida"),0,IF(O45="Fechamento vencido",3,IF(O45="Parada",2,1))*1E+15+MIN(N(N45),500)*1E+12+MIN(ROUND(N(E45)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
         <v/>
       </c>
       <c r="P46" s="35">
-        <f>IF(OR(F46="",O46="Fechada",O46="Perdida"),0,IF(O46="Fechamento vencido",3,IF(O46="Parada",2,1))*1E+13+MIN(N(N46),500)*1E+10+MIN(ROUND(N(E46),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F46="",O46="Fechada",O46="Perdida"),0,IF(O46="Fechamento vencido",3,IF(O46="Parada",2,1))*1E+15+MIN(N(N46),500)*1E+12+MIN(ROUND(N(E46)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="P47" s="35">
-        <f>IF(OR(F47="",O47="Fechada",O47="Perdida"),0,IF(O47="Fechamento vencido",3,IF(O47="Parada",2,1))*1E+13+MIN(N(N47),500)*1E+10+MIN(ROUND(N(E47),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F47="",O47="Fechada",O47="Perdida"),0,IF(O47="Fechamento vencido",3,IF(O47="Parada",2,1))*1E+15+MIN(N(N47),500)*1E+12+MIN(ROUND(N(E47)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
         <v/>
       </c>
       <c r="P48" s="35">
-        <f>IF(OR(F48="",O48="Fechada",O48="Perdida"),0,IF(O48="Fechamento vencido",3,IF(O48="Parada",2,1))*1E+13+MIN(N(N48),500)*1E+10+MIN(ROUND(N(E48),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F48="",O48="Fechada",O48="Perdida"),0,IF(O48="Fechamento vencido",3,IF(O48="Parada",2,1))*1E+15+MIN(N(N48),500)*1E+12+MIN(ROUND(N(E48)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
         <v/>
       </c>
       <c r="P49" s="35">
-        <f>IF(OR(F49="",O49="Fechada",O49="Perdida"),0,IF(O49="Fechamento vencido",3,IF(O49="Parada",2,1))*1E+13+MIN(N(N49),500)*1E+10+MIN(ROUND(N(E49),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F49="",O49="Fechada",O49="Perdida"),0,IF(O49="Fechamento vencido",3,IF(O49="Parada",2,1))*1E+15+MIN(N(N49),500)*1E+12+MIN(ROUND(N(E49)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
         <v/>
       </c>
       <c r="P50" s="35">
-        <f>IF(OR(F50="",O50="Fechada",O50="Perdida"),0,IF(O50="Fechamento vencido",3,IF(O50="Parada",2,1))*1E+13+MIN(N(N50),500)*1E+10+MIN(ROUND(N(E50),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F50="",O50="Fechada",O50="Perdida"),0,IF(O50="Fechamento vencido",3,IF(O50="Parada",2,1))*1E+15+MIN(N(N50),500)*1E+12+MIN(ROUND(N(E50)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
         <v/>
       </c>
       <c r="P51" s="35">
-        <f>IF(OR(F51="",O51="Fechada",O51="Perdida"),0,IF(O51="Fechamento vencido",3,IF(O51="Parada",2,1))*1E+13+MIN(N(N51),500)*1E+10+MIN(ROUND(N(E51),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F51="",O51="Fechada",O51="Perdida"),0,IF(O51="Fechamento vencido",3,IF(O51="Parada",2,1))*1E+15+MIN(N(N51),500)*1E+12+MIN(ROUND(N(E51)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
         <v/>
       </c>
       <c r="P52" s="35">
-        <f>IF(OR(F52="",O52="Fechada",O52="Perdida"),0,IF(O52="Fechamento vencido",3,IF(O52="Parada",2,1))*1E+13+MIN(N(N52),500)*1E+10+MIN(ROUND(N(E52),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F52="",O52="Fechada",O52="Perdida"),0,IF(O52="Fechamento vencido",3,IF(O52="Parada",2,1))*1E+15+MIN(N(N52),500)*1E+12+MIN(ROUND(N(E52)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
         <v/>
       </c>
       <c r="P53" s="35">
-        <f>IF(OR(F53="",O53="Fechada",O53="Perdida"),0,IF(O53="Fechamento vencido",3,IF(O53="Parada",2,1))*1E+13+MIN(N(N53),500)*1E+10+MIN(ROUND(N(E53),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F53="",O53="Fechada",O53="Perdida"),0,IF(O53="Fechamento vencido",3,IF(O53="Parada",2,1))*1E+15+MIN(N(N53),500)*1E+12+MIN(ROUND(N(E53)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
         <v/>
       </c>
       <c r="P54" s="35">
-        <f>IF(OR(F54="",O54="Fechada",O54="Perdida"),0,IF(O54="Fechamento vencido",3,IF(O54="Parada",2,1))*1E+13+MIN(N(N54),500)*1E+10+MIN(ROUND(N(E54),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F54="",O54="Fechada",O54="Perdida"),0,IF(O54="Fechamento vencido",3,IF(O54="Parada",2,1))*1E+15+MIN(N(N54),500)*1E+12+MIN(ROUND(N(E54)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         <v/>
       </c>
       <c r="P55" s="35">
-        <f>IF(OR(F55="",O55="Fechada",O55="Perdida"),0,IF(O55="Fechamento vencido",3,IF(O55="Parada",2,1))*1E+13+MIN(N(N55),500)*1E+10+MIN(ROUND(N(E55),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F55="",O55="Fechada",O55="Perdida"),0,IF(O55="Fechamento vencido",3,IF(O55="Parada",2,1))*1E+15+MIN(N(N55),500)*1E+12+MIN(ROUND(N(E55)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
         <v/>
       </c>
       <c r="P56" s="35">
-        <f>IF(OR(F56="",O56="Fechada",O56="Perdida"),0,IF(O56="Fechamento vencido",3,IF(O56="Parada",2,1))*1E+13+MIN(N(N56),500)*1E+10+MIN(ROUND(N(E56),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F56="",O56="Fechada",O56="Perdida"),0,IF(O56="Fechamento vencido",3,IF(O56="Parada",2,1))*1E+15+MIN(N(N56),500)*1E+12+MIN(ROUND(N(E56)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
         <v/>
       </c>
       <c r="P57" s="35">
-        <f>IF(OR(F57="",O57="Fechada",O57="Perdida"),0,IF(O57="Fechamento vencido",3,IF(O57="Parada",2,1))*1E+13+MIN(N(N57),500)*1E+10+MIN(ROUND(N(E57),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F57="",O57="Fechada",O57="Perdida"),0,IF(O57="Fechamento vencido",3,IF(O57="Parada",2,1))*1E+15+MIN(N(N57),500)*1E+12+MIN(ROUND(N(E57)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
         <v/>
       </c>
       <c r="P58" s="35">
-        <f>IF(OR(F58="",O58="Fechada",O58="Perdida"),0,IF(O58="Fechamento vencido",3,IF(O58="Parada",2,1))*1E+13+MIN(N(N58),500)*1E+10+MIN(ROUND(N(E58),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F58="",O58="Fechada",O58="Perdida"),0,IF(O58="Fechamento vencido",3,IF(O58="Parada",2,1))*1E+15+MIN(N(N58),500)*1E+12+MIN(ROUND(N(E58)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="P59" s="35">
-        <f>IF(OR(F59="",O59="Fechada",O59="Perdida"),0,IF(O59="Fechamento vencido",3,IF(O59="Parada",2,1))*1E+13+MIN(N(N59),500)*1E+10+MIN(ROUND(N(E59),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F59="",O59="Fechada",O59="Perdida"),0,IF(O59="Fechamento vencido",3,IF(O59="Parada",2,1))*1E+15+MIN(N(N59),500)*1E+12+MIN(ROUND(N(E59)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
         <v/>
       </c>
       <c r="P60" s="35">
-        <f>IF(OR(F60="",O60="Fechada",O60="Perdida"),0,IF(O60="Fechamento vencido",3,IF(O60="Parada",2,1))*1E+13+MIN(N(N60),500)*1E+10+MIN(ROUND(N(E60),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F60="",O60="Fechada",O60="Perdida"),0,IF(O60="Fechamento vencido",3,IF(O60="Parada",2,1))*1E+15+MIN(N(N60),500)*1E+12+MIN(ROUND(N(E60)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4763,7 +4763,7 @@
         <v/>
       </c>
       <c r="P61" s="35">
-        <f>IF(OR(F61="",O61="Fechada",O61="Perdida"),0,IF(O61="Fechamento vencido",3,IF(O61="Parada",2,1))*1E+13+MIN(N(N61),500)*1E+10+MIN(ROUND(N(E61),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F61="",O61="Fechada",O61="Perdida"),0,IF(O61="Fechamento vencido",3,IF(O61="Parada",2,1))*1E+15+MIN(N(N61),500)*1E+12+MIN(ROUND(N(E61)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
         <v/>
       </c>
       <c r="P62" s="35">
-        <f>IF(OR(F62="",O62="Fechada",O62="Perdida"),0,IF(O62="Fechamento vencido",3,IF(O62="Parada",2,1))*1E+13+MIN(N(N62),500)*1E+10+MIN(ROUND(N(E62),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F62="",O62="Fechada",O62="Perdida"),0,IF(O62="Fechamento vencido",3,IF(O62="Parada",2,1))*1E+15+MIN(N(N62),500)*1E+12+MIN(ROUND(N(E62)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
         <v/>
       </c>
       <c r="P63" s="35">
-        <f>IF(OR(F63="",O63="Fechada",O63="Perdida"),0,IF(O63="Fechamento vencido",3,IF(O63="Parada",2,1))*1E+13+MIN(N(N63),500)*1E+10+MIN(ROUND(N(E63),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F63="",O63="Fechada",O63="Perdida"),0,IF(O63="Fechamento vencido",3,IF(O63="Parada",2,1))*1E+15+MIN(N(N63),500)*1E+12+MIN(ROUND(N(E63)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
         <v/>
       </c>
       <c r="P64" s="35">
-        <f>IF(OR(F64="",O64="Fechada",O64="Perdida"),0,IF(O64="Fechamento vencido",3,IF(O64="Parada",2,1))*1E+13+MIN(N(N64),500)*1E+10+MIN(ROUND(N(E64),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F64="",O64="Fechada",O64="Perdida"),0,IF(O64="Fechamento vencido",3,IF(O64="Parada",2,1))*1E+15+MIN(N(N64),500)*1E+12+MIN(ROUND(N(E64)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
         <v/>
       </c>
       <c r="P65" s="35">
-        <f>IF(OR(F65="",O65="Fechada",O65="Perdida"),0,IF(O65="Fechamento vencido",3,IF(O65="Parada",2,1))*1E+13+MIN(N(N65),500)*1E+10+MIN(ROUND(N(E65),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F65="",O65="Fechada",O65="Perdida"),0,IF(O65="Fechamento vencido",3,IF(O65="Parada",2,1))*1E+15+MIN(N(N65),500)*1E+12+MIN(ROUND(N(E65)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
         <v/>
       </c>
       <c r="P66" s="35">
-        <f>IF(OR(F66="",O66="Fechada",O66="Perdida"),0,IF(O66="Fechamento vencido",3,IF(O66="Parada",2,1))*1E+13+MIN(N(N66),500)*1E+10+MIN(ROUND(N(E66),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F66="",O66="Fechada",O66="Perdida"),0,IF(O66="Fechamento vencido",3,IF(O66="Parada",2,1))*1E+15+MIN(N(N66),500)*1E+12+MIN(ROUND(N(E66)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
         <v/>
       </c>
       <c r="P67" s="35">
-        <f>IF(OR(F67="",O67="Fechada",O67="Perdida"),0,IF(O67="Fechamento vencido",3,IF(O67="Parada",2,1))*1E+13+MIN(N(N67),500)*1E+10+MIN(ROUND(N(E67),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F67="",O67="Fechada",O67="Perdida"),0,IF(O67="Fechamento vencido",3,IF(O67="Parada",2,1))*1E+15+MIN(N(N67),500)*1E+12+MIN(ROUND(N(E67)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
         <v/>
       </c>
       <c r="P68" s="35">
-        <f>IF(OR(F68="",O68="Fechada",O68="Perdida"),0,IF(O68="Fechamento vencido",3,IF(O68="Parada",2,1))*1E+13+MIN(N(N68),500)*1E+10+MIN(ROUND(N(E68),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F68="",O68="Fechada",O68="Perdida"),0,IF(O68="Fechamento vencido",3,IF(O68="Parada",2,1))*1E+15+MIN(N(N68),500)*1E+12+MIN(ROUND(N(E68)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="P69" s="35">
-        <f>IF(OR(F69="",O69="Fechada",O69="Perdida"),0,IF(O69="Fechamento vencido",3,IF(O69="Parada",2,1))*1E+13+MIN(N(N69),500)*1E+10+MIN(ROUND(N(E69),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F69="",O69="Fechada",O69="Perdida"),0,IF(O69="Fechamento vencido",3,IF(O69="Parada",2,1))*1E+15+MIN(N(N69),500)*1E+12+MIN(ROUND(N(E69)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
         <v/>
       </c>
       <c r="P70" s="35">
-        <f>IF(OR(F70="",O70="Fechada",O70="Perdida"),0,IF(O70="Fechamento vencido",3,IF(O70="Parada",2,1))*1E+13+MIN(N(N70),500)*1E+10+MIN(ROUND(N(E70),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F70="",O70="Fechada",O70="Perdida"),0,IF(O70="Fechamento vencido",3,IF(O70="Parada",2,1))*1E+15+MIN(N(N70),500)*1E+12+MIN(ROUND(N(E70)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
         <v/>
       </c>
       <c r="P71" s="35">
-        <f>IF(OR(F71="",O71="Fechada",O71="Perdida"),0,IF(O71="Fechamento vencido",3,IF(O71="Parada",2,1))*1E+13+MIN(N(N71),500)*1E+10+MIN(ROUND(N(E71),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F71="",O71="Fechada",O71="Perdida"),0,IF(O71="Fechamento vencido",3,IF(O71="Parada",2,1))*1E+15+MIN(N(N71),500)*1E+12+MIN(ROUND(N(E71)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
         <v/>
       </c>
       <c r="P72" s="35">
-        <f>IF(OR(F72="",O72="Fechada",O72="Perdida"),0,IF(O72="Fechamento vencido",3,IF(O72="Parada",2,1))*1E+13+MIN(N(N72),500)*1E+10+MIN(ROUND(N(E72),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F72="",O72="Fechada",O72="Perdida"),0,IF(O72="Fechamento vencido",3,IF(O72="Parada",2,1))*1E+15+MIN(N(N72),500)*1E+12+MIN(ROUND(N(E72)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
         <v/>
       </c>
       <c r="P73" s="35">
-        <f>IF(OR(F73="",O73="Fechada",O73="Perdida"),0,IF(O73="Fechamento vencido",3,IF(O73="Parada",2,1))*1E+13+MIN(N(N73),500)*1E+10+MIN(ROUND(N(E73),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F73="",O73="Fechada",O73="Perdida"),0,IF(O73="Fechamento vencido",3,IF(O73="Parada",2,1))*1E+15+MIN(N(N73),500)*1E+12+MIN(ROUND(N(E73)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
         <v/>
       </c>
       <c r="P74" s="35">
-        <f>IF(OR(F74="",O74="Fechada",O74="Perdida"),0,IF(O74="Fechamento vencido",3,IF(O74="Parada",2,1))*1E+13+MIN(N(N74),500)*1E+10+MIN(ROUND(N(E74),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F74="",O74="Fechada",O74="Perdida"),0,IF(O74="Fechamento vencido",3,IF(O74="Parada",2,1))*1E+15+MIN(N(N74),500)*1E+12+MIN(ROUND(N(E74)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v/>
       </c>
       <c r="P75" s="35">
-        <f>IF(OR(F75="",O75="Fechada",O75="Perdida"),0,IF(O75="Fechamento vencido",3,IF(O75="Parada",2,1))*1E+13+MIN(N(N75),500)*1E+10+MIN(ROUND(N(E75),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F75="",O75="Fechada",O75="Perdida"),0,IF(O75="Fechamento vencido",3,IF(O75="Parada",2,1))*1E+15+MIN(N(N75),500)*1E+12+MIN(ROUND(N(E75)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="P76" s="35">
-        <f>IF(OR(F76="",O76="Fechada",O76="Perdida"),0,IF(O76="Fechamento vencido",3,IF(O76="Parada",2,1))*1E+13+MIN(N(N76),500)*1E+10+MIN(ROUND(N(E76),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F76="",O76="Fechada",O76="Perdida"),0,IF(O76="Fechamento vencido",3,IF(O76="Parada",2,1))*1E+15+MIN(N(N76),500)*1E+12+MIN(ROUND(N(E76)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
         <v/>
       </c>
       <c r="P77" s="35">
-        <f>IF(OR(F77="",O77="Fechada",O77="Perdida"),0,IF(O77="Fechamento vencido",3,IF(O77="Parada",2,1))*1E+13+MIN(N(N77),500)*1E+10+MIN(ROUND(N(E77),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F77="",O77="Fechada",O77="Perdida"),0,IF(O77="Fechamento vencido",3,IF(O77="Parada",2,1))*1E+15+MIN(N(N77),500)*1E+12+MIN(ROUND(N(E77)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
         <v/>
       </c>
       <c r="P78" s="35">
-        <f>IF(OR(F78="",O78="Fechada",O78="Perdida"),0,IF(O78="Fechamento vencido",3,IF(O78="Parada",2,1))*1E+13+MIN(N(N78),500)*1E+10+MIN(ROUND(N(E78),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F78="",O78="Fechada",O78="Perdida"),0,IF(O78="Fechamento vencido",3,IF(O78="Parada",2,1))*1E+15+MIN(N(N78),500)*1E+12+MIN(ROUND(N(E78)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
         <v/>
       </c>
       <c r="P79" s="35">
-        <f>IF(OR(F79="",O79="Fechada",O79="Perdida"),0,IF(O79="Fechamento vencido",3,IF(O79="Parada",2,1))*1E+13+MIN(N(N79),500)*1E+10+MIN(ROUND(N(E79),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F79="",O79="Fechada",O79="Perdida"),0,IF(O79="Fechamento vencido",3,IF(O79="Parada",2,1))*1E+15+MIN(N(N79),500)*1E+12+MIN(ROUND(N(E79)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v/>
       </c>
       <c r="P80" s="35">
-        <f>IF(OR(F80="",O80="Fechada",O80="Perdida"),0,IF(O80="Fechamento vencido",3,IF(O80="Parada",2,1))*1E+13+MIN(N(N80),500)*1E+10+MIN(ROUND(N(E80),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F80="",O80="Fechada",O80="Perdida"),0,IF(O80="Fechamento vencido",3,IF(O80="Parada",2,1))*1E+15+MIN(N(N80),500)*1E+12+MIN(ROUND(N(E80)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
         <v/>
       </c>
       <c r="P81" s="35">
-        <f>IF(OR(F81="",O81="Fechada",O81="Perdida"),0,IF(O81="Fechamento vencido",3,IF(O81="Parada",2,1))*1E+13+MIN(N(N81),500)*1E+10+MIN(ROUND(N(E81),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F81="",O81="Fechada",O81="Perdida"),0,IF(O81="Fechamento vencido",3,IF(O81="Parada",2,1))*1E+15+MIN(N(N81),500)*1E+12+MIN(ROUND(N(E81)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
         <v/>
       </c>
       <c r="P82" s="35">
-        <f>IF(OR(F82="",O82="Fechada",O82="Perdida"),0,IF(O82="Fechamento vencido",3,IF(O82="Parada",2,1))*1E+13+MIN(N(N82),500)*1E+10+MIN(ROUND(N(E82),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F82="",O82="Fechada",O82="Perdida"),0,IF(O82="Fechamento vencido",3,IF(O82="Parada",2,1))*1E+15+MIN(N(N82),500)*1E+12+MIN(ROUND(N(E82)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
         <v/>
       </c>
       <c r="P83" s="35">
-        <f>IF(OR(F83="",O83="Fechada",O83="Perdida"),0,IF(O83="Fechamento vencido",3,IF(O83="Parada",2,1))*1E+13+MIN(N(N83),500)*1E+10+MIN(ROUND(N(E83),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F83="",O83="Fechada",O83="Perdida"),0,IF(O83="Fechamento vencido",3,IF(O83="Parada",2,1))*1E+15+MIN(N(N83),500)*1E+12+MIN(ROUND(N(E83)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
         <v/>
       </c>
       <c r="P84" s="35">
-        <f>IF(OR(F84="",O84="Fechada",O84="Perdida"),0,IF(O84="Fechamento vencido",3,IF(O84="Parada",2,1))*1E+13+MIN(N(N84),500)*1E+10+MIN(ROUND(N(E84),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F84="",O84="Fechada",O84="Perdida"),0,IF(O84="Fechamento vencido",3,IF(O84="Parada",2,1))*1E+15+MIN(N(N84),500)*1E+12+MIN(ROUND(N(E84)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="P85" s="35">
-        <f>IF(OR(F85="",O85="Fechada",O85="Perdida"),0,IF(O85="Fechamento vencido",3,IF(O85="Parada",2,1))*1E+13+MIN(N(N85),500)*1E+10+MIN(ROUND(N(E85),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F85="",O85="Fechada",O85="Perdida"),0,IF(O85="Fechamento vencido",3,IF(O85="Parada",2,1))*1E+15+MIN(N(N85),500)*1E+12+MIN(ROUND(N(E85)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
         <v/>
       </c>
       <c r="P86" s="35">
-        <f>IF(OR(F86="",O86="Fechada",O86="Perdida"),0,IF(O86="Fechamento vencido",3,IF(O86="Parada",2,1))*1E+13+MIN(N(N86),500)*1E+10+MIN(ROUND(N(E86),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F86="",O86="Fechada",O86="Perdida"),0,IF(O86="Fechamento vencido",3,IF(O86="Parada",2,1))*1E+15+MIN(N(N86),500)*1E+12+MIN(ROUND(N(E86)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="P87" s="35">
-        <f>IF(OR(F87="",O87="Fechada",O87="Perdida"),0,IF(O87="Fechamento vencido",3,IF(O87="Parada",2,1))*1E+13+MIN(N(N87),500)*1E+10+MIN(ROUND(N(E87),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F87="",O87="Fechada",O87="Perdida"),0,IF(O87="Fechamento vencido",3,IF(O87="Parada",2,1))*1E+15+MIN(N(N87),500)*1E+12+MIN(ROUND(N(E87)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
         <v/>
       </c>
       <c r="P88" s="35">
-        <f>IF(OR(F88="",O88="Fechada",O88="Perdida"),0,IF(O88="Fechamento vencido",3,IF(O88="Parada",2,1))*1E+13+MIN(N(N88),500)*1E+10+MIN(ROUND(N(E88),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F88="",O88="Fechada",O88="Perdida"),0,IF(O88="Fechamento vencido",3,IF(O88="Parada",2,1))*1E+15+MIN(N(N88),500)*1E+12+MIN(ROUND(N(E88)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
         <v/>
       </c>
       <c r="P89" s="35">
-        <f>IF(OR(F89="",O89="Fechada",O89="Perdida"),0,IF(O89="Fechamento vencido",3,IF(O89="Parada",2,1))*1E+13+MIN(N(N89),500)*1E+10+MIN(ROUND(N(E89),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F89="",O89="Fechada",O89="Perdida"),0,IF(O89="Fechamento vencido",3,IF(O89="Parada",2,1))*1E+15+MIN(N(N89),500)*1E+12+MIN(ROUND(N(E89)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
         <v/>
       </c>
       <c r="P90" s="35">
-        <f>IF(OR(F90="",O90="Fechada",O90="Perdida"),0,IF(O90="Fechamento vencido",3,IF(O90="Parada",2,1))*1E+13+MIN(N(N90),500)*1E+10+MIN(ROUND(N(E90),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F90="",O90="Fechada",O90="Perdida"),0,IF(O90="Fechamento vencido",3,IF(O90="Parada",2,1))*1E+15+MIN(N(N90),500)*1E+12+MIN(ROUND(N(E90)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
         <v/>
       </c>
       <c r="P91" s="35">
-        <f>IF(OR(F91="",O91="Fechada",O91="Perdida"),0,IF(O91="Fechamento vencido",3,IF(O91="Parada",2,1))*1E+13+MIN(N(N91),500)*1E+10+MIN(ROUND(N(E91),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F91="",O91="Fechada",O91="Perdida"),0,IF(O91="Fechamento vencido",3,IF(O91="Parada",2,1))*1E+15+MIN(N(N91),500)*1E+12+MIN(ROUND(N(E91)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
         <v/>
       </c>
       <c r="P92" s="35">
-        <f>IF(OR(F92="",O92="Fechada",O92="Perdida"),0,IF(O92="Fechamento vencido",3,IF(O92="Parada",2,1))*1E+13+MIN(N(N92),500)*1E+10+MIN(ROUND(N(E92),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F92="",O92="Fechada",O92="Perdida"),0,IF(O92="Fechamento vencido",3,IF(O92="Parada",2,1))*1E+15+MIN(N(N92),500)*1E+12+MIN(ROUND(N(E92)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
         <v/>
       </c>
       <c r="P93" s="35">
-        <f>IF(OR(F93="",O93="Fechada",O93="Perdida"),0,IF(O93="Fechamento vencido",3,IF(O93="Parada",2,1))*1E+13+MIN(N(N93),500)*1E+10+MIN(ROUND(N(E93),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F93="",O93="Fechada",O93="Perdida"),0,IF(O93="Fechamento vencido",3,IF(O93="Parada",2,1))*1E+15+MIN(N(N93),500)*1E+12+MIN(ROUND(N(E93)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="P94" s="35">
-        <f>IF(OR(F94="",O94="Fechada",O94="Perdida"),0,IF(O94="Fechamento vencido",3,IF(O94="Parada",2,1))*1E+13+MIN(N(N94),500)*1E+10+MIN(ROUND(N(E94),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F94="",O94="Fechada",O94="Perdida"),0,IF(O94="Fechamento vencido",3,IF(O94="Parada",2,1))*1E+15+MIN(N(N94),500)*1E+12+MIN(ROUND(N(E94)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
         <v/>
       </c>
       <c r="P95" s="35">
-        <f>IF(OR(F95="",O95="Fechada",O95="Perdida"),0,IF(O95="Fechamento vencido",3,IF(O95="Parada",2,1))*1E+13+MIN(N(N95),500)*1E+10+MIN(ROUND(N(E95),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F95="",O95="Fechada",O95="Perdida"),0,IF(O95="Fechamento vencido",3,IF(O95="Parada",2,1))*1E+15+MIN(N(N95),500)*1E+12+MIN(ROUND(N(E95)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
         <v/>
       </c>
       <c r="P96" s="35">
-        <f>IF(OR(F96="",O96="Fechada",O96="Perdida"),0,IF(O96="Fechamento vencido",3,IF(O96="Parada",2,1))*1E+13+MIN(N(N96),500)*1E+10+MIN(ROUND(N(E96),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F96="",O96="Fechada",O96="Perdida"),0,IF(O96="Fechamento vencido",3,IF(O96="Parada",2,1))*1E+15+MIN(N(N96),500)*1E+12+MIN(ROUND(N(E96)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
         <v/>
       </c>
       <c r="P97" s="35">
-        <f>IF(OR(F97="",O97="Fechada",O97="Perdida"),0,IF(O97="Fechamento vencido",3,IF(O97="Parada",2,1))*1E+13+MIN(N(N97),500)*1E+10+MIN(ROUND(N(E97),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F97="",O97="Fechada",O97="Perdida"),0,IF(O97="Fechamento vencido",3,IF(O97="Parada",2,1))*1E+15+MIN(N(N97),500)*1E+12+MIN(ROUND(N(E97)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
         <v/>
       </c>
       <c r="P98" s="35">
-        <f>IF(OR(F98="",O98="Fechada",O98="Perdida"),0,IF(O98="Fechamento vencido",3,IF(O98="Parada",2,1))*1E+13+MIN(N(N98),500)*1E+10+MIN(ROUND(N(E98),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F98="",O98="Fechada",O98="Perdida"),0,IF(O98="Fechamento vencido",3,IF(O98="Parada",2,1))*1E+15+MIN(N(N98),500)*1E+12+MIN(ROUND(N(E98)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
         <v/>
       </c>
       <c r="P99" s="35">
-        <f>IF(OR(F99="",O99="Fechada",O99="Perdida"),0,IF(O99="Fechamento vencido",3,IF(O99="Parada",2,1))*1E+13+MIN(N(N99),500)*1E+10+MIN(ROUND(N(E99),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F99="",O99="Fechada",O99="Perdida"),0,IF(O99="Fechamento vencido",3,IF(O99="Parada",2,1))*1E+15+MIN(N(N99),500)*1E+12+MIN(ROUND(N(E99)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="P100" s="35">
-        <f>IF(OR(F100="",O100="Fechada",O100="Perdida"),0,IF(O100="Fechamento vencido",3,IF(O100="Parada",2,1))*1E+13+MIN(N(N100),500)*1E+10+MIN(ROUND(N(E100),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F100="",O100="Fechada",O100="Perdida"),0,IF(O100="Fechamento vencido",3,IF(O100="Parada",2,1))*1E+15+MIN(N(N100),500)*1E+12+MIN(ROUND(N(E100)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
         <v/>
       </c>
       <c r="P101" s="35">
-        <f>IF(OR(F101="",O101="Fechada",O101="Perdida"),0,IF(O101="Fechamento vencido",3,IF(O101="Parada",2,1))*1E+13+MIN(N(N101),500)*1E+10+MIN(ROUND(N(E101),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F101="",O101="Fechada",O101="Perdida"),0,IF(O101="Fechamento vencido",3,IF(O101="Parada",2,1))*1E+15+MIN(N(N101),500)*1E+12+MIN(ROUND(N(E101)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
         <v/>
       </c>
       <c r="P102" s="35">
-        <f>IF(OR(F102="",O102="Fechada",O102="Perdida"),0,IF(O102="Fechamento vencido",3,IF(O102="Parada",2,1))*1E+13+MIN(N(N102),500)*1E+10+MIN(ROUND(N(E102),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F102="",O102="Fechada",O102="Perdida"),0,IF(O102="Fechamento vencido",3,IF(O102="Parada",2,1))*1E+15+MIN(N(N102),500)*1E+12+MIN(ROUND(N(E102)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
         <v/>
       </c>
       <c r="P103" s="35">
-        <f>IF(OR(F103="",O103="Fechada",O103="Perdida"),0,IF(O103="Fechamento vencido",3,IF(O103="Parada",2,1))*1E+13+MIN(N(N103),500)*1E+10+MIN(ROUND(N(E103),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F103="",O103="Fechada",O103="Perdida"),0,IF(O103="Fechamento vencido",3,IF(O103="Parada",2,1))*1E+15+MIN(N(N103),500)*1E+12+MIN(ROUND(N(E103)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
         <v/>
       </c>
       <c r="P104" s="35">
-        <f>IF(OR(F104="",O104="Fechada",O104="Perdida"),0,IF(O104="Fechamento vencido",3,IF(O104="Parada",2,1))*1E+13+MIN(N(N104),500)*1E+10+MIN(ROUND(N(E104),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F104="",O104="Fechada",O104="Perdida"),0,IF(O104="Fechamento vencido",3,IF(O104="Parada",2,1))*1E+15+MIN(N(N104),500)*1E+12+MIN(ROUND(N(E104)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v/>
       </c>
       <c r="P105" s="35">
-        <f>IF(OR(F105="",O105="Fechada",O105="Perdida"),0,IF(O105="Fechamento vencido",3,IF(O105="Parada",2,1))*1E+13+MIN(N(N105),500)*1E+10+MIN(ROUND(N(E105),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F105="",O105="Fechada",O105="Perdida"),0,IF(O105="Fechamento vencido",3,IF(O105="Parada",2,1))*1E+15+MIN(N(N105),500)*1E+12+MIN(ROUND(N(E105)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
         <v/>
       </c>
       <c r="P106" s="35">
-        <f>IF(OR(F106="",O106="Fechada",O106="Perdida"),0,IF(O106="Fechamento vencido",3,IF(O106="Parada",2,1))*1E+13+MIN(N(N106),500)*1E+10+MIN(ROUND(N(E106),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F106="",O106="Fechada",O106="Perdida"),0,IF(O106="Fechamento vencido",3,IF(O106="Parada",2,1))*1E+15+MIN(N(N106),500)*1E+12+MIN(ROUND(N(E106)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
         <v/>
       </c>
       <c r="P107" s="35">
-        <f>IF(OR(F107="",O107="Fechada",O107="Perdida"),0,IF(O107="Fechamento vencido",3,IF(O107="Parada",2,1))*1E+13+MIN(N(N107),500)*1E+10+MIN(ROUND(N(E107),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F107="",O107="Fechada",O107="Perdida"),0,IF(O107="Fechamento vencido",3,IF(O107="Parada",2,1))*1E+15+MIN(N(N107),500)*1E+12+MIN(ROUND(N(E107)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
         <v/>
       </c>
       <c r="P108" s="35">
-        <f>IF(OR(F108="",O108="Fechada",O108="Perdida"),0,IF(O108="Fechamento vencido",3,IF(O108="Parada",2,1))*1E+13+MIN(N(N108),500)*1E+10+MIN(ROUND(N(E108),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F108="",O108="Fechada",O108="Perdida"),0,IF(O108="Fechamento vencido",3,IF(O108="Parada",2,1))*1E+15+MIN(N(N108),500)*1E+12+MIN(ROUND(N(E108)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
         <v/>
       </c>
       <c r="P109" s="35">
-        <f>IF(OR(F109="",O109="Fechada",O109="Perdida"),0,IF(O109="Fechamento vencido",3,IF(O109="Parada",2,1))*1E+13+MIN(N(N109),500)*1E+10+MIN(ROUND(N(E109),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F109="",O109="Fechada",O109="Perdida"),0,IF(O109="Fechamento vencido",3,IF(O109="Parada",2,1))*1E+15+MIN(N(N109),500)*1E+12+MIN(ROUND(N(E109)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
         <v/>
       </c>
       <c r="P110" s="35">
-        <f>IF(OR(F110="",O110="Fechada",O110="Perdida"),0,IF(O110="Fechamento vencido",3,IF(O110="Parada",2,1))*1E+13+MIN(N(N110),500)*1E+10+MIN(ROUND(N(E110),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F110="",O110="Fechada",O110="Perdida"),0,IF(O110="Fechamento vencido",3,IF(O110="Parada",2,1))*1E+15+MIN(N(N110),500)*1E+12+MIN(ROUND(N(E110)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
         <v/>
       </c>
       <c r="P111" s="35">
-        <f>IF(OR(F111="",O111="Fechada",O111="Perdida"),0,IF(O111="Fechamento vencido",3,IF(O111="Parada",2,1))*1E+13+MIN(N(N111),500)*1E+10+MIN(ROUND(N(E111),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F111="",O111="Fechada",O111="Perdida"),0,IF(O111="Fechamento vencido",3,IF(O111="Parada",2,1))*1E+15+MIN(N(N111),500)*1E+12+MIN(ROUND(N(E111)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
         <v/>
       </c>
       <c r="P112" s="35">
-        <f>IF(OR(F112="",O112="Fechada",O112="Perdida"),0,IF(O112="Fechamento vencido",3,IF(O112="Parada",2,1))*1E+13+MIN(N(N112),500)*1E+10+MIN(ROUND(N(E112),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F112="",O112="Fechada",O112="Perdida"),0,IF(O112="Fechamento vencido",3,IF(O112="Parada",2,1))*1E+15+MIN(N(N112),500)*1E+12+MIN(ROUND(N(E112)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
         <v/>
       </c>
       <c r="P113" s="35">
-        <f>IF(OR(F113="",O113="Fechada",O113="Perdida"),0,IF(O113="Fechamento vencido",3,IF(O113="Parada",2,1))*1E+13+MIN(N(N113),500)*1E+10+MIN(ROUND(N(E113),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F113="",O113="Fechada",O113="Perdida"),0,IF(O113="Fechamento vencido",3,IF(O113="Parada",2,1))*1E+15+MIN(N(N113),500)*1E+12+MIN(ROUND(N(E113)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
         <v/>
       </c>
       <c r="P114" s="35">
-        <f>IF(OR(F114="",O114="Fechada",O114="Perdida"),0,IF(O114="Fechamento vencido",3,IF(O114="Parada",2,1))*1E+13+MIN(N(N114),500)*1E+10+MIN(ROUND(N(E114),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F114="",O114="Fechada",O114="Perdida"),0,IF(O114="Fechamento vencido",3,IF(O114="Parada",2,1))*1E+15+MIN(N(N114),500)*1E+12+MIN(ROUND(N(E114)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
         <v/>
       </c>
       <c r="P115" s="35">
-        <f>IF(OR(F115="",O115="Fechada",O115="Perdida"),0,IF(O115="Fechamento vencido",3,IF(O115="Parada",2,1))*1E+13+MIN(N(N115),500)*1E+10+MIN(ROUND(N(E115),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F115="",O115="Fechada",O115="Perdida"),0,IF(O115="Fechamento vencido",3,IF(O115="Parada",2,1))*1E+15+MIN(N(N115),500)*1E+12+MIN(ROUND(N(E115)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
         <v/>
       </c>
       <c r="P116" s="35">
-        <f>IF(OR(F116="",O116="Fechada",O116="Perdida"),0,IF(O116="Fechamento vencido",3,IF(O116="Parada",2,1))*1E+13+MIN(N(N116),500)*1E+10+MIN(ROUND(N(E116),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F116="",O116="Fechada",O116="Perdida"),0,IF(O116="Fechamento vencido",3,IF(O116="Parada",2,1))*1E+15+MIN(N(N116),500)*1E+12+MIN(ROUND(N(E116)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
         <v/>
       </c>
       <c r="P117" s="35">
-        <f>IF(OR(F117="",O117="Fechada",O117="Perdida"),0,IF(O117="Fechamento vencido",3,IF(O117="Parada",2,1))*1E+13+MIN(N(N117),500)*1E+10+MIN(ROUND(N(E117),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F117="",O117="Fechada",O117="Perdida"),0,IF(O117="Fechamento vencido",3,IF(O117="Parada",2,1))*1E+15+MIN(N(N117),500)*1E+12+MIN(ROUND(N(E117)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
         <v/>
       </c>
       <c r="P118" s="35">
-        <f>IF(OR(F118="",O118="Fechada",O118="Perdida"),0,IF(O118="Fechamento vencido",3,IF(O118="Parada",2,1))*1E+13+MIN(N(N118),500)*1E+10+MIN(ROUND(N(E118),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F118="",O118="Fechada",O118="Perdida"),0,IF(O118="Fechamento vencido",3,IF(O118="Parada",2,1))*1E+15+MIN(N(N118),500)*1E+12+MIN(ROUND(N(E118)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
         <v/>
       </c>
       <c r="P119" s="35">
-        <f>IF(OR(F119="",O119="Fechada",O119="Perdida"),0,IF(O119="Fechamento vencido",3,IF(O119="Parada",2,1))*1E+13+MIN(N(N119),500)*1E+10+MIN(ROUND(N(E119),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F119="",O119="Fechada",O119="Perdida"),0,IF(O119="Fechamento vencido",3,IF(O119="Parada",2,1))*1E+15+MIN(N(N119),500)*1E+12+MIN(ROUND(N(E119)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
         <v/>
       </c>
       <c r="P120" s="35">
-        <f>IF(OR(F120="",O120="Fechada",O120="Perdida"),0,IF(O120="Fechamento vencido",3,IF(O120="Parada",2,1))*1E+13+MIN(N(N120),500)*1E+10+MIN(ROUND(N(E120),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F120="",O120="Fechada",O120="Perdida"),0,IF(O120="Fechamento vencido",3,IF(O120="Parada",2,1))*1E+15+MIN(N(N120),500)*1E+12+MIN(ROUND(N(E120)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
         <v/>
       </c>
       <c r="P121" s="35">
-        <f>IF(OR(F121="",O121="Fechada",O121="Perdida"),0,IF(O121="Fechamento vencido",3,IF(O121="Parada",2,1))*1E+13+MIN(N(N121),500)*1E+10+MIN(ROUND(N(E121),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F121="",O121="Fechada",O121="Perdida"),0,IF(O121="Fechamento vencido",3,IF(O121="Parada",2,1))*1E+15+MIN(N(N121),500)*1E+12+MIN(ROUND(N(E121)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
         <v/>
       </c>
       <c r="P122" s="35">
-        <f>IF(OR(F122="",O122="Fechada",O122="Perdida"),0,IF(O122="Fechamento vencido",3,IF(O122="Parada",2,1))*1E+13+MIN(N(N122),500)*1E+10+MIN(ROUND(N(E122),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F122="",O122="Fechada",O122="Perdida"),0,IF(O122="Fechamento vencido",3,IF(O122="Parada",2,1))*1E+15+MIN(N(N122),500)*1E+12+MIN(ROUND(N(E122)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
         <v/>
       </c>
       <c r="P123" s="35">
-        <f>IF(OR(F123="",O123="Fechada",O123="Perdida"),0,IF(O123="Fechamento vencido",3,IF(O123="Parada",2,1))*1E+13+MIN(N(N123),500)*1E+10+MIN(ROUND(N(E123),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F123="",O123="Fechada",O123="Perdida"),0,IF(O123="Fechamento vencido",3,IF(O123="Parada",2,1))*1E+15+MIN(N(N123),500)*1E+12+MIN(ROUND(N(E123)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
         <v/>
       </c>
       <c r="P124" s="35">
-        <f>IF(OR(F124="",O124="Fechada",O124="Perdida"),0,IF(O124="Fechamento vencido",3,IF(O124="Parada",2,1))*1E+13+MIN(N(N124),500)*1E+10+MIN(ROUND(N(E124),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F124="",O124="Fechada",O124="Perdida"),0,IF(O124="Fechamento vencido",3,IF(O124="Parada",2,1))*1E+15+MIN(N(N124),500)*1E+12+MIN(ROUND(N(E124)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
         <v/>
       </c>
       <c r="P125" s="35">
-        <f>IF(OR(F125="",O125="Fechada",O125="Perdida"),0,IF(O125="Fechamento vencido",3,IF(O125="Parada",2,1))*1E+13+MIN(N(N125),500)*1E+10+MIN(ROUND(N(E125),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F125="",O125="Fechada",O125="Perdida"),0,IF(O125="Fechamento vencido",3,IF(O125="Parada",2,1))*1E+15+MIN(N(N125),500)*1E+12+MIN(ROUND(N(E125)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
         <v/>
       </c>
       <c r="P126" s="35">
-        <f>IF(OR(F126="",O126="Fechada",O126="Perdida"),0,IF(O126="Fechamento vencido",3,IF(O126="Parada",2,1))*1E+13+MIN(N(N126),500)*1E+10+MIN(ROUND(N(E126),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F126="",O126="Fechada",O126="Perdida"),0,IF(O126="Fechamento vencido",3,IF(O126="Parada",2,1))*1E+15+MIN(N(N126),500)*1E+12+MIN(ROUND(N(E126)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
         <v/>
       </c>
       <c r="P127" s="35">
-        <f>IF(OR(F127="",O127="Fechada",O127="Perdida"),0,IF(O127="Fechamento vencido",3,IF(O127="Parada",2,1))*1E+13+MIN(N(N127),500)*1E+10+MIN(ROUND(N(E127),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F127="",O127="Fechada",O127="Perdida"),0,IF(O127="Fechamento vencido",3,IF(O127="Parada",2,1))*1E+15+MIN(N(N127),500)*1E+12+MIN(ROUND(N(E127)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v/>
       </c>
       <c r="P128" s="35">
-        <f>IF(OR(F128="",O128="Fechada",O128="Perdida"),0,IF(O128="Fechamento vencido",3,IF(O128="Parada",2,1))*1E+13+MIN(N(N128),500)*1E+10+MIN(ROUND(N(E128),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F128="",O128="Fechada",O128="Perdida"),0,IF(O128="Fechamento vencido",3,IF(O128="Parada",2,1))*1E+15+MIN(N(N128),500)*1E+12+MIN(ROUND(N(E128)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
         <v/>
       </c>
       <c r="P129" s="35">
-        <f>IF(OR(F129="",O129="Fechada",O129="Perdida"),0,IF(O129="Fechamento vencido",3,IF(O129="Parada",2,1))*1E+13+MIN(N(N129),500)*1E+10+MIN(ROUND(N(E129),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F129="",O129="Fechada",O129="Perdida"),0,IF(O129="Fechamento vencido",3,IF(O129="Parada",2,1))*1E+15+MIN(N(N129),500)*1E+12+MIN(ROUND(N(E129)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
         <v/>
       </c>
       <c r="P130" s="35">
-        <f>IF(OR(F130="",O130="Fechada",O130="Perdida"),0,IF(O130="Fechamento vencido",3,IF(O130="Parada",2,1))*1E+13+MIN(N(N130),500)*1E+10+MIN(ROUND(N(E130),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F130="",O130="Fechada",O130="Perdida"),0,IF(O130="Fechamento vencido",3,IF(O130="Parada",2,1))*1E+15+MIN(N(N130),500)*1E+12+MIN(ROUND(N(E130)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
         <v/>
       </c>
       <c r="P131" s="35">
-        <f>IF(OR(F131="",O131="Fechada",O131="Perdida"),0,IF(O131="Fechamento vencido",3,IF(O131="Parada",2,1))*1E+13+MIN(N(N131),500)*1E+10+MIN(ROUND(N(E131),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F131="",O131="Fechada",O131="Perdida"),0,IF(O131="Fechamento vencido",3,IF(O131="Parada",2,1))*1E+15+MIN(N(N131),500)*1E+12+MIN(ROUND(N(E131)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
         <v/>
       </c>
       <c r="P132" s="35">
-        <f>IF(OR(F132="",O132="Fechada",O132="Perdida"),0,IF(O132="Fechamento vencido",3,IF(O132="Parada",2,1))*1E+13+MIN(N(N132),500)*1E+10+MIN(ROUND(N(E132),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F132="",O132="Fechada",O132="Perdida"),0,IF(O132="Fechamento vencido",3,IF(O132="Parada",2,1))*1E+15+MIN(N(N132),500)*1E+12+MIN(ROUND(N(E132)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
         <v/>
       </c>
       <c r="P133" s="35">
-        <f>IF(OR(F133="",O133="Fechada",O133="Perdida"),0,IF(O133="Fechamento vencido",3,IF(O133="Parada",2,1))*1E+13+MIN(N(N133),500)*1E+10+MIN(ROUND(N(E133),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F133="",O133="Fechada",O133="Perdida"),0,IF(O133="Fechamento vencido",3,IF(O133="Parada",2,1))*1E+15+MIN(N(N133),500)*1E+12+MIN(ROUND(N(E133)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
         <v/>
       </c>
       <c r="P134" s="35">
-        <f>IF(OR(F134="",O134="Fechada",O134="Perdida"),0,IF(O134="Fechamento vencido",3,IF(O134="Parada",2,1))*1E+13+MIN(N(N134),500)*1E+10+MIN(ROUND(N(E134),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F134="",O134="Fechada",O134="Perdida"),0,IF(O134="Fechamento vencido",3,IF(O134="Parada",2,1))*1E+15+MIN(N(N134),500)*1E+12+MIN(ROUND(N(E134)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
         <v/>
       </c>
       <c r="P135" s="35">
-        <f>IF(OR(F135="",O135="Fechada",O135="Perdida"),0,IF(O135="Fechamento vencido",3,IF(O135="Parada",2,1))*1E+13+MIN(N(N135),500)*1E+10+MIN(ROUND(N(E135),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F135="",O135="Fechada",O135="Perdida"),0,IF(O135="Fechamento vencido",3,IF(O135="Parada",2,1))*1E+15+MIN(N(N135),500)*1E+12+MIN(ROUND(N(E135)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
         <v/>
       </c>
       <c r="P136" s="35">
-        <f>IF(OR(F136="",O136="Fechada",O136="Perdida"),0,IF(O136="Fechamento vencido",3,IF(O136="Parada",2,1))*1E+13+MIN(N(N136),500)*1E+10+MIN(ROUND(N(E136),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F136="",O136="Fechada",O136="Perdida"),0,IF(O136="Fechamento vencido",3,IF(O136="Parada",2,1))*1E+15+MIN(N(N136),500)*1E+12+MIN(ROUND(N(E136)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         <v/>
       </c>
       <c r="P137" s="35">
-        <f>IF(OR(F137="",O137="Fechada",O137="Perdida"),0,IF(O137="Fechamento vencido",3,IF(O137="Parada",2,1))*1E+13+MIN(N(N137),500)*1E+10+MIN(ROUND(N(E137),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F137="",O137="Fechada",O137="Perdida"),0,IF(O137="Fechamento vencido",3,IF(O137="Parada",2,1))*1E+15+MIN(N(N137),500)*1E+12+MIN(ROUND(N(E137)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
         <v/>
       </c>
       <c r="P138" s="35">
-        <f>IF(OR(F138="",O138="Fechada",O138="Perdida"),0,IF(O138="Fechamento vencido",3,IF(O138="Parada",2,1))*1E+13+MIN(N(N138),500)*1E+10+MIN(ROUND(N(E138),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F138="",O138="Fechada",O138="Perdida"),0,IF(O138="Fechamento vencido",3,IF(O138="Parada",2,1))*1E+15+MIN(N(N138),500)*1E+12+MIN(ROUND(N(E138)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
         <v/>
       </c>
       <c r="P139" s="35">
-        <f>IF(OR(F139="",O139="Fechada",O139="Perdida"),0,IF(O139="Fechamento vencido",3,IF(O139="Parada",2,1))*1E+13+MIN(N(N139),500)*1E+10+MIN(ROUND(N(E139),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F139="",O139="Fechada",O139="Perdida"),0,IF(O139="Fechamento vencido",3,IF(O139="Parada",2,1))*1E+15+MIN(N(N139),500)*1E+12+MIN(ROUND(N(E139)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
         <v/>
       </c>
       <c r="P140" s="35">
-        <f>IF(OR(F140="",O140="Fechada",O140="Perdida"),0,IF(O140="Fechamento vencido",3,IF(O140="Parada",2,1))*1E+13+MIN(N(N140),500)*1E+10+MIN(ROUND(N(E140),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F140="",O140="Fechada",O140="Perdida"),0,IF(O140="Fechamento vencido",3,IF(O140="Parada",2,1))*1E+15+MIN(N(N140),500)*1E+12+MIN(ROUND(N(E140)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
         <v/>
       </c>
       <c r="P141" s="35">
-        <f>IF(OR(F141="",O141="Fechada",O141="Perdida"),0,IF(O141="Fechamento vencido",3,IF(O141="Parada",2,1))*1E+13+MIN(N(N141),500)*1E+10+MIN(ROUND(N(E141),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F141="",O141="Fechada",O141="Perdida"),0,IF(O141="Fechamento vencido",3,IF(O141="Parada",2,1))*1E+15+MIN(N(N141),500)*1E+12+MIN(ROUND(N(E141)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
         <v/>
       </c>
       <c r="P142" s="35">
-        <f>IF(OR(F142="",O142="Fechada",O142="Perdida"),0,IF(O142="Fechamento vencido",3,IF(O142="Parada",2,1))*1E+13+MIN(N(N142),500)*1E+10+MIN(ROUND(N(E142),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F142="",O142="Fechada",O142="Perdida"),0,IF(O142="Fechamento vencido",3,IF(O142="Parada",2,1))*1E+15+MIN(N(N142),500)*1E+12+MIN(ROUND(N(E142)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
         <v/>
       </c>
       <c r="P143" s="35">
-        <f>IF(OR(F143="",O143="Fechada",O143="Perdida"),0,IF(O143="Fechamento vencido",3,IF(O143="Parada",2,1))*1E+13+MIN(N(N143),500)*1E+10+MIN(ROUND(N(E143),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F143="",O143="Fechada",O143="Perdida"),0,IF(O143="Fechamento vencido",3,IF(O143="Parada",2,1))*1E+15+MIN(N(N143),500)*1E+12+MIN(ROUND(N(E143)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="P144" s="35">
-        <f>IF(OR(F144="",O144="Fechada",O144="Perdida"),0,IF(O144="Fechamento vencido",3,IF(O144="Parada",2,1))*1E+13+MIN(N(N144),500)*1E+10+MIN(ROUND(N(E144),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F144="",O144="Fechada",O144="Perdida"),0,IF(O144="Fechamento vencido",3,IF(O144="Parada",2,1))*1E+15+MIN(N(N144),500)*1E+12+MIN(ROUND(N(E144)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
         <v/>
       </c>
       <c r="P145" s="35">
-        <f>IF(OR(F145="",O145="Fechada",O145="Perdida"),0,IF(O145="Fechamento vencido",3,IF(O145="Parada",2,1))*1E+13+MIN(N(N145),500)*1E+10+MIN(ROUND(N(E145),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F145="",O145="Fechada",O145="Perdida"),0,IF(O145="Fechamento vencido",3,IF(O145="Parada",2,1))*1E+15+MIN(N(N145),500)*1E+12+MIN(ROUND(N(E145)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         <v/>
       </c>
       <c r="P146" s="35">
-        <f>IF(OR(F146="",O146="Fechada",O146="Perdida"),0,IF(O146="Fechamento vencido",3,IF(O146="Parada",2,1))*1E+13+MIN(N(N146),500)*1E+10+MIN(ROUND(N(E146),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F146="",O146="Fechada",O146="Perdida"),0,IF(O146="Fechamento vencido",3,IF(O146="Parada",2,1))*1E+15+MIN(N(N146),500)*1E+12+MIN(ROUND(N(E146)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
         <v/>
       </c>
       <c r="P147" s="35">
-        <f>IF(OR(F147="",O147="Fechada",O147="Perdida"),0,IF(O147="Fechamento vencido",3,IF(O147="Parada",2,1))*1E+13+MIN(N(N147),500)*1E+10+MIN(ROUND(N(E147),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F147="",O147="Fechada",O147="Perdida"),0,IF(O147="Fechamento vencido",3,IF(O147="Parada",2,1))*1E+15+MIN(N(N147),500)*1E+12+MIN(ROUND(N(E147)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
         <v/>
       </c>
       <c r="P148" s="35">
-        <f>IF(OR(F148="",O148="Fechada",O148="Perdida"),0,IF(O148="Fechamento vencido",3,IF(O148="Parada",2,1))*1E+13+MIN(N(N148),500)*1E+10+MIN(ROUND(N(E148),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F148="",O148="Fechada",O148="Perdida"),0,IF(O148="Fechamento vencido",3,IF(O148="Parada",2,1))*1E+15+MIN(N(N148),500)*1E+12+MIN(ROUND(N(E148)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
         <v/>
       </c>
       <c r="P149" s="35">
-        <f>IF(OR(F149="",O149="Fechada",O149="Perdida"),0,IF(O149="Fechamento vencido",3,IF(O149="Parada",2,1))*1E+13+MIN(N(N149),500)*1E+10+MIN(ROUND(N(E149),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F149="",O149="Fechada",O149="Perdida"),0,IF(O149="Fechamento vencido",3,IF(O149="Parada",2,1))*1E+15+MIN(N(N149),500)*1E+12+MIN(ROUND(N(E149)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
         <v/>
       </c>
       <c r="P150" s="35">
-        <f>IF(OR(F150="",O150="Fechada",O150="Perdida"),0,IF(O150="Fechamento vencido",3,IF(O150="Parada",2,1))*1E+13+MIN(N(N150),500)*1E+10+MIN(ROUND(N(E150),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F150="",O150="Fechada",O150="Perdida"),0,IF(O150="Fechamento vencido",3,IF(O150="Parada",2,1))*1E+15+MIN(N(N150),500)*1E+12+MIN(ROUND(N(E150)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v/>
       </c>
       <c r="P151" s="35">
-        <f>IF(OR(F151="",O151="Fechada",O151="Perdida"),0,IF(O151="Fechamento vencido",3,IF(O151="Parada",2,1))*1E+13+MIN(N(N151),500)*1E+10+MIN(ROUND(N(E151),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F151="",O151="Fechada",O151="Perdida"),0,IF(O151="Fechamento vencido",3,IF(O151="Parada",2,1))*1E+15+MIN(N(N151),500)*1E+12+MIN(ROUND(N(E151)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
         <v/>
       </c>
       <c r="P152" s="35">
-        <f>IF(OR(F152="",O152="Fechada",O152="Perdida"),0,IF(O152="Fechamento vencido",3,IF(O152="Parada",2,1))*1E+13+MIN(N(N152),500)*1E+10+MIN(ROUND(N(E152),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F152="",O152="Fechada",O152="Perdida"),0,IF(O152="Fechamento vencido",3,IF(O152="Parada",2,1))*1E+15+MIN(N(N152),500)*1E+12+MIN(ROUND(N(E152)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="P153" s="35">
-        <f>IF(OR(F153="",O153="Fechada",O153="Perdida"),0,IF(O153="Fechamento vencido",3,IF(O153="Parada",2,1))*1E+13+MIN(N(N153),500)*1E+10+MIN(ROUND(N(E153),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F153="",O153="Fechada",O153="Perdida"),0,IF(O153="Fechamento vencido",3,IF(O153="Parada",2,1))*1E+15+MIN(N(N153),500)*1E+12+MIN(ROUND(N(E153)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
         <v/>
       </c>
       <c r="P154" s="35">
-        <f>IF(OR(F154="",O154="Fechada",O154="Perdida"),0,IF(O154="Fechamento vencido",3,IF(O154="Parada",2,1))*1E+13+MIN(N(N154),500)*1E+10+MIN(ROUND(N(E154),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F154="",O154="Fechada",O154="Perdida"),0,IF(O154="Fechamento vencido",3,IF(O154="Parada",2,1))*1E+15+MIN(N(N154),500)*1E+12+MIN(ROUND(N(E154)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
         <v/>
       </c>
       <c r="P155" s="35">
-        <f>IF(OR(F155="",O155="Fechada",O155="Perdida"),0,IF(O155="Fechamento vencido",3,IF(O155="Parada",2,1))*1E+13+MIN(N(N155),500)*1E+10+MIN(ROUND(N(E155),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F155="",O155="Fechada",O155="Perdida"),0,IF(O155="Fechamento vencido",3,IF(O155="Parada",2,1))*1E+15+MIN(N(N155),500)*1E+12+MIN(ROUND(N(E155)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
         <v/>
       </c>
       <c r="P156" s="35">
-        <f>IF(OR(F156="",O156="Fechada",O156="Perdida"),0,IF(O156="Fechamento vencido",3,IF(O156="Parada",2,1))*1E+13+MIN(N(N156),500)*1E+10+MIN(ROUND(N(E156),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F156="",O156="Fechada",O156="Perdida"),0,IF(O156="Fechamento vencido",3,IF(O156="Parada",2,1))*1E+15+MIN(N(N156),500)*1E+12+MIN(ROUND(N(E156)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         <v/>
       </c>
       <c r="P157" s="35">
-        <f>IF(OR(F157="",O157="Fechada",O157="Perdida"),0,IF(O157="Fechamento vencido",3,IF(O157="Parada",2,1))*1E+13+MIN(N(N157),500)*1E+10+MIN(ROUND(N(E157),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F157="",O157="Fechada",O157="Perdida"),0,IF(O157="Fechamento vencido",3,IF(O157="Parada",2,1))*1E+15+MIN(N(N157),500)*1E+12+MIN(ROUND(N(E157)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
         <v/>
       </c>
       <c r="P158" s="35">
-        <f>IF(OR(F158="",O158="Fechada",O158="Perdida"),0,IF(O158="Fechamento vencido",3,IF(O158="Parada",2,1))*1E+13+MIN(N(N158),500)*1E+10+MIN(ROUND(N(E158),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F158="",O158="Fechada",O158="Perdida"),0,IF(O158="Fechamento vencido",3,IF(O158="Parada",2,1))*1E+15+MIN(N(N158),500)*1E+12+MIN(ROUND(N(E158)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
         <v/>
       </c>
       <c r="P159" s="35">
-        <f>IF(OR(F159="",O159="Fechada",O159="Perdida"),0,IF(O159="Fechamento vencido",3,IF(O159="Parada",2,1))*1E+13+MIN(N(N159),500)*1E+10+MIN(ROUND(N(E159),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F159="",O159="Fechada",O159="Perdida"),0,IF(O159="Fechamento vencido",3,IF(O159="Parada",2,1))*1E+15+MIN(N(N159),500)*1E+12+MIN(ROUND(N(E159)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         <v/>
       </c>
       <c r="P160" s="35">
-        <f>IF(OR(F160="",O160="Fechada",O160="Perdida"),0,IF(O160="Fechamento vencido",3,IF(O160="Parada",2,1))*1E+13+MIN(N(N160),500)*1E+10+MIN(ROUND(N(E160),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F160="",O160="Fechada",O160="Perdida"),0,IF(O160="Fechamento vencido",3,IF(O160="Parada",2,1))*1E+15+MIN(N(N160),500)*1E+12+MIN(ROUND(N(E160)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
         <v/>
       </c>
       <c r="P161" s="35">
-        <f>IF(OR(F161="",O161="Fechada",O161="Perdida"),0,IF(O161="Fechamento vencido",3,IF(O161="Parada",2,1))*1E+13+MIN(N(N161),500)*1E+10+MIN(ROUND(N(E161),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F161="",O161="Fechada",O161="Perdida"),0,IF(O161="Fechamento vencido",3,IF(O161="Parada",2,1))*1E+15+MIN(N(N161),500)*1E+12+MIN(ROUND(N(E161)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
         <v/>
       </c>
       <c r="P162" s="35">
-        <f>IF(OR(F162="",O162="Fechada",O162="Perdida"),0,IF(O162="Fechamento vencido",3,IF(O162="Parada",2,1))*1E+13+MIN(N(N162),500)*1E+10+MIN(ROUND(N(E162),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F162="",O162="Fechada",O162="Perdida"),0,IF(O162="Fechamento vencido",3,IF(O162="Parada",2,1))*1E+15+MIN(N(N162),500)*1E+12+MIN(ROUND(N(E162)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         <v/>
       </c>
       <c r="P163" s="35">
-        <f>IF(OR(F163="",O163="Fechada",O163="Perdida"),0,IF(O163="Fechamento vencido",3,IF(O163="Parada",2,1))*1E+13+MIN(N(N163),500)*1E+10+MIN(ROUND(N(E163),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F163="",O163="Fechada",O163="Perdida"),0,IF(O163="Fechamento vencido",3,IF(O163="Parada",2,1))*1E+15+MIN(N(N163),500)*1E+12+MIN(ROUND(N(E163)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
         <v/>
       </c>
       <c r="P164" s="35">
-        <f>IF(OR(F164="",O164="Fechada",O164="Perdida"),0,IF(O164="Fechamento vencido",3,IF(O164="Parada",2,1))*1E+13+MIN(N(N164),500)*1E+10+MIN(ROUND(N(E164),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F164="",O164="Fechada",O164="Perdida"),0,IF(O164="Fechamento vencido",3,IF(O164="Parada",2,1))*1E+15+MIN(N(N164),500)*1E+12+MIN(ROUND(N(E164)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
         <v/>
       </c>
       <c r="P165" s="35">
-        <f>IF(OR(F165="",O165="Fechada",O165="Perdida"),0,IF(O165="Fechamento vencido",3,IF(O165="Parada",2,1))*1E+13+MIN(N(N165),500)*1E+10+MIN(ROUND(N(E165),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F165="",O165="Fechada",O165="Perdida"),0,IF(O165="Fechamento vencido",3,IF(O165="Parada",2,1))*1E+15+MIN(N(N165),500)*1E+12+MIN(ROUND(N(E165)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
         <v/>
       </c>
       <c r="P166" s="35">
-        <f>IF(OR(F166="",O166="Fechada",O166="Perdida"),0,IF(O166="Fechamento vencido",3,IF(O166="Parada",2,1))*1E+13+MIN(N(N166),500)*1E+10+MIN(ROUND(N(E166),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F166="",O166="Fechada",O166="Perdida"),0,IF(O166="Fechamento vencido",3,IF(O166="Parada",2,1))*1E+15+MIN(N(N166),500)*1E+12+MIN(ROUND(N(E166)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
         <v/>
       </c>
       <c r="P167" s="35">
-        <f>IF(OR(F167="",O167="Fechada",O167="Perdida"),0,IF(O167="Fechamento vencido",3,IF(O167="Parada",2,1))*1E+13+MIN(N(N167),500)*1E+10+MIN(ROUND(N(E167),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F167="",O167="Fechada",O167="Perdida"),0,IF(O167="Fechamento vencido",3,IF(O167="Parada",2,1))*1E+15+MIN(N(N167),500)*1E+12+MIN(ROUND(N(E167)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
         <v/>
       </c>
       <c r="P168" s="35">
-        <f>IF(OR(F168="",O168="Fechada",O168="Perdida"),0,IF(O168="Fechamento vencido",3,IF(O168="Parada",2,1))*1E+13+MIN(N(N168),500)*1E+10+MIN(ROUND(N(E168),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F168="",O168="Fechada",O168="Perdida"),0,IF(O168="Fechamento vencido",3,IF(O168="Parada",2,1))*1E+15+MIN(N(N168),500)*1E+12+MIN(ROUND(N(E168)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
         <v/>
       </c>
       <c r="P169" s="35">
-        <f>IF(OR(F169="",O169="Fechada",O169="Perdida"),0,IF(O169="Fechamento vencido",3,IF(O169="Parada",2,1))*1E+13+MIN(N(N169),500)*1E+10+MIN(ROUND(N(E169),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F169="",O169="Fechada",O169="Perdida"),0,IF(O169="Fechamento vencido",3,IF(O169="Parada",2,1))*1E+15+MIN(N(N169),500)*1E+12+MIN(ROUND(N(E169)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
         <v/>
       </c>
       <c r="P170" s="35">
-        <f>IF(OR(F170="",O170="Fechada",O170="Perdida"),0,IF(O170="Fechamento vencido",3,IF(O170="Parada",2,1))*1E+13+MIN(N(N170),500)*1E+10+MIN(ROUND(N(E170),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F170="",O170="Fechada",O170="Perdida"),0,IF(O170="Fechamento vencido",3,IF(O170="Parada",2,1))*1E+15+MIN(N(N170),500)*1E+12+MIN(ROUND(N(E170)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
         <v/>
       </c>
       <c r="P171" s="35">
-        <f>IF(OR(F171="",O171="Fechada",O171="Perdida"),0,IF(O171="Fechamento vencido",3,IF(O171="Parada",2,1))*1E+13+MIN(N(N171),500)*1E+10+MIN(ROUND(N(E171),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F171="",O171="Fechada",O171="Perdida"),0,IF(O171="Fechamento vencido",3,IF(O171="Parada",2,1))*1E+15+MIN(N(N171),500)*1E+12+MIN(ROUND(N(E171)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
         <v/>
       </c>
       <c r="P172" s="35">
-        <f>IF(OR(F172="",O172="Fechada",O172="Perdida"),0,IF(O172="Fechamento vencido",3,IF(O172="Parada",2,1))*1E+13+MIN(N(N172),500)*1E+10+MIN(ROUND(N(E172),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F172="",O172="Fechada",O172="Perdida"),0,IF(O172="Fechamento vencido",3,IF(O172="Parada",2,1))*1E+15+MIN(N(N172),500)*1E+12+MIN(ROUND(N(E172)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
         <v/>
       </c>
       <c r="P173" s="35">
-        <f>IF(OR(F173="",O173="Fechada",O173="Perdida"),0,IF(O173="Fechamento vencido",3,IF(O173="Parada",2,1))*1E+13+MIN(N(N173),500)*1E+10+MIN(ROUND(N(E173),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F173="",O173="Fechada",O173="Perdida"),0,IF(O173="Fechamento vencido",3,IF(O173="Parada",2,1))*1E+15+MIN(N(N173),500)*1E+12+MIN(ROUND(N(E173)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v/>
       </c>
       <c r="P174" s="35">
-        <f>IF(OR(F174="",O174="Fechada",O174="Perdida"),0,IF(O174="Fechamento vencido",3,IF(O174="Parada",2,1))*1E+13+MIN(N(N174),500)*1E+10+MIN(ROUND(N(E174),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F174="",O174="Fechada",O174="Perdida"),0,IF(O174="Fechamento vencido",3,IF(O174="Parada",2,1))*1E+15+MIN(N(N174),500)*1E+12+MIN(ROUND(N(E174)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
         <v/>
       </c>
       <c r="P175" s="35">
-        <f>IF(OR(F175="",O175="Fechada",O175="Perdida"),0,IF(O175="Fechamento vencido",3,IF(O175="Parada",2,1))*1E+13+MIN(N(N175),500)*1E+10+MIN(ROUND(N(E175),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F175="",O175="Fechada",O175="Perdida"),0,IF(O175="Fechamento vencido",3,IF(O175="Parada",2,1))*1E+15+MIN(N(N175),500)*1E+12+MIN(ROUND(N(E175)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
         <v/>
       </c>
       <c r="P176" s="35">
-        <f>IF(OR(F176="",O176="Fechada",O176="Perdida"),0,IF(O176="Fechamento vencido",3,IF(O176="Parada",2,1))*1E+13+MIN(N(N176),500)*1E+10+MIN(ROUND(N(E176),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F176="",O176="Fechada",O176="Perdida"),0,IF(O176="Fechamento vencido",3,IF(O176="Parada",2,1))*1E+15+MIN(N(N176),500)*1E+12+MIN(ROUND(N(E176)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
         <v/>
       </c>
       <c r="P177" s="35">
-        <f>IF(OR(F177="",O177="Fechada",O177="Perdida"),0,IF(O177="Fechamento vencido",3,IF(O177="Parada",2,1))*1E+13+MIN(N(N177),500)*1E+10+MIN(ROUND(N(E177),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F177="",O177="Fechada",O177="Perdida"),0,IF(O177="Fechamento vencido",3,IF(O177="Parada",2,1))*1E+15+MIN(N(N177),500)*1E+12+MIN(ROUND(N(E177)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8624,7 +8624,7 @@
         <v/>
       </c>
       <c r="P178" s="35">
-        <f>IF(OR(F178="",O178="Fechada",O178="Perdida"),0,IF(O178="Fechamento vencido",3,IF(O178="Parada",2,1))*1E+13+MIN(N(N178),500)*1E+10+MIN(ROUND(N(E178),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F178="",O178="Fechada",O178="Perdida"),0,IF(O178="Fechamento vencido",3,IF(O178="Parada",2,1))*1E+15+MIN(N(N178),500)*1E+12+MIN(ROUND(N(E178)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
         <v/>
       </c>
       <c r="P179" s="35">
-        <f>IF(OR(F179="",O179="Fechada",O179="Perdida"),0,IF(O179="Fechamento vencido",3,IF(O179="Parada",2,1))*1E+13+MIN(N(N179),500)*1E+10+MIN(ROUND(N(E179),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F179="",O179="Fechada",O179="Perdida"),0,IF(O179="Fechamento vencido",3,IF(O179="Parada",2,1))*1E+15+MIN(N(N179),500)*1E+12+MIN(ROUND(N(E179)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
         <v/>
       </c>
       <c r="P180" s="35">
-        <f>IF(OR(F180="",O180="Fechada",O180="Perdida"),0,IF(O180="Fechamento vencido",3,IF(O180="Parada",2,1))*1E+13+MIN(N(N180),500)*1E+10+MIN(ROUND(N(E180),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F180="",O180="Fechada",O180="Perdida"),0,IF(O180="Fechamento vencido",3,IF(O180="Parada",2,1))*1E+15+MIN(N(N180),500)*1E+12+MIN(ROUND(N(E180)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
         <v/>
       </c>
       <c r="P181" s="35">
-        <f>IF(OR(F181="",O181="Fechada",O181="Perdida"),0,IF(O181="Fechamento vencido",3,IF(O181="Parada",2,1))*1E+13+MIN(N(N181),500)*1E+10+MIN(ROUND(N(E181),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F181="",O181="Fechada",O181="Perdida"),0,IF(O181="Fechamento vencido",3,IF(O181="Parada",2,1))*1E+15+MIN(N(N181),500)*1E+12+MIN(ROUND(N(E181)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
         <v/>
       </c>
       <c r="P182" s="35">
-        <f>IF(OR(F182="",O182="Fechada",O182="Perdida"),0,IF(O182="Fechamento vencido",3,IF(O182="Parada",2,1))*1E+13+MIN(N(N182),500)*1E+10+MIN(ROUND(N(E182),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F182="",O182="Fechada",O182="Perdida"),0,IF(O182="Fechamento vencido",3,IF(O182="Parada",2,1))*1E+15+MIN(N(N182),500)*1E+12+MIN(ROUND(N(E182)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
         <v/>
       </c>
       <c r="P183" s="35">
-        <f>IF(OR(F183="",O183="Fechada",O183="Perdida"),0,IF(O183="Fechamento vencido",3,IF(O183="Parada",2,1))*1E+13+MIN(N(N183),500)*1E+10+MIN(ROUND(N(E183),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F183="",O183="Fechada",O183="Perdida"),0,IF(O183="Fechamento vencido",3,IF(O183="Parada",2,1))*1E+15+MIN(N(N183),500)*1E+12+MIN(ROUND(N(E183)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
         <v/>
       </c>
       <c r="P184" s="35">
-        <f>IF(OR(F184="",O184="Fechada",O184="Perdida"),0,IF(O184="Fechamento vencido",3,IF(O184="Parada",2,1))*1E+13+MIN(N(N184),500)*1E+10+MIN(ROUND(N(E184),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F184="",O184="Fechada",O184="Perdida"),0,IF(O184="Fechamento vencido",3,IF(O184="Parada",2,1))*1E+15+MIN(N(N184),500)*1E+12+MIN(ROUND(N(E184)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
         <v/>
       </c>
       <c r="P185" s="35">
-        <f>IF(OR(F185="",O185="Fechada",O185="Perdida"),0,IF(O185="Fechamento vencido",3,IF(O185="Parada",2,1))*1E+13+MIN(N(N185),500)*1E+10+MIN(ROUND(N(E185),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F185="",O185="Fechada",O185="Perdida"),0,IF(O185="Fechamento vencido",3,IF(O185="Parada",2,1))*1E+15+MIN(N(N185),500)*1E+12+MIN(ROUND(N(E185)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
         <v/>
       </c>
       <c r="P186" s="35">
-        <f>IF(OR(F186="",O186="Fechada",O186="Perdida"),0,IF(O186="Fechamento vencido",3,IF(O186="Parada",2,1))*1E+13+MIN(N(N186),500)*1E+10+MIN(ROUND(N(E186),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F186="",O186="Fechada",O186="Perdida"),0,IF(O186="Fechamento vencido",3,IF(O186="Parada",2,1))*1E+15+MIN(N(N186),500)*1E+12+MIN(ROUND(N(E186)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
         <v/>
       </c>
       <c r="P187" s="35">
-        <f>IF(OR(F187="",O187="Fechada",O187="Perdida"),0,IF(O187="Fechamento vencido",3,IF(O187="Parada",2,1))*1E+13+MIN(N(N187),500)*1E+10+MIN(ROUND(N(E187),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F187="",O187="Fechada",O187="Perdida"),0,IF(O187="Fechamento vencido",3,IF(O187="Parada",2,1))*1E+15+MIN(N(N187),500)*1E+12+MIN(ROUND(N(E187)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
         <v/>
       </c>
       <c r="P188" s="35">
-        <f>IF(OR(F188="",O188="Fechada",O188="Perdida"),0,IF(O188="Fechamento vencido",3,IF(O188="Parada",2,1))*1E+13+MIN(N(N188),500)*1E+10+MIN(ROUND(N(E188),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F188="",O188="Fechada",O188="Perdida"),0,IF(O188="Fechamento vencido",3,IF(O188="Parada",2,1))*1E+15+MIN(N(N188),500)*1E+12+MIN(ROUND(N(E188)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
         <v/>
       </c>
       <c r="P189" s="35">
-        <f>IF(OR(F189="",O189="Fechada",O189="Perdida"),0,IF(O189="Fechamento vencido",3,IF(O189="Parada",2,1))*1E+13+MIN(N(N189),500)*1E+10+MIN(ROUND(N(E189),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F189="",O189="Fechada",O189="Perdida"),0,IF(O189="Fechamento vencido",3,IF(O189="Parada",2,1))*1E+15+MIN(N(N189),500)*1E+12+MIN(ROUND(N(E189)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
         <v/>
       </c>
       <c r="P190" s="35">
-        <f>IF(OR(F190="",O190="Fechada",O190="Perdida"),0,IF(O190="Fechamento vencido",3,IF(O190="Parada",2,1))*1E+13+MIN(N(N190),500)*1E+10+MIN(ROUND(N(E190),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F190="",O190="Fechada",O190="Perdida"),0,IF(O190="Fechamento vencido",3,IF(O190="Parada",2,1))*1E+15+MIN(N(N190),500)*1E+12+MIN(ROUND(N(E190)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
         <v/>
       </c>
       <c r="P191" s="35">
-        <f>IF(OR(F191="",O191="Fechada",O191="Perdida"),0,IF(O191="Fechamento vencido",3,IF(O191="Parada",2,1))*1E+13+MIN(N(N191),500)*1E+10+MIN(ROUND(N(E191),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F191="",O191="Fechada",O191="Perdida"),0,IF(O191="Fechamento vencido",3,IF(O191="Parada",2,1))*1E+15+MIN(N(N191),500)*1E+12+MIN(ROUND(N(E191)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="P192" s="35">
-        <f>IF(OR(F192="",O192="Fechada",O192="Perdida"),0,IF(O192="Fechamento vencido",3,IF(O192="Parada",2,1))*1E+13+MIN(N(N192),500)*1E+10+MIN(ROUND(N(E192),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F192="",O192="Fechada",O192="Perdida"),0,IF(O192="Fechamento vencido",3,IF(O192="Parada",2,1))*1E+15+MIN(N(N192),500)*1E+12+MIN(ROUND(N(E192)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
         <v/>
       </c>
       <c r="P193" s="35">
-        <f>IF(OR(F193="",O193="Fechada",O193="Perdida"),0,IF(O193="Fechamento vencido",3,IF(O193="Parada",2,1))*1E+13+MIN(N(N193),500)*1E+10+MIN(ROUND(N(E193),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F193="",O193="Fechada",O193="Perdida"),0,IF(O193="Fechamento vencido",3,IF(O193="Parada",2,1))*1E+15+MIN(N(N193),500)*1E+12+MIN(ROUND(N(E193)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
         <v/>
       </c>
       <c r="P194" s="35">
-        <f>IF(OR(F194="",O194="Fechada",O194="Perdida"),0,IF(O194="Fechamento vencido",3,IF(O194="Parada",2,1))*1E+13+MIN(N(N194),500)*1E+10+MIN(ROUND(N(E194),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F194="",O194="Fechada",O194="Perdida"),0,IF(O194="Fechamento vencido",3,IF(O194="Parada",2,1))*1E+15+MIN(N(N194),500)*1E+12+MIN(ROUND(N(E194)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
         <v/>
       </c>
       <c r="P195" s="35">
-        <f>IF(OR(F195="",O195="Fechada",O195="Perdida"),0,IF(O195="Fechamento vencido",3,IF(O195="Parada",2,1))*1E+13+MIN(N(N195),500)*1E+10+MIN(ROUND(N(E195),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F195="",O195="Fechada",O195="Perdida"),0,IF(O195="Fechamento vencido",3,IF(O195="Parada",2,1))*1E+15+MIN(N(N195),500)*1E+12+MIN(ROUND(N(E195)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
         <v/>
       </c>
       <c r="P196" s="35">
-        <f>IF(OR(F196="",O196="Fechada",O196="Perdida"),0,IF(O196="Fechamento vencido",3,IF(O196="Parada",2,1))*1E+13+MIN(N(N196),500)*1E+10+MIN(ROUND(N(E196),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F196="",O196="Fechada",O196="Perdida"),0,IF(O196="Fechamento vencido",3,IF(O196="Parada",2,1))*1E+15+MIN(N(N196),500)*1E+12+MIN(ROUND(N(E196)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v/>
       </c>
       <c r="P197" s="35">
-        <f>IF(OR(F197="",O197="Fechada",O197="Perdida"),0,IF(O197="Fechamento vencido",3,IF(O197="Parada",2,1))*1E+13+MIN(N(N197),500)*1E+10+MIN(ROUND(N(E197),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F197="",O197="Fechada",O197="Perdida"),0,IF(O197="Fechamento vencido",3,IF(O197="Parada",2,1))*1E+15+MIN(N(N197),500)*1E+12+MIN(ROUND(N(E197)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
         <v/>
       </c>
       <c r="P198" s="35">
-        <f>IF(OR(F198="",O198="Fechada",O198="Perdida"),0,IF(O198="Fechamento vencido",3,IF(O198="Parada",2,1))*1E+13+MIN(N(N198),500)*1E+10+MIN(ROUND(N(E198),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F198="",O198="Fechada",O198="Perdida"),0,IF(O198="Fechamento vencido",3,IF(O198="Parada",2,1))*1E+15+MIN(N(N198),500)*1E+12+MIN(ROUND(N(E198)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v/>
       </c>
       <c r="P199" s="35">
-        <f>IF(OR(F199="",O199="Fechada",O199="Perdida"),0,IF(O199="Fechamento vencido",3,IF(O199="Parada",2,1))*1E+13+MIN(N(N199),500)*1E+10+MIN(ROUND(N(E199),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F199="",O199="Fechada",O199="Perdida"),0,IF(O199="Fechamento vencido",3,IF(O199="Parada",2,1))*1E+15+MIN(N(N199),500)*1E+12+MIN(ROUND(N(E199)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
         <v/>
       </c>
       <c r="P200" s="35">
-        <f>IF(OR(F200="",O200="Fechada",O200="Perdida"),0,IF(O200="Fechamento vencido",3,IF(O200="Parada",2,1))*1E+13+MIN(N(N200),500)*1E+10+MIN(ROUND(N(E200),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F200="",O200="Fechada",O200="Perdida"),0,IF(O200="Fechamento vencido",3,IF(O200="Parada",2,1))*1E+15+MIN(N(N200),500)*1E+12+MIN(ROUND(N(E200)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
         <v/>
       </c>
       <c r="P201" s="35">
-        <f>IF(OR(F201="",O201="Fechada",O201="Perdida"),0,IF(O201="Fechamento vencido",3,IF(O201="Parada",2,1))*1E+13+MIN(N(N201),500)*1E+10+MIN(ROUND(N(E201),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F201="",O201="Fechada",O201="Perdida"),0,IF(O201="Fechamento vencido",3,IF(O201="Parada",2,1))*1E+15+MIN(N(N201),500)*1E+12+MIN(ROUND(N(E201)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
         <v/>
       </c>
       <c r="P202" s="35">
-        <f>IF(OR(F202="",O202="Fechada",O202="Perdida"),0,IF(O202="Fechamento vencido",3,IF(O202="Parada",2,1))*1E+13+MIN(N(N202),500)*1E+10+MIN(ROUND(N(E202),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F202="",O202="Fechada",O202="Perdida"),0,IF(O202="Fechamento vencido",3,IF(O202="Parada",2,1))*1E+15+MIN(N(N202),500)*1E+12+MIN(ROUND(N(E202)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="P203" s="35">
-        <f>IF(OR(F203="",O203="Fechada",O203="Perdida"),0,IF(O203="Fechamento vencido",3,IF(O203="Parada",2,1))*1E+13+MIN(N(N203),500)*1E+10+MIN(ROUND(N(E203),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F203="",O203="Fechada",O203="Perdida"),0,IF(O203="Fechamento vencido",3,IF(O203="Parada",2,1))*1E+15+MIN(N(N203),500)*1E+12+MIN(ROUND(N(E203)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
         <v/>
       </c>
       <c r="P204" s="35">
-        <f>IF(OR(F204="",O204="Fechada",O204="Perdida"),0,IF(O204="Fechamento vencido",3,IF(O204="Parada",2,1))*1E+13+MIN(N(N204),500)*1E+10+MIN(ROUND(N(E204),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F204="",O204="Fechada",O204="Perdida"),0,IF(O204="Fechamento vencido",3,IF(O204="Parada",2,1))*1E+15+MIN(N(N204),500)*1E+12+MIN(ROUND(N(E204)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
         <v/>
       </c>
       <c r="P205" s="35">
-        <f>IF(OR(F205="",O205="Fechada",O205="Perdida"),0,IF(O205="Fechamento vencido",3,IF(O205="Parada",2,1))*1E+13+MIN(N(N205),500)*1E+10+MIN(ROUND(N(E205),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F205="",O205="Fechada",O205="Perdida"),0,IF(O205="Fechamento vencido",3,IF(O205="Parada",2,1))*1E+15+MIN(N(N205),500)*1E+12+MIN(ROUND(N(E205)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="P206" s="35">
-        <f>IF(OR(F206="",O206="Fechada",O206="Perdida"),0,IF(O206="Fechamento vencido",3,IF(O206="Parada",2,1))*1E+13+MIN(N(N206),500)*1E+10+MIN(ROUND(N(E206),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F206="",O206="Fechada",O206="Perdida"),0,IF(O206="Fechamento vencido",3,IF(O206="Parada",2,1))*1E+15+MIN(N(N206),500)*1E+12+MIN(ROUND(N(E206)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
         <v/>
       </c>
       <c r="P207" s="35">
-        <f>IF(OR(F207="",O207="Fechada",O207="Perdida"),0,IF(O207="Fechamento vencido",3,IF(O207="Parada",2,1))*1E+13+MIN(N(N207),500)*1E+10+MIN(ROUND(N(E207),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F207="",O207="Fechada",O207="Perdida"),0,IF(O207="Fechamento vencido",3,IF(O207="Parada",2,1))*1E+15+MIN(N(N207),500)*1E+12+MIN(ROUND(N(E207)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
         <v/>
       </c>
       <c r="P208" s="35">
-        <f>IF(OR(F208="",O208="Fechada",O208="Perdida"),0,IF(O208="Fechamento vencido",3,IF(O208="Parada",2,1))*1E+13+MIN(N(N208),500)*1E+10+MIN(ROUND(N(E208),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F208="",O208="Fechada",O208="Perdida"),0,IF(O208="Fechamento vencido",3,IF(O208="Parada",2,1))*1E+15+MIN(N(N208),500)*1E+12+MIN(ROUND(N(E208)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
         <v/>
       </c>
       <c r="P209" s="35">
-        <f>IF(OR(F209="",O209="Fechada",O209="Perdida"),0,IF(O209="Fechamento vencido",3,IF(O209="Parada",2,1))*1E+13+MIN(N(N209),500)*1E+10+MIN(ROUND(N(E209),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F209="",O209="Fechada",O209="Perdida"),0,IF(O209="Fechamento vencido",3,IF(O209="Parada",2,1))*1E+15+MIN(N(N209),500)*1E+12+MIN(ROUND(N(E209)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9680,7 +9680,7 @@
         <v/>
       </c>
       <c r="P210" s="35">
-        <f>IF(OR(F210="",O210="Fechada",O210="Perdida"),0,IF(O210="Fechamento vencido",3,IF(O210="Parada",2,1))*1E+13+MIN(N(N210),500)*1E+10+MIN(ROUND(N(E210),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F210="",O210="Fechada",O210="Perdida"),0,IF(O210="Fechamento vencido",3,IF(O210="Parada",2,1))*1E+15+MIN(N(N210),500)*1E+12+MIN(ROUND(N(E210)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
         <v/>
       </c>
       <c r="P211" s="35">
-        <f>IF(OR(F211="",O211="Fechada",O211="Perdida"),0,IF(O211="Fechamento vencido",3,IF(O211="Parada",2,1))*1E+13+MIN(N(N211),500)*1E+10+MIN(ROUND(N(E211),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F211="",O211="Fechada",O211="Perdida"),0,IF(O211="Fechamento vencido",3,IF(O211="Parada",2,1))*1E+15+MIN(N(N211),500)*1E+12+MIN(ROUND(N(E211)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
         <v/>
       </c>
       <c r="P212" s="35">
-        <f>IF(OR(F212="",O212="Fechada",O212="Perdida"),0,IF(O212="Fechamento vencido",3,IF(O212="Parada",2,1))*1E+13+MIN(N(N212),500)*1E+10+MIN(ROUND(N(E212),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F212="",O212="Fechada",O212="Perdida"),0,IF(O212="Fechamento vencido",3,IF(O212="Parada",2,1))*1E+15+MIN(N(N212),500)*1E+12+MIN(ROUND(N(E212)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
         <v/>
       </c>
       <c r="P213" s="35">
-        <f>IF(OR(F213="",O213="Fechada",O213="Perdida"),0,IF(O213="Fechamento vencido",3,IF(O213="Parada",2,1))*1E+13+MIN(N(N213),500)*1E+10+MIN(ROUND(N(E213),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F213="",O213="Fechada",O213="Perdida"),0,IF(O213="Fechamento vencido",3,IF(O213="Parada",2,1))*1E+15+MIN(N(N213),500)*1E+12+MIN(ROUND(N(E213)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
         <v/>
       </c>
       <c r="P214" s="35">
-        <f>IF(OR(F214="",O214="Fechada",O214="Perdida"),0,IF(O214="Fechamento vencido",3,IF(O214="Parada",2,1))*1E+13+MIN(N(N214),500)*1E+10+MIN(ROUND(N(E214),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F214="",O214="Fechada",O214="Perdida"),0,IF(O214="Fechamento vencido",3,IF(O214="Parada",2,1))*1E+15+MIN(N(N214),500)*1E+12+MIN(ROUND(N(E214)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
         <v/>
       </c>
       <c r="P215" s="35">
-        <f>IF(OR(F215="",O215="Fechada",O215="Perdida"),0,IF(O215="Fechamento vencido",3,IF(O215="Parada",2,1))*1E+13+MIN(N(N215),500)*1E+10+MIN(ROUND(N(E215),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F215="",O215="Fechada",O215="Perdida"),0,IF(O215="Fechamento vencido",3,IF(O215="Parada",2,1))*1E+15+MIN(N(N215),500)*1E+12+MIN(ROUND(N(E215)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v/>
       </c>
       <c r="P216" s="35">
-        <f>IF(OR(F216="",O216="Fechada",O216="Perdida"),0,IF(O216="Fechamento vencido",3,IF(O216="Parada",2,1))*1E+13+MIN(N(N216),500)*1E+10+MIN(ROUND(N(E216),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F216="",O216="Fechada",O216="Perdida"),0,IF(O216="Fechamento vencido",3,IF(O216="Parada",2,1))*1E+15+MIN(N(N216),500)*1E+12+MIN(ROUND(N(E216)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
         <v/>
       </c>
       <c r="P217" s="35">
-        <f>IF(OR(F217="",O217="Fechada",O217="Perdida"),0,IF(O217="Fechamento vencido",3,IF(O217="Parada",2,1))*1E+13+MIN(N(N217),500)*1E+10+MIN(ROUND(N(E217),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F217="",O217="Fechada",O217="Perdida"),0,IF(O217="Fechamento vencido",3,IF(O217="Parada",2,1))*1E+15+MIN(N(N217),500)*1E+12+MIN(ROUND(N(E217)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
         <v/>
       </c>
       <c r="P218" s="35">
-        <f>IF(OR(F218="",O218="Fechada",O218="Perdida"),0,IF(O218="Fechamento vencido",3,IF(O218="Parada",2,1))*1E+13+MIN(N(N218),500)*1E+10+MIN(ROUND(N(E218),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F218="",O218="Fechada",O218="Perdida"),0,IF(O218="Fechamento vencido",3,IF(O218="Parada",2,1))*1E+15+MIN(N(N218),500)*1E+12+MIN(ROUND(N(E218)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
         <v/>
       </c>
       <c r="P219" s="35">
-        <f>IF(OR(F219="",O219="Fechada",O219="Perdida"),0,IF(O219="Fechamento vencido",3,IF(O219="Parada",2,1))*1E+13+MIN(N(N219),500)*1E+10+MIN(ROUND(N(E219),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F219="",O219="Fechada",O219="Perdida"),0,IF(O219="Fechamento vencido",3,IF(O219="Parada",2,1))*1E+15+MIN(N(N219),500)*1E+12+MIN(ROUND(N(E219)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v/>
       </c>
       <c r="P220" s="35">
-        <f>IF(OR(F220="",O220="Fechada",O220="Perdida"),0,IF(O220="Fechamento vencido",3,IF(O220="Parada",2,1))*1E+13+MIN(N(N220),500)*1E+10+MIN(ROUND(N(E220),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F220="",O220="Fechada",O220="Perdida"),0,IF(O220="Fechamento vencido",3,IF(O220="Parada",2,1))*1E+15+MIN(N(N220),500)*1E+12+MIN(ROUND(N(E220)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
         <v/>
       </c>
       <c r="P221" s="35">
-        <f>IF(OR(F221="",O221="Fechada",O221="Perdida"),0,IF(O221="Fechamento vencido",3,IF(O221="Parada",2,1))*1E+13+MIN(N(N221),500)*1E+10+MIN(ROUND(N(E221),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F221="",O221="Fechada",O221="Perdida"),0,IF(O221="Fechamento vencido",3,IF(O221="Parada",2,1))*1E+15+MIN(N(N221),500)*1E+12+MIN(ROUND(N(E221)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
         <v/>
       </c>
       <c r="P222" s="35">
-        <f>IF(OR(F222="",O222="Fechada",O222="Perdida"),0,IF(O222="Fechamento vencido",3,IF(O222="Parada",2,1))*1E+13+MIN(N(N222),500)*1E+10+MIN(ROUND(N(E222),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F222="",O222="Fechada",O222="Perdida"),0,IF(O222="Fechamento vencido",3,IF(O222="Parada",2,1))*1E+15+MIN(N(N222),500)*1E+12+MIN(ROUND(N(E222)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
         <v/>
       </c>
       <c r="P223" s="35">
-        <f>IF(OR(F223="",O223="Fechada",O223="Perdida"),0,IF(O223="Fechamento vencido",3,IF(O223="Parada",2,1))*1E+13+MIN(N(N223),500)*1E+10+MIN(ROUND(N(E223),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F223="",O223="Fechada",O223="Perdida"),0,IF(O223="Fechamento vencido",3,IF(O223="Parada",2,1))*1E+15+MIN(N(N223),500)*1E+12+MIN(ROUND(N(E223)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
         <v/>
       </c>
       <c r="P224" s="35">
-        <f>IF(OR(F224="",O224="Fechada",O224="Perdida"),0,IF(O224="Fechamento vencido",3,IF(O224="Parada",2,1))*1E+13+MIN(N(N224),500)*1E+10+MIN(ROUND(N(E224),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F224="",O224="Fechada",O224="Perdida"),0,IF(O224="Fechamento vencido",3,IF(O224="Parada",2,1))*1E+15+MIN(N(N224),500)*1E+12+MIN(ROUND(N(E224)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
         <v/>
       </c>
       <c r="P225" s="35">
-        <f>IF(OR(F225="",O225="Fechada",O225="Perdida"),0,IF(O225="Fechamento vencido",3,IF(O225="Parada",2,1))*1E+13+MIN(N(N225),500)*1E+10+MIN(ROUND(N(E225),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F225="",O225="Fechada",O225="Perdida"),0,IF(O225="Fechamento vencido",3,IF(O225="Parada",2,1))*1E+15+MIN(N(N225),500)*1E+12+MIN(ROUND(N(E225)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
         <v/>
       </c>
       <c r="P226" s="35">
-        <f>IF(OR(F226="",O226="Fechada",O226="Perdida"),0,IF(O226="Fechamento vencido",3,IF(O226="Parada",2,1))*1E+13+MIN(N(N226),500)*1E+10+MIN(ROUND(N(E226),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F226="",O226="Fechada",O226="Perdida"),0,IF(O226="Fechamento vencido",3,IF(O226="Parada",2,1))*1E+15+MIN(N(N226),500)*1E+12+MIN(ROUND(N(E226)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
         <v/>
       </c>
       <c r="P227" s="35">
-        <f>IF(OR(F227="",O227="Fechada",O227="Perdida"),0,IF(O227="Fechamento vencido",3,IF(O227="Parada",2,1))*1E+13+MIN(N(N227),500)*1E+10+MIN(ROUND(N(E227),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F227="",O227="Fechada",O227="Perdida"),0,IF(O227="Fechamento vencido",3,IF(O227="Parada",2,1))*1E+15+MIN(N(N227),500)*1E+12+MIN(ROUND(N(E227)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
         <v/>
       </c>
       <c r="P228" s="35">
-        <f>IF(OR(F228="",O228="Fechada",O228="Perdida"),0,IF(O228="Fechamento vencido",3,IF(O228="Parada",2,1))*1E+13+MIN(N(N228),500)*1E+10+MIN(ROUND(N(E228),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F228="",O228="Fechada",O228="Perdida"),0,IF(O228="Fechamento vencido",3,IF(O228="Parada",2,1))*1E+15+MIN(N(N228),500)*1E+12+MIN(ROUND(N(E228)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
         <v/>
       </c>
       <c r="P229" s="35">
-        <f>IF(OR(F229="",O229="Fechada",O229="Perdida"),0,IF(O229="Fechamento vencido",3,IF(O229="Parada",2,1))*1E+13+MIN(N(N229),500)*1E+10+MIN(ROUND(N(E229),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F229="",O229="Fechada",O229="Perdida"),0,IF(O229="Fechamento vencido",3,IF(O229="Parada",2,1))*1E+15+MIN(N(N229),500)*1E+12+MIN(ROUND(N(E229)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
         <v/>
       </c>
       <c r="P230" s="35">
-        <f>IF(OR(F230="",O230="Fechada",O230="Perdida"),0,IF(O230="Fechamento vencido",3,IF(O230="Parada",2,1))*1E+13+MIN(N(N230),500)*1E+10+MIN(ROUND(N(E230),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F230="",O230="Fechada",O230="Perdida"),0,IF(O230="Fechamento vencido",3,IF(O230="Parada",2,1))*1E+15+MIN(N(N230),500)*1E+12+MIN(ROUND(N(E230)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
         <v/>
       </c>
       <c r="P231" s="35">
-        <f>IF(OR(F231="",O231="Fechada",O231="Perdida"),0,IF(O231="Fechamento vencido",3,IF(O231="Parada",2,1))*1E+13+MIN(N(N231),500)*1E+10+MIN(ROUND(N(E231),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F231="",O231="Fechada",O231="Perdida"),0,IF(O231="Fechamento vencido",3,IF(O231="Parada",2,1))*1E+15+MIN(N(N231),500)*1E+12+MIN(ROUND(N(E231)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
         <v/>
       </c>
       <c r="P232" s="35">
-        <f>IF(OR(F232="",O232="Fechada",O232="Perdida"),0,IF(O232="Fechamento vencido",3,IF(O232="Parada",2,1))*1E+13+MIN(N(N232),500)*1E+10+MIN(ROUND(N(E232),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F232="",O232="Fechada",O232="Perdida"),0,IF(O232="Fechamento vencido",3,IF(O232="Parada",2,1))*1E+15+MIN(N(N232),500)*1E+12+MIN(ROUND(N(E232)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
         <v/>
       </c>
       <c r="P233" s="35">
-        <f>IF(OR(F233="",O233="Fechada",O233="Perdida"),0,IF(O233="Fechamento vencido",3,IF(O233="Parada",2,1))*1E+13+MIN(N(N233),500)*1E+10+MIN(ROUND(N(E233),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F233="",O233="Fechada",O233="Perdida"),0,IF(O233="Fechamento vencido",3,IF(O233="Parada",2,1))*1E+15+MIN(N(N233),500)*1E+12+MIN(ROUND(N(E233)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
         <v/>
       </c>
       <c r="P234" s="35">
-        <f>IF(OR(F234="",O234="Fechada",O234="Perdida"),0,IF(O234="Fechamento vencido",3,IF(O234="Parada",2,1))*1E+13+MIN(N(N234),500)*1E+10+MIN(ROUND(N(E234),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F234="",O234="Fechada",O234="Perdida"),0,IF(O234="Fechamento vencido",3,IF(O234="Parada",2,1))*1E+15+MIN(N(N234),500)*1E+12+MIN(ROUND(N(E234)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
         <v/>
       </c>
       <c r="P235" s="35">
-        <f>IF(OR(F235="",O235="Fechada",O235="Perdida"),0,IF(O235="Fechamento vencido",3,IF(O235="Parada",2,1))*1E+13+MIN(N(N235),500)*1E+10+MIN(ROUND(N(E235),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F235="",O235="Fechada",O235="Perdida"),0,IF(O235="Fechamento vencido",3,IF(O235="Parada",2,1))*1E+15+MIN(N(N235),500)*1E+12+MIN(ROUND(N(E235)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
         <v/>
       </c>
       <c r="P236" s="35">
-        <f>IF(OR(F236="",O236="Fechada",O236="Perdida"),0,IF(O236="Fechamento vencido",3,IF(O236="Parada",2,1))*1E+13+MIN(N(N236),500)*1E+10+MIN(ROUND(N(E236),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F236="",O236="Fechada",O236="Perdida"),0,IF(O236="Fechamento vencido",3,IF(O236="Parada",2,1))*1E+15+MIN(N(N236),500)*1E+12+MIN(ROUND(N(E236)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
         <v/>
       </c>
       <c r="P237" s="35">
-        <f>IF(OR(F237="",O237="Fechada",O237="Perdida"),0,IF(O237="Fechamento vencido",3,IF(O237="Parada",2,1))*1E+13+MIN(N(N237),500)*1E+10+MIN(ROUND(N(E237),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F237="",O237="Fechada",O237="Perdida"),0,IF(O237="Fechamento vencido",3,IF(O237="Parada",2,1))*1E+15+MIN(N(N237),500)*1E+12+MIN(ROUND(N(E237)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
         <v/>
       </c>
       <c r="P238" s="35">
-        <f>IF(OR(F238="",O238="Fechada",O238="Perdida"),0,IF(O238="Fechamento vencido",3,IF(O238="Parada",2,1))*1E+13+MIN(N(N238),500)*1E+10+MIN(ROUND(N(E238),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F238="",O238="Fechada",O238="Perdida"),0,IF(O238="Fechamento vencido",3,IF(O238="Parada",2,1))*1E+15+MIN(N(N238),500)*1E+12+MIN(ROUND(N(E238)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10637,7 +10637,7 @@
         <v/>
       </c>
       <c r="P239" s="35">
-        <f>IF(OR(F239="",O239="Fechada",O239="Perdida"),0,IF(O239="Fechamento vencido",3,IF(O239="Parada",2,1))*1E+13+MIN(N(N239),500)*1E+10+MIN(ROUND(N(E239),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F239="",O239="Fechada",O239="Perdida"),0,IF(O239="Fechamento vencido",3,IF(O239="Parada",2,1))*1E+15+MIN(N(N239),500)*1E+12+MIN(ROUND(N(E239)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
         <v/>
       </c>
       <c r="P240" s="35">
-        <f>IF(OR(F240="",O240="Fechada",O240="Perdida"),0,IF(O240="Fechamento vencido",3,IF(O240="Parada",2,1))*1E+13+MIN(N(N240),500)*1E+10+MIN(ROUND(N(E240),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F240="",O240="Fechada",O240="Perdida"),0,IF(O240="Fechamento vencido",3,IF(O240="Parada",2,1))*1E+15+MIN(N(N240),500)*1E+12+MIN(ROUND(N(E240)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
         <v/>
       </c>
       <c r="P241" s="35">
-        <f>IF(OR(F241="",O241="Fechada",O241="Perdida"),0,IF(O241="Fechamento vencido",3,IF(O241="Parada",2,1))*1E+13+MIN(N(N241),500)*1E+10+MIN(ROUND(N(E241),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F241="",O241="Fechada",O241="Perdida"),0,IF(O241="Fechamento vencido",3,IF(O241="Parada",2,1))*1E+15+MIN(N(N241),500)*1E+12+MIN(ROUND(N(E241)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
         <v/>
       </c>
       <c r="P242" s="35">
-        <f>IF(OR(F242="",O242="Fechada",O242="Perdida"),0,IF(O242="Fechamento vencido",3,IF(O242="Parada",2,1))*1E+13+MIN(N(N242),500)*1E+10+MIN(ROUND(N(E242),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F242="",O242="Fechada",O242="Perdida"),0,IF(O242="Fechamento vencido",3,IF(O242="Parada",2,1))*1E+15+MIN(N(N242),500)*1E+12+MIN(ROUND(N(E242)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
         <v/>
       </c>
       <c r="P243" s="35">
-        <f>IF(OR(F243="",O243="Fechada",O243="Perdida"),0,IF(O243="Fechamento vencido",3,IF(O243="Parada",2,1))*1E+13+MIN(N(N243),500)*1E+10+MIN(ROUND(N(E243),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F243="",O243="Fechada",O243="Perdida"),0,IF(O243="Fechamento vencido",3,IF(O243="Parada",2,1))*1E+15+MIN(N(N243),500)*1E+12+MIN(ROUND(N(E243)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
         <v/>
       </c>
       <c r="P244" s="35">
-        <f>IF(OR(F244="",O244="Fechada",O244="Perdida"),0,IF(O244="Fechamento vencido",3,IF(O244="Parada",2,1))*1E+13+MIN(N(N244),500)*1E+10+MIN(ROUND(N(E244),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F244="",O244="Fechada",O244="Perdida"),0,IF(O244="Fechamento vencido",3,IF(O244="Parada",2,1))*1E+15+MIN(N(N244),500)*1E+12+MIN(ROUND(N(E244)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10835,7 +10835,7 @@
         <v/>
       </c>
       <c r="P245" s="35">
-        <f>IF(OR(F245="",O245="Fechada",O245="Perdida"),0,IF(O245="Fechamento vencido",3,IF(O245="Parada",2,1))*1E+13+MIN(N(N245),500)*1E+10+MIN(ROUND(N(E245),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F245="",O245="Fechada",O245="Perdida"),0,IF(O245="Fechamento vencido",3,IF(O245="Parada",2,1))*1E+15+MIN(N(N245),500)*1E+12+MIN(ROUND(N(E245)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
         <v/>
       </c>
       <c r="P246" s="35">
-        <f>IF(OR(F246="",O246="Fechada",O246="Perdida"),0,IF(O246="Fechamento vencido",3,IF(O246="Parada",2,1))*1E+13+MIN(N(N246),500)*1E+10+MIN(ROUND(N(E246),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F246="",O246="Fechada",O246="Perdida"),0,IF(O246="Fechamento vencido",3,IF(O246="Parada",2,1))*1E+15+MIN(N(N246),500)*1E+12+MIN(ROUND(N(E246)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
         <v/>
       </c>
       <c r="P247" s="35">
-        <f>IF(OR(F247="",O247="Fechada",O247="Perdida"),0,IF(O247="Fechamento vencido",3,IF(O247="Parada",2,1))*1E+13+MIN(N(N247),500)*1E+10+MIN(ROUND(N(E247),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F247="",O247="Fechada",O247="Perdida"),0,IF(O247="Fechamento vencido",3,IF(O247="Parada",2,1))*1E+15+MIN(N(N247),500)*1E+12+MIN(ROUND(N(E247)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
         <v/>
       </c>
       <c r="P248" s="35">
-        <f>IF(OR(F248="",O248="Fechada",O248="Perdida"),0,IF(O248="Fechamento vencido",3,IF(O248="Parada",2,1))*1E+13+MIN(N(N248),500)*1E+10+MIN(ROUND(N(E248),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F248="",O248="Fechada",O248="Perdida"),0,IF(O248="Fechamento vencido",3,IF(O248="Parada",2,1))*1E+15+MIN(N(N248),500)*1E+12+MIN(ROUND(N(E248)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
         <v/>
       </c>
       <c r="P249" s="35">
-        <f>IF(OR(F249="",O249="Fechada",O249="Perdida"),0,IF(O249="Fechamento vencido",3,IF(O249="Parada",2,1))*1E+13+MIN(N(N249),500)*1E+10+MIN(ROUND(N(E249),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F249="",O249="Fechada",O249="Perdida"),0,IF(O249="Fechamento vencido",3,IF(O249="Parada",2,1))*1E+15+MIN(N(N249),500)*1E+12+MIN(ROUND(N(E249)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
         <v/>
       </c>
       <c r="P250" s="35">
-        <f>IF(OR(F250="",O250="Fechada",O250="Perdida"),0,IF(O250="Fechamento vencido",3,IF(O250="Parada",2,1))*1E+13+MIN(N(N250),500)*1E+10+MIN(ROUND(N(E250),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F250="",O250="Fechada",O250="Perdida"),0,IF(O250="Fechamento vencido",3,IF(O250="Parada",2,1))*1E+15+MIN(N(N250),500)*1E+12+MIN(ROUND(N(E250)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11033,7 +11033,7 @@
         <v/>
       </c>
       <c r="P251" s="35">
-        <f>IF(OR(F251="",O251="Fechada",O251="Perdida"),0,IF(O251="Fechamento vencido",3,IF(O251="Parada",2,1))*1E+13+MIN(N(N251),500)*1E+10+MIN(ROUND(N(E251),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F251="",O251="Fechada",O251="Perdida"),0,IF(O251="Fechamento vencido",3,IF(O251="Parada",2,1))*1E+15+MIN(N(N251),500)*1E+12+MIN(ROUND(N(E251)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
         <v/>
       </c>
       <c r="P252" s="35">
-        <f>IF(OR(F252="",O252="Fechada",O252="Perdida"),0,IF(O252="Fechamento vencido",3,IF(O252="Parada",2,1))*1E+13+MIN(N(N252),500)*1E+10+MIN(ROUND(N(E252),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F252="",O252="Fechada",O252="Perdida"),0,IF(O252="Fechamento vencido",3,IF(O252="Parada",2,1))*1E+15+MIN(N(N252),500)*1E+12+MIN(ROUND(N(E252)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
         <v/>
       </c>
       <c r="P253" s="35">
-        <f>IF(OR(F253="",O253="Fechada",O253="Perdida"),0,IF(O253="Fechamento vencido",3,IF(O253="Parada",2,1))*1E+13+MIN(N(N253),500)*1E+10+MIN(ROUND(N(E253),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F253="",O253="Fechada",O253="Perdida"),0,IF(O253="Fechamento vencido",3,IF(O253="Parada",2,1))*1E+15+MIN(N(N253),500)*1E+12+MIN(ROUND(N(E253)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
         <v/>
       </c>
       <c r="P254" s="35">
-        <f>IF(OR(F254="",O254="Fechada",O254="Perdida"),0,IF(O254="Fechamento vencido",3,IF(O254="Parada",2,1))*1E+13+MIN(N(N254),500)*1E+10+MIN(ROUND(N(E254),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F254="",O254="Fechada",O254="Perdida"),0,IF(O254="Fechamento vencido",3,IF(O254="Parada",2,1))*1E+15+MIN(N(N254),500)*1E+12+MIN(ROUND(N(E254)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11165,7 +11165,7 @@
         <v/>
       </c>
       <c r="P255" s="35">
-        <f>IF(OR(F255="",O255="Fechada",O255="Perdida"),0,IF(O255="Fechamento vencido",3,IF(O255="Parada",2,1))*1E+13+MIN(N(N255),500)*1E+10+MIN(ROUND(N(E255),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F255="",O255="Fechada",O255="Perdida"),0,IF(O255="Fechamento vencido",3,IF(O255="Parada",2,1))*1E+15+MIN(N(N255),500)*1E+12+MIN(ROUND(N(E255)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
         <v/>
       </c>
       <c r="P256" s="35">
-        <f>IF(OR(F256="",O256="Fechada",O256="Perdida"),0,IF(O256="Fechamento vencido",3,IF(O256="Parada",2,1))*1E+13+MIN(N(N256),500)*1E+10+MIN(ROUND(N(E256),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F256="",O256="Fechada",O256="Perdida"),0,IF(O256="Fechamento vencido",3,IF(O256="Parada",2,1))*1E+15+MIN(N(N256),500)*1E+12+MIN(ROUND(N(E256)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11231,7 +11231,7 @@
         <v/>
       </c>
       <c r="P257" s="35">
-        <f>IF(OR(F257="",O257="Fechada",O257="Perdida"),0,IF(O257="Fechamento vencido",3,IF(O257="Parada",2,1))*1E+13+MIN(N(N257),500)*1E+10+MIN(ROUND(N(E257),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F257="",O257="Fechada",O257="Perdida"),0,IF(O257="Fechamento vencido",3,IF(O257="Parada",2,1))*1E+15+MIN(N(N257),500)*1E+12+MIN(ROUND(N(E257)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11264,7 +11264,7 @@
         <v/>
       </c>
       <c r="P258" s="35">
-        <f>IF(OR(F258="",O258="Fechada",O258="Perdida"),0,IF(O258="Fechamento vencido",3,IF(O258="Parada",2,1))*1E+13+MIN(N(N258),500)*1E+10+MIN(ROUND(N(E258),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F258="",O258="Fechada",O258="Perdida"),0,IF(O258="Fechamento vencido",3,IF(O258="Parada",2,1))*1E+15+MIN(N(N258),500)*1E+12+MIN(ROUND(N(E258)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
         <v/>
       </c>
       <c r="P259" s="35">
-        <f>IF(OR(F259="",O259="Fechada",O259="Perdida"),0,IF(O259="Fechamento vencido",3,IF(O259="Parada",2,1))*1E+13+MIN(N(N259),500)*1E+10+MIN(ROUND(N(E259),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F259="",O259="Fechada",O259="Perdida"),0,IF(O259="Fechamento vencido",3,IF(O259="Parada",2,1))*1E+15+MIN(N(N259),500)*1E+12+MIN(ROUND(N(E259)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
         <v/>
       </c>
       <c r="P260" s="35">
-        <f>IF(OR(F260="",O260="Fechada",O260="Perdida"),0,IF(O260="Fechamento vencido",3,IF(O260="Parada",2,1))*1E+13+MIN(N(N260),500)*1E+10+MIN(ROUND(N(E260),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F260="",O260="Fechada",O260="Perdida"),0,IF(O260="Fechamento vencido",3,IF(O260="Parada",2,1))*1E+15+MIN(N(N260),500)*1E+12+MIN(ROUND(N(E260)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
         <v/>
       </c>
       <c r="P261" s="35">
-        <f>IF(OR(F261="",O261="Fechada",O261="Perdida"),0,IF(O261="Fechamento vencido",3,IF(O261="Parada",2,1))*1E+13+MIN(N(N261),500)*1E+10+MIN(ROUND(N(E261),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F261="",O261="Fechada",O261="Perdida"),0,IF(O261="Fechamento vencido",3,IF(O261="Parada",2,1))*1E+15+MIN(N(N261),500)*1E+12+MIN(ROUND(N(E261)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
         <v/>
       </c>
       <c r="P262" s="35">
-        <f>IF(OR(F262="",O262="Fechada",O262="Perdida"),0,IF(O262="Fechamento vencido",3,IF(O262="Parada",2,1))*1E+13+MIN(N(N262),500)*1E+10+MIN(ROUND(N(E262),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F262="",O262="Fechada",O262="Perdida"),0,IF(O262="Fechamento vencido",3,IF(O262="Parada",2,1))*1E+15+MIN(N(N262),500)*1E+12+MIN(ROUND(N(E262)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
         <v/>
       </c>
       <c r="P263" s="35">
-        <f>IF(OR(F263="",O263="Fechada",O263="Perdida"),0,IF(O263="Fechamento vencido",3,IF(O263="Parada",2,1))*1E+13+MIN(N(N263),500)*1E+10+MIN(ROUND(N(E263),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F263="",O263="Fechada",O263="Perdida"),0,IF(O263="Fechamento vencido",3,IF(O263="Parada",2,1))*1E+15+MIN(N(N263),500)*1E+12+MIN(ROUND(N(E263)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11462,7 +11462,7 @@
         <v/>
       </c>
       <c r="P264" s="35">
-        <f>IF(OR(F264="",O264="Fechada",O264="Perdida"),0,IF(O264="Fechamento vencido",3,IF(O264="Parada",2,1))*1E+13+MIN(N(N264),500)*1E+10+MIN(ROUND(N(E264),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F264="",O264="Fechada",O264="Perdida"),0,IF(O264="Fechamento vencido",3,IF(O264="Parada",2,1))*1E+15+MIN(N(N264),500)*1E+12+MIN(ROUND(N(E264)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
         <v/>
       </c>
       <c r="P265" s="35">
-        <f>IF(OR(F265="",O265="Fechada",O265="Perdida"),0,IF(O265="Fechamento vencido",3,IF(O265="Parada",2,1))*1E+13+MIN(N(N265),500)*1E+10+MIN(ROUND(N(E265),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F265="",O265="Fechada",O265="Perdida"),0,IF(O265="Fechamento vencido",3,IF(O265="Parada",2,1))*1E+15+MIN(N(N265),500)*1E+12+MIN(ROUND(N(E265)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v/>
       </c>
       <c r="P266" s="35">
-        <f>IF(OR(F266="",O266="Fechada",O266="Perdida"),0,IF(O266="Fechamento vencido",3,IF(O266="Parada",2,1))*1E+13+MIN(N(N266),500)*1E+10+MIN(ROUND(N(E266),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F266="",O266="Fechada",O266="Perdida"),0,IF(O266="Fechamento vencido",3,IF(O266="Parada",2,1))*1E+15+MIN(N(N266),500)*1E+12+MIN(ROUND(N(E266)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
         <v/>
       </c>
       <c r="P267" s="35">
-        <f>IF(OR(F267="",O267="Fechada",O267="Perdida"),0,IF(O267="Fechamento vencido",3,IF(O267="Parada",2,1))*1E+13+MIN(N(N267),500)*1E+10+MIN(ROUND(N(E267),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F267="",O267="Fechada",O267="Perdida"),0,IF(O267="Fechamento vencido",3,IF(O267="Parada",2,1))*1E+15+MIN(N(N267),500)*1E+12+MIN(ROUND(N(E267)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
         <v/>
       </c>
       <c r="P268" s="35">
-        <f>IF(OR(F268="",O268="Fechada",O268="Perdida"),0,IF(O268="Fechamento vencido",3,IF(O268="Parada",2,1))*1E+13+MIN(N(N268),500)*1E+10+MIN(ROUND(N(E268),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F268="",O268="Fechada",O268="Perdida"),0,IF(O268="Fechamento vencido",3,IF(O268="Parada",2,1))*1E+15+MIN(N(N268),500)*1E+12+MIN(ROUND(N(E268)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
         <v/>
       </c>
       <c r="P269" s="35">
-        <f>IF(OR(F269="",O269="Fechada",O269="Perdida"),0,IF(O269="Fechamento vencido",3,IF(O269="Parada",2,1))*1E+13+MIN(N(N269),500)*1E+10+MIN(ROUND(N(E269),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F269="",O269="Fechada",O269="Perdida"),0,IF(O269="Fechamento vencido",3,IF(O269="Parada",2,1))*1E+15+MIN(N(N269),500)*1E+12+MIN(ROUND(N(E269)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
         <v/>
       </c>
       <c r="P270" s="35">
-        <f>IF(OR(F270="",O270="Fechada",O270="Perdida"),0,IF(O270="Fechamento vencido",3,IF(O270="Parada",2,1))*1E+13+MIN(N(N270),500)*1E+10+MIN(ROUND(N(E270),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F270="",O270="Fechada",O270="Perdida"),0,IF(O270="Fechamento vencido",3,IF(O270="Parada",2,1))*1E+15+MIN(N(N270),500)*1E+12+MIN(ROUND(N(E270)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
         <v/>
       </c>
       <c r="P271" s="35">
-        <f>IF(OR(F271="",O271="Fechada",O271="Perdida"),0,IF(O271="Fechamento vencido",3,IF(O271="Parada",2,1))*1E+13+MIN(N(N271),500)*1E+10+MIN(ROUND(N(E271),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F271="",O271="Fechada",O271="Perdida"),0,IF(O271="Fechamento vencido",3,IF(O271="Parada",2,1))*1E+15+MIN(N(N271),500)*1E+12+MIN(ROUND(N(E271)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
         <v/>
       </c>
       <c r="P272" s="35">
-        <f>IF(OR(F272="",O272="Fechada",O272="Perdida"),0,IF(O272="Fechamento vencido",3,IF(O272="Parada",2,1))*1E+13+MIN(N(N272),500)*1E+10+MIN(ROUND(N(E272),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F272="",O272="Fechada",O272="Perdida"),0,IF(O272="Fechamento vencido",3,IF(O272="Parada",2,1))*1E+15+MIN(N(N272),500)*1E+12+MIN(ROUND(N(E272)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
         <v/>
       </c>
       <c r="P273" s="35">
-        <f>IF(OR(F273="",O273="Fechada",O273="Perdida"),0,IF(O273="Fechamento vencido",3,IF(O273="Parada",2,1))*1E+13+MIN(N(N273),500)*1E+10+MIN(ROUND(N(E273),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F273="",O273="Fechada",O273="Perdida"),0,IF(O273="Fechamento vencido",3,IF(O273="Parada",2,1))*1E+15+MIN(N(N273),500)*1E+12+MIN(ROUND(N(E273)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11792,7 +11792,7 @@
         <v/>
       </c>
       <c r="P274" s="35">
-        <f>IF(OR(F274="",O274="Fechada",O274="Perdida"),0,IF(O274="Fechamento vencido",3,IF(O274="Parada",2,1))*1E+13+MIN(N(N274),500)*1E+10+MIN(ROUND(N(E274),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F274="",O274="Fechada",O274="Perdida"),0,IF(O274="Fechamento vencido",3,IF(O274="Parada",2,1))*1E+15+MIN(N(N274),500)*1E+12+MIN(ROUND(N(E274)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
         <v/>
       </c>
       <c r="P275" s="35">
-        <f>IF(OR(F275="",O275="Fechada",O275="Perdida"),0,IF(O275="Fechamento vencido",3,IF(O275="Parada",2,1))*1E+13+MIN(N(N275),500)*1E+10+MIN(ROUND(N(E275),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F275="",O275="Fechada",O275="Perdida"),0,IF(O275="Fechamento vencido",3,IF(O275="Parada",2,1))*1E+15+MIN(N(N275),500)*1E+12+MIN(ROUND(N(E275)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
         <v/>
       </c>
       <c r="P276" s="35">
-        <f>IF(OR(F276="",O276="Fechada",O276="Perdida"),0,IF(O276="Fechamento vencido",3,IF(O276="Parada",2,1))*1E+13+MIN(N(N276),500)*1E+10+MIN(ROUND(N(E276),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F276="",O276="Fechada",O276="Perdida"),0,IF(O276="Fechamento vencido",3,IF(O276="Parada",2,1))*1E+15+MIN(N(N276),500)*1E+12+MIN(ROUND(N(E276)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
         <v/>
       </c>
       <c r="P277" s="35">
-        <f>IF(OR(F277="",O277="Fechada",O277="Perdida"),0,IF(O277="Fechamento vencido",3,IF(O277="Parada",2,1))*1E+13+MIN(N(N277),500)*1E+10+MIN(ROUND(N(E277),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F277="",O277="Fechada",O277="Perdida"),0,IF(O277="Fechamento vencido",3,IF(O277="Parada",2,1))*1E+15+MIN(N(N277),500)*1E+12+MIN(ROUND(N(E277)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
         <v/>
       </c>
       <c r="P278" s="35">
-        <f>IF(OR(F278="",O278="Fechada",O278="Perdida"),0,IF(O278="Fechamento vencido",3,IF(O278="Parada",2,1))*1E+13+MIN(N(N278),500)*1E+10+MIN(ROUND(N(E278),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F278="",O278="Fechada",O278="Perdida"),0,IF(O278="Fechamento vencido",3,IF(O278="Parada",2,1))*1E+15+MIN(N(N278),500)*1E+12+MIN(ROUND(N(E278)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11957,7 +11957,7 @@
         <v/>
       </c>
       <c r="P279" s="35">
-        <f>IF(OR(F279="",O279="Fechada",O279="Perdida"),0,IF(O279="Fechamento vencido",3,IF(O279="Parada",2,1))*1E+13+MIN(N(N279),500)*1E+10+MIN(ROUND(N(E279),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F279="",O279="Fechada",O279="Perdida"),0,IF(O279="Fechamento vencido",3,IF(O279="Parada",2,1))*1E+15+MIN(N(N279),500)*1E+12+MIN(ROUND(N(E279)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
         <v/>
       </c>
       <c r="P280" s="35">
-        <f>IF(OR(F280="",O280="Fechada",O280="Perdida"),0,IF(O280="Fechamento vencido",3,IF(O280="Parada",2,1))*1E+13+MIN(N(N280),500)*1E+10+MIN(ROUND(N(E280),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F280="",O280="Fechada",O280="Perdida"),0,IF(O280="Fechamento vencido",3,IF(O280="Parada",2,1))*1E+15+MIN(N(N280),500)*1E+12+MIN(ROUND(N(E280)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
         <v/>
       </c>
       <c r="P281" s="35">
-        <f>IF(OR(F281="",O281="Fechada",O281="Perdida"),0,IF(O281="Fechamento vencido",3,IF(O281="Parada",2,1))*1E+13+MIN(N(N281),500)*1E+10+MIN(ROUND(N(E281),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F281="",O281="Fechada",O281="Perdida"),0,IF(O281="Fechamento vencido",3,IF(O281="Parada",2,1))*1E+15+MIN(N(N281),500)*1E+12+MIN(ROUND(N(E281)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
         <v/>
       </c>
       <c r="P282" s="35">
-        <f>IF(OR(F282="",O282="Fechada",O282="Perdida"),0,IF(O282="Fechamento vencido",3,IF(O282="Parada",2,1))*1E+13+MIN(N(N282),500)*1E+10+MIN(ROUND(N(E282),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F282="",O282="Fechada",O282="Perdida"),0,IF(O282="Fechamento vencido",3,IF(O282="Parada",2,1))*1E+15+MIN(N(N282),500)*1E+12+MIN(ROUND(N(E282)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
         <v/>
       </c>
       <c r="P283" s="35">
-        <f>IF(OR(F283="",O283="Fechada",O283="Perdida"),0,IF(O283="Fechamento vencido",3,IF(O283="Parada",2,1))*1E+13+MIN(N(N283),500)*1E+10+MIN(ROUND(N(E283),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F283="",O283="Fechada",O283="Perdida"),0,IF(O283="Fechamento vencido",3,IF(O283="Parada",2,1))*1E+15+MIN(N(N283),500)*1E+12+MIN(ROUND(N(E283)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
         <v/>
       </c>
       <c r="P284" s="35">
-        <f>IF(OR(F284="",O284="Fechada",O284="Perdida"),0,IF(O284="Fechamento vencido",3,IF(O284="Parada",2,1))*1E+13+MIN(N(N284),500)*1E+10+MIN(ROUND(N(E284),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F284="",O284="Fechada",O284="Perdida"),0,IF(O284="Fechamento vencido",3,IF(O284="Parada",2,1))*1E+15+MIN(N(N284),500)*1E+12+MIN(ROUND(N(E284)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         <v/>
       </c>
       <c r="P285" s="35">
-        <f>IF(OR(F285="",O285="Fechada",O285="Perdida"),0,IF(O285="Fechamento vencido",3,IF(O285="Parada",2,1))*1E+13+MIN(N(N285),500)*1E+10+MIN(ROUND(N(E285),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F285="",O285="Fechada",O285="Perdida"),0,IF(O285="Fechamento vencido",3,IF(O285="Parada",2,1))*1E+15+MIN(N(N285),500)*1E+12+MIN(ROUND(N(E285)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12188,7 +12188,7 @@
         <v/>
       </c>
       <c r="P286" s="35">
-        <f>IF(OR(F286="",O286="Fechada",O286="Perdida"),0,IF(O286="Fechamento vencido",3,IF(O286="Parada",2,1))*1E+13+MIN(N(N286),500)*1E+10+MIN(ROUND(N(E286),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F286="",O286="Fechada",O286="Perdida"),0,IF(O286="Fechamento vencido",3,IF(O286="Parada",2,1))*1E+15+MIN(N(N286),500)*1E+12+MIN(ROUND(N(E286)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
         <v/>
       </c>
       <c r="P287" s="35">
-        <f>IF(OR(F287="",O287="Fechada",O287="Perdida"),0,IF(O287="Fechamento vencido",3,IF(O287="Parada",2,1))*1E+13+MIN(N(N287),500)*1E+10+MIN(ROUND(N(E287),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F287="",O287="Fechada",O287="Perdida"),0,IF(O287="Fechamento vencido",3,IF(O287="Parada",2,1))*1E+15+MIN(N(N287),500)*1E+12+MIN(ROUND(N(E287)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
         <v/>
       </c>
       <c r="P288" s="35">
-        <f>IF(OR(F288="",O288="Fechada",O288="Perdida"),0,IF(O288="Fechamento vencido",3,IF(O288="Parada",2,1))*1E+13+MIN(N(N288),500)*1E+10+MIN(ROUND(N(E288),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F288="",O288="Fechada",O288="Perdida"),0,IF(O288="Fechamento vencido",3,IF(O288="Parada",2,1))*1E+15+MIN(N(N288),500)*1E+12+MIN(ROUND(N(E288)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         <v/>
       </c>
       <c r="P289" s="35">
-        <f>IF(OR(F289="",O289="Fechada",O289="Perdida"),0,IF(O289="Fechamento vencido",3,IF(O289="Parada",2,1))*1E+13+MIN(N(N289),500)*1E+10+MIN(ROUND(N(E289),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F289="",O289="Fechada",O289="Perdida"),0,IF(O289="Fechamento vencido",3,IF(O289="Parada",2,1))*1E+15+MIN(N(N289),500)*1E+12+MIN(ROUND(N(E289)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
         <v/>
       </c>
       <c r="P290" s="35">
-        <f>IF(OR(F290="",O290="Fechada",O290="Perdida"),0,IF(O290="Fechamento vencido",3,IF(O290="Parada",2,1))*1E+13+MIN(N(N290),500)*1E+10+MIN(ROUND(N(E290),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F290="",O290="Fechada",O290="Perdida"),0,IF(O290="Fechamento vencido",3,IF(O290="Parada",2,1))*1E+15+MIN(N(N290),500)*1E+12+MIN(ROUND(N(E290)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
         <v/>
       </c>
       <c r="P291" s="35">
-        <f>IF(OR(F291="",O291="Fechada",O291="Perdida"),0,IF(O291="Fechamento vencido",3,IF(O291="Parada",2,1))*1E+13+MIN(N(N291),500)*1E+10+MIN(ROUND(N(E291),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F291="",O291="Fechada",O291="Perdida"),0,IF(O291="Fechamento vencido",3,IF(O291="Parada",2,1))*1E+15+MIN(N(N291),500)*1E+12+MIN(ROUND(N(E291)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
         <v/>
       </c>
       <c r="P292" s="35">
-        <f>IF(OR(F292="",O292="Fechada",O292="Perdida"),0,IF(O292="Fechamento vencido",3,IF(O292="Parada",2,1))*1E+13+MIN(N(N292),500)*1E+10+MIN(ROUND(N(E292),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F292="",O292="Fechada",O292="Perdida"),0,IF(O292="Fechamento vencido",3,IF(O292="Parada",2,1))*1E+15+MIN(N(N292),500)*1E+12+MIN(ROUND(N(E292)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12419,7 +12419,7 @@
         <v/>
       </c>
       <c r="P293" s="35">
-        <f>IF(OR(F293="",O293="Fechada",O293="Perdida"),0,IF(O293="Fechamento vencido",3,IF(O293="Parada",2,1))*1E+13+MIN(N(N293),500)*1E+10+MIN(ROUND(N(E293),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F293="",O293="Fechada",O293="Perdida"),0,IF(O293="Fechamento vencido",3,IF(O293="Parada",2,1))*1E+15+MIN(N(N293),500)*1E+12+MIN(ROUND(N(E293)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
         <v/>
       </c>
       <c r="P294" s="35">
-        <f>IF(OR(F294="",O294="Fechada",O294="Perdida"),0,IF(O294="Fechamento vencido",3,IF(O294="Parada",2,1))*1E+13+MIN(N(N294),500)*1E+10+MIN(ROUND(N(E294),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F294="",O294="Fechada",O294="Perdida"),0,IF(O294="Fechamento vencido",3,IF(O294="Parada",2,1))*1E+15+MIN(N(N294),500)*1E+12+MIN(ROUND(N(E294)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
         <v/>
       </c>
       <c r="P295" s="35">
-        <f>IF(OR(F295="",O295="Fechada",O295="Perdida"),0,IF(O295="Fechamento vencido",3,IF(O295="Parada",2,1))*1E+13+MIN(N(N295),500)*1E+10+MIN(ROUND(N(E295),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F295="",O295="Fechada",O295="Perdida"),0,IF(O295="Fechamento vencido",3,IF(O295="Parada",2,1))*1E+15+MIN(N(N295),500)*1E+12+MIN(ROUND(N(E295)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
         <v/>
       </c>
       <c r="P296" s="35">
-        <f>IF(OR(F296="",O296="Fechada",O296="Perdida"),0,IF(O296="Fechamento vencido",3,IF(O296="Parada",2,1))*1E+13+MIN(N(N296),500)*1E+10+MIN(ROUND(N(E296),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F296="",O296="Fechada",O296="Perdida"),0,IF(O296="Fechamento vencido",3,IF(O296="Parada",2,1))*1E+15+MIN(N(N296),500)*1E+12+MIN(ROUND(N(E296)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
         <v/>
       </c>
       <c r="P297" s="35">
-        <f>IF(OR(F297="",O297="Fechada",O297="Perdida"),0,IF(O297="Fechamento vencido",3,IF(O297="Parada",2,1))*1E+13+MIN(N(N297),500)*1E+10+MIN(ROUND(N(E297),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F297="",O297="Fechada",O297="Perdida"),0,IF(O297="Fechamento vencido",3,IF(O297="Parada",2,1))*1E+15+MIN(N(N297),500)*1E+12+MIN(ROUND(N(E297)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
         <v/>
       </c>
       <c r="P298" s="35">
-        <f>IF(OR(F298="",O298="Fechada",O298="Perdida"),0,IF(O298="Fechamento vencido",3,IF(O298="Parada",2,1))*1E+13+MIN(N(N298),500)*1E+10+MIN(ROUND(N(E298),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F298="",O298="Fechada",O298="Perdida"),0,IF(O298="Fechamento vencido",3,IF(O298="Parada",2,1))*1E+15+MIN(N(N298),500)*1E+12+MIN(ROUND(N(E298)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12617,7 +12617,7 @@
         <v/>
       </c>
       <c r="P299" s="35">
-        <f>IF(OR(F299="",O299="Fechada",O299="Perdida"),0,IF(O299="Fechamento vencido",3,IF(O299="Parada",2,1))*1E+13+MIN(N(N299),500)*1E+10+MIN(ROUND(N(E299),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F299="",O299="Fechada",O299="Perdida"),0,IF(O299="Fechamento vencido",3,IF(O299="Parada",2,1))*1E+15+MIN(N(N299),500)*1E+12+MIN(ROUND(N(E299)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
         <v/>
       </c>
       <c r="P300" s="35">
-        <f>IF(OR(F300="",O300="Fechada",O300="Perdida"),0,IF(O300="Fechamento vencido",3,IF(O300="Parada",2,1))*1E+13+MIN(N(N300),500)*1E+10+MIN(ROUND(N(E300),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F300="",O300="Fechada",O300="Perdida"),0,IF(O300="Fechamento vencido",3,IF(O300="Parada",2,1))*1E+15+MIN(N(N300),500)*1E+12+MIN(ROUND(N(E300)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12683,7 +12683,7 @@
         <v/>
       </c>
       <c r="P301" s="35">
-        <f>IF(OR(F301="",O301="Fechada",O301="Perdida"),0,IF(O301="Fechamento vencido",3,IF(O301="Parada",2,1))*1E+13+MIN(N(N301),500)*1E+10+MIN(ROUND(N(E301),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F301="",O301="Fechada",O301="Perdida"),0,IF(O301="Fechamento vencido",3,IF(O301="Parada",2,1))*1E+15+MIN(N(N301),500)*1E+12+MIN(ROUND(N(E301)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
         <v/>
       </c>
       <c r="P302" s="35">
-        <f>IF(OR(F302="",O302="Fechada",O302="Perdida"),0,IF(O302="Fechamento vencido",3,IF(O302="Parada",2,1))*1E+13+MIN(N(N302),500)*1E+10+MIN(ROUND(N(E302),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F302="",O302="Fechada",O302="Perdida"),0,IF(O302="Fechamento vencido",3,IF(O302="Parada",2,1))*1E+15+MIN(N(N302),500)*1E+12+MIN(ROUND(N(E302)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12749,7 +12749,7 @@
         <v/>
       </c>
       <c r="P303" s="35">
-        <f>IF(OR(F303="",O303="Fechada",O303="Perdida"),0,IF(O303="Fechamento vencido",3,IF(O303="Parada",2,1))*1E+13+MIN(N(N303),500)*1E+10+MIN(ROUND(N(E303),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F303="",O303="Fechada",O303="Perdida"),0,IF(O303="Fechamento vencido",3,IF(O303="Parada",2,1))*1E+15+MIN(N(N303),500)*1E+12+MIN(ROUND(N(E303)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
         <v/>
       </c>
       <c r="P304" s="35">
-        <f>IF(OR(F304="",O304="Fechada",O304="Perdida"),0,IF(O304="Fechamento vencido",3,IF(O304="Parada",2,1))*1E+13+MIN(N(N304),500)*1E+10+MIN(ROUND(N(E304),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F304="",O304="Fechada",O304="Perdida"),0,IF(O304="Fechamento vencido",3,IF(O304="Parada",2,1))*1E+15+MIN(N(N304),500)*1E+12+MIN(ROUND(N(E304)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
         <v/>
       </c>
       <c r="P305" s="35">
-        <f>IF(OR(F305="",O305="Fechada",O305="Perdida"),0,IF(O305="Fechamento vencido",3,IF(O305="Parada",2,1))*1E+13+MIN(N(N305),500)*1E+10+MIN(ROUND(N(E305),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F305="",O305="Fechada",O305="Perdida"),0,IF(O305="Fechamento vencido",3,IF(O305="Parada",2,1))*1E+15+MIN(N(N305),500)*1E+12+MIN(ROUND(N(E305)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12848,7 +12848,7 @@
         <v/>
       </c>
       <c r="P306" s="35">
-        <f>IF(OR(F306="",O306="Fechada",O306="Perdida"),0,IF(O306="Fechamento vencido",3,IF(O306="Parada",2,1))*1E+13+MIN(N(N306),500)*1E+10+MIN(ROUND(N(E306),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F306="",O306="Fechada",O306="Perdida"),0,IF(O306="Fechamento vencido",3,IF(O306="Parada",2,1))*1E+15+MIN(N(N306),500)*1E+12+MIN(ROUND(N(E306)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
         <v/>
       </c>
       <c r="P307" s="35">
-        <f>IF(OR(F307="",O307="Fechada",O307="Perdida"),0,IF(O307="Fechamento vencido",3,IF(O307="Parada",2,1))*1E+13+MIN(N(N307),500)*1E+10+MIN(ROUND(N(E307),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F307="",O307="Fechada",O307="Perdida"),0,IF(O307="Fechamento vencido",3,IF(O307="Parada",2,1))*1E+15+MIN(N(N307),500)*1E+12+MIN(ROUND(N(E307)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
         <v/>
       </c>
       <c r="P308" s="35">
-        <f>IF(OR(F308="",O308="Fechada",O308="Perdida"),0,IF(O308="Fechamento vencido",3,IF(O308="Parada",2,1))*1E+13+MIN(N(N308),500)*1E+10+MIN(ROUND(N(E308),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F308="",O308="Fechada",O308="Perdida"),0,IF(O308="Fechamento vencido",3,IF(O308="Parada",2,1))*1E+15+MIN(N(N308),500)*1E+12+MIN(ROUND(N(E308)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12947,7 +12947,7 @@
         <v/>
       </c>
       <c r="P309" s="35">
-        <f>IF(OR(F309="",O309="Fechada",O309="Perdida"),0,IF(O309="Fechamento vencido",3,IF(O309="Parada",2,1))*1E+13+MIN(N(N309),500)*1E+10+MIN(ROUND(N(E309),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F309="",O309="Fechada",O309="Perdida"),0,IF(O309="Fechamento vencido",3,IF(O309="Parada",2,1))*1E+15+MIN(N(N309),500)*1E+12+MIN(ROUND(N(E309)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
         <v/>
       </c>
       <c r="P310" s="35">
-        <f>IF(OR(F310="",O310="Fechada",O310="Perdida"),0,IF(O310="Fechamento vencido",3,IF(O310="Parada",2,1))*1E+13+MIN(N(N310),500)*1E+10+MIN(ROUND(N(E310),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F310="",O310="Fechada",O310="Perdida"),0,IF(O310="Fechamento vencido",3,IF(O310="Parada",2,1))*1E+15+MIN(N(N310),500)*1E+12+MIN(ROUND(N(E310)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13013,7 +13013,7 @@
         <v/>
       </c>
       <c r="P311" s="35">
-        <f>IF(OR(F311="",O311="Fechada",O311="Perdida"),0,IF(O311="Fechamento vencido",3,IF(O311="Parada",2,1))*1E+13+MIN(N(N311),500)*1E+10+MIN(ROUND(N(E311),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F311="",O311="Fechada",O311="Perdida"),0,IF(O311="Fechamento vencido",3,IF(O311="Parada",2,1))*1E+15+MIN(N(N311),500)*1E+12+MIN(ROUND(N(E311)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13046,7 +13046,7 @@
         <v/>
       </c>
       <c r="P312" s="35">
-        <f>IF(OR(F312="",O312="Fechada",O312="Perdida"),0,IF(O312="Fechamento vencido",3,IF(O312="Parada",2,1))*1E+13+MIN(N(N312),500)*1E+10+MIN(ROUND(N(E312),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F312="",O312="Fechada",O312="Perdida"),0,IF(O312="Fechamento vencido",3,IF(O312="Parada",2,1))*1E+15+MIN(N(N312),500)*1E+12+MIN(ROUND(N(E312)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
         <v/>
       </c>
       <c r="P313" s="35">
-        <f>IF(OR(F313="",O313="Fechada",O313="Perdida"),0,IF(O313="Fechamento vencido",3,IF(O313="Parada",2,1))*1E+13+MIN(N(N313),500)*1E+10+MIN(ROUND(N(E313),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F313="",O313="Fechada",O313="Perdida"),0,IF(O313="Fechamento vencido",3,IF(O313="Parada",2,1))*1E+15+MIN(N(N313),500)*1E+12+MIN(ROUND(N(E313)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
         <v/>
       </c>
       <c r="P314" s="35">
-        <f>IF(OR(F314="",O314="Fechada",O314="Perdida"),0,IF(O314="Fechamento vencido",3,IF(O314="Parada",2,1))*1E+13+MIN(N(N314),500)*1E+10+MIN(ROUND(N(E314),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F314="",O314="Fechada",O314="Perdida"),0,IF(O314="Fechamento vencido",3,IF(O314="Parada",2,1))*1E+15+MIN(N(N314),500)*1E+12+MIN(ROUND(N(E314)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
         <v/>
       </c>
       <c r="P315" s="35">
-        <f>IF(OR(F315="",O315="Fechada",O315="Perdida"),0,IF(O315="Fechamento vencido",3,IF(O315="Parada",2,1))*1E+13+MIN(N(N315),500)*1E+10+MIN(ROUND(N(E315),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F315="",O315="Fechada",O315="Perdida"),0,IF(O315="Fechamento vencido",3,IF(O315="Parada",2,1))*1E+15+MIN(N(N315),500)*1E+12+MIN(ROUND(N(E315)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
         <v/>
       </c>
       <c r="P316" s="35">
-        <f>IF(OR(F316="",O316="Fechada",O316="Perdida"),0,IF(O316="Fechamento vencido",3,IF(O316="Parada",2,1))*1E+13+MIN(N(N316),500)*1E+10+MIN(ROUND(N(E316),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F316="",O316="Fechada",O316="Perdida"),0,IF(O316="Fechamento vencido",3,IF(O316="Parada",2,1))*1E+15+MIN(N(N316),500)*1E+12+MIN(ROUND(N(E316)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13211,7 +13211,7 @@
         <v/>
       </c>
       <c r="P317" s="35">
-        <f>IF(OR(F317="",O317="Fechada",O317="Perdida"),0,IF(O317="Fechamento vencido",3,IF(O317="Parada",2,1))*1E+13+MIN(N(N317),500)*1E+10+MIN(ROUND(N(E317),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F317="",O317="Fechada",O317="Perdida"),0,IF(O317="Fechamento vencido",3,IF(O317="Parada",2,1))*1E+15+MIN(N(N317),500)*1E+12+MIN(ROUND(N(E317)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
         <v/>
       </c>
       <c r="P318" s="35">
-        <f>IF(OR(F318="",O318="Fechada",O318="Perdida"),0,IF(O318="Fechamento vencido",3,IF(O318="Parada",2,1))*1E+13+MIN(N(N318),500)*1E+10+MIN(ROUND(N(E318),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F318="",O318="Fechada",O318="Perdida"),0,IF(O318="Fechamento vencido",3,IF(O318="Parada",2,1))*1E+15+MIN(N(N318),500)*1E+12+MIN(ROUND(N(E318)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
         <v/>
       </c>
       <c r="P319" s="35">
-        <f>IF(OR(F319="",O319="Fechada",O319="Perdida"),0,IF(O319="Fechamento vencido",3,IF(O319="Parada",2,1))*1E+13+MIN(N(N319),500)*1E+10+MIN(ROUND(N(E319),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F319="",O319="Fechada",O319="Perdida"),0,IF(O319="Fechamento vencido",3,IF(O319="Parada",2,1))*1E+15+MIN(N(N319),500)*1E+12+MIN(ROUND(N(E319)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13310,7 +13310,7 @@
         <v/>
       </c>
       <c r="P320" s="35">
-        <f>IF(OR(F320="",O320="Fechada",O320="Perdida"),0,IF(O320="Fechamento vencido",3,IF(O320="Parada",2,1))*1E+13+MIN(N(N320),500)*1E+10+MIN(ROUND(N(E320),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F320="",O320="Fechada",O320="Perdida"),0,IF(O320="Fechamento vencido",3,IF(O320="Parada",2,1))*1E+15+MIN(N(N320),500)*1E+12+MIN(ROUND(N(E320)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
         <v/>
       </c>
       <c r="P321" s="35">
-        <f>IF(OR(F321="",O321="Fechada",O321="Perdida"),0,IF(O321="Fechamento vencido",3,IF(O321="Parada",2,1))*1E+13+MIN(N(N321),500)*1E+10+MIN(ROUND(N(E321),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F321="",O321="Fechada",O321="Perdida"),0,IF(O321="Fechamento vencido",3,IF(O321="Parada",2,1))*1E+15+MIN(N(N321),500)*1E+12+MIN(ROUND(N(E321)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v/>
       </c>
       <c r="P322" s="35">
-        <f>IF(OR(F322="",O322="Fechada",O322="Perdida"),0,IF(O322="Fechamento vencido",3,IF(O322="Parada",2,1))*1E+13+MIN(N(N322),500)*1E+10+MIN(ROUND(N(E322),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F322="",O322="Fechada",O322="Perdida"),0,IF(O322="Fechamento vencido",3,IF(O322="Parada",2,1))*1E+15+MIN(N(N322),500)*1E+12+MIN(ROUND(N(E322)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
         <v/>
       </c>
       <c r="P323" s="35">
-        <f>IF(OR(F323="",O323="Fechada",O323="Perdida"),0,IF(O323="Fechamento vencido",3,IF(O323="Parada",2,1))*1E+13+MIN(N(N323),500)*1E+10+MIN(ROUND(N(E323),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F323="",O323="Fechada",O323="Perdida"),0,IF(O323="Fechamento vencido",3,IF(O323="Parada",2,1))*1E+15+MIN(N(N323),500)*1E+12+MIN(ROUND(N(E323)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13442,7 +13442,7 @@
         <v/>
       </c>
       <c r="P324" s="35">
-        <f>IF(OR(F324="",O324="Fechada",O324="Perdida"),0,IF(O324="Fechamento vencido",3,IF(O324="Parada",2,1))*1E+13+MIN(N(N324),500)*1E+10+MIN(ROUND(N(E324),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F324="",O324="Fechada",O324="Perdida"),0,IF(O324="Fechamento vencido",3,IF(O324="Parada",2,1))*1E+15+MIN(N(N324),500)*1E+12+MIN(ROUND(N(E324)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
         <v/>
       </c>
       <c r="P325" s="35">
-        <f>IF(OR(F325="",O325="Fechada",O325="Perdida"),0,IF(O325="Fechamento vencido",3,IF(O325="Parada",2,1))*1E+13+MIN(N(N325),500)*1E+10+MIN(ROUND(N(E325),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F325="",O325="Fechada",O325="Perdida"),0,IF(O325="Fechamento vencido",3,IF(O325="Parada",2,1))*1E+15+MIN(N(N325),500)*1E+12+MIN(ROUND(N(E325)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
         <v/>
       </c>
       <c r="P326" s="35">
-        <f>IF(OR(F326="",O326="Fechada",O326="Perdida"),0,IF(O326="Fechamento vencido",3,IF(O326="Parada",2,1))*1E+13+MIN(N(N326),500)*1E+10+MIN(ROUND(N(E326),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F326="",O326="Fechada",O326="Perdida"),0,IF(O326="Fechamento vencido",3,IF(O326="Parada",2,1))*1E+15+MIN(N(N326),500)*1E+12+MIN(ROUND(N(E326)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
         <v/>
       </c>
       <c r="P327" s="35">
-        <f>IF(OR(F327="",O327="Fechada",O327="Perdida"),0,IF(O327="Fechamento vencido",3,IF(O327="Parada",2,1))*1E+13+MIN(N(N327),500)*1E+10+MIN(ROUND(N(E327),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F327="",O327="Fechada",O327="Perdida"),0,IF(O327="Fechamento vencido",3,IF(O327="Parada",2,1))*1E+15+MIN(N(N327),500)*1E+12+MIN(ROUND(N(E327)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
         <v/>
       </c>
       <c r="P328" s="35">
-        <f>IF(OR(F328="",O328="Fechada",O328="Perdida"),0,IF(O328="Fechamento vencido",3,IF(O328="Parada",2,1))*1E+13+MIN(N(N328),500)*1E+10+MIN(ROUND(N(E328),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F328="",O328="Fechada",O328="Perdida"),0,IF(O328="Fechamento vencido",3,IF(O328="Parada",2,1))*1E+15+MIN(N(N328),500)*1E+12+MIN(ROUND(N(E328)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13607,7 +13607,7 @@
         <v/>
       </c>
       <c r="P329" s="35">
-        <f>IF(OR(F329="",O329="Fechada",O329="Perdida"),0,IF(O329="Fechamento vencido",3,IF(O329="Parada",2,1))*1E+13+MIN(N(N329),500)*1E+10+MIN(ROUND(N(E329),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F329="",O329="Fechada",O329="Perdida"),0,IF(O329="Fechamento vencido",3,IF(O329="Parada",2,1))*1E+15+MIN(N(N329),500)*1E+12+MIN(ROUND(N(E329)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
         <v/>
       </c>
       <c r="P330" s="35">
-        <f>IF(OR(F330="",O330="Fechada",O330="Perdida"),0,IF(O330="Fechamento vencido",3,IF(O330="Parada",2,1))*1E+13+MIN(N(N330),500)*1E+10+MIN(ROUND(N(E330),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F330="",O330="Fechada",O330="Perdida"),0,IF(O330="Fechamento vencido",3,IF(O330="Parada",2,1))*1E+15+MIN(N(N330),500)*1E+12+MIN(ROUND(N(E330)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
         <v/>
       </c>
       <c r="P331" s="35">
-        <f>IF(OR(F331="",O331="Fechada",O331="Perdida"),0,IF(O331="Fechamento vencido",3,IF(O331="Parada",2,1))*1E+13+MIN(N(N331),500)*1E+10+MIN(ROUND(N(E331),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F331="",O331="Fechada",O331="Perdida"),0,IF(O331="Fechamento vencido",3,IF(O331="Parada",2,1))*1E+15+MIN(N(N331),500)*1E+12+MIN(ROUND(N(E331)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13706,7 +13706,7 @@
         <v/>
       </c>
       <c r="P332" s="35">
-        <f>IF(OR(F332="",O332="Fechada",O332="Perdida"),0,IF(O332="Fechamento vencido",3,IF(O332="Parada",2,1))*1E+13+MIN(N(N332),500)*1E+10+MIN(ROUND(N(E332),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F332="",O332="Fechada",O332="Perdida"),0,IF(O332="Fechamento vencido",3,IF(O332="Parada",2,1))*1E+15+MIN(N(N332),500)*1E+12+MIN(ROUND(N(E332)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13739,7 +13739,7 @@
         <v/>
       </c>
       <c r="P333" s="35">
-        <f>IF(OR(F333="",O333="Fechada",O333="Perdida"),0,IF(O333="Fechamento vencido",3,IF(O333="Parada",2,1))*1E+13+MIN(N(N333),500)*1E+10+MIN(ROUND(N(E333),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F333="",O333="Fechada",O333="Perdida"),0,IF(O333="Fechamento vencido",3,IF(O333="Parada",2,1))*1E+15+MIN(N(N333),500)*1E+12+MIN(ROUND(N(E333)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
         <v/>
       </c>
       <c r="P334" s="35">
-        <f>IF(OR(F334="",O334="Fechada",O334="Perdida"),0,IF(O334="Fechamento vencido",3,IF(O334="Parada",2,1))*1E+13+MIN(N(N334),500)*1E+10+MIN(ROUND(N(E334),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F334="",O334="Fechada",O334="Perdida"),0,IF(O334="Fechamento vencido",3,IF(O334="Parada",2,1))*1E+15+MIN(N(N334),500)*1E+12+MIN(ROUND(N(E334)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13805,7 +13805,7 @@
         <v/>
       </c>
       <c r="P335" s="35">
-        <f>IF(OR(F335="",O335="Fechada",O335="Perdida"),0,IF(O335="Fechamento vencido",3,IF(O335="Parada",2,1))*1E+13+MIN(N(N335),500)*1E+10+MIN(ROUND(N(E335),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F335="",O335="Fechada",O335="Perdida"),0,IF(O335="Fechamento vencido",3,IF(O335="Parada",2,1))*1E+15+MIN(N(N335),500)*1E+12+MIN(ROUND(N(E335)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
         <v/>
       </c>
       <c r="P336" s="35">
-        <f>IF(OR(F336="",O336="Fechada",O336="Perdida"),0,IF(O336="Fechamento vencido",3,IF(O336="Parada",2,1))*1E+13+MIN(N(N336),500)*1E+10+MIN(ROUND(N(E336),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F336="",O336="Fechada",O336="Perdida"),0,IF(O336="Fechamento vencido",3,IF(O336="Parada",2,1))*1E+15+MIN(N(N336),500)*1E+12+MIN(ROUND(N(E336)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
         <v/>
       </c>
       <c r="P337" s="35">
-        <f>IF(OR(F337="",O337="Fechada",O337="Perdida"),0,IF(O337="Fechamento vencido",3,IF(O337="Parada",2,1))*1E+13+MIN(N(N337),500)*1E+10+MIN(ROUND(N(E337),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F337="",O337="Fechada",O337="Perdida"),0,IF(O337="Fechamento vencido",3,IF(O337="Parada",2,1))*1E+15+MIN(N(N337),500)*1E+12+MIN(ROUND(N(E337)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
         <v/>
       </c>
       <c r="P338" s="35">
-        <f>IF(OR(F338="",O338="Fechada",O338="Perdida"),0,IF(O338="Fechamento vencido",3,IF(O338="Parada",2,1))*1E+13+MIN(N(N338),500)*1E+10+MIN(ROUND(N(E338),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F338="",O338="Fechada",O338="Perdida"),0,IF(O338="Fechamento vencido",3,IF(O338="Parada",2,1))*1E+15+MIN(N(N338),500)*1E+12+MIN(ROUND(N(E338)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
         <v/>
       </c>
       <c r="P339" s="35">
-        <f>IF(OR(F339="",O339="Fechada",O339="Perdida"),0,IF(O339="Fechamento vencido",3,IF(O339="Parada",2,1))*1E+13+MIN(N(N339),500)*1E+10+MIN(ROUND(N(E339),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F339="",O339="Fechada",O339="Perdida"),0,IF(O339="Fechamento vencido",3,IF(O339="Parada",2,1))*1E+15+MIN(N(N339),500)*1E+12+MIN(ROUND(N(E339)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
         <v/>
       </c>
       <c r="P340" s="35">
-        <f>IF(OR(F340="",O340="Fechada",O340="Perdida"),0,IF(O340="Fechamento vencido",3,IF(O340="Parada",2,1))*1E+13+MIN(N(N340),500)*1E+10+MIN(ROUND(N(E340),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F340="",O340="Fechada",O340="Perdida"),0,IF(O340="Fechamento vencido",3,IF(O340="Parada",2,1))*1E+15+MIN(N(N340),500)*1E+12+MIN(ROUND(N(E340)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14003,7 +14003,7 @@
         <v/>
       </c>
       <c r="P341" s="35">
-        <f>IF(OR(F341="",O341="Fechada",O341="Perdida"),0,IF(O341="Fechamento vencido",3,IF(O341="Parada",2,1))*1E+13+MIN(N(N341),500)*1E+10+MIN(ROUND(N(E341),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F341="",O341="Fechada",O341="Perdida"),0,IF(O341="Fechamento vencido",3,IF(O341="Parada",2,1))*1E+15+MIN(N(N341),500)*1E+12+MIN(ROUND(N(E341)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14036,7 +14036,7 @@
         <v/>
       </c>
       <c r="P342" s="35">
-        <f>IF(OR(F342="",O342="Fechada",O342="Perdida"),0,IF(O342="Fechamento vencido",3,IF(O342="Parada",2,1))*1E+13+MIN(N(N342),500)*1E+10+MIN(ROUND(N(E342),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F342="",O342="Fechada",O342="Perdida"),0,IF(O342="Fechamento vencido",3,IF(O342="Parada",2,1))*1E+15+MIN(N(N342),500)*1E+12+MIN(ROUND(N(E342)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14069,7 +14069,7 @@
         <v/>
       </c>
       <c r="P343" s="35">
-        <f>IF(OR(F343="",O343="Fechada",O343="Perdida"),0,IF(O343="Fechamento vencido",3,IF(O343="Parada",2,1))*1E+13+MIN(N(N343),500)*1E+10+MIN(ROUND(N(E343),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F343="",O343="Fechada",O343="Perdida"),0,IF(O343="Fechamento vencido",3,IF(O343="Parada",2,1))*1E+15+MIN(N(N343),500)*1E+12+MIN(ROUND(N(E343)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
         <v/>
       </c>
       <c r="P344" s="35">
-        <f>IF(OR(F344="",O344="Fechada",O344="Perdida"),0,IF(O344="Fechamento vencido",3,IF(O344="Parada",2,1))*1E+13+MIN(N(N344),500)*1E+10+MIN(ROUND(N(E344),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F344="",O344="Fechada",O344="Perdida"),0,IF(O344="Fechamento vencido",3,IF(O344="Parada",2,1))*1E+15+MIN(N(N344),500)*1E+12+MIN(ROUND(N(E344)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14135,7 +14135,7 @@
         <v/>
       </c>
       <c r="P345" s="35">
-        <f>IF(OR(F345="",O345="Fechada",O345="Perdida"),0,IF(O345="Fechamento vencido",3,IF(O345="Parada",2,1))*1E+13+MIN(N(N345),500)*1E+10+MIN(ROUND(N(E345),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F345="",O345="Fechada",O345="Perdida"),0,IF(O345="Fechamento vencido",3,IF(O345="Parada",2,1))*1E+15+MIN(N(N345),500)*1E+12+MIN(ROUND(N(E345)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
         <v/>
       </c>
       <c r="P346" s="35">
-        <f>IF(OR(F346="",O346="Fechada",O346="Perdida"),0,IF(O346="Fechamento vencido",3,IF(O346="Parada",2,1))*1E+13+MIN(N(N346),500)*1E+10+MIN(ROUND(N(E346),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F346="",O346="Fechada",O346="Perdida"),0,IF(O346="Fechamento vencido",3,IF(O346="Parada",2,1))*1E+15+MIN(N(N346),500)*1E+12+MIN(ROUND(N(E346)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
         <v/>
       </c>
       <c r="P347" s="35">
-        <f>IF(OR(F347="",O347="Fechada",O347="Perdida"),0,IF(O347="Fechamento vencido",3,IF(O347="Parada",2,1))*1E+13+MIN(N(N347),500)*1E+10+MIN(ROUND(N(E347),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F347="",O347="Fechada",O347="Perdida"),0,IF(O347="Fechamento vencido",3,IF(O347="Parada",2,1))*1E+15+MIN(N(N347),500)*1E+12+MIN(ROUND(N(E347)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14234,7 +14234,7 @@
         <v/>
       </c>
       <c r="P348" s="35">
-        <f>IF(OR(F348="",O348="Fechada",O348="Perdida"),0,IF(O348="Fechamento vencido",3,IF(O348="Parada",2,1))*1E+13+MIN(N(N348),500)*1E+10+MIN(ROUND(N(E348),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F348="",O348="Fechada",O348="Perdida"),0,IF(O348="Fechamento vencido",3,IF(O348="Parada",2,1))*1E+15+MIN(N(N348),500)*1E+12+MIN(ROUND(N(E348)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
         <v/>
       </c>
       <c r="P349" s="35">
-        <f>IF(OR(F349="",O349="Fechada",O349="Perdida"),0,IF(O349="Fechamento vencido",3,IF(O349="Parada",2,1))*1E+13+MIN(N(N349),500)*1E+10+MIN(ROUND(N(E349),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F349="",O349="Fechada",O349="Perdida"),0,IF(O349="Fechamento vencido",3,IF(O349="Parada",2,1))*1E+15+MIN(N(N349),500)*1E+12+MIN(ROUND(N(E349)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
         <v/>
       </c>
       <c r="P350" s="35">
-        <f>IF(OR(F350="",O350="Fechada",O350="Perdida"),0,IF(O350="Fechamento vencido",3,IF(O350="Parada",2,1))*1E+13+MIN(N(N350),500)*1E+10+MIN(ROUND(N(E350),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F350="",O350="Fechada",O350="Perdida"),0,IF(O350="Fechamento vencido",3,IF(O350="Parada",2,1))*1E+15+MIN(N(N350),500)*1E+12+MIN(ROUND(N(E350)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14333,7 +14333,7 @@
         <v/>
       </c>
       <c r="P351" s="35">
-        <f>IF(OR(F351="",O351="Fechada",O351="Perdida"),0,IF(O351="Fechamento vencido",3,IF(O351="Parada",2,1))*1E+13+MIN(N(N351),500)*1E+10+MIN(ROUND(N(E351),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F351="",O351="Fechada",O351="Perdida"),0,IF(O351="Fechamento vencido",3,IF(O351="Parada",2,1))*1E+15+MIN(N(N351),500)*1E+12+MIN(ROUND(N(E351)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
         <v/>
       </c>
       <c r="P352" s="35">
-        <f>IF(OR(F352="",O352="Fechada",O352="Perdida"),0,IF(O352="Fechamento vencido",3,IF(O352="Parada",2,1))*1E+13+MIN(N(N352),500)*1E+10+MIN(ROUND(N(E352),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F352="",O352="Fechada",O352="Perdida"),0,IF(O352="Fechamento vencido",3,IF(O352="Parada",2,1))*1E+15+MIN(N(N352),500)*1E+12+MIN(ROUND(N(E352)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14399,7 +14399,7 @@
         <v/>
       </c>
       <c r="P353" s="35">
-        <f>IF(OR(F353="",O353="Fechada",O353="Perdida"),0,IF(O353="Fechamento vencido",3,IF(O353="Parada",2,1))*1E+13+MIN(N(N353),500)*1E+10+MIN(ROUND(N(E353),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F353="",O353="Fechada",O353="Perdida"),0,IF(O353="Fechamento vencido",3,IF(O353="Parada",2,1))*1E+15+MIN(N(N353),500)*1E+12+MIN(ROUND(N(E353)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
         <v/>
       </c>
       <c r="P354" s="35">
-        <f>IF(OR(F354="",O354="Fechada",O354="Perdida"),0,IF(O354="Fechamento vencido",3,IF(O354="Parada",2,1))*1E+13+MIN(N(N354),500)*1E+10+MIN(ROUND(N(E354),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F354="",O354="Fechada",O354="Perdida"),0,IF(O354="Fechamento vencido",3,IF(O354="Parada",2,1))*1E+15+MIN(N(N354),500)*1E+12+MIN(ROUND(N(E354)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14465,7 +14465,7 @@
         <v/>
       </c>
       <c r="P355" s="35">
-        <f>IF(OR(F355="",O355="Fechada",O355="Perdida"),0,IF(O355="Fechamento vencido",3,IF(O355="Parada",2,1))*1E+13+MIN(N(N355),500)*1E+10+MIN(ROUND(N(E355),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F355="",O355="Fechada",O355="Perdida"),0,IF(O355="Fechamento vencido",3,IF(O355="Parada",2,1))*1E+15+MIN(N(N355),500)*1E+12+MIN(ROUND(N(E355)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
         <v/>
       </c>
       <c r="P356" s="35">
-        <f>IF(OR(F356="",O356="Fechada",O356="Perdida"),0,IF(O356="Fechamento vencido",3,IF(O356="Parada",2,1))*1E+13+MIN(N(N356),500)*1E+10+MIN(ROUND(N(E356),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F356="",O356="Fechada",O356="Perdida"),0,IF(O356="Fechamento vencido",3,IF(O356="Parada",2,1))*1E+15+MIN(N(N356),500)*1E+12+MIN(ROUND(N(E356)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         <v/>
       </c>
       <c r="P357" s="35">
-        <f>IF(OR(F357="",O357="Fechada",O357="Perdida"),0,IF(O357="Fechamento vencido",3,IF(O357="Parada",2,1))*1E+13+MIN(N(N357),500)*1E+10+MIN(ROUND(N(E357),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F357="",O357="Fechada",O357="Perdida"),0,IF(O357="Fechamento vencido",3,IF(O357="Parada",2,1))*1E+15+MIN(N(N357),500)*1E+12+MIN(ROUND(N(E357)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
         <v/>
       </c>
       <c r="P358" s="35">
-        <f>IF(OR(F358="",O358="Fechada",O358="Perdida"),0,IF(O358="Fechamento vencido",3,IF(O358="Parada",2,1))*1E+13+MIN(N(N358),500)*1E+10+MIN(ROUND(N(E358),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F358="",O358="Fechada",O358="Perdida"),0,IF(O358="Fechamento vencido",3,IF(O358="Parada",2,1))*1E+15+MIN(N(N358),500)*1E+12+MIN(ROUND(N(E358)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14597,7 +14597,7 @@
         <v/>
       </c>
       <c r="P359" s="35">
-        <f>IF(OR(F359="",O359="Fechada",O359="Perdida"),0,IF(O359="Fechamento vencido",3,IF(O359="Parada",2,1))*1E+13+MIN(N(N359),500)*1E+10+MIN(ROUND(N(E359),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F359="",O359="Fechada",O359="Perdida"),0,IF(O359="Fechamento vencido",3,IF(O359="Parada",2,1))*1E+15+MIN(N(N359),500)*1E+12+MIN(ROUND(N(E359)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
         <v/>
       </c>
       <c r="P360" s="35">
-        <f>IF(OR(F360="",O360="Fechada",O360="Perdida"),0,IF(O360="Fechamento vencido",3,IF(O360="Parada",2,1))*1E+13+MIN(N(N360),500)*1E+10+MIN(ROUND(N(E360),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F360="",O360="Fechada",O360="Perdida"),0,IF(O360="Fechamento vencido",3,IF(O360="Parada",2,1))*1E+15+MIN(N(N360),500)*1E+12+MIN(ROUND(N(E360)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
         <v/>
       </c>
       <c r="P361" s="35">
-        <f>IF(OR(F361="",O361="Fechada",O361="Perdida"),0,IF(O361="Fechamento vencido",3,IF(O361="Parada",2,1))*1E+13+MIN(N(N361),500)*1E+10+MIN(ROUND(N(E361),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F361="",O361="Fechada",O361="Perdida"),0,IF(O361="Fechamento vencido",3,IF(O361="Parada",2,1))*1E+15+MIN(N(N361),500)*1E+12+MIN(ROUND(N(E361)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
         <v/>
       </c>
       <c r="P362" s="35">
-        <f>IF(OR(F362="",O362="Fechada",O362="Perdida"),0,IF(O362="Fechamento vencido",3,IF(O362="Parada",2,1))*1E+13+MIN(N(N362),500)*1E+10+MIN(ROUND(N(E362),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F362="",O362="Fechada",O362="Perdida"),0,IF(O362="Fechamento vencido",3,IF(O362="Parada",2,1))*1E+15+MIN(N(N362),500)*1E+12+MIN(ROUND(N(E362)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
         <v/>
       </c>
       <c r="P363" s="35">
-        <f>IF(OR(F363="",O363="Fechada",O363="Perdida"),0,IF(O363="Fechamento vencido",3,IF(O363="Parada",2,1))*1E+13+MIN(N(N363),500)*1E+10+MIN(ROUND(N(E363),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F363="",O363="Fechada",O363="Perdida"),0,IF(O363="Fechamento vencido",3,IF(O363="Parada",2,1))*1E+15+MIN(N(N363),500)*1E+12+MIN(ROUND(N(E363)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
         <v/>
       </c>
       <c r="P364" s="35">
-        <f>IF(OR(F364="",O364="Fechada",O364="Perdida"),0,IF(O364="Fechamento vencido",3,IF(O364="Parada",2,1))*1E+13+MIN(N(N364),500)*1E+10+MIN(ROUND(N(E364),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F364="",O364="Fechada",O364="Perdida"),0,IF(O364="Fechamento vencido",3,IF(O364="Parada",2,1))*1E+15+MIN(N(N364),500)*1E+12+MIN(ROUND(N(E364)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14795,7 +14795,7 @@
         <v/>
       </c>
       <c r="P365" s="35">
-        <f>IF(OR(F365="",O365="Fechada",O365="Perdida"),0,IF(O365="Fechamento vencido",3,IF(O365="Parada",2,1))*1E+13+MIN(N(N365),500)*1E+10+MIN(ROUND(N(E365),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F365="",O365="Fechada",O365="Perdida"),0,IF(O365="Fechamento vencido",3,IF(O365="Parada",2,1))*1E+15+MIN(N(N365),500)*1E+12+MIN(ROUND(N(E365)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
         <v/>
       </c>
       <c r="P366" s="35">
-        <f>IF(OR(F366="",O366="Fechada",O366="Perdida"),0,IF(O366="Fechamento vencido",3,IF(O366="Parada",2,1))*1E+13+MIN(N(N366),500)*1E+10+MIN(ROUND(N(E366),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F366="",O366="Fechada",O366="Perdida"),0,IF(O366="Fechamento vencido",3,IF(O366="Parada",2,1))*1E+15+MIN(N(N366),500)*1E+12+MIN(ROUND(N(E366)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14861,7 +14861,7 @@
         <v/>
       </c>
       <c r="P367" s="35">
-        <f>IF(OR(F367="",O367="Fechada",O367="Perdida"),0,IF(O367="Fechamento vencido",3,IF(O367="Parada",2,1))*1E+13+MIN(N(N367),500)*1E+10+MIN(ROUND(N(E367),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F367="",O367="Fechada",O367="Perdida"),0,IF(O367="Fechamento vencido",3,IF(O367="Parada",2,1))*1E+15+MIN(N(N367),500)*1E+12+MIN(ROUND(N(E367)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14894,7 +14894,7 @@
         <v/>
       </c>
       <c r="P368" s="35">
-        <f>IF(OR(F368="",O368="Fechada",O368="Perdida"),0,IF(O368="Fechamento vencido",3,IF(O368="Parada",2,1))*1E+13+MIN(N(N368),500)*1E+10+MIN(ROUND(N(E368),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F368="",O368="Fechada",O368="Perdida"),0,IF(O368="Fechamento vencido",3,IF(O368="Parada",2,1))*1E+15+MIN(N(N368),500)*1E+12+MIN(ROUND(N(E368)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
         <v/>
       </c>
       <c r="P369" s="35">
-        <f>IF(OR(F369="",O369="Fechada",O369="Perdida"),0,IF(O369="Fechamento vencido",3,IF(O369="Parada",2,1))*1E+13+MIN(N(N369),500)*1E+10+MIN(ROUND(N(E369),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F369="",O369="Fechada",O369="Perdida"),0,IF(O369="Fechamento vencido",3,IF(O369="Parada",2,1))*1E+15+MIN(N(N369),500)*1E+12+MIN(ROUND(N(E369)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14960,7 +14960,7 @@
         <v/>
       </c>
       <c r="P370" s="35">
-        <f>IF(OR(F370="",O370="Fechada",O370="Perdida"),0,IF(O370="Fechamento vencido",3,IF(O370="Parada",2,1))*1E+13+MIN(N(N370),500)*1E+10+MIN(ROUND(N(E370),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F370="",O370="Fechada",O370="Perdida"),0,IF(O370="Fechamento vencido",3,IF(O370="Parada",2,1))*1E+15+MIN(N(N370),500)*1E+12+MIN(ROUND(N(E370)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
         <v/>
       </c>
       <c r="P371" s="35">
-        <f>IF(OR(F371="",O371="Fechada",O371="Perdida"),0,IF(O371="Fechamento vencido",3,IF(O371="Parada",2,1))*1E+13+MIN(N(N371),500)*1E+10+MIN(ROUND(N(E371),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F371="",O371="Fechada",O371="Perdida"),0,IF(O371="Fechamento vencido",3,IF(O371="Parada",2,1))*1E+15+MIN(N(N371),500)*1E+12+MIN(ROUND(N(E371)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
         <v/>
       </c>
       <c r="P372" s="35">
-        <f>IF(OR(F372="",O372="Fechada",O372="Perdida"),0,IF(O372="Fechamento vencido",3,IF(O372="Parada",2,1))*1E+13+MIN(N(N372),500)*1E+10+MIN(ROUND(N(E372),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F372="",O372="Fechada",O372="Perdida"),0,IF(O372="Fechamento vencido",3,IF(O372="Parada",2,1))*1E+15+MIN(N(N372),500)*1E+12+MIN(ROUND(N(E372)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
         <v/>
       </c>
       <c r="P373" s="35">
-        <f>IF(OR(F373="",O373="Fechada",O373="Perdida"),0,IF(O373="Fechamento vencido",3,IF(O373="Parada",2,1))*1E+13+MIN(N(N373),500)*1E+10+MIN(ROUND(N(E373),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F373="",O373="Fechada",O373="Perdida"),0,IF(O373="Fechamento vencido",3,IF(O373="Parada",2,1))*1E+15+MIN(N(N373),500)*1E+12+MIN(ROUND(N(E373)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
         <v/>
       </c>
       <c r="P374" s="35">
-        <f>IF(OR(F374="",O374="Fechada",O374="Perdida"),0,IF(O374="Fechamento vencido",3,IF(O374="Parada",2,1))*1E+13+MIN(N(N374),500)*1E+10+MIN(ROUND(N(E374),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F374="",O374="Fechada",O374="Perdida"),0,IF(O374="Fechamento vencido",3,IF(O374="Parada",2,1))*1E+15+MIN(N(N374),500)*1E+12+MIN(ROUND(N(E374)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15125,7 +15125,7 @@
         <v/>
       </c>
       <c r="P375" s="35">
-        <f>IF(OR(F375="",O375="Fechada",O375="Perdida"),0,IF(O375="Fechamento vencido",3,IF(O375="Parada",2,1))*1E+13+MIN(N(N375),500)*1E+10+MIN(ROUND(N(E375),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F375="",O375="Fechada",O375="Perdida"),0,IF(O375="Fechamento vencido",3,IF(O375="Parada",2,1))*1E+15+MIN(N(N375),500)*1E+12+MIN(ROUND(N(E375)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
         <v/>
       </c>
       <c r="P376" s="35">
-        <f>IF(OR(F376="",O376="Fechada",O376="Perdida"),0,IF(O376="Fechamento vencido",3,IF(O376="Parada",2,1))*1E+13+MIN(N(N376),500)*1E+10+MIN(ROUND(N(E376),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F376="",O376="Fechada",O376="Perdida"),0,IF(O376="Fechamento vencido",3,IF(O376="Parada",2,1))*1E+15+MIN(N(N376),500)*1E+12+MIN(ROUND(N(E376)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15191,7 +15191,7 @@
         <v/>
       </c>
       <c r="P377" s="35">
-        <f>IF(OR(F377="",O377="Fechada",O377="Perdida"),0,IF(O377="Fechamento vencido",3,IF(O377="Parada",2,1))*1E+13+MIN(N(N377),500)*1E+10+MIN(ROUND(N(E377),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F377="",O377="Fechada",O377="Perdida"),0,IF(O377="Fechamento vencido",3,IF(O377="Parada",2,1))*1E+15+MIN(N(N377),500)*1E+12+MIN(ROUND(N(E377)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
         <v/>
       </c>
       <c r="P378" s="35">
-        <f>IF(OR(F378="",O378="Fechada",O378="Perdida"),0,IF(O378="Fechamento vencido",3,IF(O378="Parada",2,1))*1E+13+MIN(N(N378),500)*1E+10+MIN(ROUND(N(E378),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F378="",O378="Fechada",O378="Perdida"),0,IF(O378="Fechamento vencido",3,IF(O378="Parada",2,1))*1E+15+MIN(N(N378),500)*1E+12+MIN(ROUND(N(E378)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15257,7 +15257,7 @@
         <v/>
       </c>
       <c r="P379" s="35">
-        <f>IF(OR(F379="",O379="Fechada",O379="Perdida"),0,IF(O379="Fechamento vencido",3,IF(O379="Parada",2,1))*1E+13+MIN(N(N379),500)*1E+10+MIN(ROUND(N(E379),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F379="",O379="Fechada",O379="Perdida"),0,IF(O379="Fechamento vencido",3,IF(O379="Parada",2,1))*1E+15+MIN(N(N379),500)*1E+12+MIN(ROUND(N(E379)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
         <v/>
       </c>
       <c r="P380" s="35">
-        <f>IF(OR(F380="",O380="Fechada",O380="Perdida"),0,IF(O380="Fechamento vencido",3,IF(O380="Parada",2,1))*1E+13+MIN(N(N380),500)*1E+10+MIN(ROUND(N(E380),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F380="",O380="Fechada",O380="Perdida"),0,IF(O380="Fechamento vencido",3,IF(O380="Parada",2,1))*1E+15+MIN(N(N380),500)*1E+12+MIN(ROUND(N(E380)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
         <v/>
       </c>
       <c r="P381" s="35">
-        <f>IF(OR(F381="",O381="Fechada",O381="Perdida"),0,IF(O381="Fechamento vencido",3,IF(O381="Parada",2,1))*1E+13+MIN(N(N381),500)*1E+10+MIN(ROUND(N(E381),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F381="",O381="Fechada",O381="Perdida"),0,IF(O381="Fechamento vencido",3,IF(O381="Parada",2,1))*1E+15+MIN(N(N381),500)*1E+12+MIN(ROUND(N(E381)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15356,7 +15356,7 @@
         <v/>
       </c>
       <c r="P382" s="35">
-        <f>IF(OR(F382="",O382="Fechada",O382="Perdida"),0,IF(O382="Fechamento vencido",3,IF(O382="Parada",2,1))*1E+13+MIN(N(N382),500)*1E+10+MIN(ROUND(N(E382),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F382="",O382="Fechada",O382="Perdida"),0,IF(O382="Fechamento vencido",3,IF(O382="Parada",2,1))*1E+15+MIN(N(N382),500)*1E+12+MIN(ROUND(N(E382)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15389,7 +15389,7 @@
         <v/>
       </c>
       <c r="P383" s="35">
-        <f>IF(OR(F383="",O383="Fechada",O383="Perdida"),0,IF(O383="Fechamento vencido",3,IF(O383="Parada",2,1))*1E+13+MIN(N(N383),500)*1E+10+MIN(ROUND(N(E383),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F383="",O383="Fechada",O383="Perdida"),0,IF(O383="Fechamento vencido",3,IF(O383="Parada",2,1))*1E+15+MIN(N(N383),500)*1E+12+MIN(ROUND(N(E383)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15422,7 +15422,7 @@
         <v/>
       </c>
       <c r="P384" s="35">
-        <f>IF(OR(F384="",O384="Fechada",O384="Perdida"),0,IF(O384="Fechamento vencido",3,IF(O384="Parada",2,1))*1E+13+MIN(N(N384),500)*1E+10+MIN(ROUND(N(E384),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F384="",O384="Fechada",O384="Perdida"),0,IF(O384="Fechamento vencido",3,IF(O384="Parada",2,1))*1E+15+MIN(N(N384),500)*1E+12+MIN(ROUND(N(E384)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15455,7 +15455,7 @@
         <v/>
       </c>
       <c r="P385" s="35">
-        <f>IF(OR(F385="",O385="Fechada",O385="Perdida"),0,IF(O385="Fechamento vencido",3,IF(O385="Parada",2,1))*1E+13+MIN(N(N385),500)*1E+10+MIN(ROUND(N(E385),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F385="",O385="Fechada",O385="Perdida"),0,IF(O385="Fechamento vencido",3,IF(O385="Parada",2,1))*1E+15+MIN(N(N385),500)*1E+12+MIN(ROUND(N(E385)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15488,7 +15488,7 @@
         <v/>
       </c>
       <c r="P386" s="35">
-        <f>IF(OR(F386="",O386="Fechada",O386="Perdida"),0,IF(O386="Fechamento vencido",3,IF(O386="Parada",2,1))*1E+13+MIN(N(N386),500)*1E+10+MIN(ROUND(N(E386),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F386="",O386="Fechada",O386="Perdida"),0,IF(O386="Fechamento vencido",3,IF(O386="Parada",2,1))*1E+15+MIN(N(N386),500)*1E+12+MIN(ROUND(N(E386)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
         <v/>
       </c>
       <c r="P387" s="35">
-        <f>IF(OR(F387="",O387="Fechada",O387="Perdida"),0,IF(O387="Fechamento vencido",3,IF(O387="Parada",2,1))*1E+13+MIN(N(N387),500)*1E+10+MIN(ROUND(N(E387),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F387="",O387="Fechada",O387="Perdida"),0,IF(O387="Fechamento vencido",3,IF(O387="Parada",2,1))*1E+15+MIN(N(N387),500)*1E+12+MIN(ROUND(N(E387)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15554,7 +15554,7 @@
         <v/>
       </c>
       <c r="P388" s="35">
-        <f>IF(OR(F388="",O388="Fechada",O388="Perdida"),0,IF(O388="Fechamento vencido",3,IF(O388="Parada",2,1))*1E+13+MIN(N(N388),500)*1E+10+MIN(ROUND(N(E388),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F388="",O388="Fechada",O388="Perdida"),0,IF(O388="Fechamento vencido",3,IF(O388="Parada",2,1))*1E+15+MIN(N(N388),500)*1E+12+MIN(ROUND(N(E388)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
         <v/>
       </c>
       <c r="P389" s="35">
-        <f>IF(OR(F389="",O389="Fechada",O389="Perdida"),0,IF(O389="Fechamento vencido",3,IF(O389="Parada",2,1))*1E+13+MIN(N(N389),500)*1E+10+MIN(ROUND(N(E389),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F389="",O389="Fechada",O389="Perdida"),0,IF(O389="Fechamento vencido",3,IF(O389="Parada",2,1))*1E+15+MIN(N(N389),500)*1E+12+MIN(ROUND(N(E389)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15620,7 +15620,7 @@
         <v/>
       </c>
       <c r="P390" s="35">
-        <f>IF(OR(F390="",O390="Fechada",O390="Perdida"),0,IF(O390="Fechamento vencido",3,IF(O390="Parada",2,1))*1E+13+MIN(N(N390),500)*1E+10+MIN(ROUND(N(E390),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F390="",O390="Fechada",O390="Perdida"),0,IF(O390="Fechamento vencido",3,IF(O390="Parada",2,1))*1E+15+MIN(N(N390),500)*1E+12+MIN(ROUND(N(E390)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15653,7 +15653,7 @@
         <v/>
       </c>
       <c r="P391" s="35">
-        <f>IF(OR(F391="",O391="Fechada",O391="Perdida"),0,IF(O391="Fechamento vencido",3,IF(O391="Parada",2,1))*1E+13+MIN(N(N391),500)*1E+10+MIN(ROUND(N(E391),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F391="",O391="Fechada",O391="Perdida"),0,IF(O391="Fechamento vencido",3,IF(O391="Parada",2,1))*1E+15+MIN(N(N391),500)*1E+12+MIN(ROUND(N(E391)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15686,7 +15686,7 @@
         <v/>
       </c>
       <c r="P392" s="35">
-        <f>IF(OR(F392="",O392="Fechada",O392="Perdida"),0,IF(O392="Fechamento vencido",3,IF(O392="Parada",2,1))*1E+13+MIN(N(N392),500)*1E+10+MIN(ROUND(N(E392),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F392="",O392="Fechada",O392="Perdida"),0,IF(O392="Fechamento vencido",3,IF(O392="Parada",2,1))*1E+15+MIN(N(N392),500)*1E+12+MIN(ROUND(N(E392)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
         <v/>
       </c>
       <c r="P393" s="35">
-        <f>IF(OR(F393="",O393="Fechada",O393="Perdida"),0,IF(O393="Fechamento vencido",3,IF(O393="Parada",2,1))*1E+13+MIN(N(N393),500)*1E+10+MIN(ROUND(N(E393),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F393="",O393="Fechada",O393="Perdida"),0,IF(O393="Fechamento vencido",3,IF(O393="Parada",2,1))*1E+15+MIN(N(N393),500)*1E+12+MIN(ROUND(N(E393)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
         <v/>
       </c>
       <c r="P394" s="35">
-        <f>IF(OR(F394="",O394="Fechada",O394="Perdida"),0,IF(O394="Fechamento vencido",3,IF(O394="Parada",2,1))*1E+13+MIN(N(N394),500)*1E+10+MIN(ROUND(N(E394),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F394="",O394="Fechada",O394="Perdida"),0,IF(O394="Fechamento vencido",3,IF(O394="Parada",2,1))*1E+15+MIN(N(N394),500)*1E+12+MIN(ROUND(N(E394)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
         <v/>
       </c>
       <c r="P395" s="35">
-        <f>IF(OR(F395="",O395="Fechada",O395="Perdida"),0,IF(O395="Fechamento vencido",3,IF(O395="Parada",2,1))*1E+13+MIN(N(N395),500)*1E+10+MIN(ROUND(N(E395),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F395="",O395="Fechada",O395="Perdida"),0,IF(O395="Fechamento vencido",3,IF(O395="Parada",2,1))*1E+15+MIN(N(N395),500)*1E+12+MIN(ROUND(N(E395)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15818,7 +15818,7 @@
         <v/>
       </c>
       <c r="P396" s="35">
-        <f>IF(OR(F396="",O396="Fechada",O396="Perdida"),0,IF(O396="Fechamento vencido",3,IF(O396="Parada",2,1))*1E+13+MIN(N(N396),500)*1E+10+MIN(ROUND(N(E396),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F396="",O396="Fechada",O396="Perdida"),0,IF(O396="Fechamento vencido",3,IF(O396="Parada",2,1))*1E+15+MIN(N(N396),500)*1E+12+MIN(ROUND(N(E396)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
         <v/>
       </c>
       <c r="P397" s="35">
-        <f>IF(OR(F397="",O397="Fechada",O397="Perdida"),0,IF(O397="Fechamento vencido",3,IF(O397="Parada",2,1))*1E+13+MIN(N(N397),500)*1E+10+MIN(ROUND(N(E397),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F397="",O397="Fechada",O397="Perdida"),0,IF(O397="Fechamento vencido",3,IF(O397="Parada",2,1))*1E+15+MIN(N(N397),500)*1E+12+MIN(ROUND(N(E397)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         <v/>
       </c>
       <c r="P398" s="35">
-        <f>IF(OR(F398="",O398="Fechada",O398="Perdida"),0,IF(O398="Fechamento vencido",3,IF(O398="Parada",2,1))*1E+13+MIN(N(N398),500)*1E+10+MIN(ROUND(N(E398),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F398="",O398="Fechada",O398="Perdida"),0,IF(O398="Fechamento vencido",3,IF(O398="Parada",2,1))*1E+15+MIN(N(N398),500)*1E+12+MIN(ROUND(N(E398)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15917,7 +15917,7 @@
         <v/>
       </c>
       <c r="P399" s="35">
-        <f>IF(OR(F399="",O399="Fechada",O399="Perdida"),0,IF(O399="Fechamento vencido",3,IF(O399="Parada",2,1))*1E+13+MIN(N(N399),500)*1E+10+MIN(ROUND(N(E399),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F399="",O399="Fechada",O399="Perdida"),0,IF(O399="Fechamento vencido",3,IF(O399="Parada",2,1))*1E+15+MIN(N(N399),500)*1E+12+MIN(ROUND(N(E399)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15950,7 +15950,7 @@
         <v/>
       </c>
       <c r="P400" s="35">
-        <f>IF(OR(F400="",O400="Fechada",O400="Perdida"),0,IF(O400="Fechamento vencido",3,IF(O400="Parada",2,1))*1E+13+MIN(N(N400),500)*1E+10+MIN(ROUND(N(E400),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F400="",O400="Fechada",O400="Perdida"),0,IF(O400="Fechamento vencido",3,IF(O400="Parada",2,1))*1E+15+MIN(N(N400),500)*1E+12+MIN(ROUND(N(E400)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
         <v/>
       </c>
       <c r="P401" s="35">
-        <f>IF(OR(F401="",O401="Fechada",O401="Perdida"),0,IF(O401="Fechamento vencido",3,IF(O401="Parada",2,1))*1E+13+MIN(N(N401),500)*1E+10+MIN(ROUND(N(E401),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F401="",O401="Fechada",O401="Perdida"),0,IF(O401="Fechamento vencido",3,IF(O401="Parada",2,1))*1E+15+MIN(N(N401),500)*1E+12+MIN(ROUND(N(E401)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -16016,7 +16016,7 @@
         <v/>
       </c>
       <c r="P402" s="35">
-        <f>IF(OR(F402="",O402="Fechada",O402="Perdida"),0,IF(O402="Fechamento vencido",3,IF(O402="Parada",2,1))*1E+13+MIN(N(N402),500)*1E+10+MIN(ROUND(N(E402),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F402="",O402="Fechada",O402="Perdida"),0,IF(O402="Fechamento vencido",3,IF(O402="Parada",2,1))*1E+15+MIN(N(N402),500)*1E+12+MIN(ROUND(N(E402)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -16049,7 +16049,7 @@
         <v/>
       </c>
       <c r="P403" s="35">
-        <f>IF(OR(F403="",O403="Fechada",O403="Perdida"),0,IF(O403="Fechamento vencido",3,IF(O403="Parada",2,1))*1E+13+MIN(N(N403),500)*1E+10+MIN(ROUND(N(E403),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F403="",O403="Fechada",O403="Perdida"),0,IF(O403="Fechamento vencido",3,IF(O403="Parada",2,1))*1E+15+MIN(N(N403),500)*1E+12+MIN(ROUND(N(E403)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
         <v/>
       </c>
       <c r="P404" s="35">
-        <f>IF(OR(F404="",O404="Fechada",O404="Perdida"),0,IF(O404="Fechamento vencido",3,IF(O404="Parada",2,1))*1E+13+MIN(N(N404),500)*1E+10+MIN(ROUND(N(E404),0),999999)*1E+4+(404+1-ROW()))</f>
+        <f>IF(OR(F404="",O404="Fechada",O404="Perdida"),0,IF(O404="Fechamento vencido",3,IF(O404="Parada",2,1))*1E+15+MIN(N(N404),500)*1E+12+MIN(ROUND(N(E404)*100,0),99999999)*1E+4+(404+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/08-funil-de-propostas.xlsx
@@ -1029,7 +1029,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>Config!B4&amp;" · funil em "&amp;TEXT(Config!B5,"dd/mm/yyyy")</f>
+        <f>Config!B4&amp;" · funil em "&amp;TEXT(DAY(Config!B5),"00")&amp;"/"&amp;TEXT(MONTH(Config!B5),"00")&amp;"/"&amp;YEAR(Config!B5)</f>
         <v>Prisma Comunicação (exemplo fictício) · funil em 14/09/2026</v>
       </c>
     </row>
